--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -103,7 +103,7 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">17/12/2025</t>
+    <t xml:space="preserve">04/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
@@ -1465,7 +1465,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.719582201338366</v>
+        <v>0.721351108080181</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1523,7 +1523,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.517798544482969</v>
+        <v>0.520347421128504</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1593,7 +1593,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.140483209748487</v>
+        <v>0.185066455903565</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1623,7 +1623,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.000141351572502414</v>
+        <v>0.000146866307519825</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -15574,7 +15574,7 @@
         <v>297</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.00513391683993949</v>
+        <v>0.00543756979155652</v>
       </c>
     </row>
     <row r="6">
@@ -15582,7 +15582,7 @@
         <v>298</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.139847778429657</v>
+        <v>0.139907470762606</v>
       </c>
     </row>
     <row r="7">
@@ -15590,7 +15590,7 @@
         <v>299</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.386283856276448</v>
+        <v>0.384546133510046</v>
       </c>
     </row>
     <row r="8">
@@ -15598,7 +15598,7 @@
         <v>300</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.644351050655969</v>
+        <v>0.641496500806375</v>
       </c>
     </row>
     <row r="9">
@@ -15606,7 +15606,7 @@
         <v>301</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.719582201338366</v>
+        <v>0.721351108080181</v>
       </c>
     </row>
     <row r="10">
@@ -15614,7 +15614,7 @@
         <v>302</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.509525079563481</v>
+        <v>0.510349514612105</v>
       </c>
     </row>
     <row r="11">
@@ -15622,7 +15622,7 @@
         <v>303</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.161197065381121</v>
+        <v>0.160640808108537</v>
       </c>
     </row>
     <row r="12">
@@ -15630,7 +15630,7 @@
         <v>304</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.0497666782125254</v>
+        <v>-0.0491192693391144</v>
       </c>
     </row>
     <row r="13">
@@ -15638,7 +15638,7 @@
         <v>305</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.103881232832795</v>
+        <v>-0.104889571770122</v>
       </c>
     </row>
     <row r="14">
@@ -15696,237 +15696,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
-    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C37B459-F03B-46A2-821E-34A4FC8CB59F}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65850890-7C4E-4EE6-A905-2C82CECB618A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{665FC71B-315E-4379-AA56-0622C7202C55}"/>
 </file>
--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -103,13 +103,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">04/03/2026</t>
+    <t xml:space="preserve">09/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">focampo</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>

--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -109,7 +109,7 @@
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">focampo</t>
+    <t xml:space="preserve">pcohan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>

--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -103,13 +103,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">09/03/2026</t>
+    <t xml:space="preserve">10/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">focampo</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>

--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Correlograma" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Referencias" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Correlograma" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="325">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -899,6 +900,63 @@
   </si>
   <si>
     <t xml:space="preserve">2030T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencias de las series incluidas en la hoja Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original | serie de datos brutos transformados, se importa directo desde base de datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_normal | serie original con 4 forecasts obtenidos del mejor modelo ARIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_optimista | serie original con 4 forecasts, intervalo y límite optimista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_pesimista | serie original con 4 forecasts, intervalo y límite pesimista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b_d16 | salida D16 del X13-ARIMA-SEATS con los factores estacionales de la serie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_c17 | salida C17 del X13-ARIMA-SEATS con pesos del irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_d12 | salida D12 del X13-ARIMA-SEATS con el componente tendencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_hp_1600 | tendencia HP de largo plazo con un lambda de 1.600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_hp_200 | suavizado con filtro HP usando lambda de 200, sirve para determinar PG automáticos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e_ajustada | serie ajustada por estacionalidad usando el mejor modelo (LOG o NIV según el caso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f_filtrada | serie ajustada por estacionalidad y corregida por irregularidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_final | serie f_filtrada con o sin suavizado 2x2 según el caso (es la vieja española)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_final_fct_normal | a_original_fct ajustada por D16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_final_tctl | tasas de cambio trimestral logarítmicas de la serie g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_var_interanual | variaciones interanuales de g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_final_var_trimestral | variaciones trimestrales de g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h_irregular | g_final/d_d12 componente irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i_dt | g_final/d_hp_1600 desvíos respecto de la tendencia</t>
   </si>
   <si>
     <t xml:space="preserve">Coeficientes de correlación de TCTL del ICA-SFE y serie específica</t>
@@ -15547,6 +15605,112 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>313</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -15555,7 +15719,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -15565,13 +15729,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0.00543756979155652</v>
@@ -15579,7 +15743,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>0.139907470762606</v>
@@ -15587,7 +15751,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>0.384546133510046</v>
@@ -15595,7 +15759,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>0.641496500806375</v>
@@ -15603,7 +15767,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0.721351108080181</v>
@@ -15611,7 +15775,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>0.510349514612105</v>
@@ -15619,7 +15783,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>0.160640808108537</v>
@@ -15627,7 +15791,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>-0.0491192693391144</v>
@@ -15635,7 +15799,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>-0.104889571770122</v>

--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">focampo</t>
+    <t xml:space="preserve">pcohan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>

--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -104,13 +104,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">10/03/2026</t>
+    <t xml:space="preserve">19/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">focampo</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1523,7 +1523,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.721351108080181</v>
+        <v>0.72114005649416</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1581,7 +1581,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.520347421128504</v>
+        <v>0.520042981080401</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1651,7 +1651,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.185066455903565</v>
+        <v>0.177124125660377</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1681,7 +1681,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.000146866307519825</v>
+        <v>0.000155068376420352</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -15738,7 +15738,7 @@
         <v>316</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.00543756979155652</v>
+        <v>0.00439937513385089</v>
       </c>
     </row>
     <row r="6">
@@ -15746,7 +15746,7 @@
         <v>317</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.139907470762606</v>
+        <v>0.139183420276649</v>
       </c>
     </row>
     <row r="7">
@@ -15754,7 +15754,7 @@
         <v>318</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.384546133510046</v>
+        <v>0.384914465135252</v>
       </c>
     </row>
     <row r="8">
@@ -15762,7 +15762,7 @@
         <v>319</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.641496500806375</v>
+        <v>0.642044945631027</v>
       </c>
     </row>
     <row r="9">
@@ -15770,7 +15770,7 @@
         <v>320</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.721351108080181</v>
+        <v>0.72114005649416</v>
       </c>
     </row>
     <row r="10">
@@ -15778,7 +15778,7 @@
         <v>321</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.510349514612105</v>
+        <v>0.509907861023004</v>
       </c>
     </row>
     <row r="11">
@@ -15786,7 +15786,7 @@
         <v>322</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.160640808108537</v>
+        <v>0.160309882800666</v>
       </c>
     </row>
     <row r="12">
@@ -15794,7 +15794,7 @@
         <v>323</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.0491192693391144</v>
+        <v>-0.0493548644001488</v>
       </c>
     </row>
     <row r="13">
@@ -15802,7 +15802,7 @@
         <v>324</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.104889571770122</v>
+        <v>-0.105263379863882</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -104,13 +104,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">19/03/2026</t>
+    <t xml:space="preserve">25/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">focampo</t>
+    <t xml:space="preserve">pcohan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1523,7 +1523,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.72114005649416</v>
+        <v>0.721251404033602</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1581,7 +1581,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.520042981080401</v>
+        <v>0.520203587820442</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1651,7 +1651,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.177124125660377</v>
+        <v>0.181327766662582</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1681,7 +1681,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.000155068376420352</v>
+        <v>0.000115221997963427</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1950,7 +1950,7 @@
         <v>285684.43920487</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>282483.955622642</v>
+        <v>282483.955622677</v>
       </c>
       <c r="J2" s="10" t="n">
         <v>282294.983959635</v>
@@ -1974,7 +1974,7 @@
         <v>1.00046103871543</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>1.01179605107749</v>
+        <v>1.01179605107736</v>
       </c>
     </row>
     <row r="3">
@@ -2003,7 +2003,7 @@
         <v>285340.804386349</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>284815.242766601</v>
+        <v>284815.242766627</v>
       </c>
       <c r="J3" s="10" t="n">
         <v>284438.088812099</v>
@@ -2031,7 +2031,7 @@
         <v>0.999308938785785</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>1.00115293568495</v>
+        <v>1.00115293568486</v>
       </c>
     </row>
     <row r="4">
@@ -2060,7 +2060,7 @@
         <v>284470.468347331</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>287148.612532541</v>
+        <v>287148.612532557</v>
       </c>
       <c r="J4" s="10" t="n">
         <v>286598.799498723</v>
@@ -2088,7 +2088,7 @@
         <v>1.00252443782754</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.993174209839259</v>
+        <v>0.993174209839202</v>
       </c>
     </row>
     <row r="5">
@@ -2117,7 +2117,7 @@
         <v>285056.703379466</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>289486.352775978</v>
+        <v>289486.352775985</v>
       </c>
       <c r="J5" s="10" t="n">
         <v>288798.249491725</v>
@@ -2145,7 +2145,7 @@
         <v>0.996881092842427</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>0.981627062077388</v>
+        <v>0.981627062077366</v>
       </c>
     </row>
     <row r="6">
@@ -2174,7 +2174,7 @@
         <v>290673.079365178</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>291829.526342319</v>
+        <v>291829.526342316</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>291050.521247623</v>
@@ -2204,7 +2204,7 @@
         <v>0.9979510621121</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.993996433176573</v>
+        <v>0.993996433176583</v>
       </c>
     </row>
     <row r="7">
@@ -2233,7 +2233,7 @@
         <v>297333.983694748</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>294175.87188023</v>
+        <v>294175.871880217</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>293346.544165409</v>
@@ -2263,7 +2263,7 @@
         <v>1.00495324005029</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>1.01574187026717</v>
+        <v>1.01574187026721</v>
       </c>
     </row>
     <row r="8">
@@ -2292,7 +2292,7 @@
         <v>298338.509036201</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>296522.033027084</v>
+        <v>296522.033027061</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>295672.382579237</v>
@@ -2322,7 +2322,7 @@
         <v>0.999310471405389</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>1.00543218680858</v>
+        <v>1.00543218680866</v>
       </c>
     </row>
     <row r="9">
@@ -2351,7 +2351,7 @@
         <v>296554.107385995</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>298867.547719265</v>
+        <v>298867.547719231</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>298041.401853891</v>
@@ -2381,7 +2381,7 @@
         <v>0.997763136093149</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.990039763315801</v>
+        <v>0.990039763315912</v>
       </c>
     </row>
     <row r="10">
@@ -2410,7 +2410,7 @@
         <v>296207.924142963</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>301212.960620077</v>
+        <v>301212.960620033</v>
       </c>
       <c r="J10" s="10" t="n">
         <v>300479.269421772</v>
@@ -2440,7 +2440,7 @@
         <v>1.00305934664891</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>0.986392239734405</v>
+        <v>0.98639223973455</v>
       </c>
     </row>
     <row r="11">
@@ -2469,7 +2469,7 @@
         <v>299499.92135201</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>303556.95589813</v>
+        <v>303556.955898074</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>303000.899487049</v>
@@ -2499,7 +2499,7 @@
         <v>0.99462528575941</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>0.981332132476754</v>
+        <v>0.981332132476933</v>
       </c>
     </row>
     <row r="12">
@@ -2528,7 +2528,7 @@
         <v>304816.47810658</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>305895.655950935</v>
+        <v>305895.655950868</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>305604.380541096</v>
@@ -2558,7 +2558,7 @@
         <v>1.00526111923555</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.00171463040328</v>
+        <v>1.00171463040349</v>
       </c>
     </row>
     <row r="13">
@@ -2587,7 +2587,7 @@
         <v>307991.10820172</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>308221.641450354</v>
+        <v>308221.641450276</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>308262.24755215</v>
@@ -2617,7 +2617,7 @@
         <v>0.99942684316382</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>0.998679325514371</v>
+        <v>0.998679325514624</v>
       </c>
     </row>
     <row r="14">
@@ -2646,7 +2646,7 @@
         <v>307864.733218995</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>310527.820879495</v>
+        <v>310527.820879405</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>310951.114355457</v>
@@ -2676,7 +2676,7 @@
         <v>0.999547953598189</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>0.990975826908329</v>
+        <v>0.990975826908616</v>
       </c>
     </row>
     <row r="15">
@@ -2705,7 +2705,7 @@
         <v>308739.245868716</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>312806.848308678</v>
+        <v>312806.848308577</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>313645.356453464</v>
@@ -2735,7 +2735,7 @@
         <v>1.00081826239076</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>0.987804062643952</v>
+        <v>0.987804062644271</v>
       </c>
     </row>
     <row r="16">
@@ -2764,7 +2764,7 @@
         <v>314007.629332199</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>315049.626397722</v>
+        <v>315049.62639761</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>316303.221597213</v>
@@ -2794,7 +2794,7 @@
         <v>0.99577591035529</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>0.992482475005524</v>
+        <v>0.992482475005879</v>
       </c>
     </row>
     <row r="17">
@@ -2823,7 +2823,7 @@
         <v>321887.695157495</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>317244.673448491</v>
+        <v>317244.673448367</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>318859.690133388</v>
@@ -2853,7 +2853,7 @@
         <v>1.0043935652066</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.01909332699282</v>
+        <v>1.01909332699322</v>
       </c>
     </row>
     <row r="18">
@@ -2882,7 +2882,7 @@
         <v>327936.667010804</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>319379.027516946</v>
+        <v>319379.027516813</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>321231.632465472</v>
@@ -2912,7 +2912,7 @@
         <v>0.998052480804151</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.02479491719102</v>
+        <v>1.02479491719145</v>
       </c>
     </row>
     <row r="19">
@@ -2941,7 +2941,7 @@
         <v>329514.964258324</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>321443.512444232</v>
+        <v>321443.51244409</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>323358.130194958</v>
@@ -2971,7 +2971,7 @@
         <v>1.00260703748024</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>1.0277825164624</v>
+        <v>1.02778251646286</v>
       </c>
     </row>
     <row r="20">
@@ -3000,7 +3000,7 @@
         <v>330901.555524192</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>323433.901431827</v>
+        <v>323433.901431678</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>325208.596781295</v>
@@ -3030,7 +3030,7 @@
         <v>0.995793882687134</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.01878542510208</v>
+        <v>1.01878542510255</v>
       </c>
     </row>
     <row r="21">
@@ -3059,7 +3059,7 @@
         <v>332302.217379835</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>325351.54924976</v>
+        <v>325351.549249606</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>326787.525143558</v>
@@ -3089,7 +3089,7 @@
         <v>1.00357975971416</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.0250197985519</v>
+        <v>1.02501979855239</v>
       </c>
     </row>
     <row r="22">
@@ -3118,7 +3118,7 @@
         <v>333294.719506483</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>327201.608070138</v>
+        <v>327201.608069983</v>
       </c>
       <c r="J22" s="10" t="n">
         <v>328120.913940731</v>
@@ -3148,7 +3148,7 @@
         <v>0.997183429393455</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.0157528667309</v>
+        <v>1.01575286673139</v>
       </c>
     </row>
     <row r="23">
@@ -3177,7 +3177,7 @@
         <v>331290.922220052</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>328994.317708961</v>
+        <v>328994.317708807</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>329268.283103432</v>
@@ -3207,7 +3207,7 @@
         <v>1.00348709509507</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>1.01049211878504</v>
+        <v>1.01049211878551</v>
       </c>
     </row>
     <row r="24">
@@ -3236,7 +3236,7 @@
         <v>327970.113392138</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>330743.139459302</v>
+        <v>330743.139459155</v>
       </c>
       <c r="J24" s="10" t="n">
         <v>330310.327849557</v>
@@ -3266,7 +3266,7 @@
         <v>1</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>0.991615771466348</v>
+        <v>0.991615771466788</v>
       </c>
     </row>
     <row r="25">
@@ -3295,7 +3295,7 @@
         <v>326990.187117292</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>332463.692018903</v>
+        <v>332463.692018768</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>331343.632807333</v>
@@ -3325,7 +3325,7 @@
         <v>0.997481089023311</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>0.981059092393006</v>
+        <v>0.981059092393403</v>
       </c>
     </row>
     <row r="26">
@@ -3354,7 +3354,7 @@
         <v>327370.941931502</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>334169.860944209</v>
+        <v>334169.860944093</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>332453.081532702</v>
@@ -3384,7 +3384,7 @@
         <v>1.00536347685521</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>0.984908655351685</v>
+        <v>0.984908655352026</v>
       </c>
     </row>
     <row r="27">
@@ -3413,7 +3413,7 @@
         <v>326147.212558088</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>335871.596064122</v>
+        <v>335871.596064033</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>333697.672057297</v>
@@ -3443,7 +3443,7 @@
         <v>0.996551430987198</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>0.967698594331858</v>
+        <v>0.967698594332113</v>
       </c>
     </row>
     <row r="28">
@@ -3472,7 +3472,7 @@
         <v>326044.54700968</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>337575.695287205</v>
+        <v>337575.695287152</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>335119.770947094</v>
@@ -3502,7 +3502,7 @@
         <v>1.00174562212335</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>0.967527289860896</v>
+        <v>0.967527289861047</v>
       </c>
     </row>
     <row r="29">
@@ -3531,7 +3531,7 @@
         <v>332763.639378441</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>339282.175819097</v>
+        <v>339282.17581909</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>336718.368764721</v>
@@ -3561,7 +3561,7 @@
         <v>0.995551500331859</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>0.976424239320296</v>
+        <v>0.976424239320315</v>
       </c>
     </row>
     <row r="30">
@@ -3590,7 +3590,7 @@
         <v>343187.168381237</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>340984.203616872</v>
+        <v>340984.203616923</v>
       </c>
       <c r="J30" s="10" t="n">
         <v>338449.92570599</v>
@@ -3620,7 +3620,7 @@
         <v>1.00354258138292</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>1.01002607511336</v>
+        <v>1.0100260751132</v>
       </c>
     </row>
     <row r="31">
@@ -3649,7 +3649,7 @@
         <v>352724.681542238</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>342669.945365492</v>
+        <v>342669.945365615</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>340243.726825086</v>
@@ -3679,7 +3679,7 @@
         <v>0.996913237538612</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>1.02616499927063</v>
+        <v>1.02616499927027</v>
       </c>
     </row>
     <row r="32">
@@ -3708,7 +3708,7 @@
         <v>353387.797369463</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>344329.704458195</v>
+        <v>344329.704458402</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>342058.822231937</v>
@@ -3738,7 +3738,7 @@
         <v>1.00599607166605</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>1.03246025923842</v>
+        <v>1.0324602592378</v>
       </c>
     </row>
     <row r="33">
@@ -3767,7 +3767,7 @@
         <v>343392.460694242</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>345959.38801251</v>
+        <v>345959.388012817</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>343911.222923526</v>
@@ -3797,7 +3797,7 @@
         <v>0.999987305577951</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.992567663788909</v>
+        <v>0.992567663788028</v>
       </c>
     </row>
     <row r="34">
@@ -3826,7 +3826,7 @@
         <v>333104.883162749</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>347561.888790635</v>
+        <v>347561.888791059</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>345884.179465318</v>
@@ -3856,7 +3856,7 @@
         <v>0.993702135237003</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.952368612129649</v>
+        <v>0.952368612128487</v>
       </c>
     </row>
     <row r="35">
@@ -3885,7 +3885,7 @@
         <v>332714.377374735</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>349138.492500715</v>
+        <v>349138.492501274</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>348058.326815788</v>
@@ -3915,7 +3915,7 @@
         <v>1.00316322292748</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.955972584778416</v>
+        <v>0.955972584776887</v>
       </c>
     </row>
     <row r="36">
@@ -3944,7 +3944,7 @@
         <v>338498.644473076</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>350680.138066437</v>
+        <v>350680.138067148</v>
       </c>
       <c r="J36" s="10" t="n">
         <v>350439.914204369</v>
@@ -3974,7 +3974,7 @@
         <v>1.00019944674052</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.965455753471396</v>
+        <v>0.96545575346944</v>
       </c>
     </row>
     <row r="37">
@@ -4003,7 +4003,7 @@
         <v>347979.550422056</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>352168.157120624</v>
+        <v>352168.157121505</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>352963.733362019</v>
@@ -4033,7 +4033,7 @@
         <v>0.996142045898126</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.984294162545215</v>
+        <v>0.984294162542754</v>
       </c>
     </row>
     <row r="38">
@@ -4062,10 +4062,10 @@
         <v>358541.643456487</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>353576.310057887</v>
+        <v>353576.310058956</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>355505.207233302</v>
+        <v>355505.207233301</v>
       </c>
       <c r="K38" s="11" t="n">
         <v>360131.033724994</v>
@@ -4092,7 +4092,7 @@
         <v>1.00443293072789</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>1.01853835644711</v>
+        <v>1.01853835644403</v>
       </c>
     </row>
     <row r="39">
@@ -4121,7 +4121,7 @@
         <v>362366.703625266</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>354874.900337939</v>
+        <v>354874.900339214</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>357908.125402406</v>
@@ -4151,7 +4151,7 @@
         <v>1.00151625597356</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>1.02265937646946</v>
+        <v>1.02265937646578</v>
       </c>
     </row>
     <row r="40">
@@ -4180,7 +4180,7 @@
         <v>362245.570448144</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>356038.328122788</v>
+        <v>356038.328124284</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>360039.406585983</v>
@@ -4210,7 +4210,7 @@
         <v>0.998134267168734</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>1.01553593654019</v>
+        <v>1.01553593653592</v>
       </c>
     </row>
     <row r="41">
@@ -4239,7 +4239,7 @@
         <v>364723.397409161</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>357046.019351919</v>
+        <v>357046.019353651</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>361791.00959519</v>
@@ -4269,7 +4269,7 @@
         <v>1.00322284927594</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>1.02479463742677</v>
+        <v>1.0247946374218</v>
       </c>
     </row>
     <row r="42">
@@ -4298,7 +4298,7 @@
         <v>368497.713638057</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>357880.857082863</v>
+        <v>357880.857084841</v>
       </c>
       <c r="J42" s="10" t="n">
         <v>363062.54479323</v>
@@ -4328,7 +4328,7 @@
         <v>0.999748465691122</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>1.02940690045077</v>
+        <v>1.02940690044508</v>
       </c>
     </row>
     <row r="43">
@@ -4357,7 +4357,7 @@
         <v>375399.56719607</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>358531.257389772</v>
+        <v>358531.257392002</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>363774.161725059</v>
@@ -4387,7 +4387,7 @@
         <v>0.994527370073768</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.04131825773969</v>
+        <v>1.04131825773322</v>
       </c>
     </row>
     <row r="44">
@@ -4416,10 +4416,10 @@
         <v>382089.935726599</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>358992.213951008</v>
+        <v>358992.213953491</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>363872.72233077</v>
+        <v>363872.722330769</v>
       </c>
       <c r="K44" s="11" t="n">
         <v>384777.026136385</v>
@@ -4446,7 +4446,7 @@
         <v>1.00703261237351</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>1.07182554713818</v>
+        <v>1.07182554713076</v>
       </c>
     </row>
     <row r="45">
@@ -4475,7 +4475,7 @@
         <v>378915.098444103</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>359267.979124248</v>
+        <v>359267.979126978</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>363352.943463281</v>
@@ -4505,7 +4505,7 @@
         <v>0.999641361114807</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>1.05430827895914</v>
+        <v>1.05430827895113</v>
       </c>
     </row>
     <row r="46">
@@ -4534,7 +4534,7 @@
         <v>370046.929067076</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>359378.920774783</v>
+        <v>359378.920777746</v>
       </c>
       <c r="J46" s="10" t="n">
         <v>362314.063494539</v>
@@ -4564,7 +4564,7 @@
         <v>0.994538256865323</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.02406069615689</v>
+        <v>1.02406069614845</v>
       </c>
     </row>
     <row r="47">
@@ -4593,7 +4593,7 @@
         <v>360467.602791213</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>359357.601283924</v>
+        <v>359357.601287096</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>360932.452102955</v>
@@ -4623,7 +4623,7 @@
         <v>1.00796936386056</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>1.01108282941461</v>
+        <v>1.01108282940569</v>
       </c>
     </row>
     <row r="48">
@@ -4652,7 +4652,7 @@
         <v>350284.101753595</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>359241.987349868</v>
+        <v>359241.987353213</v>
       </c>
       <c r="J48" s="10" t="n">
         <v>359413.037788426</v>
@@ -4682,7 +4682,7 @@
         <v>0.993537962472264</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>0.968763577192201</v>
+        <v>0.968763577183183</v>
       </c>
     </row>
     <row r="49">
@@ -4711,7 +4711,7 @@
         <v>344341.392450618</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>359072.534857685</v>
+        <v>359072.534861151</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>357972.788291728</v>
@@ -4741,7 +4741,7 @@
         <v>1.00042552866671</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>0.959382537349386</v>
+        <v>0.959382537340125</v>
       </c>
     </row>
     <row r="50">
@@ -4770,7 +4770,7 @@
         <v>343038.137188109</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>358882.686295813</v>
+        <v>358882.686299335</v>
       </c>
       <c r="J50" s="10" t="n">
         <v>356771.708928405</v>
@@ -4800,7 +4800,7 @@
         <v>1.00496537941978</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.960596498128486</v>
+        <v>0.960596498119059</v>
       </c>
     </row>
     <row r="51">
@@ -4829,7 +4829,7 @@
         <v>342533.362705206</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>358696.768768146</v>
+        <v>358696.768771639</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>355902.380670466</v>
@@ -4859,7 +4859,7 @@
         <v>1</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.954938523370452</v>
+        <v>0.954938523361153</v>
       </c>
     </row>
     <row r="52">
@@ -4888,7 +4888,7 @@
         <v>345738.843049346</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>358530.271106951</v>
+        <v>358530.27111031</v>
       </c>
       <c r="J52" s="10" t="n">
         <v>355397.233203749</v>
@@ -4918,7 +4918,7 @@
         <v>1.00137704659263</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.965650516694669</v>
+        <v>0.965650516685622</v>
       </c>
     </row>
     <row r="53">
@@ -4947,7 +4947,7 @@
         <v>352241.305163862</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>358388.580015706</v>
+        <v>358388.580018804</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>355221.851124268</v>
@@ -4977,7 +4977,7 @@
         <v>0.999366239739379</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>0.982224569228944</v>
+        <v>0.982224569220454</v>
       </c>
     </row>
     <row r="54">
@@ -5006,7 +5006,7 @@
         <v>356720.359659079</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>358269.385116913</v>
+        <v>358269.385119598</v>
       </c>
       <c r="J54" s="10" t="n">
         <v>355295.907569743</v>
@@ -5036,7 +5036,7 @@
         <v>1.00233064329099</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.997996933104961</v>
+        <v>0.997996933097483</v>
       </c>
     </row>
     <row r="55">
@@ -5065,10 +5065,10 @@
         <v>360288.803230216</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>358166.394463454</v>
+        <v>358166.394465547</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>355523.056765383</v>
+        <v>355523.056765384</v>
       </c>
       <c r="K55" s="11" t="n">
         <v>358762.708721785</v>
@@ -5095,7 +5095,7 @@
         <v>0.995764246641171</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>1.0016649084547</v>
+        <v>1.00166490844885</v>
       </c>
     </row>
     <row r="56">
@@ -5124,7 +5124,7 @@
         <v>360482.886469362</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>358072.867584745</v>
+        <v>358072.867586038</v>
       </c>
       <c r="J56" s="10" t="n">
         <v>355818.232136414</v>
@@ -5154,7 +5154,7 @@
         <v>1.00676178425865</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>1.01353782101547</v>
+        <v>1.01353782101181</v>
       </c>
     </row>
     <row r="57">
@@ -5183,10 +5183,10 @@
         <v>358110.320672532</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>357982.436706611</v>
+        <v>357982.436706869</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>356112.565367837</v>
+        <v>356112.565367838</v>
       </c>
       <c r="K57" s="11" t="n">
         <v>356510.291460031</v>
@@ -5213,7 +5213,7 @@
         <v>0.99553202150249</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>0.995887660690496</v>
+        <v>0.99588766068978</v>
       </c>
     </row>
     <row r="58">
@@ -5242,7 +5242,7 @@
         <v>360331.469236293</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>357891.763758877</v>
+        <v>357891.763757831</v>
       </c>
       <c r="J58" s="10" t="n">
         <v>356372.698953861</v>
@@ -5272,7 +5272,7 @@
         <v>0.996899940129559</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.00369568814797</v>
+        <v>1.0036956881509</v>
       </c>
     </row>
     <row r="59">
@@ -5301,7 +5301,7 @@
         <v>366903.325694328</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>357796.590580584</v>
+        <v>357796.590577938</v>
       </c>
       <c r="J59" s="10" t="n">
         <v>356567.26401915</v>
@@ -5331,7 +5331,7 @@
         <v>1.00550717037844</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.03109960948119</v>
+        <v>1.03109960948882</v>
       </c>
     </row>
     <row r="60">
@@ -5360,10 +5360,10 @@
         <v>370115.454503361</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>357693.485670995</v>
+        <v>357693.48566642</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>356679.100294145</v>
+        <v>356679.100294146</v>
       </c>
       <c r="K60" s="11" t="n">
         <v>368316.805233327</v>
@@ -5390,7 +5390,7 @@
         <v>0.995140302172879</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.02969950526889</v>
+        <v>1.02969950528206</v>
       </c>
     </row>
     <row r="61">
@@ -5419,10 +5419,10 @@
         <v>365416.806395414</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>357585.97211327</v>
+        <v>357585.972106412</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>356752.830813296</v>
+        <v>356752.830813297</v>
       </c>
       <c r="K61" s="11" t="n">
         <v>368231.377306891</v>
@@ -5449,7 +5449,7 @@
         <v>1.00654752764113</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>1.02859007824645</v>
+        <v>1.02859007826618</v>
       </c>
     </row>
     <row r="62">
@@ -5478,7 +5478,7 @@
         <v>353257.410748033</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>357484.212565299</v>
+        <v>357484.212555776</v>
       </c>
       <c r="J62" s="10" t="n">
         <v>356891.26713575</v>
@@ -5508,7 +5508,7 @@
         <v>0.997695543902323</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.985899047190529</v>
+        <v>0.985899047216793</v>
       </c>
     </row>
     <row r="63">
@@ -5537,10 +5537,10 @@
         <v>337044.713219182</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>357404.759316797</v>
+        <v>357404.759304207</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>357252.503581765</v>
+        <v>357252.503581766</v>
       </c>
       <c r="K63" s="11" t="n">
         <v>338171.190723661</v>
@@ -5567,7 +5567,7 @@
         <v>1.00334221977173</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>0.946185471536803</v>
+        <v>0.946185471570135</v>
       </c>
     </row>
     <row r="64">
@@ -5596,10 +5596,10 @@
         <v>332593.296431408</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>357361.014114971</v>
+        <v>357361.014098896</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>357972.394858691</v>
+        <v>357972.394858692</v>
       </c>
       <c r="K64" s="11" t="n">
         <v>328979.870909493</v>
@@ -5626,7 +5626,7 @@
         <v>0.989135603270764</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.92058131109862</v>
+        <v>0.920581311140031</v>
       </c>
     </row>
     <row r="65">
@@ -5655,7 +5655,7 @@
         <v>342073.449961899</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>357354.357726659</v>
+        <v>357354.357706674</v>
       </c>
       <c r="J65" s="10" t="n">
         <v>359091.389109587</v>
@@ -5685,7 +5685,7 @@
         <v>1.00685268504747</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>0.963798437407151</v>
+        <v>0.963798437461052</v>
       </c>
     </row>
     <row r="66">
@@ -5714,10 +5714,10 @@
         <v>354399.556297719</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>357368.432704194</v>
+        <v>357368.432679878</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>360504.971857764</v>
+        <v>360504.971857765</v>
       </c>
       <c r="K66" s="11" t="n">
         <v>354821.064943417</v>
@@ -5744,7 +5744,7 @@
         <v>1.00118935997014</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.99287187247765</v>
+        <v>0.992871872545209</v>
       </c>
     </row>
     <row r="67">
@@ -5773,7 +5773,7 @@
         <v>364796.360074642</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>357378.796108567</v>
+        <v>357378.796079512</v>
       </c>
       <c r="J67" s="10" t="n">
         <v>362035.259538877</v>
@@ -5803,7 +5803,7 @@
         <v>0.993573036357098</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>1.01419510916163</v>
+        <v>1.01419510924408</v>
       </c>
     </row>
     <row r="68">
@@ -5832,10 +5832,10 @@
         <v>372019.460486237</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>357359.412895918</v>
+        <v>357359.412861748</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>363475.949054006</v>
+        <v>363475.949054005</v>
       </c>
       <c r="K68" s="11" t="n">
         <v>375311.880583483</v>
@@ -5862,7 +5862,7 @@
         <v>1.00885012868129</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>1.05023644834786</v>
+        <v>1.05023644844828</v>
       </c>
     </row>
     <row r="69">
@@ -5891,10 +5891,10 @@
         <v>369996.847424842</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>357287.418666776</v>
+        <v>357287.418627163</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>364622.820142194</v>
+        <v>364622.820142193</v>
       </c>
       <c r="K69" s="11" t="n">
         <v>369472.941943006</v>
@@ -5921,7 +5921,7 @@
         <v>0.998584027173522</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>1.03410566014807</v>
+        <v>1.03410566026272</v>
       </c>
     </row>
     <row r="70">
@@ -5950,10 +5950,10 @@
         <v>368433.755783655</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>357151.169313975</v>
+        <v>357151.169268662</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>365330.832200133</v>
+        <v>365330.832200131</v>
       </c>
       <c r="K70" s="11" t="n">
         <v>365846.353939529</v>
@@ -5980,7 +5980,7 @@
         <v>0.992977294280155</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>1.02434595032198</v>
+        <v>1.02434595045194</v>
       </c>
     </row>
     <row r="71">
@@ -6009,10 +6009,10 @@
         <v>377461.405183315</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>356946.636682396</v>
+        <v>356946.63663122</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>365479.195233516</v>
+        <v>365479.195233515</v>
       </c>
       <c r="K71" s="11" t="n">
         <v>378208.365597628</v>
@@ -6039,7 +6039,7 @@
         <v>1.00197890540346</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.05956556731518</v>
+        <v>1.05956556746709</v>
       </c>
     </row>
     <row r="72">
@@ -6068,10 +6068,10 @@
         <v>381959.884844545</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>356675.227107314</v>
+        <v>356675.227050234</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>364949.696856737</v>
+        <v>364949.696856735</v>
       </c>
       <c r="K72" s="11" t="n">
         <v>385097.277017122</v>
@@ -6098,7 +6098,7 @@
         <v>1.00821393108822</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.07968607783702</v>
+        <v>1.0796860780098</v>
       </c>
     </row>
     <row r="73">
@@ -6127,10 +6127,10 @@
         <v>379478.493938744</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>356351.635504571</v>
+        <v>356351.635441703</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>363687.770536008</v>
+        <v>363687.770536005</v>
       </c>
       <c r="K73" s="11" t="n">
         <v>370679.133906637</v>
@@ -6157,7 +6157,7 @@
         <v>0.987289442631454</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>1.05136352255243</v>
+        <v>1.05136352273792</v>
       </c>
     </row>
     <row r="74">
@@ -6186,10 +6186,10 @@
         <v>377691.66064559</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>356008.320571207</v>
+        <v>356008.320502856</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>361739.587638343</v>
+        <v>361739.587638339</v>
       </c>
       <c r="K74" s="11" t="n">
         <v>380028.85074581</v>
@@ -6216,7 +6216,7 @@
         <v>1.00618809029626</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.06747182238905</v>
+        <v>1.06747182259399</v>
       </c>
     </row>
     <row r="75">
@@ -6245,10 +6245,10 @@
         <v>372086.14075127</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>355689.180676301</v>
+        <v>355689.180603004</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>359206.156231933</v>
+        <v>359206.156231929</v>
       </c>
       <c r="K75" s="11" t="n">
         <v>373012.106097125</v>
@@ -6275,7 +6275,7 @@
         <v>1.00248857789754</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.04870242436918</v>
+        <v>1.04870242458529</v>
       </c>
     </row>
     <row r="76">
@@ -6304,10 +6304,10 @@
         <v>361519.532084026</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>355453.127020293</v>
+        <v>355453.126942857</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>356279.930700507</v>
+        <v>356279.930700503</v>
       </c>
       <c r="K76" s="11" t="n">
         <v>359505.457165796</v>
@@ -6334,7 +6334,7 @@
         <v>0.994428862787525</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.01140046278246</v>
+        <v>1.01140046300279</v>
       </c>
     </row>
     <row r="77">
@@ -6363,10 +6363,10 @@
         <v>358299.904962271</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>355369.89763201</v>
+        <v>355369.897551563</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>353222.395177121</v>
+        <v>353222.395177116</v>
       </c>
       <c r="K77" s="11" t="n">
         <v>357451.083452559</v>
@@ -6393,7 +6393,7 @@
         <v>0.997630974784095</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>1.00585639311156</v>
+        <v>1.00585639333927</v>
       </c>
     </row>
     <row r="78">
@@ -6422,10 +6422,10 @@
         <v>354000.663396406</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>355511.763246619</v>
+        <v>355511.763164654</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>350311.161427155</v>
+        <v>350311.161427149</v>
       </c>
       <c r="K78" s="11" t="n">
         <v>365527.148096089</v>
@@ -6452,7 +6452,7 @@
         <v>1.00891203463004</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>1.00462366225529</v>
+        <v>1.00462366248691</v>
       </c>
     </row>
     <row r="79">
@@ -6481,10 +6481,10 @@
         <v>339078.88804116</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>355952.295340428</v>
+        <v>355952.295258856</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>347844.984657367</v>
+        <v>347844.984657361</v>
       </c>
       <c r="K79" s="11" t="n">
         <v>338188.610243677</v>
@@ -6511,7 +6511,7 @@
         <v>0.99737442279988</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>0.950095320835726</v>
+        <v>0.950095321053455</v>
       </c>
     </row>
     <row r="80">
@@ -6540,10 +6540,10 @@
         <v>327611.800456159</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>356766.092743692</v>
+        <v>356766.092664893</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>346156.841915219</v>
+        <v>346156.841915214</v>
       </c>
       <c r="K80" s="11" t="n">
         <v>324654.814132488</v>
@@ -6570,7 +6570,7 @@
         <v>0.990974115341529</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>0.909993468369557</v>
+        <v>0.909993468570549</v>
       </c>
     </row>
     <row r="81">
@@ -6599,10 +6599,10 @@
         <v>326146.061960052</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>358016.651983483</v>
+        <v>358016.651910355</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>345531.428376102</v>
+        <v>345531.428376099</v>
       </c>
       <c r="K81" s="11" t="n">
         <v>338630.833598453</v>
@@ -6629,7 +6629,7 @@
         <v>1.00770166791766</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>0.917996212749015</v>
+        <v>0.917996212936523</v>
       </c>
     </row>
     <row r="82">
@@ -6658,10 +6658,10 @@
         <v>325272.179419449</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>359747.40003774</v>
+        <v>359747.399973752</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>346145.929076497</v>
+        <v>346145.929076495</v>
       </c>
       <c r="K82" s="11" t="n">
         <v>324622.055794528</v>
@@ -6688,7 +6688,7 @@
         <v>0.998001293482641</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>0.902361089365685</v>
+        <v>0.902361089526187</v>
       </c>
     </row>
     <row r="83">
@@ -6717,10 +6717,10 @@
         <v>328709.244678886</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>361983.414683551</v>
+        <v>361983.414632784</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>348093.161564109</v>
+        <v>348093.161564111</v>
       </c>
       <c r="K83" s="11" t="n">
         <v>326509.110206825</v>
@@ -6747,7 +6747,7 @@
         <v>0.993306745983946</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>0.902000193827284</v>
+        <v>0.902000193953785</v>
       </c>
     </row>
     <row r="84">
@@ -6776,10 +6776,10 @@
         <v>340224.194523046</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>364727.820357852</v>
+        <v>364727.820325043</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>351358.324020238</v>
+        <v>351358.324020244</v>
       </c>
       <c r="K84" s="11" t="n">
         <v>342224.446725735</v>
@@ -6806,7 +6806,7 @@
         <v>1.00587921798299</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>0.938300912691445</v>
+        <v>0.938300912775851</v>
       </c>
     </row>
     <row r="85">
@@ -6835,10 +6835,10 @@
         <v>348079.280310373</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>367961.570057282</v>
+        <v>367961.570047853</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>355818.694369394</v>
+        <v>355818.694369407</v>
       </c>
       <c r="K85" s="11" t="n">
         <v>349010.307845754</v>
@@ -6865,7 +6865,7 @@
         <v>1.00267475712588</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>0.94849662640428</v>
+        <v>0.948496626428586</v>
       </c>
     </row>
     <row r="86">
@@ -6894,10 +6894,10 @@
         <v>353836.163763914</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>371651.552169959</v>
+        <v>371651.552190039</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>361305.881149618</v>
+        <v>361305.881149638</v>
       </c>
       <c r="K86" s="11" t="n">
         <v>351350.466059895</v>
@@ -6924,7 +6924,7 @@
         <v>0.992975003805214</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>0.945376022267277</v>
+        <v>0.945376022216199</v>
       </c>
     </row>
     <row r="87">
@@ -6953,10 +6953,10 @@
         <v>364755.318896553</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>375752.810545118</v>
+        <v>375752.810601548</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>367617.450966329</v>
+        <v>367617.450966359</v>
       </c>
       <c r="K87" s="11" t="n">
         <v>366408.402200179</v>
@@ -6983,7 +6983,7 @@
         <v>1.00453203344266</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>0.975131501128674</v>
+        <v>0.975131500982229</v>
       </c>
     </row>
     <row r="88">
@@ -7012,10 +7012,10 @@
         <v>378303.712625868</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>380207.700853176</v>
+        <v>380207.700953498</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>374501.1933495</v>
+        <v>374501.193349542</v>
       </c>
       <c r="K88" s="11" t="n">
         <v>377494.761701028</v>
@@ -7042,7 +7042,7 @@
         <v>0.997861636304797</v>
       </c>
       <c r="S88" s="19" t="n">
-        <v>0.992864586524523</v>
+        <v>0.992864586262546</v>
       </c>
     </row>
     <row r="89">
@@ -7071,10 +7071,10 @@
         <v>389765.083737746</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>384952.738509336</v>
+        <v>384952.738661756</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>381698.852585272</v>
+        <v>381698.852585328</v>
       </c>
       <c r="K89" s="11" t="n">
         <v>390433.610227195</v>
@@ -7101,7 +7101,7 @@
         <v>1.00171520363763</v>
       </c>
       <c r="S89" s="19" t="n">
-        <v>1.01423777822463</v>
+        <v>1.01423777782305</v>
       </c>
     </row>
     <row r="90">
@@ -7130,10 +7130,10 @@
         <v>401055.607921127</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>389922.743341829</v>
+        <v>389922.743555154</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>388967.140801545</v>
+        <v>388967.140801616</v>
       </c>
       <c r="K90" s="11" t="n">
         <v>400031.872276562</v>
@@ -7160,7 +7160,7 @@
         <v>0.997447397257774</v>
       </c>
       <c r="S90" s="19" t="n">
-        <v>1.0259259792032</v>
+        <v>1.02592597864192</v>
       </c>
     </row>
     <row r="91">
@@ -7189,10 +7189,10 @@
         <v>409029.445827794</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>395055.960723709</v>
+        <v>395055.961007255</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>396106.443914427</v>
+        <v>396106.443914514</v>
       </c>
       <c r="K91" s="11" t="n">
         <v>410201.166441417</v>
@@ -7219,7 +7219,7 @@
         <v>1.00286463633749</v>
       </c>
       <c r="S91" s="19" t="n">
-        <v>1.03833686166882</v>
+        <v>1.03833686092357</v>
       </c>
     </row>
     <row r="92">
@@ -7248,10 +7248,10 @@
         <v>410309.333992197</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>400296.954233618</v>
+        <v>400296.954597071</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>402972.471497402</v>
+        <v>402972.471497505</v>
       </c>
       <c r="K92" s="11" t="n">
         <v>410910.806821399</v>
@@ -7278,7 +7278,7 @@
         <v>1.00146590091761</v>
       </c>
       <c r="S92" s="19" t="n">
-        <v>1.02651494715492</v>
+        <v>1.02651494622289</v>
       </c>
     </row>
     <row r="93">
@@ -7307,10 +7307,10 @@
         <v>409913.621396463</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>405599.753203766</v>
+        <v>405599.753657012</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>409491.406736589</v>
+        <v>409491.406736707</v>
       </c>
       <c r="K93" s="11" t="n">
         <v>408087.826349299</v>
@@ -7337,7 +7337,7 @@
         <v>0.99554590296135</v>
       </c>
       <c r="S93" s="19" t="n">
-        <v>1.00613430635961</v>
+        <v>1.00613430523528</v>
       </c>
     </row>
     <row r="94">
@@ -7366,10 +7366,10 @@
         <v>415049.750870997</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>410925.020624235</v>
+        <v>410925.021177127</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>415629.124494726</v>
+        <v>415629.124494856</v>
       </c>
       <c r="K94" s="11" t="n">
         <v>415850.74506037</v>
@@ -7396,7 +7396,7 @@
         <v>1.00192987512387</v>
       </c>
       <c r="S94" s="19" t="n">
-        <v>1.01198691778041</v>
+        <v>1.0119869164188</v>
       </c>
     </row>
     <row r="95">
@@ -7425,10 +7425,10 @@
         <v>423625.21344142</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>416234.974530821</v>
+        <v>416234.975192897</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>421344.481732616</v>
+        <v>421344.481732751</v>
       </c>
       <c r="K95" s="11" t="n">
         <v>423452.493299921</v>
@@ -7455,7 +7455,7 @@
         <v>0.999592280780231</v>
       </c>
       <c r="S95" s="19" t="n">
-        <v>1.0173400103565</v>
+        <v>1.01734000873828</v>
       </c>
     </row>
     <row r="96">
@@ -7484,10 +7484,10 @@
         <v>430592.388294132</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>421494.911537092</v>
+        <v>421494.912317232</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>426597.44351389</v>
+        <v>426597.443514021</v>
       </c>
       <c r="K96" s="11" t="n">
         <v>431054.779420915</v>
@@ -7514,7 +7514,7 @@
         <v>1.00107384881701</v>
       </c>
       <c r="S96" s="19" t="n">
-        <v>1.02268086190877</v>
+        <v>1.0226808600159</v>
       </c>
     </row>
     <row r="97">
@@ -7543,10 +7543,10 @@
         <v>436858.365102814</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>426674.639205848</v>
+        <v>426674.640111858</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>431358.514960014</v>
+        <v>431358.514960128</v>
       </c>
       <c r="K97" s="11" t="n">
         <v>436467.027944467</v>
@@ -7573,7 +7573,7 @@
         <v>0.999104201293582</v>
       </c>
       <c r="S97" s="19" t="n">
-        <v>1.02295048226172</v>
+        <v>1.02295048008956</v>
       </c>
     </row>
     <row r="98">
@@ -7602,10 +7602,10 @@
         <v>444117.892457186</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>431749.940017317</v>
+        <v>431749.941055439</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>435620.48787199</v>
+        <v>435620.487872071</v>
       </c>
       <c r="K98" s="11" t="n">
         <v>443795.99016597</v>
@@ -7632,7 +7632,7 @@
         <v>0.999275187294447</v>
       </c>
       <c r="S98" s="19" t="n">
-        <v>1.02790052535542</v>
+        <v>1.02790052288388</v>
       </c>
     </row>
     <row r="99">
@@ -7661,10 +7661,10 @@
         <v>450989.582453002</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>436702.716694686</v>
+        <v>436702.717869038</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>439401.696615744</v>
+        <v>439401.696615768</v>
       </c>
       <c r="K99" s="11" t="n">
         <v>451818.777986187</v>
@@ -7691,7 +7691,7 @@
         <v>1.00183861349674</v>
       </c>
       <c r="S99" s="19" t="n">
-        <v>1.03461407661008</v>
+        <v>1.03461407382787</v>
       </c>
     </row>
     <row r="100">
@@ -7720,10 +7720,10 @@
         <v>456279.911013051</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>441522.400742487</v>
+        <v>441522.40205441</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>442761.353068668</v>
+        <v>442761.353068608</v>
       </c>
       <c r="K100" s="11" t="n">
         <v>451476.953294478</v>
@@ -7750,7 +7750,7 @@
         <v>0.997401110119194</v>
       </c>
       <c r="S100" s="19" t="n">
-        <v>1.03073839289738</v>
+        <v>1.03073838983468</v>
       </c>
     </row>
     <row r="101">
@@ -7779,10 +7779,10 @@
         <v>457513.638957149</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>446207.871203559</v>
+        <v>446207.872650883</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>445820.754515011</v>
+        <v>445820.754514833</v>
       </c>
       <c r="K101" s="11" t="n">
         <v>458811.120946735</v>
@@ -7809,7 +7809,7 @@
         <v>1.00283594166186</v>
       </c>
       <c r="S101" s="19" t="n">
-        <v>1.02824524298323</v>
+        <v>1.02824523964801</v>
       </c>
     </row>
     <row r="102">
@@ -7838,10 +7838,10 @@
         <v>449809.913939866</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>450766.489426382</v>
+        <v>450766.491002606</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>448762.861922522</v>
+        <v>448762.861922188</v>
       </c>
       <c r="K102" s="11" t="n">
         <v>451435.755328579</v>
@@ -7868,7 +7868,7 @@
         <v>1.00277742148344</v>
       </c>
       <c r="S102" s="19" t="n">
-        <v>1.0006494187984</v>
+        <v>1.00064941529937</v>
       </c>
     </row>
     <row r="103">
@@ -7897,10 +7897,10 @@
         <v>437134.935307832</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>455213.493790526</v>
+        <v>455213.495483916</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>451835.588091111</v>
+        <v>451835.588090578</v>
       </c>
       <c r="K103" s="11" t="n">
         <v>435460.48737933</v>
@@ -7927,7 +7927,7 @@
         <v>0.996492461639749</v>
       </c>
       <c r="S103" s="19" t="n">
-        <v>0.956917300773345</v>
+        <v>0.956917297213621</v>
       </c>
     </row>
     <row r="104">
@@ -7956,10 +7956,10 @@
         <v>431217.531936571</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>459564.305635706</v>
+        <v>459564.307428307</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>455298.327639367</v>
+        <v>455298.327638588</v>
       </c>
       <c r="K104" s="11" t="n">
         <v>431360.130054406</v>
@@ -7986,7 +7986,7 @@
         <v>1.00033068719909</v>
       </c>
       <c r="S104" s="19" t="n">
-        <v>0.938628446040243</v>
+        <v>0.938628442378978</v>
       </c>
     </row>
     <row r="105">
@@ -8015,10 +8015,10 @@
         <v>436762.485230905</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>463822.088910364</v>
+        <v>463822.090776944</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>459329.305584189</v>
+        <v>459329.305583119</v>
       </c>
       <c r="K105" s="11" t="n">
         <v>435799.091109637</v>
@@ -8045,7 +8045,7 @@
         <v>0.997794237935158</v>
       </c>
       <c r="S105" s="19" t="n">
-        <v>0.939582442339991</v>
+        <v>0.939582438558789</v>
       </c>
     </row>
     <row r="106">
@@ -8074,10 +8074,10 @@
         <v>447666.430741407</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>467972.379953204</v>
+        <v>467972.38186013</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>463987.055954554</v>
+        <v>463987.055953151</v>
       </c>
       <c r="K106" s="11" t="n">
         <v>448988.703096293</v>
@@ -8104,7 +8104,7 @@
         <v>1.00295370004111</v>
       </c>
       <c r="S106" s="19" t="n">
-        <v>0.95943419383253</v>
+        <v>0.959434189922962</v>
       </c>
     </row>
     <row r="107">
@@ -8133,10 +8133,10 @@
         <v>458155.610156058</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>471983.200729303</v>
+        <v>471983.202633378</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>469212.461707066</v>
+        <v>469212.461705296</v>
       </c>
       <c r="K107" s="11" t="n">
         <v>457790.588486101</v>
@@ -8163,7 +8163,7 @@
         <v>0.999203280147913</v>
       </c>
       <c r="S107" s="19" t="n">
-        <v>0.969929836016893</v>
+        <v>0.969929832104001</v>
       </c>
     </row>
     <row r="108">
@@ -8192,10 +8192,10 @@
         <v>467135.994843473</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>475810.708405705</v>
+        <v>475810.710252975</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>474871.414034037</v>
+        <v>474871.414031884</v>
       </c>
       <c r="K108" s="11" t="n">
         <v>467074.459917332</v>
@@ -8222,7 +8222,7 @@
         <v>0.999868271923335</v>
       </c>
       <c r="S108" s="19" t="n">
-        <v>0.981639235237799</v>
+        <v>0.981639231426718</v>
       </c>
     </row>
     <row r="109">
@@ -8251,10 +8251,10 @@
         <v>476668.53884325</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>479402.189766799</v>
+        <v>479402.191491363</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>480772.694761672</v>
+        <v>480772.694759145</v>
       </c>
       <c r="K109" s="11" t="n">
         <v>476738.782523127</v>
@@ -8281,7 +8281,7 @@
         <v>1.00014736378459</v>
       </c>
       <c r="S109" s="19" t="n">
-        <v>0.994444315648688</v>
+        <v>0.994444312071352</v>
       </c>
     </row>
     <row r="110">
@@ -8310,10 +8310,10 @@
         <v>485545.679474004</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>482699.471441672</v>
+        <v>482699.472964526</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>486686.100945597</v>
+        <v>486686.10094274</v>
       </c>
       <c r="K110" s="11" t="n">
         <v>485843.974347272</v>
@@ -8340,7 +8340,7 @@
         <v>1.00061434976332</v>
       </c>
       <c r="S110" s="19" t="n">
-        <v>1.0065144113297</v>
+        <v>1.00651440815428</v>
       </c>
     </row>
     <row r="111">
@@ -8369,10 +8369,10 @@
         <v>495321.718474782</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>485642.715429882</v>
+        <v>485642.716657844</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>492361.260080242</v>
+        <v>492361.260077147</v>
       </c>
       <c r="K111" s="11" t="n">
         <v>494407.10545474</v>
@@ -8399,7 +8399,7 @@
         <v>0.998153497038535</v>
       </c>
       <c r="S111" s="19" t="n">
-        <v>1.01804699163891</v>
+        <v>1.01804698906474</v>
       </c>
     </row>
     <row r="112">
@@ -8428,10 +8428,10 @@
         <v>505624.920127525</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>488174.049045301</v>
+        <v>488174.049870057</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>497543.589027047</v>
+        <v>497543.58902387</v>
       </c>
       <c r="K112" s="11" t="n">
         <v>506507.737994056</v>
@@ -8458,7 +8458,7 @@
         <v>1.00174599358415</v>
       </c>
       <c r="S112" s="19" t="n">
-        <v>1.03755564021604</v>
+        <v>1.03755563846313</v>
       </c>
     </row>
     <row r="113">
@@ -8487,10 +8487,10 @@
         <v>513826.620962883</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>490241.077345571</v>
+        <v>490241.077642907</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>501988.733874322</v>
+        <v>501988.733871297</v>
       </c>
       <c r="K113" s="11" t="n">
         <v>513769.275840799</v>
@@ -8517,7 +8517,7 @@
         <v>0.999888395969099</v>
       </c>
       <c r="S113" s="19" t="n">
-        <v>1.04799311926822</v>
+        <v>1.04799311863261</v>
       </c>
     </row>
     <row r="114">
@@ -8546,10 +8546,10 @@
         <v>521028.173614833</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>491802.863943922</v>
+        <v>491802.863573212</v>
       </c>
       <c r="J114" s="10" t="n">
-        <v>505497.161455216</v>
+        <v>505497.16145267</v>
       </c>
       <c r="K114" s="11" t="n">
         <v>515013.015787657</v>
@@ -8576,7 +8576,7 @@
         <v>1</v>
       </c>
       <c r="S114" s="19" t="n">
-        <v>1.05942484644466</v>
+        <v>1.05942484724323</v>
       </c>
     </row>
     <row r="115">
@@ -8605,10 +8605,10 @@
         <v>526357.985138881</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>492833.177577648</v>
+        <v>492833.176381664</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>507928.241312707</v>
+        <v>507928.241311077</v>
       </c>
       <c r="K115" s="11" t="n">
         <v>527580.251263441</v>
@@ -8635,7 +8635,7 @@
         <v>1.00232211946825</v>
       </c>
       <c r="S115" s="19" t="n">
-        <v>1.07050473723498</v>
+        <v>1.07050473983283</v>
       </c>
     </row>
     <row r="116">
@@ -8664,10 +8664,10 @@
         <v>522900.172314504</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>493324.052802584</v>
+        <v>493324.05060773</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>509218.998050573</v>
+        <v>509218.998050417</v>
       </c>
       <c r="K116" s="11" t="n">
         <v>523655.331164008</v>
@@ -8694,7 +8694,7 @@
         <v>1.0014441740307</v>
       </c>
       <c r="S116" s="19" t="n">
-        <v>1.0614834776231</v>
+        <v>1.06148348234576</v>
       </c>
     </row>
     <row r="117">
@@ -8723,10 +8723,10 @@
         <v>512622.376606041</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>493289.241095621</v>
+        <v>493289.237712681</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>509404.716322344</v>
+        <v>509404.716324352</v>
       </c>
       <c r="K117" s="11" t="n">
         <v>511369.68752324</v>
@@ -8753,7 +8753,7 @@
         <v>0.997556312131564</v>
       </c>
       <c r="S117" s="19" t="n">
-        <v>1.03665282945856</v>
+        <v>1.03665283656784</v>
       </c>
     </row>
     <row r="118">
@@ -8779,13 +8779,13 @@
         <v>1</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>503892.850307585</v>
+        <v>503892.850307584</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>492761.450982625</v>
+        <v>492761.446208132</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>508592.862447119</v>
+        <v>508592.862452111</v>
       </c>
       <c r="K118" s="11" t="n">
         <v>504314.051060221</v>
@@ -8812,7 +8812,7 @@
         <v>1.00083589348882</v>
       </c>
       <c r="S118" s="19" t="n">
-        <v>1.02344461007361</v>
+        <v>1.02344461999003</v>
       </c>
     </row>
     <row r="119">
@@ -8832,7 +8832,7 @@
         <v>516391.046914062</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>17372.3266905497</v>
+        <v>17372.3266905498</v>
       </c>
       <c r="G119" s="7" t="n">
         <v>1</v>
@@ -8841,10 +8841,10 @@
         <v>498764.219123199</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>491784.691268479</v>
+        <v>491784.684886833</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>506900.7276</v>
+        <v>506900.727608917</v>
       </c>
       <c r="K119" s="11" t="n">
         <v>499018.720223512</v>
@@ -8859,19 +8859,19 @@
         <v>499018.720223512</v>
       </c>
       <c r="O119" s="15" t="n">
-        <v>-0.0105555806716335</v>
+        <v>-0.0105555806716336</v>
       </c>
       <c r="P119" s="16" t="n">
-        <v>-0.0541368464257893</v>
+        <v>-0.0541368464257894</v>
       </c>
       <c r="Q119" s="17" t="n">
-        <v>-0.0105000660314274</v>
+        <v>-0.0105000660314275</v>
       </c>
       <c r="R119" s="18" t="n">
         <v>1.000510263348</v>
       </c>
       <c r="S119" s="19" t="n">
-        <v>1.01470974815498</v>
+        <v>1.01470976132236</v>
       </c>
     </row>
     <row r="120">
@@ -8891,19 +8891,19 @@
         <v>502076.175540002</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>4325.82897098316</v>
+        <v>4325.82897098321</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>499613.110810706</v>
+        <v>499613.110810707</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>490410.191133114</v>
+        <v>490410.182919563</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>504424.208899155</v>
+        <v>504424.208913034</v>
       </c>
       <c r="K120" s="11" t="n">
         <v>497750.346569019</v>
@@ -8921,16 +8921,16 @@
         <v>-0.00254497131048995</v>
       </c>
       <c r="P120" s="16" t="n">
-        <v>-0.0494695328268809</v>
+        <v>-0.049469532826881</v>
       </c>
       <c r="Q120" s="17" t="n">
         <v>-0.00254173561650251</v>
       </c>
       <c r="R120" s="18" t="n">
-        <v>0.996271586550912</v>
+        <v>0.99627158655091</v>
       </c>
       <c r="S120" s="19" t="n">
-        <v>1.01496737948888</v>
+        <v>1.01496739648789</v>
       </c>
     </row>
     <row r="121">
@@ -8950,46 +8950,46 @@
         <v>511259.942382052</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5018.29812513437</v>
+        <v>5018.29812513245</v>
       </c>
       <c r="G121" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>504696.229750186</v>
+        <v>504696.229750189</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>488693.70102456</v>
+        <v>488693.690749189</v>
       </c>
       <c r="J121" s="10" t="n">
-        <v>501219.79342587</v>
+        <v>501219.793445799</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>506241.644256918</v>
+        <v>506241.64425692</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>506241.644256918</v>
+        <v>506241.64425692</v>
       </c>
       <c r="M121" s="13" t="n">
-        <v>506241.644256918</v>
+        <v>506241.64425692</v>
       </c>
       <c r="N121" s="14" t="n">
-        <v>506241.644256918</v>
+        <v>506241.64425692</v>
       </c>
       <c r="O121" s="15" t="n">
-        <v>0.0169154738976955</v>
+        <v>0.0169154738976995</v>
       </c>
       <c r="P121" s="16" t="n">
-        <v>-0.0100280548328138</v>
+        <v>-0.01002805483281</v>
       </c>
       <c r="Q121" s="17" t="n">
-        <v>0.0170593506291448</v>
+        <v>0.0170593506291488</v>
       </c>
       <c r="R121" s="18" t="n">
         <v>1.00306206865761</v>
       </c>
       <c r="S121" s="19" t="n">
-        <v>1.03590785638442</v>
+        <v>1.03590787816562</v>
       </c>
     </row>
     <row r="122">
@@ -9009,46 +9009,46 @@
         <v>476984.733765134</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>-27871.5187716495</v>
+        <v>-27871.5187716517</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>503615.456241019</v>
+        <v>503615.456241015</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>486695.55898799</v>
+        <v>486695.546420859</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>497310.598949781</v>
+        <v>497310.598976829</v>
       </c>
       <c r="K122" s="11" t="n">
-        <v>504856.252536784</v>
+        <v>504856.252536786</v>
       </c>
       <c r="L122" s="12" t="n">
-        <v>504856.252536784</v>
+        <v>504856.252536786</v>
       </c>
       <c r="M122" s="13" t="n">
-        <v>504856.252536784</v>
+        <v>504856.252536786</v>
       </c>
       <c r="N122" s="14" t="n">
-        <v>504856.252536784</v>
+        <v>504856.252536786</v>
       </c>
       <c r="O122" s="15" t="n">
-        <v>-0.00274037279972715</v>
+        <v>-0.00274037279972659</v>
       </c>
       <c r="P122" s="16" t="n">
-        <v>0.00107512665059084</v>
+        <v>0.00107512665059528</v>
       </c>
       <c r="Q122" s="17" t="n">
-        <v>-0.00273662140570818</v>
+        <v>-0.00273662140570763</v>
       </c>
       <c r="R122" s="18" t="n">
-        <v>1.00246377723398</v>
+        <v>1.00246377723399</v>
       </c>
       <c r="S122" s="19" t="n">
-        <v>1.03731427832741</v>
+        <v>1.03731430511226</v>
       </c>
     </row>
     <row r="123">
@@ -9068,46 +9068,46 @@
         <v>514340.804852638</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>19335.9204361036</v>
+        <v>19335.9204361233</v>
       </c>
       <c r="G123" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>496922.135204692</v>
+        <v>496922.135204673</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>484487.070533102</v>
+        <v>484487.05545066</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>492744.852494677</v>
+        <v>492744.852529797</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>495004.884416534</v>
+        <v>495004.884416514</v>
       </c>
       <c r="L123" s="12" t="n">
-        <v>495004.884416534</v>
+        <v>495004.884416514</v>
       </c>
       <c r="M123" s="13" t="n">
-        <v>495004.884416534</v>
+        <v>495004.884416514</v>
       </c>
       <c r="N123" s="14" t="n">
-        <v>495004.884416534</v>
+        <v>495004.884416514</v>
       </c>
       <c r="O123" s="15" t="n">
-        <v>-0.0197061102851336</v>
+        <v>-0.0197061102851779</v>
       </c>
       <c r="P123" s="16" t="n">
-        <v>-0.00804345737807299</v>
+        <v>-0.00804345737811241</v>
       </c>
       <c r="Q123" s="17" t="n">
-        <v>-0.0195132140500366</v>
+        <v>-0.01951321405008</v>
       </c>
       <c r="R123" s="18" t="n">
-        <v>0.996141748068099</v>
+        <v>0.996141748068097</v>
       </c>
       <c r="S123" s="19" t="n">
-        <v>1.02170917352213</v>
+        <v>1.02170920532866</v>
       </c>
     </row>
     <row r="124">
@@ -9127,46 +9127,46 @@
         <v>499002.622761819</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>4005.90602017125</v>
+        <v>4005.906020175</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>494767.383727439</v>
+        <v>494767.383727462</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>482150.89160306</v>
+        <v>482150.873796006</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>487608.509352284</v>
+        <v>487608.509396174</v>
       </c>
       <c r="K124" s="11" t="n">
-        <v>494996.716741648</v>
+        <v>494996.716741644</v>
       </c>
       <c r="L124" s="12" t="n">
-        <v>494996.716741648</v>
+        <v>494996.716741644</v>
       </c>
       <c r="M124" s="13" t="n">
-        <v>494996.716741648</v>
+        <v>494996.716741644</v>
       </c>
       <c r="N124" s="14" t="n">
-        <v>494996.716741648</v>
+        <v>494996.716741644</v>
       </c>
       <c r="O124" s="15" t="n">
-        <v>-0.0000165003266186844</v>
+        <v>-0.0000165003265864874</v>
       </c>
       <c r="P124" s="16" t="n">
-        <v>-0.00553215049743583</v>
+        <v>-0.00553215049744327</v>
       </c>
       <c r="Q124" s="17" t="n">
-        <v>-0.0000165001904890438</v>
+        <v>-0.0000165001904568474</v>
       </c>
       <c r="R124" s="18" t="n">
-        <v>1.00046351683994</v>
+        <v>1.00046351683988</v>
       </c>
       <c r="S124" s="19" t="n">
-        <v>1.02664274890352</v>
+        <v>1.02664278682003</v>
       </c>
     </row>
     <row r="125">
@@ -9186,46 +9186,46 @@
         <v>501389.215538927</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>4359.41896289777</v>
+        <v>4359.41896280493</v>
       </c>
       <c r="G125" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>496803.49684113</v>
+        <v>496803.496841176</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>479776.251774705</v>
+        <v>479776.231057413</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>481998.824973936</v>
+        <v>481998.825026868</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>497029.796576029</v>
+        <v>497029.796576122</v>
       </c>
       <c r="L125" s="12" t="n">
-        <v>497029.796576029</v>
+        <v>497029.796576122</v>
       </c>
       <c r="M125" s="13" t="n">
-        <v>497029.796576029</v>
+        <v>497029.796576122</v>
       </c>
       <c r="N125" s="14" t="n">
-        <v>497029.796576029</v>
+        <v>497029.796576122</v>
       </c>
       <c r="O125" s="15" t="n">
-        <v>0.00409884746726366</v>
+        <v>0.00409884746745826</v>
       </c>
       <c r="P125" s="16" t="n">
-        <v>-0.0181965426696777</v>
+        <v>-0.0181965426694981</v>
       </c>
       <c r="Q125" s="17" t="n">
-        <v>0.00410725923146305</v>
+        <v>0.00410725923165844</v>
       </c>
       <c r="R125" s="18" t="n">
-        <v>1.00045551155807</v>
+        <v>1.00045551155816</v>
       </c>
       <c r="S125" s="19" t="n">
-        <v>1.03596164824229</v>
+        <v>1.0359616929765</v>
       </c>
     </row>
     <row r="126">
@@ -9245,46 +9245,46 @@
         <v>467327.980201225</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>-29097.4880234906</v>
+        <v>-29097.488023433</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>497163.376366457</v>
+        <v>497163.376366403</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>477460.409265591</v>
+        <v>477460.385487236</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>476049.995847915</v>
+        <v>476049.995909511</v>
       </c>
       <c r="K126" s="11" t="n">
-        <v>496425.468224716</v>
+        <v>496425.468224658</v>
       </c>
       <c r="L126" s="12" t="n">
-        <v>496425.468224716</v>
+        <v>496425.468224658</v>
       </c>
       <c r="M126" s="13" t="n">
-        <v>496425.468224716</v>
+        <v>496425.468224658</v>
       </c>
       <c r="N126" s="14" t="n">
-        <v>496425.468224716</v>
+        <v>496425.468224658</v>
       </c>
       <c r="O126" s="15" t="n">
-        <v>-0.00121661930288642</v>
+        <v>-0.00121661930318922</v>
       </c>
       <c r="P126" s="16" t="n">
-        <v>-0.016699375851453</v>
+        <v>-0.0166993758515712</v>
       </c>
       <c r="Q126" s="17" t="n">
-        <v>-0.00121587952166347</v>
+        <v>-0.00121587952196589</v>
       </c>
       <c r="R126" s="18" t="n">
-        <v>0.998515763274571</v>
+        <v>0.998515763274564</v>
       </c>
       <c r="S126" s="19" t="n">
-        <v>1.03972069430489</v>
+        <v>1.03972074608466</v>
       </c>
     </row>
     <row r="127">
@@ -9304,46 +9304,46 @@
         <v>513476.440667766</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>21889.3778092505</v>
+        <v>21889.3778094036</v>
       </c>
       <c r="G127" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>489881.398318571</v>
+        <v>489881.398318449</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>475311.405758772</v>
+        <v>475311.378816283</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>469971.373320512</v>
+        <v>469971.373389482</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>491587.062858516</v>
+        <v>491587.062858363</v>
       </c>
       <c r="L127" s="12" t="n">
-        <v>491587.062858516</v>
+        <v>491587.062858363</v>
       </c>
       <c r="M127" s="13" t="n">
-        <v>491587.062858516</v>
+        <v>491587.062858363</v>
       </c>
       <c r="N127" s="14" t="n">
-        <v>491587.062858516</v>
+        <v>491587.062858363</v>
       </c>
       <c r="O127" s="15" t="n">
-        <v>-0.00979429691878002</v>
+        <v>-0.00979429691897544</v>
       </c>
       <c r="P127" s="16" t="n">
-        <v>-0.00690462188478558</v>
+        <v>-0.00690462188505525</v>
       </c>
       <c r="Q127" s="17" t="n">
-        <v>-0.00974648900166775</v>
+        <v>-0.00974648900186126</v>
       </c>
       <c r="R127" s="18" t="n">
-        <v>1.00348179078814</v>
+        <v>1.00348179078807</v>
       </c>
       <c r="S127" s="19" t="n">
-        <v>1.03424209245255</v>
+        <v>1.03424215107707</v>
       </c>
     </row>
     <row r="128">
@@ -9363,46 +9363,46 @@
         <v>474407.554522122</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>3539.24899474489</v>
+        <v>3539.24899468328</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>471132.771689423</v>
+        <v>471132.771689566</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>473449.13609915</v>
+        <v>473449.10595207</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>464074.186099903</v>
+        <v>464074.186173737</v>
       </c>
       <c r="K128" s="11" t="n">
-        <v>470868.305527377</v>
+        <v>470868.305527439</v>
       </c>
       <c r="L128" s="12" t="n">
-        <v>470868.305527377</v>
+        <v>470868.305527439</v>
       </c>
       <c r="M128" s="13" t="n">
-        <v>470868.305527377</v>
+        <v>470868.305527439</v>
       </c>
       <c r="N128" s="14" t="n">
-        <v>470868.305527377</v>
+        <v>470868.305527439</v>
       </c>
       <c r="O128" s="15" t="n">
-        <v>-0.0430606121267773</v>
+        <v>-0.043060612126335</v>
       </c>
       <c r="P128" s="16" t="n">
-        <v>-0.0487445883946422</v>
+        <v>-0.0487445883945105</v>
       </c>
       <c r="Q128" s="17" t="n">
-        <v>-0.0421466692200193</v>
+        <v>-0.0421466692195956</v>
       </c>
       <c r="R128" s="18" t="n">
-        <v>0.999438658955739</v>
+        <v>0.999438658955566</v>
       </c>
       <c r="S128" s="19" t="n">
-        <v>0.994548874683694</v>
+        <v>0.994548938012162</v>
       </c>
     </row>
     <row r="129">
@@ -9422,46 +9422,46 @@
         <v>448693.775149267</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>2841.32727639944</v>
+        <v>2841.32727597507</v>
       </c>
       <c r="G129" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>445533.431675557</v>
+        <v>445533.431675761</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>472003.667417317</v>
+        <v>472003.634104639</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>458777.741341955</v>
+        <v>458777.741416576</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>445852.447872867</v>
+        <v>445852.447873291</v>
       </c>
       <c r="L129" s="12" t="n">
-        <v>445852.447872867</v>
+        <v>445852.447873291</v>
       </c>
       <c r="M129" s="13" t="n">
-        <v>445852.447872867</v>
+        <v>445852.447873291</v>
       </c>
       <c r="N129" s="14" t="n">
-        <v>445852.447872867</v>
+        <v>445852.447873291</v>
       </c>
       <c r="O129" s="15" t="n">
-        <v>-0.0545903859038242</v>
+        <v>-0.0545903859030033</v>
       </c>
       <c r="P129" s="16" t="n">
-        <v>-0.102966359473247</v>
+        <v>-0.10296635947256</v>
       </c>
       <c r="Q129" s="17" t="n">
-        <v>-0.053127078974857</v>
+        <v>-0.0531270789740798</v>
       </c>
       <c r="R129" s="18" t="n">
-        <v>1.00071603200709</v>
+        <v>1.00071603200759</v>
       </c>
       <c r="S129" s="19" t="n">
-        <v>0.944595304338327</v>
+        <v>0.944595371006083</v>
       </c>
     </row>
     <row r="130">
@@ -9481,46 +9481,46 @@
         <v>390971.781617488</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>-29496.4285177723</v>
+        <v>-29496.4285174423</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>0.284622345919783</v>
+        <v>0.284622345919805</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>425765.319877603</v>
+        <v>425765.319877388</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>471103.453824755</v>
+        <v>471103.417483769</v>
       </c>
       <c r="J130" s="10" t="n">
-        <v>454535.31679967</v>
+        <v>454535.316869067</v>
       </c>
       <c r="K130" s="11" t="n">
-        <v>420468.21013526</v>
+        <v>420468.21013493</v>
       </c>
       <c r="L130" s="12" t="n">
-        <v>424257.644076143</v>
+        <v>424257.644075895</v>
       </c>
       <c r="M130" s="13" t="n">
-        <v>424257.644076143</v>
+        <v>424257.644075895</v>
       </c>
       <c r="N130" s="14" t="n">
-        <v>424257.644076143</v>
+        <v>424257.644075895</v>
       </c>
       <c r="O130" s="15" t="n">
-        <v>-0.0496471411067852</v>
+        <v>-0.0496471411083209</v>
       </c>
       <c r="P130" s="16" t="n">
-        <v>-0.145374943003337</v>
+        <v>-0.145374943003737</v>
       </c>
       <c r="Q130" s="17" t="n">
-        <v>-0.0484348665118957</v>
+        <v>-0.048434866513357</v>
       </c>
       <c r="R130" s="18" t="n">
-        <v>0.996458904163699</v>
+        <v>0.99645890416362</v>
       </c>
       <c r="S130" s="19" t="n">
-        <v>0.900561523443981</v>
+        <v>0.900561592912901</v>
       </c>
     </row>
     <row r="131">
@@ -9540,46 +9540,46 @@
         <v>444096.358125271</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>24896.3322009631</v>
+        <v>24896.3322014246</v>
       </c>
       <c r="G131" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H131" s="8" t="n">
-        <v>419507.296760817</v>
+        <v>419507.296760419</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>470860.604920733</v>
+        <v>470860.565807843</v>
       </c>
       <c r="J131" s="10" t="n">
-        <v>451735.563758706</v>
+        <v>451735.563814561</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>419200.025924307</v>
+        <v>419200.025923846</v>
       </c>
       <c r="L131" s="12" t="n">
-        <v>419200.025924307</v>
+        <v>419200.025923846</v>
       </c>
       <c r="M131" s="13" t="n">
-        <v>419200.025924307</v>
+        <v>419200.025923846</v>
       </c>
       <c r="N131" s="14" t="n">
-        <v>419200.025924307</v>
+        <v>419200.025923846</v>
       </c>
       <c r="O131" s="15" t="n">
-        <v>-0.0119927269605814</v>
+        <v>-0.0119927269610981</v>
       </c>
       <c r="P131" s="16" t="n">
-        <v>-0.147251712673818</v>
+        <v>-0.147251712674492</v>
       </c>
       <c r="Q131" s="17" t="n">
-        <v>-0.0119211008274203</v>
+        <v>-0.0119211008279309</v>
       </c>
       <c r="R131" s="18" t="n">
-        <v>0.999267543523361</v>
+        <v>0.99926754352321</v>
       </c>
       <c r="S131" s="19" t="n">
-        <v>0.890284771211381</v>
+        <v>0.890284845163527</v>
       </c>
     </row>
     <row r="132">
@@ -9599,46 +9599,46 @@
         <v>428054.007663138</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>2785.14180516687</v>
+        <v>2785.14180496253</v>
       </c>
       <c r="G132" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>424956.232144888</v>
+        <v>424956.232145161</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>471357.951673425</v>
+        <v>471357.910186863</v>
       </c>
       <c r="J132" s="10" t="n">
-        <v>450615.745141104</v>
+        <v>450615.745172444</v>
       </c>
       <c r="K132" s="11" t="n">
-        <v>425268.865857971</v>
+        <v>425268.865858176</v>
       </c>
       <c r="L132" s="12" t="n">
-        <v>425268.865857971</v>
+        <v>425268.865858176</v>
       </c>
       <c r="M132" s="13" t="n">
-        <v>425268.865857971</v>
+        <v>425268.865858176</v>
       </c>
       <c r="N132" s="14" t="n">
-        <v>425268.865857971</v>
+        <v>425268.865858176</v>
       </c>
       <c r="O132" s="15" t="n">
-        <v>0.0143733996002311</v>
+        <v>0.0143733996018125</v>
       </c>
       <c r="P132" s="16" t="n">
-        <v>-0.0968411743456251</v>
+        <v>-0.0968411743453095</v>
       </c>
       <c r="Q132" s="17" t="n">
-        <v>0.0144771936029406</v>
+        <v>0.0144771936045449</v>
       </c>
       <c r="R132" s="18" t="n">
-        <v>1.0007356844998</v>
+        <v>1.00073568449964</v>
       </c>
       <c r="S132" s="19" t="n">
-        <v>0.902220625213117</v>
+        <v>0.90222070462249</v>
       </c>
     </row>
     <row r="133">
@@ -9658,46 +9658,46 @@
         <v>433362.880156828</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>-559.100830081926</v>
+        <v>-559.10083105406</v>
       </c>
       <c r="G133" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H133" s="8" t="n">
-        <v>433334.880015453</v>
+        <v>433334.880016396</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>472646.037189133</v>
+        <v>472645.993893404</v>
       </c>
       <c r="J133" s="10" t="n">
-        <v>451250.446179732</v>
+        <v>451250.44617265</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>433921.98098691</v>
+        <v>433921.980987882</v>
       </c>
       <c r="L133" s="12" t="n">
-        <v>433921.98098691</v>
+        <v>433921.980987882</v>
       </c>
       <c r="M133" s="13" t="n">
-        <v>433921.98098691</v>
+        <v>433921.980987882</v>
       </c>
       <c r="N133" s="14" t="n">
-        <v>433921.98098691</v>
+        <v>433921.980987882</v>
       </c>
       <c r="O133" s="15" t="n">
-        <v>0.0201431561796591</v>
+        <v>0.0201431561814191</v>
       </c>
       <c r="P133" s="16" t="n">
-        <v>-0.0267587784767737</v>
+        <v>-0.0267587784755196</v>
       </c>
       <c r="Q133" s="17" t="n">
-        <v>0.0203473986074219</v>
+        <v>0.0203473986092177</v>
       </c>
       <c r="R133" s="18" t="n">
-        <v>1.00135484355987</v>
+        <v>1.00135484355994</v>
       </c>
       <c r="S133" s="19" t="n">
-        <v>0.918069647991722</v>
+        <v>0.918069732091592</v>
       </c>
     </row>
     <row r="134">
@@ -9717,46 +9717,46 @@
         <v>412150.09254573</v>
       </c>
       <c r="F134" s="6" t="n">
-        <v>-28461.549095093</v>
+        <v>-28461.5490952954</v>
       </c>
       <c r="G134" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>439922.402852121</v>
+        <v>439922.40285131</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>474746.598895526</v>
+        <v>474746.55454734</v>
       </c>
       <c r="J134" s="10" t="n">
-        <v>453587.517711042</v>
+        <v>453587.517648538</v>
       </c>
       <c r="K134" s="11" t="n">
-        <v>440611.641640823</v>
+        <v>440611.641641025</v>
       </c>
       <c r="L134" s="12" t="n">
-        <v>440611.641640823</v>
+        <v>440611.641641025</v>
       </c>
       <c r="M134" s="13" t="n">
-        <v>440611.641640823</v>
+        <v>440611.641641025</v>
       </c>
       <c r="N134" s="14" t="n">
-        <v>440611.641640823</v>
+        <v>440611.641641025</v>
       </c>
       <c r="O134" s="15" t="n">
-        <v>0.0152991056343889</v>
+        <v>0.015299105632608</v>
       </c>
       <c r="P134" s="16" t="n">
-        <v>0.0385473256475846</v>
+        <v>0.0385473256486684</v>
       </c>
       <c r="Q134" s="17" t="n">
-        <v>0.0154167360655442</v>
+        <v>0.0154167360637358</v>
       </c>
       <c r="R134" s="18" t="n">
-        <v>1.00156672809621</v>
+        <v>1.00156672809852</v>
       </c>
       <c r="S134" s="19" t="n">
-        <v>0.928098574409767</v>
+        <v>0.928098661108007</v>
       </c>
     </row>
     <row r="135">
@@ -9776,46 +9776,46 @@
         <v>478511.050017991</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>29725.17578112</v>
+        <v>29725.1757844635</v>
       </c>
       <c r="G135" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H135" s="8" t="n">
-        <v>451101.618071877</v>
+        <v>451101.618070857</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>477657.171685145</v>
+        <v>477657.127260471</v>
       </c>
       <c r="J135" s="10" t="n">
-        <v>457488.168245522</v>
+        <v>457488.168107546</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>448785.874236871</v>
+        <v>448785.874233527</v>
       </c>
       <c r="L135" s="12" t="n">
-        <v>448785.874236871</v>
+        <v>448785.874233527</v>
       </c>
       <c r="M135" s="13" t="n">
-        <v>448785.874236871</v>
+        <v>448785.874233527</v>
       </c>
       <c r="N135" s="14" t="n">
-        <v>448785.874236871</v>
+        <v>448785.874233527</v>
       </c>
       <c r="O135" s="15" t="n">
-        <v>0.0183820229329316</v>
+        <v>0.0183820229250221</v>
       </c>
       <c r="P135" s="16" t="n">
-        <v>0.0705769238618932</v>
+        <v>0.070576923855096</v>
       </c>
       <c r="Q135" s="17" t="n">
-        <v>0.0185520123018252</v>
+        <v>0.018552012293769</v>
       </c>
       <c r="R135" s="18" t="n">
-        <v>0.994866469677267</v>
+        <v>0.994866469672104</v>
       </c>
       <c r="S135" s="19" t="n">
-        <v>0.939556445166692</v>
+        <v>0.939556532543478</v>
       </c>
     </row>
     <row r="136">
@@ -9835,46 +9835,46 @@
         <v>471537.267275214</v>
       </c>
       <c r="F136" s="6" t="n">
-        <v>257.786198776708</v>
+        <v>257.786195876191</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>471107.283703016</v>
+        <v>471107.283703288</v>
       </c>
       <c r="I136" s="9" t="n">
-        <v>481353.956102245</v>
+        <v>481353.912824037</v>
       </c>
       <c r="J136" s="10" t="n">
-        <v>462748.72691331</v>
+        <v>462748.726677073</v>
       </c>
       <c r="K136" s="11" t="n">
-        <v>471279.481076438</v>
+        <v>471279.481079338</v>
       </c>
       <c r="L136" s="12" t="n">
-        <v>471279.481076438</v>
+        <v>471279.481079338</v>
       </c>
       <c r="M136" s="13" t="n">
-        <v>471279.481076438</v>
+        <v>471279.481079338</v>
       </c>
       <c r="N136" s="14" t="n">
-        <v>471279.481076438</v>
+        <v>471279.481079338</v>
       </c>
       <c r="O136" s="15" t="n">
-        <v>0.0489054169224862</v>
+        <v>0.0489054169360907</v>
       </c>
       <c r="P136" s="16" t="n">
-        <v>0.108191826188923</v>
+        <v>0.108191826195211</v>
       </c>
       <c r="Q136" s="17" t="n">
-        <v>0.0501210223646533</v>
+        <v>0.0501210223789397</v>
       </c>
       <c r="R136" s="18" t="n">
-        <v>1.00036551626217</v>
+        <v>1.00036551626775</v>
       </c>
       <c r="S136" s="19" t="n">
-        <v>0.979070546947644</v>
+        <v>0.979070634981248</v>
       </c>
     </row>
     <row r="137">
@@ -9894,46 +9894,46 @@
         <v>484205.691494541</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>-5183.34740390415</v>
+        <v>-5183.34740376056</v>
       </c>
       <c r="G137" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H137" s="8" t="n">
-        <v>487083.264351049</v>
+        <v>487083.264352766</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>485795.108130181</v>
+        <v>485795.067496133</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>469122.011374499</v>
+        <v>469122.01101515</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>489389.038898445</v>
+        <v>489389.038898301</v>
       </c>
       <c r="L137" s="12" t="n">
-        <v>489389.038898445</v>
+        <v>489389.038898301</v>
       </c>
       <c r="M137" s="13" t="n">
-        <v>489389.038898445</v>
+        <v>489389.038898301</v>
       </c>
       <c r="N137" s="14" t="n">
-        <v>489389.038898445</v>
+        <v>489389.038898301</v>
       </c>
       <c r="O137" s="15" t="n">
-        <v>0.0377064576189578</v>
+        <v>0.0377064576125098</v>
       </c>
       <c r="P137" s="16" t="n">
-        <v>0.127827260065003</v>
+        <v>0.127827260062146</v>
       </c>
       <c r="Q137" s="17" t="n">
-        <v>0.0384263659870014</v>
+        <v>0.0384263659803057</v>
       </c>
       <c r="R137" s="18" t="n">
-        <v>1.00473384063086</v>
+        <v>1.00473384062702</v>
       </c>
       <c r="S137" s="19" t="n">
-        <v>1.00739803820194</v>
+        <v>1.00739812246487</v>
       </c>
     </row>
     <row r="138">
@@ -9953,46 +9953,46 @@
         <v>460369.442232949</v>
       </c>
       <c r="F138" s="6" t="n">
-        <v>-26386.8464373716</v>
+        <v>-26386.8464416182</v>
       </c>
       <c r="G138" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>486395.45546425</v>
+        <v>486395.455470643</v>
       </c>
       <c r="I138" s="9" t="n">
-        <v>490932.487205411</v>
+        <v>490932.451015016</v>
       </c>
       <c r="J138" s="10" t="n">
-        <v>476403.493060001</v>
+        <v>476403.492551816</v>
       </c>
       <c r="K138" s="11" t="n">
-        <v>486756.28867032</v>
+        <v>486756.288674567</v>
       </c>
       <c r="L138" s="12" t="n">
-        <v>486756.28867032</v>
+        <v>486756.288674567</v>
       </c>
       <c r="M138" s="13" t="n">
-        <v>486756.28867032</v>
+        <v>486756.288674567</v>
       </c>
       <c r="N138" s="14" t="n">
-        <v>486756.28867032</v>
+        <v>486756.288674567</v>
       </c>
       <c r="O138" s="15" t="n">
-        <v>-0.00539418985593499</v>
+        <v>-0.00539418984691721</v>
       </c>
       <c r="P138" s="16" t="n">
-        <v>0.104728615107981</v>
+        <v>0.104728615117111</v>
       </c>
       <c r="Q138" s="17" t="n">
-        <v>-0.00537966733797413</v>
+        <v>-0.00537966732900486</v>
       </c>
       <c r="R138" s="18" t="n">
-        <v>1.00074185151612</v>
+        <v>1.0007418515117</v>
       </c>
       <c r="S138" s="19" t="n">
-        <v>0.991493334330218</v>
+        <v>0.991493407429445</v>
       </c>
     </row>
     <row r="139">
@@ -10012,46 +10012,46 @@
         <v>514395.681772362</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>35970.2570530974</v>
+        <v>35970.25704564</v>
       </c>
       <c r="G139" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>480597.13811891</v>
+        <v>480597.138120829</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>496720.198971128</v>
+        <v>496720.169351066</v>
       </c>
       <c r="J139" s="10" t="n">
-        <v>484489.978538343</v>
+        <v>484489.977856529</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>478425.424719264</v>
+        <v>478425.424726722</v>
       </c>
       <c r="L139" s="12" t="n">
-        <v>478425.424719264</v>
+        <v>478425.424726722</v>
       </c>
       <c r="M139" s="13" t="n">
-        <v>478425.424719264</v>
+        <v>478425.424726722</v>
       </c>
       <c r="N139" s="14" t="n">
-        <v>478425.424719264</v>
+        <v>478425.424726722</v>
       </c>
       <c r="O139" s="15" t="n">
-        <v>-0.0172632173414389</v>
+        <v>-0.0172632173345758</v>
       </c>
       <c r="P139" s="16" t="n">
-        <v>0.0660438578482296</v>
+        <v>0.0660438578727887</v>
       </c>
       <c r="Q139" s="17" t="n">
-        <v>-0.0171150617772472</v>
+        <v>-0.0171150617705015</v>
       </c>
       <c r="R139" s="18" t="n">
-        <v>0.995481218618683</v>
+        <v>0.995481218630226</v>
       </c>
       <c r="S139" s="19" t="n">
-        <v>0.963168853834093</v>
+        <v>0.963168911284103</v>
       </c>
     </row>
     <row r="140">
@@ -10071,46 +10071,46 @@
         <v>481151.979943508</v>
       </c>
       <c r="F140" s="6" t="n">
-        <v>-3202.86604497614</v>
+        <v>-3202.86601662116</v>
       </c>
       <c r="G140" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>483033.808066592</v>
+        <v>483033.808020358</v>
       </c>
       <c r="I140" s="9" t="n">
-        <v>503109.738946438</v>
+        <v>503109.718373204</v>
       </c>
       <c r="J140" s="10" t="n">
-        <v>493330.038356107</v>
+        <v>493330.037479358</v>
       </c>
       <c r="K140" s="11" t="n">
-        <v>484354.845988484</v>
+        <v>484354.845960129</v>
       </c>
       <c r="L140" s="12" t="n">
-        <v>484354.845988484</v>
+        <v>484354.845960129</v>
       </c>
       <c r="M140" s="13" t="n">
-        <v>484354.845988484</v>
+        <v>484354.845960129</v>
       </c>
       <c r="N140" s="14" t="n">
-        <v>484354.845988484</v>
+        <v>484354.845960129</v>
       </c>
       <c r="O140" s="15" t="n">
-        <v>0.0123174444196763</v>
+        <v>0.0123174443455471</v>
       </c>
       <c r="P140" s="16" t="n">
-        <v>0.0277443967689439</v>
+        <v>0.0277443967024527</v>
       </c>
       <c r="Q140" s="17" t="n">
-        <v>0.0123936165656315</v>
+        <v>0.0123936164905836</v>
       </c>
       <c r="R140" s="18" t="n">
-        <v>1.00273487673084</v>
+        <v>1.00273487676812</v>
       </c>
       <c r="S140" s="19" t="n">
-        <v>0.962722063386751</v>
+        <v>0.962722102698158</v>
       </c>
     </row>
     <row r="141">
@@ -10130,46 +10130,46 @@
         <v>484543.676876562</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>-10382.6063399234</v>
+        <v>-10382.6062743269</v>
       </c>
       <c r="G141" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H141" s="8" t="n">
-        <v>497199.618958886</v>
+        <v>497199.618958473</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>510041.16841654</v>
+        <v>510041.159734958</v>
       </c>
       <c r="J141" s="10" t="n">
-        <v>502841.920290779</v>
+        <v>502841.919204725</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>494926.283216486</v>
+        <v>494926.283150889</v>
       </c>
       <c r="L141" s="12" t="n">
-        <v>494926.283216486</v>
+        <v>494926.283150889</v>
       </c>
       <c r="M141" s="13" t="n">
-        <v>494926.283216486</v>
+        <v>494926.283150889</v>
       </c>
       <c r="N141" s="14" t="n">
-        <v>494926.283216486</v>
+        <v>494926.283150889</v>
       </c>
       <c r="O141" s="15" t="n">
-        <v>0.0215910377234875</v>
+        <v>0.0215910376494912</v>
       </c>
       <c r="P141" s="16" t="n">
-        <v>0.0113146063314056</v>
+        <v>0.0113146061976648</v>
       </c>
       <c r="Q141" s="17" t="n">
-        <v>0.0218258107987481</v>
+        <v>0.0218258107231368</v>
       </c>
       <c r="R141" s="18" t="n">
-        <v>0.995427720264226</v>
+        <v>0.995427720133121</v>
       </c>
       <c r="S141" s="19" t="n">
-        <v>0.97036536237461</v>
+        <v>0.970365378762915</v>
       </c>
     </row>
     <row r="142">
@@ -10189,46 +10189,46 @@
         <v>493602.530577855</v>
       </c>
       <c r="F142" s="6" t="n">
-        <v>-24910.2149287359</v>
+        <v>-24910.2151055623</v>
       </c>
       <c r="G142" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>517466.951742511</v>
+        <v>517466.951876083</v>
       </c>
       <c r="I142" s="9" t="n">
-        <v>517442.826858534</v>
+        <v>517442.833294599</v>
       </c>
       <c r="J142" s="10" t="n">
-        <v>512898.996158005</v>
+        <v>512898.994859456</v>
       </c>
       <c r="K142" s="11" t="n">
-        <v>518512.745506591</v>
+        <v>518512.745683417</v>
       </c>
       <c r="L142" s="12" t="n">
-        <v>518512.745506591</v>
+        <v>518512.745683417</v>
       </c>
       <c r="M142" s="13" t="n">
-        <v>518512.745506591</v>
+        <v>518512.745683417</v>
       </c>
       <c r="N142" s="14" t="n">
-        <v>518512.745506591</v>
+        <v>518512.745683417</v>
       </c>
       <c r="O142" s="15" t="n">
-        <v>0.0465557801816149</v>
+        <v>0.046555780655179</v>
       </c>
       <c r="P142" s="16" t="n">
-        <v>0.0652409790596031</v>
+        <v>0.0652409794135846</v>
       </c>
       <c r="Q142" s="17" t="n">
-        <v>0.0476565159094373</v>
+        <v>0.0476565164055698</v>
       </c>
       <c r="R142" s="18" t="n">
-        <v>1.0020209865781</v>
+        <v>1.00202098666116</v>
       </c>
       <c r="S142" s="19" t="n">
-        <v>1.00206770408733</v>
+        <v>1.00206769196513</v>
       </c>
     </row>
     <row r="143">
@@ -10248,46 +10248,46 @@
         <v>581668.249879602</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>43713.7494066148</v>
+        <v>43713.7493417124</v>
       </c>
       <c r="G143" s="7" t="n">
-        <v>0.445514732383236</v>
+        <v>0.445514735180623</v>
       </c>
       <c r="H143" s="8" t="n">
-        <v>529792.920823574</v>
+        <v>529792.920853365</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>525233.60694627</v>
+        <v>525233.632112532</v>
       </c>
       <c r="J143" s="10" t="n">
-        <v>523335.059588063</v>
+        <v>523335.058090105</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>537954.500472988</v>
+        <v>537954.50053789</v>
       </c>
       <c r="L143" s="12" t="n">
-        <v>533429.024796907</v>
+        <v>533429.024865172</v>
       </c>
       <c r="M143" s="13" t="n">
-        <v>533429.024796907</v>
+        <v>533429.024865172</v>
       </c>
       <c r="N143" s="14" t="n">
-        <v>533429.024796907</v>
+        <v>533429.024865172</v>
       </c>
       <c r="O143" s="15" t="n">
-        <v>0.0283614160946259</v>
+        <v>0.0283614158815731</v>
       </c>
       <c r="P143" s="16" t="n">
-        <v>0.114967970420716</v>
+        <v>0.114967970546022</v>
       </c>
       <c r="Q143" s="17" t="n">
-        <v>0.0287674303468526</v>
+        <v>0.0287674301276708</v>
       </c>
       <c r="R143" s="18" t="n">
-        <v>1.00686325511424</v>
+        <v>1.00686325518648</v>
       </c>
       <c r="S143" s="19" t="n">
-        <v>1.01560337674942</v>
+        <v>1.01560332821734</v>
       </c>
     </row>
     <row r="144">
@@ -10307,46 +10307,46 @@
         <v>514697.789505428</v>
       </c>
       <c r="F144" s="6" t="n">
-        <v>-7732.82673265455</v>
+        <v>-7732.82642396056</v>
       </c>
       <c r="G144" s="7" t="n">
-        <v>0.385417576129181</v>
+        <v>0.385417578940682</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>530456.531398194</v>
+        <v>530456.531080132</v>
       </c>
       <c r="I144" s="9" t="n">
-        <v>533333.070052754</v>
+        <v>533333.117944407</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v>534011.972957971</v>
+        <v>534011.97129735</v>
       </c>
       <c r="K144" s="11" t="n">
-        <v>522430.616238083</v>
+        <v>522430.615929389</v>
       </c>
       <c r="L144" s="12" t="n">
-        <v>527363.202630966</v>
+        <v>527363.202293949</v>
       </c>
       <c r="M144" s="13" t="n">
-        <v>527363.202630966</v>
+        <v>527363.202293949</v>
       </c>
       <c r="N144" s="14" t="n">
-        <v>527363.202630966</v>
+        <v>527363.202293949</v>
       </c>
       <c r="O144" s="15" t="n">
-        <v>-0.0114365247471389</v>
+        <v>-0.0114365255141714</v>
       </c>
       <c r="P144" s="16" t="n">
-        <v>0.0887951405848095</v>
+        <v>0.0887951399527449</v>
       </c>
       <c r="Q144" s="17" t="n">
-        <v>-0.0113713762918148</v>
+        <v>-0.0113713770501251</v>
       </c>
       <c r="R144" s="18" t="n">
-        <v>0.994168553719048</v>
+        <v>0.99416855367982</v>
       </c>
       <c r="S144" s="19" t="n">
-        <v>0.988806493058459</v>
+        <v>0.988806403634811</v>
       </c>
     </row>
     <row r="145">
@@ -10366,46 +10366,46 @@
         <v>522255.200050771</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>-13431.1126716412</v>
+        <v>-13431.1123946296</v>
       </c>
       <c r="G145" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H145" s="8" t="n">
-        <v>538178.201455255</v>
+        <v>538178.201431869</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>541665.899687149</v>
+        <v>541665.974666342</v>
       </c>
       <c r="J145" s="10" t="n">
-        <v>544842.068470792</v>
+        <v>544842.06671574</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>535686.312722413</v>
+        <v>535686.312445401</v>
       </c>
       <c r="L145" s="12" t="n">
-        <v>535686.312722413</v>
+        <v>535686.312445401</v>
       </c>
       <c r="M145" s="13" t="n">
-        <v>535686.312722413</v>
+        <v>535686.312445401</v>
       </c>
       <c r="N145" s="14" t="n">
-        <v>535686.312722413</v>
+        <v>535686.312445401</v>
       </c>
       <c r="O145" s="15" t="n">
-        <v>0.0156592520816175</v>
+        <v>0.0156592522035616</v>
       </c>
       <c r="P145" s="16" t="n">
-        <v>0.082355758601121</v>
+        <v>0.0823557581848715</v>
       </c>
       <c r="Q145" s="17" t="n">
-        <v>0.01578250065595</v>
+        <v>0.0157825007798187</v>
       </c>
       <c r="R145" s="18" t="n">
-        <v>0.995369770224613</v>
+        <v>0.995369769753145</v>
       </c>
       <c r="S145" s="19" t="n">
-        <v>0.988960746895476</v>
+        <v>0.988960609488857</v>
       </c>
     </row>
     <row r="146">
@@ -10425,46 +10425,46 @@
         <v>532348.212016917</v>
       </c>
       <c r="F146" s="6" t="n">
-        <v>-25280.3119370957</v>
+        <v>-25280.3127868491</v>
       </c>
       <c r="G146" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>554181.292195926</v>
+        <v>554181.29274692</v>
       </c>
       <c r="I146" s="9" t="n">
-        <v>550153.048191476</v>
+        <v>550153.154957174</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>555704.434477955</v>
+        <v>555704.432734811</v>
       </c>
       <c r="K146" s="11" t="n">
-        <v>557628.523954013</v>
+        <v>557628.524803766</v>
       </c>
       <c r="L146" s="12" t="n">
-        <v>557628.523954013</v>
+        <v>557628.524803766</v>
       </c>
       <c r="M146" s="13" t="n">
-        <v>557628.523954013</v>
+        <v>557628.524803766</v>
       </c>
       <c r="N146" s="14" t="n">
-        <v>557628.523954013</v>
+        <v>557628.524803766</v>
       </c>
       <c r="O146" s="15" t="n">
-        <v>0.0401442607109295</v>
+        <v>0.0401442627519147</v>
       </c>
       <c r="P146" s="16" t="n">
-        <v>0.0754384126261076</v>
+        <v>0.0754384138981834</v>
       </c>
       <c r="Q146" s="17" t="n">
-        <v>0.0409609331253731</v>
+        <v>0.0409609352499589</v>
       </c>
       <c r="R146" s="18" t="n">
-        <v>1.00622040441753</v>
+        <v>1.00622040495044</v>
       </c>
       <c r="S146" s="19" t="n">
-        <v>1.01358799299052</v>
+        <v>1.01358779783272</v>
       </c>
     </row>
     <row r="147">
@@ -10484,46 +10484,46 @@
         <v>614076.392608544</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>49652.5953141627</v>
+        <v>49652.5951467335</v>
       </c>
       <c r="G147" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H147" s="8" t="n">
-        <v>565360.865227424</v>
+        <v>565360.865334907</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>558711.730665907</v>
+        <v>558711.874206855</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v>566432.380552146</v>
+        <v>566432.378972744</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>564423.797294381</v>
+        <v>564423.79746181</v>
       </c>
       <c r="L147" s="12" t="n">
-        <v>564423.797294381</v>
+        <v>564423.79746181</v>
       </c>
       <c r="M147" s="13" t="n">
-        <v>564423.797294381</v>
+        <v>564423.79746181</v>
       </c>
       <c r="N147" s="14" t="n">
-        <v>564423.797294381</v>
+        <v>564423.79746181</v>
       </c>
       <c r="O147" s="15" t="n">
-        <v>0.0121123699654294</v>
+        <v>0.0121123687381968</v>
       </c>
       <c r="P147" s="16" t="n">
-        <v>0.0581047731875386</v>
+        <v>0.0581047733660029</v>
       </c>
       <c r="Q147" s="17" t="n">
-        <v>0.0121860217841521</v>
+        <v>0.0121860205419644</v>
       </c>
       <c r="R147" s="18" t="n">
-        <v>0.998342531309333</v>
+        <v>0.99834253141568</v>
       </c>
       <c r="S147" s="19" t="n">
-        <v>1.01022363826452</v>
+        <v>1.01022337902352</v>
       </c>
     </row>
     <row r="148">
@@ -10543,46 +10543,46 @@
         <v>562978.965626877</v>
       </c>
       <c r="F148" s="6" t="n">
-        <v>-10015.5183437402</v>
+        <v>-10015.5172125205</v>
       </c>
       <c r="G148" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>573563.743629253</v>
+        <v>573563.742488649</v>
       </c>
       <c r="I148" s="9" t="n">
-        <v>567263.834382965</v>
+        <v>567264.019911486</v>
       </c>
       <c r="J148" s="10" t="n">
-        <v>576868.83671343</v>
+        <v>576868.835508067</v>
       </c>
       <c r="K148" s="11" t="n">
-        <v>572994.483970617</v>
+        <v>572994.482839397</v>
       </c>
       <c r="L148" s="12" t="n">
-        <v>572994.483970617</v>
+        <v>572994.482839397</v>
       </c>
       <c r="M148" s="13" t="n">
-        <v>572994.483970617</v>
+        <v>572994.482839397</v>
       </c>
       <c r="N148" s="14" t="n">
-        <v>572994.483970617</v>
+        <v>572994.482839397</v>
       </c>
       <c r="O148" s="15" t="n">
-        <v>0.0150707071193838</v>
+        <v>0.0150707048485219</v>
       </c>
       <c r="P148" s="16" t="n">
-        <v>0.0865272379870288</v>
+        <v>0.0865272365363354</v>
       </c>
       <c r="Q148" s="17" t="n">
-        <v>0.0151848428739538</v>
+        <v>0.0151848405686092</v>
       </c>
       <c r="R148" s="18" t="n">
-        <v>0.999007504109248</v>
+        <v>0.999007504123636</v>
       </c>
       <c r="S148" s="19" t="n">
-        <v>1.01010226501375</v>
+        <v>1.01010193265705</v>
       </c>
     </row>
     <row r="149">
@@ -10602,46 +10602,46 @@
         <v>572794.046630588</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>-14706.9157768415</v>
+        <v>-14706.9147398183</v>
       </c>
       <c r="G149" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H149" s="8" t="n">
-        <v>587400.45070232</v>
+        <v>587400.45024153</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>575734.816656812</v>
+        <v>575735.049519206</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>586846.690065587</v>
+        <v>586846.689511752</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>587500.96240743</v>
+        <v>587500.961370407</v>
       </c>
       <c r="L149" s="12" t="n">
-        <v>587500.96240743</v>
+        <v>587500.961370407</v>
       </c>
       <c r="M149" s="13" t="n">
-        <v>587500.96240743</v>
+        <v>587500.961370407</v>
       </c>
       <c r="N149" s="14" t="n">
-        <v>587500.96240743</v>
+        <v>587500.961370407</v>
       </c>
       <c r="O149" s="15" t="n">
-        <v>0.0250017940672049</v>
+        <v>0.0250017942762864</v>
       </c>
       <c r="P149" s="16" t="n">
-        <v>0.0967257300670794</v>
+        <v>0.0967257286983354</v>
       </c>
       <c r="Q149" s="17" t="n">
-        <v>0.0253169600103114</v>
+        <v>0.0253169602246861</v>
       </c>
       <c r="R149" s="18" t="n">
-        <v>1.00017111274768</v>
+        <v>1.00017111176683</v>
       </c>
       <c r="S149" s="19" t="n">
-        <v>1.02043674519971</v>
+        <v>1.02043633067159</v>
       </c>
     </row>
     <row r="150">
@@ -10661,46 +10661,46 @@
         <v>576846.885699427</v>
       </c>
       <c r="F150" s="6" t="n">
-        <v>-27503.9509315417</v>
+        <v>-27503.9535185269</v>
       </c>
       <c r="G150" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>605487.574059731</v>
+        <v>605487.577257472</v>
       </c>
       <c r="I150" s="9" t="n">
-        <v>584053.716457608</v>
+        <v>584054.002017483</v>
       </c>
       <c r="J150" s="10" t="n">
-        <v>596179.455948679</v>
+        <v>596179.456391428</v>
       </c>
       <c r="K150" s="11" t="n">
-        <v>604350.836630969</v>
+        <v>604350.839217954</v>
       </c>
       <c r="L150" s="12" t="n">
-        <v>604350.836630969</v>
+        <v>604350.839217954</v>
       </c>
       <c r="M150" s="13" t="n">
-        <v>604350.836630969</v>
+        <v>604350.839217954</v>
       </c>
       <c r="N150" s="14" t="n">
-        <v>604350.836630969</v>
+        <v>604350.839217954</v>
       </c>
       <c r="O150" s="15" t="n">
-        <v>0.0282770004956516</v>
+        <v>0.028277006541396</v>
       </c>
       <c r="P150" s="16" t="n">
-        <v>0.0837875228219298</v>
+        <v>0.0837875258096412</v>
       </c>
       <c r="Q150" s="17" t="n">
-        <v>0.0286805899934064</v>
+        <v>0.0286805962125463</v>
       </c>
       <c r="R150" s="18" t="n">
-        <v>0.998122608163302</v>
+        <v>0.998122607164516</v>
       </c>
       <c r="S150" s="19" t="n">
-        <v>1.034752146252</v>
+        <v>1.03475164476292</v>
       </c>
     </row>
     <row r="151">
@@ -10720,46 +10720,46 @@
         <v>674620.563006485</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>53299.9786409358</v>
+        <v>53299.9746109196</v>
       </c>
       <c r="G151" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H151" s="8" t="n">
-        <v>617255.464180372</v>
+        <v>617255.464077104</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>592156.926596602</v>
+        <v>592157.270088692</v>
       </c>
       <c r="J151" s="10" t="n">
-        <v>604683.92106448</v>
+        <v>604683.922914018</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>621320.584365549</v>
+        <v>621320.588395565</v>
       </c>
       <c r="L151" s="12" t="n">
-        <v>621320.584365549</v>
+        <v>621320.588395565</v>
       </c>
       <c r="M151" s="13" t="n">
-        <v>621320.584365549</v>
+        <v>621320.588395565</v>
       </c>
       <c r="N151" s="14" t="n">
-        <v>621320.584365549</v>
+        <v>621320.588395565</v>
       </c>
       <c r="O151" s="15" t="n">
-        <v>0.0276923029890102</v>
+        <v>0.0276923051946193</v>
       </c>
       <c r="P151" s="16" t="n">
-        <v>0.100805081826649</v>
+        <v>0.100805088640162</v>
       </c>
       <c r="Q151" s="17" t="n">
-        <v>0.0280792988211618</v>
+        <v>0.0280793010887028</v>
       </c>
       <c r="R151" s="18" t="n">
-        <v>1.0065857986216</v>
+        <v>1.00658580531894</v>
       </c>
       <c r="S151" s="19" t="n">
-        <v>1.04924988032575</v>
+        <v>1.04924927849405</v>
       </c>
     </row>
     <row r="152">
@@ -10779,46 +10779,46 @@
         <v>610425.694014854</v>
       </c>
       <c r="F152" s="6" t="n">
-        <v>-10279.7081479654</v>
+        <v>-10279.6974113322</v>
       </c>
       <c r="G152" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H152" s="8" t="n">
-        <v>625833.640613431</v>
+        <v>625833.634963492</v>
       </c>
       <c r="I152" s="9" t="n">
-        <v>599993.525585155</v>
+        <v>599993.931938458</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>612217.729018174</v>
+        <v>612217.732760577</v>
       </c>
       <c r="K152" s="11" t="n">
-        <v>620705.402162819</v>
+        <v>620705.391426186</v>
       </c>
       <c r="L152" s="12" t="n">
-        <v>620705.402162819</v>
+        <v>620705.391426186</v>
       </c>
       <c r="M152" s="13" t="n">
-        <v>620705.402162819</v>
+        <v>620705.391426186</v>
       </c>
       <c r="N152" s="14" t="n">
-        <v>620705.402162819</v>
+        <v>620705.391426186</v>
       </c>
       <c r="O152" s="15" t="n">
-        <v>-0.000990610920721035</v>
+        <v>-0.00099063470440211</v>
       </c>
       <c r="P152" s="16" t="n">
-        <v>0.0832659293010731</v>
+        <v>0.0832659127019229</v>
       </c>
       <c r="Q152" s="17" t="n">
-        <v>-0.00099012042769886</v>
+        <v>-0.000990144187830944</v>
       </c>
       <c r="R152" s="18" t="n">
-        <v>0.991805748176807</v>
+        <v>0.991805739974961</v>
       </c>
       <c r="S152" s="19" t="n">
-        <v>1.03452016679257</v>
+        <v>1.03451944825644</v>
       </c>
     </row>
     <row r="153">
@@ -10838,46 +10838,46 @@
         <v>625876.867863597</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>-14286.6840899157</v>
+        <v>-14286.6846396409</v>
       </c>
       <c r="G153" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H153" s="8" t="n">
-        <v>636769.947773092</v>
+        <v>636769.947140659</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>607530.819220732</v>
+        <v>607531.292846347</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>618721.70673145</v>
+        <v>618721.712939568</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>640163.551953513</v>
+        <v>640163.552503238</v>
       </c>
       <c r="L153" s="12" t="n">
-        <v>640163.551953513</v>
+        <v>640163.552503238</v>
       </c>
       <c r="M153" s="13" t="n">
-        <v>640163.551953513</v>
+        <v>640163.552503238</v>
       </c>
       <c r="N153" s="14" t="n">
-        <v>640163.551953513</v>
+        <v>640163.552503238</v>
       </c>
       <c r="O153" s="15" t="n">
-        <v>0.030867116912541</v>
+        <v>0.0308671350687374</v>
       </c>
       <c r="P153" s="16" t="n">
-        <v>0.0896383034510868</v>
+        <v>0.0896383063101549</v>
       </c>
       <c r="Q153" s="17" t="n">
-        <v>0.0313484460146354</v>
+        <v>0.0313484647400004</v>
       </c>
       <c r="R153" s="18" t="n">
-        <v>1.00532940380162</v>
+        <v>1.00532940566341</v>
       </c>
       <c r="S153" s="19" t="n">
-        <v>1.05371370751963</v>
+        <v>1.0537128869593</v>
       </c>
     </row>
     <row r="154">
@@ -10897,46 +10897,46 @@
         <v>616720.357064478</v>
       </c>
       <c r="F154" s="6" t="n">
-        <v>-30791.2149431747</v>
+        <v>-30791.225819021</v>
       </c>
       <c r="G154" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H154" s="8" t="n">
-        <v>649481.51450194</v>
+        <v>649481.526724572</v>
       </c>
       <c r="I154" s="9" t="n">
-        <v>614749.058223658</v>
+        <v>614749.602754107</v>
       </c>
       <c r="J154" s="10" t="n">
-        <v>624179.119491721</v>
+        <v>624179.128752781</v>
       </c>
       <c r="K154" s="11" t="n">
-        <v>647511.572007653</v>
+        <v>647511.582883499</v>
       </c>
       <c r="L154" s="12" t="n">
-        <v>647511.572007653</v>
+        <v>647511.582883499</v>
       </c>
       <c r="M154" s="13" t="n">
-        <v>647511.572007653</v>
+        <v>647511.582883499</v>
       </c>
       <c r="N154" s="14" t="n">
-        <v>647511.572007653</v>
+        <v>647511.582883499</v>
       </c>
       <c r="O154" s="15" t="n">
-        <v>0.0114129716067246</v>
+        <v>0.0114129875443721</v>
       </c>
       <c r="P154" s="16" t="n">
-        <v>0.0714166883879721</v>
+        <v>0.0714167017975791</v>
       </c>
       <c r="Q154" s="17" t="n">
-        <v>0.0114783480435856</v>
+        <v>0.0114783641641711</v>
       </c>
       <c r="R154" s="18" t="n">
-        <v>0.996966899826552</v>
+        <v>0.99696689781</v>
       </c>
       <c r="S154" s="19" t="n">
-        <v>1.05329412602707</v>
+        <v>1.05329321073591</v>
       </c>
     </row>
     <row r="155">
@@ -10956,46 +10956,46 @@
         <v>711405.500455233</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>54621.8429266156</v>
+        <v>54621.8335982692</v>
       </c>
       <c r="G155" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H155" s="8" t="n">
-        <v>656917.257295569</v>
+        <v>656917.255560496</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>621648.888772218</v>
+        <v>621649.50676577</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>628680.441812511</v>
+        <v>628680.454699826</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>656783.657528617</v>
+        <v>656783.666856964</v>
       </c>
       <c r="L155" s="12" t="n">
-        <v>656783.657528617</v>
+        <v>656783.666856964</v>
       </c>
       <c r="M155" s="13" t="n">
-        <v>656783.657528617</v>
+        <v>656783.666856964</v>
       </c>
       <c r="N155" s="14" t="n">
-        <v>656783.657528617</v>
+        <v>656783.666856964</v>
       </c>
       <c r="O155" s="15" t="n">
-        <v>0.0142180106280893</v>
+        <v>0.0142180080347891</v>
       </c>
       <c r="P155" s="16" t="n">
-        <v>0.0570769326744274</v>
+        <v>0.0570769408317446</v>
       </c>
       <c r="Q155" s="17" t="n">
-        <v>0.0143195672815786</v>
+        <v>0.0143195646511434</v>
       </c>
       <c r="R155" s="18" t="n">
-        <v>0.999796626187746</v>
+        <v>0.999796643028629</v>
       </c>
       <c r="S155" s="19" t="n">
-        <v>1.0565186705727</v>
+        <v>1.05651763527327</v>
       </c>
     </row>
     <row r="156">
@@ -11015,46 +11015,46 @@
         <v>647087.959742494</v>
       </c>
       <c r="F156" s="6" t="n">
-        <v>-8097.30334081217</v>
+        <v>-8097.26999271418</v>
       </c>
       <c r="G156" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H156" s="8" t="n">
-        <v>651444.868563136</v>
+        <v>651444.850890689</v>
       </c>
       <c r="I156" s="9" t="n">
-        <v>628251.433615811</v>
+        <v>628252.126222949</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v>632432.810469922</v>
+        <v>632432.827550965</v>
       </c>
       <c r="K156" s="11" t="n">
-        <v>655185.263083306</v>
+        <v>655185.229735208</v>
       </c>
       <c r="L156" s="12" t="n">
-        <v>655185.263083306</v>
+        <v>655185.229735208</v>
       </c>
       <c r="M156" s="13" t="n">
-        <v>655185.263083306</v>
+        <v>655185.229735208</v>
       </c>
       <c r="N156" s="14" t="n">
-        <v>655185.263083306</v>
+        <v>655185.229735208</v>
       </c>
       <c r="O156" s="15" t="n">
-        <v>-0.00243663582426453</v>
+        <v>-0.0024367009260695</v>
       </c>
       <c r="P156" s="16" t="n">
-        <v>0.0555494777399133</v>
+        <v>0.0555494422721201</v>
       </c>
       <c r="Q156" s="17" t="n">
-        <v>-0.00243366963685643</v>
+        <v>-0.002433734580223</v>
       </c>
       <c r="R156" s="18" t="n">
-        <v>1.00574169005033</v>
+        <v>1.0057416661432</v>
       </c>
       <c r="S156" s="19" t="n">
-        <v>1.0428710990956</v>
+        <v>1.04286989631723</v>
       </c>
     </row>
     <row r="157">
@@ -11074,46 +11074,46 @@
         <v>613490.821702641</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>-14611.5199479659</v>
+        <v>-14611.524212401</v>
       </c>
       <c r="G157" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H157" s="8" t="n">
-        <v>631536.037331088</v>
+        <v>631536.037054675</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>634599.77473431</v>
+        <v>634600.541317315</v>
       </c>
       <c r="J157" s="10" t="n">
-        <v>635783.878318639</v>
+        <v>635783.900137248</v>
       </c>
       <c r="K157" s="11" t="n">
-        <v>628102.341650607</v>
+        <v>628102.345915042</v>
       </c>
       <c r="L157" s="12" t="n">
-        <v>628102.341650607</v>
+        <v>628102.345915042</v>
       </c>
       <c r="M157" s="13" t="n">
-        <v>628102.341650607</v>
+        <v>628102.345915042</v>
       </c>
       <c r="N157" s="14" t="n">
-        <v>628102.341650607</v>
+        <v>628102.345915042</v>
       </c>
       <c r="O157" s="15" t="n">
-        <v>-0.0422149224415739</v>
+        <v>-0.0422148647534468</v>
       </c>
       <c r="P157" s="16" t="n">
-        <v>-0.0188408263264911</v>
+        <v>-0.0188408205075604</v>
       </c>
       <c r="Q157" s="17" t="n">
-        <v>-0.0413362799176025</v>
+        <v>-0.0413362246140864</v>
       </c>
       <c r="R157" s="18" t="n">
-        <v>0.994562945774255</v>
+        <v>0.99456295296204</v>
       </c>
       <c r="S157" s="19" t="n">
-        <v>0.989761368751788</v>
+        <v>0.989760179862463</v>
       </c>
     </row>
     <row r="158">
@@ -11133,46 +11133,46 @@
         <v>578553.044242405</v>
       </c>
       <c r="F158" s="6" t="n">
-        <v>-33308.4130512241</v>
+        <v>-33308.4431476597</v>
       </c>
       <c r="G158" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H158" s="8" t="n">
-        <v>608928.080391887</v>
+        <v>608928.104750917</v>
       </c>
       <c r="I158" s="9" t="n">
-        <v>640753.827751002</v>
+        <v>640754.665430232</v>
       </c>
       <c r="J158" s="10" t="n">
-        <v>639195.060476411</v>
+        <v>639195.087300643</v>
       </c>
       <c r="K158" s="11" t="n">
-        <v>611861.457293629</v>
+        <v>611861.487390064</v>
       </c>
       <c r="L158" s="12" t="n">
-        <v>611861.457293629</v>
+        <v>611861.487390064</v>
       </c>
       <c r="M158" s="13" t="n">
-        <v>611861.457293629</v>
+        <v>611861.487390064</v>
       </c>
       <c r="N158" s="14" t="n">
-        <v>611861.457293629</v>
+        <v>611861.487390064</v>
       </c>
       <c r="O158" s="15" t="n">
-        <v>-0.0261972376887389</v>
+        <v>-0.0261971952898181</v>
       </c>
       <c r="P158" s="16" t="n">
-        <v>-0.0550571082513458</v>
+        <v>-0.0550570776428093</v>
       </c>
       <c r="Q158" s="17" t="n">
-        <v>-0.0258570670414926</v>
+        <v>-0.0258570257388826</v>
       </c>
       <c r="R158" s="18" t="n">
-        <v>1.004817279735</v>
+        <v>1.00481728896443</v>
       </c>
       <c r="S158" s="19" t="n">
-        <v>0.954908782115616</v>
+        <v>0.954907580702877</v>
       </c>
     </row>
     <row r="159">
@@ -11192,46 +11192,46 @@
         <v>631197.751860069</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>55272.868241969</v>
+        <v>55272.8481908001</v>
       </c>
       <c r="G159" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H159" s="8" t="n">
-        <v>600012.417984769</v>
+        <v>600012.43914754</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>646769.447393501</v>
+        <v>646770.35057094</v>
       </c>
       <c r="J159" s="10" t="n">
-        <v>643089.364377648</v>
+        <v>643089.39611201</v>
       </c>
       <c r="K159" s="11" t="n">
-        <v>575924.8836181</v>
+        <v>575924.903669269</v>
       </c>
       <c r="L159" s="12" t="n">
-        <v>600012.417984769</v>
+        <v>600012.43914754</v>
       </c>
       <c r="M159" s="13" t="n">
-        <v>600012.417984769</v>
+        <v>600012.43914754</v>
       </c>
       <c r="N159" s="14" t="n">
-        <v>600012.417984769</v>
+        <v>600012.43914754</v>
       </c>
       <c r="O159" s="15" t="n">
-        <v>-0.0195555282707413</v>
+        <v>-0.019555542188503</v>
       </c>
       <c r="P159" s="16" t="n">
-        <v>-0.0864382645534609</v>
+        <v>-0.086438245307016</v>
       </c>
       <c r="Q159" s="17" t="n">
-        <v>-0.0193655592579242</v>
+        <v>-0.0193655729061606</v>
       </c>
       <c r="R159" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S159" s="19" t="n">
-        <v>0.927706805574746</v>
+        <v>0.927705542806462</v>
       </c>
     </row>
     <row r="160">
@@ -11251,46 +11251,46 @@
         <v>610519.854611727</v>
       </c>
       <c r="F160" s="6" t="n">
-        <v>-6724.03097625457</v>
+        <v>-6723.96681120924</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>0.283992051826819</v>
+        <v>0.283997195839132</v>
       </c>
       <c r="H160" s="8" t="n">
-        <v>608782.526006785</v>
+        <v>608782.502228805</v>
       </c>
       <c r="I160" s="9" t="n">
-        <v>652684.430657882</v>
+        <v>652685.390512403</v>
       </c>
       <c r="J160" s="10" t="n">
-        <v>647753.129440846</v>
+        <v>647753.165642654</v>
       </c>
       <c r="K160" s="11" t="n">
-        <v>617243.885587982</v>
+        <v>617243.821422937</v>
       </c>
       <c r="L160" s="12" t="n">
-        <v>611185.484875494</v>
+        <v>611185.493153038</v>
       </c>
       <c r="M160" s="13" t="n">
-        <v>611185.484875494</v>
+        <v>611185.493153038</v>
       </c>
       <c r="N160" s="14" t="n">
-        <v>611185.484875494</v>
+        <v>611185.493153038</v>
       </c>
       <c r="O160" s="15" t="n">
-        <v>0.0184501373594711</v>
+        <v>0.0184501156323412</v>
       </c>
       <c r="P160" s="16" t="n">
-        <v>-0.0671562391387583</v>
+        <v>-0.0671561790242931</v>
       </c>
       <c r="Q160" s="17" t="n">
-        <v>0.0186213927509218</v>
+        <v>0.0186213706192027</v>
       </c>
       <c r="R160" s="18" t="n">
-        <v>1.0039471547984</v>
+        <v>1.0039472076077</v>
       </c>
       <c r="S160" s="19" t="n">
-        <v>0.936418054678339</v>
+        <v>0.936416690242163</v>
       </c>
     </row>
     <row r="161">
@@ -11310,46 +11310,46 @@
         <v>615220.854937297</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>-14100.4593501796</v>
+        <v>-14100.4079027471</v>
       </c>
       <c r="G161" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>627978.286307661</v>
+        <v>627978.310355692</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>658507.351396841</v>
+        <v>658508.355332945</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>653257.310352538</v>
+        <v>653257.350179059</v>
       </c>
       <c r="K161" s="11" t="n">
-        <v>629321.314287477</v>
+        <v>629321.262840044</v>
       </c>
       <c r="L161" s="12" t="n">
-        <v>629321.314287477</v>
+        <v>629321.262840044</v>
       </c>
       <c r="M161" s="13" t="n">
-        <v>629321.314287477</v>
+        <v>629321.262840044</v>
       </c>
       <c r="N161" s="14" t="n">
-        <v>629321.314287477</v>
+        <v>629321.262840044</v>
       </c>
       <c r="O161" s="15" t="n">
-        <v>0.0292414707920862</v>
+        <v>0.0292413754979987</v>
       </c>
       <c r="P161" s="16" t="n">
-        <v>0.00194072296190884</v>
+        <v>0.00194063425002255</v>
       </c>
       <c r="Q161" s="17" t="n">
-        <v>0.029673200461686</v>
+        <v>0.0296731023399226</v>
       </c>
       <c r="R161" s="18" t="n">
-        <v>1.00213865353166</v>
+        <v>1.0021385332299</v>
       </c>
       <c r="S161" s="19" t="n">
-        <v>0.955678494632666</v>
+        <v>0.955676959515352</v>
       </c>
     </row>
     <row r="162">
@@ -11369,46 +11369,46 @@
         <v>611607.33658973</v>
       </c>
       <c r="F162" s="6" t="n">
-        <v>-35316.0661510499</v>
+        <v>-35316.2375660842</v>
       </c>
       <c r="G162" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H162" s="8" t="n">
-        <v>650523.008172571</v>
+        <v>650523.088242741</v>
       </c>
       <c r="I162" s="9" t="n">
-        <v>664220.846621959</v>
+        <v>664221.877675041</v>
       </c>
       <c r="J162" s="10" t="n">
-        <v>659490.023576429</v>
+        <v>659490.065645259</v>
       </c>
       <c r="K162" s="11" t="n">
-        <v>646923.40274078</v>
+        <v>646923.574155814</v>
       </c>
       <c r="L162" s="12" t="n">
-        <v>646923.40274078</v>
+        <v>646923.574155814</v>
       </c>
       <c r="M162" s="13" t="n">
-        <v>646923.40274078</v>
+        <v>646923.574155814</v>
       </c>
       <c r="N162" s="14" t="n">
-        <v>646923.40274078</v>
+        <v>646923.574155814</v>
       </c>
       <c r="O162" s="15" t="n">
-        <v>0.0275859393526269</v>
+        <v>0.0275862860728532</v>
       </c>
       <c r="P162" s="16" t="n">
-        <v>0.0573037327800259</v>
+        <v>0.0573039609263688</v>
       </c>
       <c r="Q162" s="17" t="n">
-        <v>0.0279699543836878</v>
+        <v>0.0279703108017249</v>
       </c>
       <c r="R162" s="18" t="n">
-        <v>0.994466597819648</v>
+        <v>0.994466738918291</v>
       </c>
       <c r="S162" s="19" t="n">
-        <v>0.973958294189126</v>
+        <v>0.973957040409786</v>
       </c>
     </row>
     <row r="163">
@@ -11428,46 +11428,46 @@
         <v>733730.773968903</v>
       </c>
       <c r="F163" s="6" t="n">
-        <v>55499.9045168264</v>
+        <v>55499.9355376401</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>0.562012023333384</v>
+        <v>0.562013015853083</v>
       </c>
       <c r="H163" s="8" t="n">
-        <v>669164.070450106</v>
+        <v>669164.077597383</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>669789.312071624</v>
+        <v>669790.348248357</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>666219.705595898</v>
+        <v>666219.747528596</v>
       </c>
       <c r="K163" s="11" t="n">
-        <v>678230.869452077</v>
+        <v>678230.838431263</v>
       </c>
       <c r="L163" s="12" t="n">
-        <v>674259.720502361</v>
+        <v>674259.715197651</v>
       </c>
       <c r="M163" s="13" t="n">
-        <v>674259.720502361</v>
+        <v>674259.715197651</v>
       </c>
       <c r="N163" s="14" t="n">
-        <v>674259.720502361</v>
+        <v>674259.715197651</v>
       </c>
       <c r="O163" s="15" t="n">
-        <v>0.041387479531343</v>
+        <v>0.0413872066943215</v>
       </c>
       <c r="P163" s="16" t="n">
-        <v>0.123742943132681</v>
+        <v>0.123742894656645</v>
       </c>
       <c r="Q163" s="17" t="n">
-        <v>0.0422558801332071</v>
+        <v>0.0422555957672559</v>
       </c>
       <c r="R163" s="18" t="n">
-        <v>1.00761494867593</v>
+        <v>1.00761492998632</v>
       </c>
       <c r="S163" s="19" t="n">
-        <v>1.00667435020262</v>
+        <v>1.00667278494081</v>
       </c>
     </row>
     <row r="164">
@@ -11487,46 +11487,46 @@
         <v>668566.509488986</v>
       </c>
       <c r="F164" s="6" t="n">
-        <v>-5886.98367547392</v>
+        <v>-5886.85712141578</v>
       </c>
       <c r="G164" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H164" s="8" t="n">
-        <v>676786.834076262</v>
+        <v>676786.677520392</v>
       </c>
       <c r="I164" s="9" t="n">
-        <v>675166.332581798</v>
+        <v>675167.34632286</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>673151.959790147</v>
+        <v>673151.998858962</v>
       </c>
       <c r="K164" s="11" t="n">
-        <v>674453.49316446</v>
+        <v>674453.366610402</v>
       </c>
       <c r="L164" s="12" t="n">
-        <v>674453.49316446</v>
+        <v>674453.366610402</v>
       </c>
       <c r="M164" s="13" t="n">
-        <v>674453.49316446</v>
+        <v>674453.366610402</v>
       </c>
       <c r="N164" s="14" t="n">
-        <v>674453.49316446</v>
+        <v>674453.366610402</v>
       </c>
       <c r="O164" s="15" t="n">
-        <v>0.000287344502105694</v>
+        <v>0.000287164730132336</v>
       </c>
       <c r="P164" s="16" t="n">
-        <v>0.103516869844929</v>
+        <v>0.103516647836276</v>
       </c>
       <c r="Q164" s="17" t="n">
-        <v>0.000287385789491612</v>
+        <v>0.000287205965870507</v>
       </c>
       <c r="R164" s="18" t="n">
-        <v>0.996552325201499</v>
+        <v>0.996552368733765</v>
       </c>
       <c r="S164" s="19" t="n">
-        <v>0.998944201772306</v>
+        <v>0.998942514450162</v>
       </c>
     </row>
     <row r="165">
@@ -11546,46 +11546,46 @@
         <v>668190.097719574</v>
       </c>
       <c r="F165" s="6" t="n">
-        <v>-13359.8713621947</v>
+        <v>-13359.7522339428</v>
       </c>
       <c r="G165" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H165" s="8" t="n">
-        <v>682784.439171819</v>
+        <v>682784.454800938</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>680308.286993714</v>
+        <v>680309.244522861</v>
       </c>
       <c r="J165" s="10" t="n">
-        <v>680032.58961291</v>
+        <v>680032.622504595</v>
       </c>
       <c r="K165" s="11" t="n">
-        <v>681549.969081769</v>
+        <v>681549.849953517</v>
       </c>
       <c r="L165" s="12" t="n">
-        <v>681549.969081769</v>
+        <v>681549.849953517</v>
       </c>
       <c r="M165" s="13" t="n">
-        <v>681549.969081769</v>
+        <v>681549.849953517</v>
       </c>
       <c r="N165" s="14" t="n">
-        <v>681549.969081769</v>
+        <v>681549.849953517</v>
       </c>
       <c r="O165" s="15" t="n">
-        <v>0.01046684747138</v>
+        <v>0.0104668603206014</v>
       </c>
       <c r="P165" s="16" t="n">
-        <v>0.082992032223516</v>
+        <v>0.0829919314624326</v>
       </c>
       <c r="Q165" s="17" t="n">
-        <v>0.0105218165362491</v>
+        <v>0.0105218295206677</v>
       </c>
       <c r="R165" s="18" t="n">
-        <v>0.998192006116092</v>
+        <v>0.998191808793038</v>
       </c>
       <c r="S165" s="19" t="n">
-        <v>1.00182517560317</v>
+        <v>1.00182359043427</v>
       </c>
     </row>
     <row r="166">
@@ -11605,46 +11605,46 @@
         <v>662325.585972695</v>
       </c>
       <c r="F166" s="6" t="n">
-        <v>-36291.0937236364</v>
+        <v>-36291.4810588085</v>
       </c>
       <c r="G166" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H166" s="8" t="n">
-        <v>697896.269198785</v>
+        <v>697896.470812913</v>
       </c>
       <c r="I166" s="9" t="n">
-        <v>685171.108623967</v>
+        <v>685171.969235349</v>
       </c>
       <c r="J166" s="10" t="n">
-        <v>686613.906184791</v>
+        <v>686613.928172492</v>
       </c>
       <c r="K166" s="11" t="n">
-        <v>698616.679696331</v>
+        <v>698617.067031504</v>
       </c>
       <c r="L166" s="12" t="n">
-        <v>698616.679696331</v>
+        <v>698617.067031504</v>
       </c>
       <c r="M166" s="13" t="n">
-        <v>698616.679696331</v>
+        <v>698617.067031504</v>
       </c>
       <c r="N166" s="14" t="n">
-        <v>698616.679696331</v>
+        <v>698617.067031504</v>
       </c>
       <c r="O166" s="15" t="n">
-        <v>0.0247326373248342</v>
+        <v>0.0247333665465029</v>
       </c>
       <c r="P166" s="16" t="n">
-        <v>0.0799063331710461</v>
+        <v>0.0799066457628252</v>
       </c>
       <c r="Q166" s="17" t="n">
-        <v>0.0250410261738496</v>
+        <v>0.0250417736562498</v>
       </c>
       <c r="R166" s="18" t="n">
-        <v>1.0010322601357</v>
+        <v>1.00103252595296</v>
       </c>
       <c r="S166" s="19" t="n">
-        <v>1.0196236690414</v>
+        <v>1.01962295365229</v>
       </c>
     </row>
     <row r="167">
@@ -11664,46 +11664,46 @@
         <v>766332.954571613</v>
       </c>
       <c r="F167" s="6" t="n">
-        <v>54624.1460812748</v>
+        <v>54624.19029005</v>
       </c>
       <c r="G167" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H167" s="8" t="n">
-        <v>711303.992071987</v>
+        <v>711304.010652527</v>
       </c>
       <c r="I167" s="9" t="n">
-        <v>689711.506840458</v>
+        <v>689712.22222571</v>
       </c>
       <c r="J167" s="10" t="n">
-        <v>692655.807523742</v>
+        <v>692655.811706891</v>
       </c>
       <c r="K167" s="11" t="n">
-        <v>711708.808490338</v>
+        <v>711708.764281563</v>
       </c>
       <c r="L167" s="12" t="n">
-        <v>711708.808490338</v>
+        <v>711708.764281563</v>
       </c>
       <c r="M167" s="13" t="n">
-        <v>711708.808490338</v>
+        <v>711708.764281563</v>
       </c>
       <c r="N167" s="14" t="n">
-        <v>711708.808490338</v>
+        <v>711708.764281563</v>
       </c>
       <c r="O167" s="15" t="n">
-        <v>0.0185666429416236</v>
+        <v>0.0185660263937825</v>
       </c>
       <c r="P167" s="16" t="n">
-        <v>0.0555410427899732</v>
+        <v>0.0555409855280087</v>
       </c>
       <c r="Q167" s="17" t="n">
-        <v>0.0187400747427002</v>
+        <v>0.0187394466409001</v>
       </c>
       <c r="R167" s="18" t="n">
-        <v>1.0005691187212</v>
+        <v>1.0005690304328</v>
       </c>
       <c r="S167" s="19" t="n">
-        <v>1.03189348217583</v>
+        <v>1.03189234777495</v>
       </c>
     </row>
     <row r="168">
@@ -11723,46 +11723,46 @@
         <v>711417.391930105</v>
       </c>
       <c r="F168" s="6" t="n">
-        <v>-5275.45188722379</v>
+        <v>-5275.13042588564</v>
       </c>
       <c r="G168" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H168" s="8" t="n">
-        <v>716562.90944814</v>
+        <v>716562.701020855</v>
       </c>
       <c r="I168" s="9" t="n">
-        <v>693894.594493008</v>
+        <v>693895.108445449</v>
       </c>
       <c r="J168" s="10" t="n">
-        <v>697978.205515269</v>
+        <v>697978.184646329</v>
       </c>
       <c r="K168" s="11" t="n">
-        <v>716692.843817329</v>
+        <v>716692.522355991</v>
       </c>
       <c r="L168" s="12" t="n">
-        <v>716692.843817329</v>
+        <v>716692.522355991</v>
       </c>
       <c r="M168" s="13" t="n">
-        <v>716692.843817329</v>
+        <v>716692.522355991</v>
       </c>
       <c r="N168" s="14" t="n">
-        <v>716692.843817329</v>
+        <v>716692.522355991</v>
       </c>
       <c r="O168" s="15" t="n">
-        <v>0.00697850712454314</v>
+        <v>0.006978120706504</v>
       </c>
       <c r="P168" s="16" t="n">
-        <v>0.0626275215132872</v>
+        <v>0.0626272442791267</v>
       </c>
       <c r="Q168" s="17" t="n">
-        <v>0.00700291364604988</v>
+        <v>0.00700252452203376</v>
       </c>
       <c r="R168" s="18" t="n">
-        <v>1.00018133002347</v>
+        <v>1.0001811723314</v>
       </c>
       <c r="S168" s="19" t="n">
-        <v>1.03285549347877</v>
+        <v>1.03285426519523</v>
       </c>
     </row>
     <row r="169">
@@ -11782,46 +11782,46 @@
         <v>703050.456407993</v>
       </c>
       <c r="F169" s="6" t="n">
-        <v>-11898.0317013444</v>
+        <v>-11897.8244469156</v>
       </c>
       <c r="G169" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H169" s="8" t="n">
-        <v>715431.607584135</v>
+        <v>715431.08778301</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>697699.23274497</v>
+        <v>697699.480684859</v>
       </c>
       <c r="J169" s="10" t="n">
-        <v>702496.277049712</v>
+        <v>702496.223292214</v>
       </c>
       <c r="K169" s="11" t="n">
-        <v>714948.488109337</v>
+        <v>714948.280854908</v>
       </c>
       <c r="L169" s="12" t="n">
-        <v>714948.488109337</v>
+        <v>714948.280854908</v>
       </c>
       <c r="M169" s="13" t="n">
-        <v>714948.488109337</v>
+        <v>714948.280854908</v>
       </c>
       <c r="N169" s="14" t="n">
-        <v>714948.488109337</v>
+        <v>714948.280854908</v>
       </c>
       <c r="O169" s="15" t="n">
-        <v>-0.00243686254692437</v>
+        <v>-0.00243670389976355</v>
       </c>
       <c r="P169" s="16" t="n">
-        <v>0.0490037716127627</v>
+        <v>0.0490036508755292</v>
       </c>
       <c r="Q169" s="17" t="n">
-        <v>-0.00243389580772257</v>
+        <v>-0.00243373754667986</v>
       </c>
       <c r="R169" s="18" t="n">
-        <v>0.999324716059961</v>
+        <v>0.999325152434181</v>
       </c>
       <c r="S169" s="19" t="n">
-        <v>1.02472305336571</v>
+        <v>1.02472239215818</v>
       </c>
     </row>
     <row r="170">
@@ -11841,46 +11841,46 @@
         <v>672685.993630504</v>
       </c>
       <c r="F170" s="6" t="n">
-        <v>-37502.645316855</v>
+        <v>-37503.3684933611</v>
       </c>
       <c r="G170" s="7" t="n">
-        <v>0.900362251774137</v>
+        <v>0.900069498159122</v>
       </c>
       <c r="H170" s="8" t="n">
-        <v>707157.903449762</v>
+        <v>707157.417898837</v>
       </c>
       <c r="I170" s="9" t="n">
-        <v>701118.531665522</v>
+        <v>701118.440117925</v>
       </c>
       <c r="J170" s="10" t="n">
-        <v>706218.772208923</v>
+        <v>706218.675634503</v>
       </c>
       <c r="K170" s="11" t="n">
-        <v>710188.638947359</v>
+        <v>710189.362123865</v>
       </c>
       <c r="L170" s="12" t="n">
-        <v>709886.663286911</v>
+        <v>709886.378415905</v>
       </c>
       <c r="M170" s="13" t="n">
-        <v>709886.663286911</v>
+        <v>709886.378415905</v>
       </c>
       <c r="N170" s="14" t="n">
-        <v>709886.663286911</v>
+        <v>709886.378415905</v>
       </c>
       <c r="O170" s="15" t="n">
-        <v>-0.00710516737644159</v>
+        <v>-0.00710527878008772</v>
       </c>
       <c r="P170" s="16" t="n">
-        <v>0.0161318558776435</v>
+        <v>0.0161308847381665</v>
       </c>
       <c r="Q170" s="17" t="n">
-        <v>-0.00707998535084997</v>
+        <v>-0.00708009596575376</v>
       </c>
       <c r="R170" s="18" t="n">
-        <v>1.00385877018957</v>
+        <v>1.00385905662303</v>
       </c>
       <c r="S170" s="19" t="n">
-        <v>1.01250591907842</v>
+        <v>1.01250564497563</v>
       </c>
     </row>
     <row r="171">
@@ -11900,46 +11900,46 @@
         <v>730838.272592776</v>
       </c>
       <c r="F171" s="6" t="n">
-        <v>54045.6598525358</v>
+        <v>54045.6251948423</v>
       </c>
       <c r="G171" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H171" s="8" t="n">
-        <v>701246.370049731</v>
+        <v>701246.123409486</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>704156.382108448</v>
+        <v>704155.868418739</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v>709216.70213005</v>
+        <v>709216.549950966</v>
       </c>
       <c r="K171" s="11" t="n">
-        <v>676792.61274024</v>
+        <v>676792.647397934</v>
       </c>
       <c r="L171" s="12" t="n">
-        <v>701246.370049731</v>
+        <v>701246.123409486</v>
       </c>
       <c r="M171" s="13" t="n">
-        <v>701246.370049731</v>
+        <v>701246.123409486</v>
       </c>
       <c r="N171" s="14" t="n">
-        <v>701246.370049731</v>
+        <v>701246.123409486</v>
       </c>
       <c r="O171" s="15" t="n">
-        <v>-0.0122460476960653</v>
+        <v>-0.0122459981221851</v>
       </c>
       <c r="P171" s="16" t="n">
-        <v>-0.0147004481549126</v>
+        <v>-0.0147007334982564</v>
       </c>
       <c r="Q171" s="17" t="n">
-        <v>-0.012171370000351</v>
+        <v>-0.0121713210298516</v>
       </c>
       <c r="R171" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S171" s="19" t="n">
-        <v>0.995867378138357</v>
+        <v>0.99586775437122</v>
       </c>
     </row>
     <row r="172">
@@ -11959,46 +11959,46 @@
         <v>703461.652530196</v>
       </c>
       <c r="F172" s="6" t="n">
-        <v>-4657.62331635545</v>
+        <v>-4657.05276153612</v>
       </c>
       <c r="G172" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H172" s="8" t="n">
-        <v>707330.892177508</v>
+        <v>707330.316025566</v>
       </c>
       <c r="I172" s="9" t="n">
-        <v>706822.155009794</v>
+        <v>706821.127222831</v>
       </c>
       <c r="J172" s="10" t="n">
-        <v>711579.417405631</v>
+        <v>711579.19303328</v>
       </c>
       <c r="K172" s="11" t="n">
-        <v>708119.275846552</v>
+        <v>708118.705291732</v>
       </c>
       <c r="L172" s="12" t="n">
-        <v>708119.275846552</v>
+        <v>708118.705291732</v>
       </c>
       <c r="M172" s="13" t="n">
-        <v>708119.275846552</v>
+        <v>708118.705291732</v>
       </c>
       <c r="N172" s="14" t="n">
-        <v>708119.275846552</v>
+        <v>708118.705291732</v>
       </c>
       <c r="O172" s="15" t="n">
-        <v>0.00975326779044118</v>
+        <v>0.00975281377449511</v>
       </c>
       <c r="P172" s="16" t="n">
-        <v>-0.0119626811467959</v>
+        <v>-0.0119630340722315</v>
       </c>
       <c r="Q172" s="17" t="n">
-        <v>0.00980098591645229</v>
+        <v>0.0098005274508064</v>
       </c>
       <c r="R172" s="18" t="n">
-        <v>1.00111458961819</v>
+        <v>1.00111459843909</v>
       </c>
       <c r="S172" s="19" t="n">
-        <v>1.00183514456581</v>
+        <v>1.00183579411951</v>
       </c>
     </row>
     <row r="173">
@@ -12018,46 +12018,46 @@
         <v>706958.039082319</v>
       </c>
       <c r="F173" s="6" t="n">
-        <v>-11464.8078052982</v>
+        <v>-11463.9289498805</v>
       </c>
       <c r="G173" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H173" s="8" t="n">
-        <v>715749.154921061</v>
+        <v>715749.07258689</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>709123.402548069</v>
+        <v>709121.759575097</v>
       </c>
       <c r="J173" s="10" t="n">
-        <v>713356.416967805</v>
+        <v>713356.099540416</v>
       </c>
       <c r="K173" s="11" t="n">
-        <v>718422.846887617</v>
+        <v>718421.968032199</v>
       </c>
       <c r="L173" s="12" t="n">
-        <v>718422.846887617</v>
+        <v>718421.968032199</v>
       </c>
       <c r="M173" s="13" t="n">
-        <v>718422.846887617</v>
+        <v>718421.968032199</v>
       </c>
       <c r="N173" s="14" t="n">
-        <v>718422.846887617</v>
+        <v>718421.968032199</v>
       </c>
       <c r="O173" s="15" t="n">
-        <v>0.0144457707285147</v>
+        <v>0.0144453531485609</v>
       </c>
       <c r="P173" s="16" t="n">
-        <v>0.00485959315400186</v>
+        <v>0.00485865519270501</v>
       </c>
       <c r="Q173" s="17" t="n">
-        <v>0.0145506151188266</v>
+        <v>0.014550191462916</v>
       </c>
       <c r="R173" s="18" t="n">
-        <v>1.00373551536621</v>
+        <v>1.00373440294606</v>
       </c>
       <c r="S173" s="19" t="n">
-        <v>1.01311400005434</v>
+        <v>1.01311510799313</v>
       </c>
     </row>
     <row r="174">
@@ -12077,46 +12077,46 @@
         <v>677085.529173151</v>
       </c>
       <c r="F174" s="6" t="n">
-        <v>-38170.6743848258</v>
+        <v>-38172.6348912062</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H174" s="8" t="n">
-        <v>717929.847210312</v>
+        <v>717930.719970636</v>
       </c>
       <c r="I174" s="9" t="n">
-        <v>711068.487602306</v>
+        <v>711066.119506727</v>
       </c>
       <c r="J174" s="10" t="n">
-        <v>714579.899040913</v>
+        <v>714579.461692635</v>
       </c>
       <c r="K174" s="11" t="n">
-        <v>715256.203557977</v>
+        <v>715258.164064357</v>
       </c>
       <c r="L174" s="12" t="n">
-        <v>715256.203557977</v>
+        <v>715258.164064357</v>
       </c>
       <c r="M174" s="13" t="n">
-        <v>715256.203557977</v>
+        <v>715258.164064357</v>
       </c>
       <c r="N174" s="14" t="n">
-        <v>715256.203557977</v>
+        <v>715258.164064357</v>
       </c>
       <c r="O174" s="15" t="n">
-        <v>-0.00441751377793696</v>
+        <v>-0.00441354948396926</v>
       </c>
       <c r="P174" s="16" t="n">
-        <v>0.00756394020167117</v>
+        <v>0.00756710624655077</v>
       </c>
       <c r="Q174" s="17" t="n">
-        <v>-0.00440777091563704</v>
+        <v>-0.0044038240875458</v>
       </c>
       <c r="R174" s="18" t="n">
-        <v>0.996275898456201</v>
+        <v>0.996277418096292</v>
       </c>
       <c r="S174" s="19" t="n">
-        <v>1.00588932856495</v>
+        <v>1.0058954356601</v>
       </c>
     </row>
     <row r="175">
@@ -12136,46 +12136,46 @@
         <v>776486.60279942</v>
       </c>
       <c r="F175" s="6" t="n">
-        <v>54400.7439247627</v>
+        <v>54401.0019806777</v>
       </c>
       <c r="G175" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H175" s="8" t="n">
-        <v>721718.898728283</v>
+        <v>721719.230278475</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>712671.585204249</v>
+        <v>712668.373679199</v>
       </c>
       <c r="J175" s="10" t="n">
-        <v>715307.393998895</v>
+        <v>715306.801052659</v>
       </c>
       <c r="K175" s="11" t="n">
-        <v>722085.858874657</v>
+        <v>722085.600818742</v>
       </c>
       <c r="L175" s="12" t="n">
-        <v>722085.858874657</v>
+        <v>722085.600818742</v>
       </c>
       <c r="M175" s="13" t="n">
-        <v>722085.858874657</v>
+        <v>722085.600818742</v>
       </c>
       <c r="N175" s="14" t="n">
-        <v>722085.858874657</v>
+        <v>722085.600818742</v>
       </c>
       <c r="O175" s="15" t="n">
-        <v>0.00950324476671517</v>
+        <v>0.00950014640994391</v>
       </c>
       <c r="P175" s="16" t="n">
-        <v>0.0297177849540218</v>
+        <v>0.0297177791271543</v>
       </c>
       <c r="Q175" s="17" t="n">
-        <v>0.00954854398005511</v>
+        <v>0.0095454160433337</v>
       </c>
       <c r="R175" s="18" t="n">
-        <v>1.00050845300992</v>
+        <v>1.00050763582969</v>
       </c>
       <c r="S175" s="19" t="n">
-        <v>1.01320983446774</v>
+        <v>1.01321403823622</v>
       </c>
     </row>
     <row r="176">
@@ -12195,46 +12195,46 @@
         <v>721458.944216182</v>
       </c>
       <c r="F176" s="6" t="n">
-        <v>-4506.90142099443</v>
+        <v>-4505.97535752763</v>
       </c>
       <c r="G176" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H176" s="8" t="n">
-        <v>724816.811034393</v>
+        <v>724815.409618577</v>
       </c>
       <c r="I176" s="9" t="n">
-        <v>713949.487708114</v>
+        <v>713945.308781837</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>715599.813738278</v>
+        <v>715599.032695067</v>
       </c>
       <c r="K176" s="11" t="n">
-        <v>725965.845637177</v>
+        <v>725964.91957371</v>
       </c>
       <c r="L176" s="12" t="n">
-        <v>725965.845637177</v>
+        <v>725964.91957371</v>
       </c>
       <c r="M176" s="13" t="n">
-        <v>725965.845637177</v>
+        <v>725964.91957371</v>
       </c>
       <c r="N176" s="14" t="n">
-        <v>725965.845637177</v>
+        <v>725964.91957371</v>
       </c>
       <c r="O176" s="15" t="n">
-        <v>0.0053589192097018</v>
+        <v>0.00535800095509338</v>
       </c>
       <c r="P176" s="16" t="n">
-        <v>0.0252027735995319</v>
+        <v>0.0252022918595622</v>
       </c>
       <c r="Q176" s="17" t="n">
-        <v>0.00537330390123736</v>
+        <v>0.00537238071299173</v>
       </c>
       <c r="R176" s="18" t="n">
-        <v>1.00158527587287</v>
+        <v>1.00158593476336</v>
       </c>
       <c r="S176" s="19" t="n">
-        <v>1.01683082365902</v>
+        <v>1.01683547835391</v>
       </c>
     </row>
     <row r="177">
@@ -12254,46 +12254,46 @@
         <v>706597.345022507</v>
       </c>
       <c r="F177" s="6" t="n">
-        <v>-12350.499330309</v>
+        <v>-12349.0344192221</v>
       </c>
       <c r="G177" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H177" s="8" t="n">
-        <v>718805.714665897</v>
+        <v>718805.619825272</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>714924.871389162</v>
+        <v>714919.597270929</v>
       </c>
       <c r="J177" s="10" t="n">
-        <v>715551.962479966</v>
+        <v>715550.96569327</v>
       </c>
       <c r="K177" s="11" t="n">
-        <v>718947.844352816</v>
+        <v>718946.379441729</v>
       </c>
       <c r="L177" s="12" t="n">
-        <v>718947.844352816</v>
+        <v>718946.379441729</v>
       </c>
       <c r="M177" s="13" t="n">
-        <v>718947.844352816</v>
+        <v>718946.379441729</v>
       </c>
       <c r="N177" s="14" t="n">
-        <v>718947.844352816</v>
+        <v>718946.379441729</v>
       </c>
       <c r="O177" s="15" t="n">
-        <v>-0.0097141531990014</v>
+        <v>-0.00971491514703616</v>
       </c>
       <c r="P177" s="16" t="n">
-        <v>0.000730763877392349</v>
+        <v>0.000729949017241438</v>
       </c>
       <c r="Q177" s="17" t="n">
-        <v>-0.00966712322148056</v>
+        <v>-0.0096678778033823</v>
       </c>
       <c r="R177" s="18" t="n">
-        <v>1.00019773032409</v>
+        <v>1.00019582431269</v>
       </c>
       <c r="S177" s="19" t="n">
-        <v>1.00562712688375</v>
+        <v>1.0056324965579</v>
       </c>
     </row>
     <row r="178">
@@ -12313,46 +12313,46 @@
         <v>671066.046635063</v>
       </c>
       <c r="F178" s="6" t="n">
-        <v>-37666.2458650297</v>
+        <v>-37669.4237177219</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H178" s="8" t="n">
-        <v>710247.163008893</v>
+        <v>710248.48314784</v>
       </c>
       <c r="I178" s="9" t="n">
-        <v>715627.922746361</v>
+        <v>715621.423859504</v>
       </c>
       <c r="J178" s="10" t="n">
-        <v>715310.47460436</v>
+        <v>715309.23855507</v>
       </c>
       <c r="K178" s="11" t="n">
-        <v>708732.292500092</v>
+        <v>708735.470352785</v>
       </c>
       <c r="L178" s="12" t="n">
-        <v>708732.292500092</v>
+        <v>708735.470352785</v>
       </c>
       <c r="M178" s="13" t="n">
-        <v>708732.292500092</v>
+        <v>708735.470352785</v>
       </c>
       <c r="N178" s="14" t="n">
-        <v>708732.292500092</v>
+        <v>708735.470352785</v>
       </c>
       <c r="O178" s="15" t="n">
-        <v>-0.0143109453392728</v>
+        <v>-0.014304423916151</v>
       </c>
       <c r="P178" s="16" t="n">
-        <v>-0.00912108280282176</v>
+        <v>-0.00911935583441381</v>
       </c>
       <c r="Q178" s="17" t="n">
-        <v>-0.0142090305061271</v>
+        <v>-0.014202601725143</v>
       </c>
       <c r="R178" s="18" t="n">
-        <v>0.997867122055957</v>
+        <v>0.997869741603179</v>
       </c>
       <c r="S178" s="19" t="n">
-        <v>0.990364224163019</v>
+        <v>0.990377658805151</v>
       </c>
     </row>
     <row r="179">
@@ -12372,46 +12372,46 @@
         <v>760576.868348004</v>
       </c>
       <c r="F179" s="6" t="n">
-        <v>55621.5698162491</v>
+        <v>55622.1741917762</v>
       </c>
       <c r="G179" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H179" s="8" t="n">
-        <v>702939.069408547</v>
+        <v>702939.590579461</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>716091.342636778</v>
+        <v>716083.489999454</v>
       </c>
       <c r="J179" s="10" t="n">
-        <v>715038.963901222</v>
+        <v>715037.466857014</v>
       </c>
       <c r="K179" s="11" t="n">
-        <v>704955.298531755</v>
+        <v>704954.694156228</v>
       </c>
       <c r="L179" s="12" t="n">
-        <v>704955.298531755</v>
+        <v>704954.694156228</v>
       </c>
       <c r="M179" s="13" t="n">
-        <v>704955.298531755</v>
+        <v>704954.694156228</v>
       </c>
       <c r="N179" s="14" t="n">
-        <v>704955.298531755</v>
+        <v>704954.694156228</v>
       </c>
       <c r="O179" s="15" t="n">
-        <v>-0.00534347613893395</v>
+        <v>-0.00534881730866089</v>
       </c>
       <c r="P179" s="16" t="n">
-        <v>-0.0237237166915297</v>
+        <v>-0.0237242047800017</v>
       </c>
       <c r="Q179" s="17" t="n">
-        <v>-0.00532922516485579</v>
+        <v>-0.00533453785609861</v>
       </c>
       <c r="R179" s="18" t="n">
-        <v>1.00286828433779</v>
+        <v>1.00286668101181</v>
       </c>
       <c r="S179" s="19" t="n">
-        <v>0.984448849690016</v>
+        <v>0.984458801245041</v>
       </c>
     </row>
     <row r="180">
@@ -12431,46 +12431,46 @@
         <v>690879.798251683</v>
       </c>
       <c r="F180" s="6" t="n">
-        <v>-5742.07905282718</v>
+        <v>-5740.96114564641</v>
       </c>
       <c r="G180" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H180" s="8" t="n">
-        <v>697901.277131205</v>
+        <v>697900.863708725</v>
       </c>
       <c r="I180" s="9" t="n">
-        <v>716343.522148578</v>
+        <v>716334.193421725</v>
       </c>
       <c r="J180" s="10" t="n">
-        <v>714868.153249796</v>
+        <v>714866.397334636</v>
       </c>
       <c r="K180" s="11" t="n">
-        <v>696621.877304511</v>
+        <v>696620.75939733</v>
       </c>
       <c r="L180" s="12" t="n">
-        <v>696621.877304511</v>
+        <v>696620.75939733</v>
       </c>
       <c r="M180" s="13" t="n">
-        <v>696621.877304511</v>
+        <v>696620.75939733</v>
       </c>
       <c r="N180" s="14" t="n">
-        <v>696621.877304511</v>
+        <v>696620.75939733</v>
       </c>
       <c r="O180" s="15" t="n">
-        <v>-0.0118916311905337</v>
+        <v>-0.0118923786214697</v>
       </c>
       <c r="P180" s="16" t="n">
-        <v>-0.0404205907330408</v>
+        <v>-0.0404209065551145</v>
       </c>
       <c r="Q180" s="17" t="n">
-        <v>-0.011821205180812</v>
+        <v>-0.0118219437759375</v>
       </c>
       <c r="R180" s="18" t="n">
-        <v>0.998166789675535</v>
+        <v>0.998165779155807</v>
       </c>
       <c r="S180" s="19" t="n">
-        <v>0.972469012095042</v>
+        <v>0.972480115837791</v>
       </c>
     </row>
     <row r="181">
@@ -12490,46 +12490,46 @@
         <v>686701.470618711</v>
       </c>
       <c r="F181" s="6" t="n">
-        <v>-13494.6934962307</v>
+        <v>-13492.6955719484</v>
       </c>
       <c r="G181" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H181" s="8" t="n">
-        <v>701400.742477462</v>
+        <v>701394.839822896</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>716405.892342362</v>
+        <v>716394.976359861</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>714878.347202476</v>
+        <v>714876.362859966</v>
       </c>
       <c r="K181" s="11" t="n">
-        <v>700196.164114941</v>
+        <v>700194.166190659</v>
       </c>
       <c r="L181" s="12" t="n">
-        <v>700196.164114941</v>
+        <v>700194.166190659</v>
       </c>
       <c r="M181" s="13" t="n">
-        <v>700196.164114941</v>
+        <v>700194.166190659</v>
       </c>
       <c r="N181" s="14" t="n">
-        <v>700196.164114941</v>
+        <v>700194.166190659</v>
       </c>
       <c r="O181" s="15" t="n">
-        <v>0.00511776696144957</v>
+        <v>0.0051165183353617</v>
       </c>
       <c r="P181" s="16" t="n">
-        <v>-0.0260821148365143</v>
+        <v>-0.0260829093619352</v>
       </c>
       <c r="Q181" s="17" t="n">
-        <v>0.00513088509976312</v>
+        <v>0.00512963006790179</v>
       </c>
       <c r="R181" s="18" t="n">
-        <v>0.998282610368694</v>
+        <v>0.998288163008812</v>
       </c>
       <c r="S181" s="19" t="n">
-        <v>0.977373541450893</v>
+        <v>0.977385645204379</v>
       </c>
     </row>
     <row r="182">
@@ -12549,46 +12549,46 @@
         <v>672749.811391699</v>
       </c>
       <c r="F182" s="6" t="n">
-        <v>-35841.4779653753</v>
+        <v>-35845.5937296366</v>
       </c>
       <c r="G182" s="7" t="n">
-        <v>0.0641586831673018</v>
+        <v>0.0660559235067559</v>
       </c>
       <c r="H182" s="8" t="n">
-        <v>713353.508648873</v>
+        <v>713342.498473123</v>
       </c>
       <c r="I182" s="9" t="n">
-        <v>716287.5582507</v>
+        <v>716274.960151144</v>
       </c>
       <c r="J182" s="10" t="n">
-        <v>715058.61893193</v>
+        <v>715056.468115347</v>
       </c>
       <c r="K182" s="11" t="n">
-        <v>708591.289357075</v>
+        <v>708595.405121336</v>
       </c>
       <c r="L182" s="12" t="n">
-        <v>713047.970930157</v>
+        <v>713028.924837798</v>
       </c>
       <c r="M182" s="13" t="n">
-        <v>713047.970930157</v>
+        <v>713028.924837798</v>
       </c>
       <c r="N182" s="14" t="n">
-        <v>713047.970930157</v>
+        <v>713028.924837798</v>
       </c>
       <c r="O182" s="15" t="n">
-        <v>0.0181881683230421</v>
+        <v>0.018164310533414</v>
       </c>
       <c r="P182" s="16" t="n">
-        <v>0.00608929277773007</v>
+        <v>0.00605790829528563</v>
       </c>
       <c r="Q182" s="17" t="n">
-        <v>0.0183545804359853</v>
+        <v>0.0183302850364568</v>
       </c>
       <c r="R182" s="18" t="n">
-        <v>0.999571688209266</v>
+        <v>0.999560416439514</v>
       </c>
       <c r="S182" s="19" t="n">
-        <v>0.995477253118211</v>
+        <v>0.995468171451002</v>
       </c>
     </row>
     <row r="183">
@@ -12608,46 +12608,46 @@
         <v>791235.96554167</v>
       </c>
       <c r="F183" s="6" t="n">
-        <v>56036.6067393058</v>
+        <v>56037.7986198276</v>
       </c>
       <c r="G183" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H183" s="8" t="n">
-        <v>723337.204341816</v>
+        <v>723329.795970137</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>715987.493826022</v>
+        <v>715973.140626495</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v>715324.63069539</v>
+        <v>715322.406799778</v>
       </c>
       <c r="K183" s="11" t="n">
-        <v>735199.358802364</v>
+        <v>735198.166921843</v>
       </c>
       <c r="L183" s="12" t="n">
-        <v>723337.204341816</v>
+        <v>723329.795970137</v>
       </c>
       <c r="M183" s="13" t="n">
-        <v>723337.204341816</v>
+        <v>723329.795970137</v>
       </c>
       <c r="N183" s="14" t="n">
-        <v>723337.204341816</v>
+        <v>723329.795970137</v>
       </c>
       <c r="O183" s="15" t="n">
-        <v>0.0143268109186827</v>
+        <v>0.0143432801041786</v>
       </c>
       <c r="P183" s="16" t="n">
-        <v>0.0260752786004246</v>
+        <v>0.0260656492767988</v>
       </c>
       <c r="Q183" s="17" t="n">
-        <v>0.0144299315489766</v>
+        <v>0.0144466385212667</v>
       </c>
       <c r="R183" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S183" s="19" t="n">
-        <v>1.01026513811927</v>
+        <v>1.01027504374983</v>
       </c>
     </row>
     <row r="184">
@@ -12667,46 +12667,46 @@
         <v>718281.265449782</v>
       </c>
       <c r="F184" s="6" t="n">
-        <v>-7446.7071850468</v>
+        <v>-7445.87685164463</v>
       </c>
       <c r="G184" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H184" s="8" t="n">
-        <v>724457.286116275</v>
+        <v>724456.111537977</v>
       </c>
       <c r="I184" s="9" t="n">
-        <v>715502.648278682</v>
+        <v>715486.48484477</v>
       </c>
       <c r="J184" s="10" t="n">
-        <v>715581.991510077</v>
+        <v>715579.734895866</v>
       </c>
       <c r="K184" s="11" t="n">
-        <v>725727.972634828</v>
+        <v>725727.142301426</v>
       </c>
       <c r="L184" s="12" t="n">
-        <v>725727.972634828</v>
+        <v>725727.142301426</v>
       </c>
       <c r="M184" s="13" t="n">
-        <v>725727.972634828</v>
+        <v>725727.142301426</v>
       </c>
       <c r="N184" s="14" t="n">
-        <v>725727.972634828</v>
+        <v>725727.142301426</v>
       </c>
       <c r="O184" s="15" t="n">
-        <v>0.00329974179254367</v>
+        <v>0.00330883963940191</v>
       </c>
       <c r="P184" s="16" t="n">
-        <v>0.0417817703959287</v>
+        <v>0.0417822502580563</v>
       </c>
       <c r="Q184" s="17" t="n">
-        <v>0.00330519193352963</v>
+        <v>0.00331431989204023</v>
       </c>
       <c r="R184" s="18" t="n">
-        <v>1.00175398404144</v>
+        <v>1.00175446206224</v>
       </c>
       <c r="S184" s="19" t="n">
-        <v>1.01429110623244</v>
+        <v>1.01431285939507</v>
       </c>
     </row>
     <row r="185">
@@ -12726,46 +12726,46 @@
         <v>703681.544169008</v>
       </c>
       <c r="F185" s="6" t="n">
-        <v>-13960.7138009175</v>
+        <v>-13959.36392403</v>
       </c>
       <c r="G185" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H185" s="8" t="n">
-        <v>718178.067136298</v>
+        <v>718178.151160283</v>
       </c>
       <c r="I185" s="9" t="n">
-        <v>714834.564388107</v>
+        <v>714816.55777441</v>
       </c>
       <c r="J185" s="10" t="n">
-        <v>715776.373261447</v>
+        <v>715774.045332075</v>
       </c>
       <c r="K185" s="11" t="n">
-        <v>717642.257969926</v>
+        <v>717640.908093038</v>
       </c>
       <c r="L185" s="12" t="n">
-        <v>717642.257969926</v>
+        <v>717640.908093038</v>
       </c>
       <c r="M185" s="13" t="n">
-        <v>717642.257969926</v>
+        <v>717640.908093038</v>
       </c>
       <c r="N185" s="14" t="n">
-        <v>717642.257969926</v>
+        <v>717640.908093038</v>
       </c>
       <c r="O185" s="15" t="n">
-        <v>-0.0112040543405322</v>
+        <v>-0.0112047911915994</v>
       </c>
       <c r="P185" s="16" t="n">
-        <v>0.0249160088973586</v>
+        <v>0.0249170055176215</v>
       </c>
       <c r="Q185" s="17" t="n">
-        <v>-0.011141522677632</v>
+        <v>-0.0111422513187879</v>
       </c>
       <c r="R185" s="18" t="n">
-        <v>0.999253932707094</v>
+        <v>0.999251936213352</v>
       </c>
       <c r="S185" s="19" t="n">
-        <v>1.00392775296788</v>
+        <v>1.00395115402394</v>
       </c>
     </row>
     <row r="186">
@@ -12785,46 +12785,46 @@
         <v>677652.089115703</v>
       </c>
       <c r="F186" s="6" t="n">
-        <v>-32426.0172676512</v>
+        <v>-32428.3737557426</v>
       </c>
       <c r="G186" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H186" s="8" t="n">
-        <v>710867.632161236</v>
+        <v>710868.335284049</v>
       </c>
       <c r="I186" s="9" t="n">
-        <v>713991.175761446</v>
+        <v>713971.32479477</v>
       </c>
       <c r="J186" s="10" t="n">
-        <v>715904.177740576</v>
+        <v>715901.668073892</v>
       </c>
       <c r="K186" s="11" t="n">
-        <v>710078.106383354</v>
+        <v>710080.462871445</v>
       </c>
       <c r="L186" s="12" t="n">
-        <v>710078.106383354</v>
+        <v>710080.462871445</v>
       </c>
       <c r="M186" s="13" t="n">
-        <v>710078.106383354</v>
+        <v>710080.462871445</v>
       </c>
       <c r="N186" s="14" t="n">
-        <v>710078.106383354</v>
+        <v>710080.462871445</v>
       </c>
       <c r="O186" s="15" t="n">
-        <v>-0.0105962239532624</v>
+        <v>-0.0105910243361935</v>
       </c>
       <c r="P186" s="16" t="n">
-        <v>-0.00416502769502214</v>
+        <v>-0.00413512252258685</v>
       </c>
       <c r="Q186" s="17" t="n">
-        <v>-0.0105402817386608</v>
+        <v>-0.0105351369136452</v>
       </c>
       <c r="R186" s="18" t="n">
-        <v>0.998889349096566</v>
+        <v>0.998891676034087</v>
       </c>
       <c r="S186" s="19" t="n">
-        <v>0.994519442941407</v>
+        <v>0.99455039468925</v>
       </c>
     </row>
     <row r="187">
@@ -12844,46 +12844,46 @@
         <v>760703.280151656</v>
       </c>
       <c r="F187" s="6" t="n">
-        <v>53452.0867509316</v>
+        <v>53452.8141571245</v>
       </c>
       <c r="G187" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H187" s="8" t="n">
-        <v>706021.301136545</v>
+        <v>706022.060046034</v>
       </c>
       <c r="I187" s="9" t="n">
-        <v>712982.170814337</v>
+        <v>712960.516504151</v>
       </c>
       <c r="J187" s="10" t="n">
-        <v>715971.136162086</v>
+        <v>715968.267400612</v>
       </c>
       <c r="K187" s="11" t="n">
-        <v>707251.193400725</v>
+        <v>707250.465994532</v>
       </c>
       <c r="L187" s="12" t="n">
-        <v>707251.193400725</v>
+        <v>707250.465994532</v>
       </c>
       <c r="M187" s="13" t="n">
-        <v>707251.193400725</v>
+        <v>707250.465994532</v>
       </c>
       <c r="N187" s="14" t="n">
-        <v>707251.193400725</v>
+        <v>707250.465994532</v>
       </c>
       <c r="O187" s="15" t="n">
-        <v>-0.00398907541347737</v>
+        <v>-0.00399342253838565</v>
       </c>
       <c r="P187" s="16" t="n">
-        <v>-0.0222386057906814</v>
+        <v>-0.0222295971563558</v>
       </c>
       <c r="Q187" s="17" t="n">
-        <v>-0.00398112962111641</v>
+        <v>-0.00398545943014583</v>
       </c>
       <c r="R187" s="18" t="n">
-        <v>1.00174200447239</v>
+        <v>1.00173989740266</v>
       </c>
       <c r="S187" s="19" t="n">
-        <v>0.991961962517146</v>
+        <v>0.991991070504693</v>
       </c>
     </row>
     <row r="188">
@@ -12903,46 +12903,46 @@
         <v>694382.47577623</v>
       </c>
       <c r="F188" s="6" t="n">
-        <v>-8242.1296059851</v>
+        <v>-8243.02913896229</v>
       </c>
       <c r="G188" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H188" s="8" t="n">
-        <v>703936.231203322</v>
+        <v>703935.941755356</v>
       </c>
       <c r="I188" s="9" t="n">
-        <v>711814.792294056</v>
+        <v>711791.431712154</v>
       </c>
       <c r="J188" s="10" t="n">
-        <v>715953.849383809</v>
+        <v>715950.401565516</v>
       </c>
       <c r="K188" s="11" t="n">
-        <v>702624.605382216</v>
+        <v>702625.504915193</v>
       </c>
       <c r="L188" s="12" t="n">
-        <v>702624.605382216</v>
+        <v>702625.504915193</v>
       </c>
       <c r="M188" s="13" t="n">
-        <v>702624.605382216</v>
+        <v>702625.504915193</v>
       </c>
       <c r="N188" s="14" t="n">
-        <v>702624.605382216</v>
+        <v>702625.504915193</v>
       </c>
       <c r="O188" s="15" t="n">
-        <v>-0.00656313787346249</v>
+        <v>-0.00656082912919341</v>
       </c>
       <c r="P188" s="16" t="n">
-        <v>-0.0318347481753166</v>
+        <v>-0.0318324009668064</v>
       </c>
       <c r="Q188" s="17" t="n">
-        <v>-0.00654164752449959</v>
+        <v>-0.00653935388057403</v>
       </c>
       <c r="R188" s="18" t="n">
-        <v>0.998136726363886</v>
+        <v>0.99813841464481</v>
       </c>
       <c r="S188" s="19" t="n">
-        <v>0.987089075681861</v>
+        <v>0.987122735131956</v>
       </c>
     </row>
     <row r="189">
@@ -12962,46 +12962,46 @@
         <v>693173.549347058</v>
       </c>
       <c r="F189" s="6" t="n">
-        <v>-13237.8406531091</v>
+        <v>-13236.3368473724</v>
       </c>
       <c r="G189" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H189" s="8" t="n">
-        <v>704954.305814893</v>
+        <v>704953.658209257</v>
       </c>
       <c r="I189" s="9" t="n">
-        <v>710492.701086996</v>
+        <v>710467.800446811</v>
       </c>
       <c r="J189" s="10" t="n">
-        <v>715785.318549775</v>
+        <v>715781.039814855</v>
       </c>
       <c r="K189" s="11" t="n">
-        <v>706411.390000167</v>
+        <v>706409.88619443</v>
       </c>
       <c r="L189" s="12" t="n">
-        <v>706411.390000167</v>
+        <v>706409.88619443</v>
       </c>
       <c r="M189" s="13" t="n">
-        <v>706411.390000167</v>
+        <v>706409.88619443</v>
       </c>
       <c r="N189" s="14" t="n">
-        <v>706411.390000167</v>
+        <v>706409.88619443</v>
       </c>
       <c r="O189" s="15" t="n">
-        <v>0.00537501348054097</v>
+        <v>0.0053716044361951</v>
       </c>
       <c r="P189" s="16" t="n">
-        <v>-0.015649674813644</v>
+        <v>-0.0156499187434167</v>
       </c>
       <c r="Q189" s="17" t="n">
-        <v>0.00538948478169421</v>
+        <v>0.00538605737019782</v>
       </c>
       <c r="R189" s="18" t="n">
-        <v>1.00206692004468</v>
+        <v>1.00206570739539</v>
       </c>
       <c r="S189" s="19" t="n">
-        <v>0.99425566078218</v>
+        <v>0.994288391043438</v>
       </c>
     </row>
     <row r="190">
@@ -13021,46 +13021,46 @@
         <v>681444.766110222</v>
       </c>
       <c r="F190" s="6" t="n">
-        <v>-29516.7343006705</v>
+        <v>-29516.2485550834</v>
       </c>
       <c r="G190" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H190" s="8" t="n">
-        <v>713983.615622654</v>
+        <v>713982.476021145</v>
       </c>
       <c r="I190" s="9" t="n">
-        <v>709013.81421273</v>
+        <v>708987.624031906</v>
       </c>
       <c r="J190" s="10" t="n">
-        <v>715331.898584002</v>
+        <v>715326.52691163</v>
       </c>
       <c r="K190" s="11" t="n">
-        <v>710961.500410893</v>
+        <v>710961.014665306</v>
       </c>
       <c r="L190" s="12" t="n">
-        <v>710961.500410893</v>
+        <v>710961.014665306</v>
       </c>
       <c r="M190" s="13" t="n">
-        <v>710961.500410893</v>
+        <v>710961.014665306</v>
       </c>
       <c r="N190" s="14" t="n">
-        <v>710961.500410893</v>
+        <v>710961.014665306</v>
       </c>
       <c r="O190" s="15" t="n">
-        <v>0.0064205066602151</v>
+        <v>0.00642195223476584</v>
       </c>
       <c r="P190" s="16" t="n">
-        <v>0.00124408008020205</v>
+        <v>0.00124007325916242</v>
       </c>
       <c r="Q190" s="17" t="n">
-        <v>0.00644116229598857</v>
+        <v>0.00644261718277117</v>
       </c>
       <c r="R190" s="18" t="n">
-        <v>0.995767248511542</v>
+        <v>0.995768157542637</v>
       </c>
       <c r="S190" s="19" t="n">
-        <v>1.00274703561358</v>
+        <v>1.00278339221519</v>
       </c>
     </row>
     <row r="191">
@@ -13080,46 +13080,46 @@
         <v>778401.676449317</v>
       </c>
       <c r="F191" s="6" t="n">
-        <v>49932.6877744046</v>
+        <v>49932.9430141731</v>
       </c>
       <c r="G191" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H191" s="8" t="n">
-        <v>724849.133882816</v>
+        <v>724849.87372788</v>
       </c>
       <c r="I191" s="9" t="n">
-        <v>707373.497871402</v>
+        <v>707346.367594815</v>
       </c>
       <c r="J191" s="10" t="n">
-        <v>714413.074767761</v>
+        <v>714406.351850737</v>
       </c>
       <c r="K191" s="11" t="n">
-        <v>728468.988674912</v>
+        <v>728468.733435144</v>
       </c>
       <c r="L191" s="12" t="n">
-        <v>728468.988674912</v>
+        <v>728468.733435144</v>
       </c>
       <c r="M191" s="13" t="n">
-        <v>728468.988674912</v>
+        <v>728468.733435144</v>
       </c>
       <c r="N191" s="14" t="n">
-        <v>728468.988674912</v>
+        <v>728468.733435144</v>
       </c>
       <c r="O191" s="15" t="n">
-        <v>0.0243267761626621</v>
+        <v>0.0243271090079507</v>
       </c>
       <c r="P191" s="16" t="n">
-        <v>0.0300003668741289</v>
+        <v>0.0300010653379701</v>
       </c>
       <c r="Q191" s="17" t="n">
-        <v>0.0246250862443338</v>
+        <v>0.0246254272860231</v>
       </c>
       <c r="R191" s="18" t="n">
-        <v>1.00499394235695</v>
+        <v>1.00499256444462</v>
       </c>
       <c r="S191" s="19" t="n">
-        <v>1.02982228040348</v>
+        <v>1.02986141840546</v>
       </c>
     </row>
     <row r="192">
@@ -13139,46 +13139,46 @@
         <v>721120.426852794</v>
       </c>
       <c r="F192" s="6" t="n">
-        <v>-8849.14902072359</v>
+        <v>-8853.03267418518</v>
       </c>
       <c r="G192" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H192" s="8" t="n">
-        <v>732338.462607125</v>
+        <v>732342.703116805</v>
       </c>
       <c r="I192" s="9" t="n">
-        <v>705568.33556703</v>
+        <v>705540.729632059</v>
       </c>
       <c r="J192" s="10" t="n">
-        <v>712826.480391459</v>
+        <v>712818.176065843</v>
       </c>
       <c r="K192" s="11" t="n">
-        <v>729969.575873518</v>
+        <v>729973.459526979</v>
       </c>
       <c r="L192" s="12" t="n">
-        <v>729969.575873518</v>
+        <v>729973.459526979</v>
       </c>
       <c r="M192" s="13" t="n">
-        <v>729969.575873518</v>
+        <v>729973.459526979</v>
       </c>
       <c r="N192" s="14" t="n">
-        <v>729969.575873518</v>
+        <v>729973.459526979</v>
       </c>
       <c r="O192" s="15" t="n">
-        <v>0.00205780039640588</v>
+        <v>0.00206347105564143</v>
       </c>
       <c r="P192" s="16" t="n">
-        <v>0.0389183217920854</v>
+        <v>0.0389225190666649</v>
       </c>
       <c r="Q192" s="17" t="n">
-        <v>0.00205991912069625</v>
+        <v>0.00206560147714252</v>
       </c>
       <c r="R192" s="18" t="n">
-        <v>0.996765311594895</v>
+        <v>0.996764843044462</v>
       </c>
       <c r="S192" s="19" t="n">
-        <v>1.03458380864963</v>
+        <v>1.03462979367281</v>
       </c>
     </row>
     <row r="193">
@@ -13198,46 +13198,46 @@
         <v>724592.921638963</v>
       </c>
       <c r="F193" s="6" t="n">
-        <v>-11205.0362366378</v>
+        <v>-11208.1110047555</v>
       </c>
       <c r="G193" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H193" s="8" t="n">
-        <v>736530.779198965</v>
+        <v>736528.336808629</v>
       </c>
       <c r="I193" s="9" t="n">
-        <v>703608.095485384</v>
+        <v>703580.610118811</v>
       </c>
       <c r="J193" s="10" t="n">
-        <v>710440.028315037</v>
+        <v>710429.972898536</v>
       </c>
       <c r="K193" s="11" t="n">
-        <v>735797.957875601</v>
+        <v>735801.032643718</v>
       </c>
       <c r="L193" s="12" t="n">
-        <v>735797.957875601</v>
+        <v>735801.032643718</v>
       </c>
       <c r="M193" s="13" t="n">
-        <v>735797.957875601</v>
+        <v>735801.032643718</v>
       </c>
       <c r="N193" s="14" t="n">
-        <v>735797.957875601</v>
+        <v>735801.032643718</v>
       </c>
       <c r="O193" s="15" t="n">
-        <v>0.00795271089876189</v>
+        <v>0.00795156943043163</v>
       </c>
       <c r="P193" s="16" t="n">
-        <v>0.0415997933943659</v>
+        <v>0.0416063634211352</v>
       </c>
       <c r="Q193" s="17" t="n">
-        <v>0.00798441770002345</v>
+        <v>0.00798326711838993</v>
       </c>
       <c r="R193" s="18" t="n">
-        <v>0.999005036389435</v>
+        <v>0.999012523852019</v>
       </c>
       <c r="S193" s="19" t="n">
-        <v>1.04574970441182</v>
+        <v>1.04579492678098</v>
       </c>
     </row>
     <row r="194">
@@ -13257,46 +13257,46 @@
         <v>707324.268057214</v>
       </c>
       <c r="F194" s="6" t="n">
-        <v>-26702.5812637156</v>
+        <v>-26686.1831600911</v>
       </c>
       <c r="G194" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H194" s="8" t="n">
-        <v>727840.062295081</v>
+        <v>727832.54784464</v>
       </c>
       <c r="I194" s="9" t="n">
-        <v>701517.796587424</v>
+        <v>701491.179486428</v>
       </c>
       <c r="J194" s="10" t="n">
-        <v>707207.346875847</v>
+        <v>707195.492107708</v>
       </c>
       <c r="K194" s="11" t="n">
-        <v>734026.84932093</v>
+        <v>734010.451217305</v>
       </c>
       <c r="L194" s="12" t="n">
-        <v>734026.84932093</v>
+        <v>734010.451217305</v>
       </c>
       <c r="M194" s="13" t="n">
-        <v>734026.84932093</v>
+        <v>734010.451217305</v>
       </c>
       <c r="N194" s="14" t="n">
-        <v>734026.84932093</v>
+        <v>734010.451217305</v>
       </c>
       <c r="O194" s="15" t="n">
-        <v>-0.00240995988528979</v>
+        <v>-0.00243647887076578</v>
       </c>
       <c r="P194" s="16" t="n">
-        <v>0.0324424724780548</v>
+        <v>0.0324201131659099</v>
       </c>
       <c r="Q194" s="17" t="n">
-        <v>-0.00240705826336429</v>
+        <v>-0.00243351306531836</v>
       </c>
       <c r="R194" s="18" t="n">
-        <v>1.00850020127546</v>
+        <v>1.00848808340732</v>
       </c>
       <c r="S194" s="19" t="n">
-        <v>1.04634102355157</v>
+        <v>1.04635734943194</v>
       </c>
     </row>
     <row r="195">
@@ -13316,46 +13316,46 @@
         <v>747428.299954575</v>
       </c>
       <c r="F195" s="6" t="n">
-        <v>44679.6636044509</v>
+        <v>44672.7763303434</v>
       </c>
       <c r="G195" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H195" s="8" t="n">
-        <v>711079.197970511</v>
+        <v>711081.235799925</v>
       </c>
       <c r="I195" s="9" t="n">
-        <v>699342.576498107</v>
+        <v>699317.745930343</v>
       </c>
       <c r="J195" s="10" t="n">
-        <v>703208.854059043</v>
+        <v>703195.33875098</v>
       </c>
       <c r="K195" s="11" t="n">
-        <v>702748.636350124</v>
+        <v>702755.523624231</v>
       </c>
       <c r="L195" s="12" t="n">
-        <v>702748.636350124</v>
+        <v>702755.523624231</v>
       </c>
       <c r="M195" s="13" t="n">
-        <v>702748.636350124</v>
+        <v>702755.523624231</v>
       </c>
       <c r="N195" s="14" t="n">
-        <v>702748.636350124</v>
+        <v>702755.523624231</v>
       </c>
       <c r="O195" s="15" t="n">
-        <v>-0.0435463380651156</v>
+        <v>-0.0435141974599334</v>
       </c>
       <c r="P195" s="16" t="n">
-        <v>-0.0353074087224684</v>
+        <v>-0.0352976162609754</v>
       </c>
       <c r="Q195" s="17" t="n">
-        <v>-0.0426118104531769</v>
+        <v>-0.0425810389228654</v>
       </c>
       <c r="R195" s="18" t="n">
-        <v>0.988284621960305</v>
+        <v>0.988291475352562</v>
       </c>
       <c r="S195" s="19" t="n">
-        <v>1.004870373929</v>
+        <v>1.00491590226888</v>
       </c>
     </row>
     <row r="196">
@@ -13375,46 +13375,46 @@
         <v>696101.583521808</v>
       </c>
       <c r="F196" s="6" t="n">
-        <v>-8212.26869593729</v>
+        <v>-8225.6349373822</v>
       </c>
       <c r="G196" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H196" s="8" t="n">
-        <v>697708.848830973</v>
+        <v>697725.731832115</v>
       </c>
       <c r="I196" s="9" t="n">
-        <v>697147.891000345</v>
+        <v>697125.942190824</v>
       </c>
       <c r="J196" s="10" t="n">
-        <v>698659.065362007</v>
+        <v>698644.192681519</v>
       </c>
       <c r="K196" s="11" t="n">
-        <v>704313.852217745</v>
+        <v>704327.21845919</v>
       </c>
       <c r="L196" s="12" t="n">
-        <v>704313.852217745</v>
+        <v>704327.21845919</v>
       </c>
       <c r="M196" s="13" t="n">
-        <v>704313.852217745</v>
+        <v>704327.21845919</v>
       </c>
       <c r="N196" s="14" t="n">
-        <v>704313.852217745</v>
+        <v>704327.21845919</v>
       </c>
       <c r="O196" s="15" t="n">
-        <v>0.00222480028563799</v>
+        <v>0.00223397735129684</v>
       </c>
       <c r="P196" s="16" t="n">
-        <v>-0.035146291713695</v>
+        <v>-0.0351331144072119</v>
       </c>
       <c r="Q196" s="17" t="n">
-        <v>0.00222727699017722</v>
+        <v>0.00223647453790643</v>
       </c>
       <c r="R196" s="18" t="n">
-        <v>1.00946670433927</v>
+        <v>1.00946143495345</v>
       </c>
       <c r="S196" s="19" t="n">
-        <v>1.01027896850856</v>
+        <v>1.01032995020345</v>
       </c>
     </row>
     <row r="197">
@@ -13434,46 +13434,46 @@
         <v>678655.620384454</v>
       </c>
       <c r="F197" s="6" t="n">
-        <v>-8963.09439244021</v>
+        <v>-8972.61334916359</v>
       </c>
       <c r="G197" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H197" s="8" t="n">
-        <v>690917.557292015</v>
+        <v>690912.361445414</v>
       </c>
       <c r="I197" s="9" t="n">
-        <v>695001.324664461</v>
+        <v>694983.549619195</v>
       </c>
       <c r="J197" s="10" t="n">
-        <v>693770.195193572</v>
+        <v>693754.534676859</v>
       </c>
       <c r="K197" s="11" t="n">
-        <v>687618.714776894</v>
+        <v>687628.233733617</v>
       </c>
       <c r="L197" s="12" t="n">
-        <v>687618.714776894</v>
+        <v>687628.233733617</v>
       </c>
       <c r="M197" s="13" t="n">
-        <v>687618.714776894</v>
+        <v>687628.233733617</v>
       </c>
       <c r="N197" s="14" t="n">
-        <v>687618.714776894</v>
+        <v>687628.233733617</v>
       </c>
       <c r="O197" s="15" t="n">
-        <v>-0.0239895789492803</v>
+        <v>-0.0239947131781326</v>
       </c>
       <c r="P197" s="16" t="n">
-        <v>-0.0654789029828383</v>
+        <v>-0.065469871300693</v>
       </c>
       <c r="Q197" s="17" t="n">
-        <v>-0.0237041162661807</v>
+        <v>-0.0237091287798077</v>
       </c>
       <c r="R197" s="18" t="n">
-        <v>0.995225418025197</v>
+        <v>0.995246679759895</v>
       </c>
       <c r="S197" s="19" t="n">
-        <v>0.989377559976405</v>
+        <v>0.98941656116953</v>
       </c>
     </row>
     <row r="198">
@@ -13493,46 +13493,46 @@
         <v>665848.715299709</v>
       </c>
       <c r="F198" s="6" t="n">
-        <v>-25664.5822293902</v>
+        <v>-25618.5128898886</v>
       </c>
       <c r="G198" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H198" s="8" t="n">
-        <v>694752.202055283</v>
+        <v>694726.186112924</v>
       </c>
       <c r="I198" s="9" t="n">
-        <v>692974.940786536</v>
+        <v>692962.850364449</v>
       </c>
       <c r="J198" s="10" t="n">
-        <v>688782.731896854</v>
+        <v>688767.260643422</v>
       </c>
       <c r="K198" s="11" t="n">
-        <v>691513.297529099</v>
+        <v>691467.228189597</v>
       </c>
       <c r="L198" s="12" t="n">
-        <v>691513.297529099</v>
+        <v>691467.228189597</v>
       </c>
       <c r="M198" s="13" t="n">
-        <v>691513.297529099</v>
+        <v>691467.228189597</v>
       </c>
       <c r="N198" s="14" t="n">
-        <v>691513.297529099</v>
+        <v>691467.228189597</v>
       </c>
       <c r="O198" s="15" t="n">
-        <v>0.0056478902238711</v>
+        <v>0.00556742368916259</v>
       </c>
       <c r="P198" s="16" t="n">
-        <v>-0.0579182516704413</v>
+        <v>-0.0579599690401583</v>
       </c>
       <c r="Q198" s="17" t="n">
-        <v>0.00566386962499843</v>
+        <v>0.00558295059400882</v>
       </c>
       <c r="R198" s="18" t="n">
-        <v>0.995338043526019</v>
+        <v>0.995309003765123</v>
       </c>
       <c r="S198" s="19" t="n">
-        <v>0.997890770399608</v>
+        <v>0.99784169934353</v>
       </c>
     </row>
     <row r="199">
@@ -13552,46 +13552,46 @@
         <v>751784.460777133</v>
       </c>
       <c r="F199" s="6" t="n">
-        <v>41863.8801024066</v>
+        <v>41858.2919019098</v>
       </c>
       <c r="G199" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H199" s="8" t="n">
-        <v>703417.025008746</v>
+        <v>703419.181475476</v>
       </c>
       <c r="I199" s="9" t="n">
-        <v>691136.188531473</v>
+        <v>691131.52950315</v>
       </c>
       <c r="J199" s="10" t="n">
-        <v>683906.406412884</v>
+        <v>683892.634982914</v>
       </c>
       <c r="K199" s="11" t="n">
-        <v>709920.580674726</v>
+        <v>709926.168875223</v>
       </c>
       <c r="L199" s="12" t="n">
-        <v>709920.580674726</v>
+        <v>709926.168875223</v>
       </c>
       <c r="M199" s="13" t="n">
-        <v>709920.580674726</v>
+        <v>709926.168875223</v>
       </c>
       <c r="N199" s="14" t="n">
-        <v>709920.580674726</v>
+        <v>709926.168875223</v>
       </c>
       <c r="O199" s="15" t="n">
-        <v>0.0262707246772298</v>
+        <v>0.0263452194973859</v>
       </c>
       <c r="P199" s="16" t="n">
-        <v>0.0102055613538452</v>
+        <v>0.0102036127926983</v>
       </c>
       <c r="Q199" s="17" t="n">
-        <v>0.0266188419100535</v>
+        <v>0.0266953225447206</v>
       </c>
       <c r="R199" s="18" t="n">
-        <v>1.0092456614423</v>
+        <v>1.00925051174479</v>
       </c>
       <c r="S199" s="19" t="n">
-        <v>1.02717900242377</v>
+        <v>1.0271940123837</v>
       </c>
     </row>
     <row r="200">
@@ -13611,46 +13611,46 @@
         <v>683900.898552578</v>
       </c>
       <c r="F200" s="6" t="n">
-        <v>-8751.85088591927</v>
+        <v>-8802.22113975885</v>
       </c>
       <c r="G200" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H200" s="8" t="n">
-        <v>697757.503852008</v>
+        <v>697794.531025909</v>
       </c>
       <c r="I200" s="9" t="n">
-        <v>689551.603537138</v>
+        <v>689556.337348003</v>
       </c>
       <c r="J200" s="10" t="n">
-        <v>679364.602510854</v>
+        <v>679354.421934771</v>
       </c>
       <c r="K200" s="11" t="n">
-        <v>692652.749438498</v>
+        <v>692703.119692337</v>
       </c>
       <c r="L200" s="12" t="n">
-        <v>692652.749438498</v>
+        <v>692703.119692337</v>
       </c>
       <c r="M200" s="13" t="n">
-        <v>692652.749438498</v>
+        <v>692703.119692337</v>
       </c>
       <c r="N200" s="14" t="n">
-        <v>692652.749438498</v>
+        <v>692703.119692337</v>
       </c>
       <c r="O200" s="15" t="n">
-        <v>-0.0246243150296528</v>
+        <v>-0.024559468439997</v>
       </c>
       <c r="P200" s="16" t="n">
-        <v>-0.0165566852654233</v>
+        <v>-0.0165038329659924</v>
       </c>
       <c r="Q200" s="17" t="n">
-        <v>-0.0243236098604388</v>
+        <v>-0.0242603385224875</v>
       </c>
       <c r="R200" s="18" t="n">
-        <v>0.992684056587956</v>
+        <v>0.992703566584154</v>
       </c>
       <c r="S200" s="19" t="n">
-        <v>1.00449733694397</v>
+        <v>1.00456348839666</v>
       </c>
     </row>
     <row r="201">
@@ -13670,46 +13670,46 @@
         <v>671361.13972242</v>
       </c>
       <c r="F201" s="6" t="n">
-        <v>-6733.08363082657</v>
+        <v>-6753.97607406567</v>
       </c>
       <c r="G201" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H201" s="8" t="n">
-        <v>672574.174751669</v>
+        <v>672616.878387971</v>
       </c>
       <c r="I201" s="9" t="n">
-        <v>688299.461686487</v>
+        <v>688315.770861321</v>
       </c>
       <c r="J201" s="10" t="n">
-        <v>675510.774831264</v>
+        <v>675506.553407892</v>
       </c>
       <c r="K201" s="11" t="n">
-        <v>678094.223353247</v>
+        <v>678115.115796486</v>
       </c>
       <c r="L201" s="12" t="n">
-        <v>678094.223353247</v>
+        <v>678115.115796486</v>
       </c>
       <c r="M201" s="13" t="n">
-        <v>678094.223353247</v>
+        <v>678115.115796486</v>
       </c>
       <c r="N201" s="14" t="n">
-        <v>678094.223353247</v>
+        <v>678115.115796486</v>
       </c>
       <c r="O201" s="15" t="n">
-        <v>-0.0212425397624749</v>
+        <v>-0.0212844478499906</v>
       </c>
       <c r="P201" s="16" t="n">
-        <v>-0.0138514138998347</v>
+        <v>-0.0138346819843014</v>
       </c>
       <c r="Q201" s="17" t="n">
-        <v>-0.021018506166406</v>
+        <v>-0.0210595325488512</v>
       </c>
       <c r="R201" s="18" t="n">
-        <v>1.00820734546285</v>
+        <v>1.0081743970233</v>
       </c>
       <c r="S201" s="19" t="n">
-        <v>0.985173258296272</v>
+        <v>0.985180268277057</v>
       </c>
     </row>
     <row r="202">
@@ -13729,46 +13729,46 @@
         <v>632389.35353461</v>
       </c>
       <c r="F202" s="6" t="n">
-        <v>-24880.7521961239</v>
+        <v>-24778.7173309361</v>
       </c>
       <c r="G202" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H202" s="8" t="n">
-        <v>636454.749721509</v>
+        <v>636437.826726455</v>
       </c>
       <c r="I202" s="9" t="n">
-        <v>687459.977078665</v>
+        <v>687490.293744382</v>
       </c>
       <c r="J202" s="10" t="n">
-        <v>672764.818749254</v>
+        <v>672769.704799964</v>
       </c>
       <c r="K202" s="11" t="n">
-        <v>657270.105730734</v>
+        <v>657168.070865546</v>
       </c>
       <c r="L202" s="12" t="n">
-        <v>636454.749721509</v>
+        <v>636437.826726455</v>
       </c>
       <c r="M202" s="13" t="n">
-        <v>636454.749721509</v>
+        <v>636437.826726455</v>
       </c>
       <c r="N202" s="14" t="n">
-        <v>636454.749721509</v>
+        <v>636437.826726455</v>
       </c>
       <c r="O202" s="15" t="n">
-        <v>-0.0633729276581574</v>
+        <v>-0.0634303275391609</v>
       </c>
       <c r="P202" s="16" t="n">
-        <v>-0.0796203746252228</v>
+        <v>-0.0795835279239779</v>
       </c>
       <c r="Q202" s="17" t="n">
-        <v>-0.0614066190179677</v>
+        <v>-0.0614604926201627</v>
       </c>
       <c r="R202" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S202" s="19" t="n">
-        <v>0.925806259189225</v>
+        <v>0.925740817750499</v>
       </c>
     </row>
     <row r="203">
@@ -13788,46 +13788,46 @@
         <v>609379.989464801</v>
       </c>
       <c r="F203" s="6" t="n">
-        <v>39247.8206298006</v>
+        <v>39262.8137599983</v>
       </c>
       <c r="G203" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H203" s="8" t="n">
-        <v>611620.720119946</v>
+        <v>611590.560069316</v>
       </c>
       <c r="I203" s="9" t="n">
-        <v>687106.985538857</v>
+        <v>687153.994289047</v>
       </c>
       <c r="J203" s="10" t="n">
-        <v>671559.546882574</v>
+        <v>671577.594320614</v>
       </c>
       <c r="K203" s="11" t="n">
-        <v>570132.168835001</v>
+        <v>570117.175704803</v>
       </c>
       <c r="L203" s="12" t="n">
-        <v>611620.720119946</v>
+        <v>611590.560069316</v>
       </c>
       <c r="M203" s="13" t="n">
-        <v>611620.720119946</v>
+        <v>611590.560069316</v>
       </c>
       <c r="N203" s="14" t="n">
-        <v>611620.720119946</v>
+        <v>611590.560069316</v>
       </c>
       <c r="O203" s="15" t="n">
-        <v>-0.0398009710948444</v>
+        <v>-0.0398236941751142</v>
       </c>
       <c r="P203" s="16" t="n">
-        <v>-0.138465996381389</v>
+        <v>-0.138515261328802</v>
       </c>
       <c r="Q203" s="17" t="n">
-        <v>-0.0390193169466164</v>
+        <v>-0.0390411531397215</v>
       </c>
       <c r="R203" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S203" s="19" t="n">
-        <v>0.890138992896846</v>
+        <v>0.890034206527589</v>
       </c>
     </row>
     <row r="204">
@@ -13847,46 +13847,46 @@
         <v>614192.478404223</v>
       </c>
       <c r="F204" s="6" t="n">
-        <v>-7470.60774935995</v>
+        <v>-7572.01828206623</v>
       </c>
       <c r="G204" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H204" s="8" t="n">
-        <v>620721.899690873</v>
+        <v>620819.081240061</v>
       </c>
       <c r="I204" s="9" t="n">
-        <v>687282.444625152</v>
+        <v>687349.052995293</v>
       </c>
       <c r="J204" s="10" t="n">
-        <v>672146.221503834</v>
+        <v>672182.280789106</v>
       </c>
       <c r="K204" s="11" t="n">
-        <v>621663.086153583</v>
+        <v>621764.496686289</v>
       </c>
       <c r="L204" s="12" t="n">
-        <v>621663.086153583</v>
+        <v>621764.496686289</v>
       </c>
       <c r="M204" s="13" t="n">
-        <v>621663.086153583</v>
+        <v>621764.496686289</v>
       </c>
       <c r="N204" s="14" t="n">
-        <v>621663.086153583</v>
+        <v>621764.496686289</v>
       </c>
       <c r="O204" s="15" t="n">
-        <v>0.0162859318257226</v>
+        <v>0.0164983592283199</v>
       </c>
       <c r="P204" s="16" t="n">
-        <v>-0.102489542331945</v>
+        <v>-0.102408406991953</v>
       </c>
       <c r="Q204" s="17" t="n">
-        <v>0.0164192704780624</v>
+        <v>0.0166352087184276</v>
       </c>
       <c r="R204" s="18" t="n">
-        <v>1.00151627719785</v>
+        <v>1.00152285178532</v>
       </c>
       <c r="S204" s="19" t="n">
-        <v>0.904523447405442</v>
+        <v>0.904583332117498</v>
       </c>
     </row>
     <row r="205">
@@ -13906,46 +13906,46 @@
         <v>642403.32319795</v>
       </c>
       <c r="F205" s="6" t="n">
-        <v>-7239.83440938991</v>
+        <v>-7395.21858026428</v>
       </c>
       <c r="G205" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H205" s="8" t="n">
-        <v>650028.070090412</v>
+        <v>650041.595424714</v>
       </c>
       <c r="I205" s="9" t="n">
-        <v>687981.132979751</v>
+        <v>688070.423216709</v>
       </c>
       <c r="J205" s="10" t="n">
-        <v>674476.410751833</v>
+        <v>674535.887853443</v>
       </c>
       <c r="K205" s="11" t="n">
-        <v>649643.15760734</v>
+        <v>649798.541778215</v>
       </c>
       <c r="L205" s="12" t="n">
-        <v>649643.15760734</v>
+        <v>649798.541778215</v>
       </c>
       <c r="M205" s="13" t="n">
-        <v>649643.15760734</v>
+        <v>649798.541778215</v>
       </c>
       <c r="N205" s="14" t="n">
-        <v>649643.15760734</v>
+        <v>649798.541778215</v>
       </c>
       <c r="O205" s="15" t="n">
-        <v>0.0440249399892853</v>
+        <v>0.0441009807711981</v>
       </c>
       <c r="P205" s="16" t="n">
-        <v>-0.0419573928903464</v>
+        <v>-0.0417577684948252</v>
       </c>
       <c r="Q205" s="17" t="n">
-        <v>0.0450084170621718</v>
+        <v>0.0450878833406114</v>
       </c>
       <c r="R205" s="18" t="n">
-        <v>0.999407852520864</v>
+        <v>0.99962609524035</v>
       </c>
       <c r="S205" s="19" t="n">
-        <v>0.944274670431203</v>
+        <v>0.944377958785709</v>
       </c>
     </row>
     <row r="206">
@@ -13965,46 +13965,46 @@
         <v>652831.976706322</v>
       </c>
       <c r="F206" s="6" t="n">
-        <v>-24404.6546119484</v>
+        <v>-24041.6412281711</v>
       </c>
       <c r="G206" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H206" s="8" t="n">
-        <v>674267.412232713</v>
+        <v>674103.307563351</v>
       </c>
       <c r="I206" s="9" t="n">
-        <v>689156.81714581</v>
+        <v>689272.06795919</v>
       </c>
       <c r="J206" s="10" t="n">
-        <v>678249.267088615</v>
+        <v>678338.450241117</v>
       </c>
       <c r="K206" s="11" t="n">
-        <v>677236.63131827</v>
+        <v>676873.617934493</v>
       </c>
       <c r="L206" s="12" t="n">
-        <v>677236.63131827</v>
+        <v>676873.617934493</v>
       </c>
       <c r="M206" s="13" t="n">
-        <v>677236.63131827</v>
+        <v>676873.617934493</v>
       </c>
       <c r="N206" s="14" t="n">
-        <v>677236.63131827</v>
+        <v>676873.617934493</v>
       </c>
       <c r="O206" s="15" t="n">
-        <v>0.0415975172707794</v>
+        <v>0.0408221967966173</v>
       </c>
       <c r="P206" s="16" t="n">
-        <v>0.0640766395640942</v>
+        <v>0.0635345504462248</v>
       </c>
       <c r="Q206" s="17" t="n">
-        <v>0.0424748161937973</v>
+        <v>0.0416668773712319</v>
       </c>
       <c r="R206" s="18" t="n">
-        <v>1.0044036224081</v>
+        <v>1.00410962287243</v>
       </c>
       <c r="S206" s="19" t="n">
-        <v>0.982703231643404</v>
+        <v>0.982012255245731</v>
       </c>
     </row>
     <row r="207">
@@ -14024,46 +14024,46 @@
         <v>723516.622490675</v>
       </c>
       <c r="F207" s="6" t="n">
-        <v>38751.8354501798</v>
+        <v>38698.0218376303</v>
       </c>
       <c r="G207" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H207" s="8" t="n">
-        <v>686111.455533856</v>
+        <v>686065.921763108</v>
       </c>
       <c r="I207" s="9" t="n">
-        <v>690739.302431877</v>
+        <v>690884.030302732</v>
       </c>
       <c r="J207" s="10" t="n">
-        <v>683039.776710506</v>
+        <v>683166.315949243</v>
       </c>
       <c r="K207" s="11" t="n">
-        <v>684764.787040495</v>
+        <v>684818.600653045</v>
       </c>
       <c r="L207" s="12" t="n">
-        <v>684764.787040495</v>
+        <v>684818.600653045</v>
       </c>
       <c r="M207" s="13" t="n">
-        <v>684764.787040495</v>
+        <v>684818.600653045</v>
       </c>
       <c r="N207" s="14" t="n">
-        <v>684764.787040495</v>
+        <v>684818.600653045</v>
       </c>
       <c r="O207" s="15" t="n">
-        <v>0.0110546615969565</v>
+        <v>0.0116694107067559</v>
       </c>
       <c r="P207" s="16" t="n">
-        <v>0.119590564077366</v>
+        <v>0.119733765307674</v>
       </c>
       <c r="Q207" s="17" t="n">
-        <v>0.0111159901489251</v>
+        <v>0.0117377639016221</v>
       </c>
       <c r="R207" s="18" t="n">
-        <v>0.998037245286463</v>
+        <v>0.998181922362711</v>
       </c>
       <c r="S207" s="19" t="n">
-        <v>0.991350549519409</v>
+        <v>0.991220770225316</v>
       </c>
     </row>
     <row r="208">
@@ -14083,46 +14083,46 @@
         <v>686756.467826674</v>
       </c>
       <c r="F208" s="6" t="n">
-        <v>-6230.37281905393</v>
+        <v>-6434.8864692473</v>
       </c>
       <c r="G208" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H208" s="8" t="n">
-        <v>692918.324070248</v>
+        <v>693194.266681655</v>
       </c>
       <c r="I208" s="9" t="n">
-        <v>692650.944030359</v>
+        <v>692828.604296066</v>
       </c>
       <c r="J208" s="10" t="n">
-        <v>688417.862634977</v>
+        <v>688588.508813402</v>
       </c>
       <c r="K208" s="11" t="n">
-        <v>692986.840645728</v>
+        <v>693191.354295922</v>
       </c>
       <c r="L208" s="12" t="n">
-        <v>692986.840645728</v>
+        <v>693191.354295922</v>
       </c>
       <c r="M208" s="13" t="n">
-        <v>692986.840645728</v>
+        <v>693191.354295922</v>
       </c>
       <c r="N208" s="14" t="n">
-        <v>692986.840645728</v>
+        <v>693191.354295922</v>
       </c>
       <c r="O208" s="15" t="n">
-        <v>0.0119356073306387</v>
+        <v>0.0121520989724534</v>
       </c>
       <c r="P208" s="16" t="n">
-        <v>0.114730560782444</v>
+        <v>0.114877671514382</v>
       </c>
       <c r="Q208" s="17" t="n">
-        <v>0.0120071209280024</v>
+        <v>0.0122262357285459</v>
       </c>
       <c r="R208" s="18" t="n">
-        <v>1.00009888117127</v>
+        <v>0.99999579860095</v>
       </c>
       <c r="S208" s="19" t="n">
-        <v>1.00048494356106</v>
+        <v>1.00052357826684</v>
       </c>
     </row>
     <row r="209">
@@ -14142,46 +14142,46 @@
         <v>696134.669112115</v>
       </c>
       <c r="F209" s="6" t="n">
-        <v>-8186.99655541271</v>
+        <v>-8427.74851886134</v>
       </c>
       <c r="G209" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H209" s="8" t="n">
-        <v>704686.154106</v>
+        <v>704670.255848506</v>
       </c>
       <c r="I209" s="9" t="n">
-        <v>694810.363061543</v>
+        <v>695024.293094393</v>
       </c>
       <c r="J209" s="10" t="n">
-        <v>693962.07293115</v>
+        <v>694182.314092695</v>
       </c>
       <c r="K209" s="11" t="n">
-        <v>704321.665667528</v>
+        <v>704562.417630976</v>
       </c>
       <c r="L209" s="12" t="n">
-        <v>704321.665667528</v>
+        <v>704562.417630976</v>
       </c>
       <c r="M209" s="13" t="n">
-        <v>704321.665667528</v>
+        <v>704562.417630976</v>
       </c>
       <c r="N209" s="14" t="n">
-        <v>704321.665667528</v>
+        <v>704562.417630976</v>
       </c>
       <c r="O209" s="15" t="n">
-        <v>0.0162241532229358</v>
+        <v>0.0162708402970175</v>
       </c>
       <c r="P209" s="16" t="n">
-        <v>0.0841669883225902</v>
+        <v>0.0842782375332778</v>
       </c>
       <c r="Q209" s="17" t="n">
-        <v>0.0163564794552775</v>
+        <v>0.0164039312732118</v>
       </c>
       <c r="R209" s="18" t="n">
-        <v>0.999482764864403</v>
+        <v>0.999846966412113</v>
       </c>
       <c r="S209" s="19" t="n">
-        <v>1.01368906267327</v>
+        <v>1.01372344050611</v>
       </c>
     </row>
     <row r="210">
@@ -14201,46 +14201,46 @@
         <v>697625.284666358</v>
       </c>
       <c r="F210" s="6" t="n">
-        <v>-24495.9814772513</v>
+        <v>-23837.3808397101</v>
       </c>
       <c r="G210" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H210" s="8" t="n">
-        <v>724664.087226037</v>
+        <v>724381.214752991</v>
       </c>
       <c r="I210" s="9" t="n">
-        <v>697136.390581099</v>
+        <v>697389.826571662</v>
       </c>
       <c r="J210" s="10" t="n">
-        <v>699273.800558201</v>
+        <v>699548.031273636</v>
       </c>
       <c r="K210" s="11" t="n">
-        <v>722121.266143609</v>
+        <v>721462.665506068</v>
       </c>
       <c r="L210" s="12" t="n">
-        <v>722121.266143609</v>
+        <v>721462.665506068</v>
       </c>
       <c r="M210" s="13" t="n">
-        <v>722121.266143609</v>
+        <v>721462.665506068</v>
       </c>
       <c r="N210" s="14" t="n">
-        <v>722121.266143609</v>
+        <v>721462.665506068</v>
       </c>
       <c r="O210" s="15" t="n">
-        <v>0.024957920171667</v>
+        <v>0.0237037053180381</v>
       </c>
       <c r="P210" s="16" t="n">
-        <v>0.0662761474345674</v>
+        <v>0.0658749970306731</v>
       </c>
       <c r="Q210" s="17" t="n">
-        <v>0.0252719763479261</v>
+        <v>0.0239868710737046</v>
       </c>
       <c r="R210" s="18" t="n">
-        <v>0.996491034774248</v>
+        <v>0.995970976072429</v>
       </c>
       <c r="S210" s="19" t="n">
-        <v>1.03583929328619</v>
+        <v>1.03451848308821</v>
       </c>
     </row>
     <row r="211">
@@ -14260,46 +14260,46 @@
         <v>782338.628533735</v>
       </c>
       <c r="F211" s="6" t="n">
-        <v>37564.9678221952</v>
+        <v>37384.3095843713</v>
       </c>
       <c r="G211" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H211" s="8" t="n">
-        <v>740186.29948398</v>
+        <v>740147.524638597</v>
       </c>
       <c r="I211" s="9" t="n">
-        <v>699553.802208828</v>
+        <v>699849.895929658</v>
       </c>
       <c r="J211" s="10" t="n">
-        <v>704006.236438987</v>
+        <v>704337.860360429</v>
       </c>
       <c r="K211" s="11" t="n">
-        <v>744773.66071154</v>
+        <v>744954.318949364</v>
       </c>
       <c r="L211" s="12" t="n">
-        <v>744773.66071154</v>
+        <v>744954.318949364</v>
       </c>
       <c r="M211" s="13" t="n">
-        <v>744773.66071154</v>
+        <v>744954.318949364</v>
       </c>
       <c r="N211" s="14" t="n">
-        <v>744773.66071154</v>
+        <v>744954.318949364</v>
       </c>
       <c r="O211" s="15" t="n">
-        <v>0.0308872776571501</v>
+        <v>0.0320422684383756</v>
       </c>
       <c r="P211" s="16" t="n">
-        <v>0.087634286702152</v>
+        <v>0.0878126240130943</v>
       </c>
       <c r="Q211" s="17" t="n">
-        <v>0.0313692389768585</v>
+        <v>0.0325611491300348</v>
       </c>
       <c r="R211" s="18" t="n">
-        <v>1.00619757651656</v>
+        <v>1.00649437328472</v>
       </c>
       <c r="S211" s="19" t="n">
-        <v>1.0646410016784</v>
+        <v>1.06444871004773</v>
       </c>
     </row>
     <row r="212">
@@ -14319,46 +14319,46 @@
         <v>732662.163875501</v>
       </c>
       <c r="F212" s="6" t="n">
-        <v>-3373.90272508948</v>
+        <v>-3689.5739411472</v>
       </c>
       <c r="G212" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H212" s="8" t="n">
-        <v>736414.668733621</v>
+        <v>736560.178839925</v>
       </c>
       <c r="I212" s="9" t="n">
-        <v>702002.989111757</v>
+        <v>702344.237894502</v>
       </c>
       <c r="J212" s="10" t="n">
-        <v>707926.808824294</v>
+        <v>708313.574528441</v>
       </c>
       <c r="K212" s="11" t="n">
-        <v>736036.066600591</v>
+        <v>736351.737816648</v>
       </c>
       <c r="L212" s="12" t="n">
-        <v>736036.066600591</v>
+        <v>736351.737816648</v>
       </c>
       <c r="M212" s="13" t="n">
-        <v>736036.066600591</v>
+        <v>736351.737816648</v>
       </c>
       <c r="N212" s="14" t="n">
-        <v>736036.066600591</v>
+        <v>736351.737816648</v>
       </c>
       <c r="O212" s="15" t="n">
-        <v>-0.0118012400325067</v>
+        <v>-0.0116149904421049</v>
       </c>
       <c r="P212" s="16" t="n">
-        <v>0.0621212747918114</v>
+        <v>0.0622633032758539</v>
       </c>
       <c r="Q212" s="17" t="n">
-        <v>-0.0117318785181011</v>
+        <v>-0.0115477968432318</v>
       </c>
       <c r="R212" s="18" t="n">
-        <v>0.999485884584997</v>
+        <v>0.999717007477101</v>
       </c>
       <c r="S212" s="19" t="n">
-        <v>1.04847996093563</v>
+        <v>1.04841998850036</v>
       </c>
     </row>
     <row r="213">
@@ -14378,46 +14378,46 @@
         <v>712740.457828738</v>
       </c>
       <c r="F213" s="6" t="n">
-        <v>-9400.73421520632</v>
+        <v>-9692.784748263</v>
       </c>
       <c r="G213" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H213" s="8" t="n">
-        <v>725517.585826448</v>
+        <v>726560.737975003</v>
       </c>
       <c r="I213" s="9" t="n">
-        <v>704452.604868476</v>
+        <v>704840.779456699</v>
       </c>
       <c r="J213" s="10" t="n">
-        <v>711006.783086269</v>
+        <v>711440.029245983</v>
       </c>
       <c r="K213" s="11" t="n">
-        <v>722141.192043945</v>
+        <v>722433.242577001</v>
       </c>
       <c r="L213" s="12" t="n">
-        <v>722141.192043945</v>
+        <v>722433.242577001</v>
       </c>
       <c r="M213" s="13" t="n">
-        <v>722141.192043945</v>
+        <v>722433.242577001</v>
       </c>
       <c r="N213" s="14" t="n">
-        <v>722141.192043945</v>
+        <v>722433.242577001</v>
       </c>
       <c r="O213" s="15" t="n">
-        <v>-0.0190584444400065</v>
+        <v>-0.0190828913106618</v>
       </c>
       <c r="P213" s="16" t="n">
-        <v>0.0253002672571889</v>
+        <v>0.0253644311686589</v>
       </c>
       <c r="Q213" s="17" t="n">
-        <v>-0.0188779805598659</v>
+        <v>-0.0189019656297911</v>
       </c>
       <c r="R213" s="18" t="n">
-        <v>0.99534622750921</v>
+        <v>0.994319132341908</v>
       </c>
       <c r="S213" s="19" t="n">
-        <v>1.02510969091919</v>
+        <v>1.02495948536613</v>
       </c>
     </row>
     <row r="214">
@@ -14437,46 +14437,46 @@
         <v>703987.504321577</v>
       </c>
       <c r="F214" s="6" t="n">
-        <v>-24973.3862323239</v>
+        <v>-23976.2753262874</v>
       </c>
       <c r="G214" s="7" t="n">
-        <v>0.30538427122904</v>
+        <v>0.843587141454005</v>
       </c>
       <c r="H214" s="8" t="n">
-        <v>721324.554961474</v>
+        <v>723301.398371429</v>
       </c>
       <c r="I214" s="9" t="n">
-        <v>706892.573731008</v>
+        <v>707328.702294208</v>
       </c>
       <c r="J214" s="10" t="n">
-        <v>713357.970885941</v>
+        <v>713822.270797809</v>
       </c>
       <c r="K214" s="11" t="n">
-        <v>728960.890553901</v>
+        <v>727963.779647865</v>
       </c>
       <c r="L214" s="12" t="n">
-        <v>723656.571741228</v>
+        <v>727234.523264786</v>
       </c>
       <c r="M214" s="13" t="n">
-        <v>723656.571741228</v>
+        <v>727234.523264786</v>
       </c>
       <c r="N214" s="14" t="n">
-        <v>723656.571741228</v>
+        <v>727234.523264786</v>
       </c>
       <c r="O214" s="15" t="n">
-        <v>0.0020962548015473</v>
+        <v>0.00662399807256098</v>
       </c>
       <c r="P214" s="16" t="n">
-        <v>0.00212610494885079</v>
+        <v>0.00800021682988827</v>
       </c>
       <c r="Q214" s="17" t="n">
-        <v>0.00209845347970528</v>
+        <v>0.00664598526869842</v>
       </c>
       <c r="R214" s="18" t="n">
-        <v>1.00323296463944</v>
+        <v>1.00543773992725</v>
       </c>
       <c r="S214" s="19" t="n">
-        <v>1.02371505746869</v>
+        <v>1.02814224971504</v>
       </c>
     </row>
     <row r="215">
@@ -14496,46 +14496,46 @@
         <v>737941.909374072</v>
       </c>
       <c r="F215" s="6" t="n">
-        <v>36202.3508786342</v>
+        <v>35888.3388976219</v>
       </c>
       <c r="G215" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H215" s="8" t="n">
-        <v>718843.746122845</v>
+        <v>720427.849700818</v>
       </c>
       <c r="I215" s="9" t="n">
-        <v>709323.875318357</v>
+        <v>709808.183374436</v>
       </c>
       <c r="J215" s="10" t="n">
-        <v>715147.855929126</v>
+        <v>715620.311535326</v>
       </c>
       <c r="K215" s="11" t="n">
-        <v>701739.558495438</v>
+        <v>702053.57047645</v>
       </c>
       <c r="L215" s="12" t="n">
-        <v>718843.746122845</v>
+        <v>720427.849700818</v>
       </c>
       <c r="M215" s="13" t="n">
-        <v>718843.746122845</v>
+        <v>720427.849700818</v>
       </c>
       <c r="N215" s="14" t="n">
-        <v>718843.746122845</v>
+        <v>720427.849700818</v>
       </c>
       <c r="O215" s="15" t="n">
-        <v>-0.00667291842850134</v>
+        <v>-0.00940374475534341</v>
       </c>
       <c r="P215" s="16" t="n">
-        <v>-0.0348158319185483</v>
+        <v>-0.032923453995322</v>
       </c>
       <c r="Q215" s="17" t="n">
-        <v>-0.00665070394759548</v>
+        <v>-0.00935966781858855</v>
       </c>
       <c r="R215" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S215" s="19" t="n">
-        <v>1.01342104944686</v>
+        <v>1.0149613185296</v>
       </c>
     </row>
     <row r="216">
@@ -14555,46 +14555,46 @@
         <v>728638.584568682</v>
       </c>
       <c r="F216" s="6" t="n">
-        <v>-1263.29818344771</v>
+        <v>-1991.47285404021</v>
       </c>
       <c r="G216" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H216" s="8" t="n">
-        <v>714697.411486266</v>
+        <v>715073.513430226</v>
       </c>
       <c r="I216" s="9" t="n">
-        <v>711757.966748286</v>
+        <v>712291.840802898</v>
       </c>
       <c r="J216" s="10" t="n">
-        <v>716595.41492592</v>
+        <v>717061.225072276</v>
       </c>
       <c r="K216" s="11" t="n">
-        <v>729901.88275213</v>
+        <v>730630.057422722</v>
       </c>
       <c r="L216" s="12" t="n">
-        <v>714697.411486266</v>
+        <v>715073.513430226</v>
       </c>
       <c r="M216" s="13" t="n">
-        <v>714697.411486266</v>
+        <v>715073.513430226</v>
       </c>
       <c r="N216" s="14" t="n">
-        <v>714697.411486266</v>
+        <v>715073.513430226</v>
       </c>
       <c r="O216" s="15" t="n">
-        <v>-0.00578476059389161</v>
+        <v>-0.00745991782242766</v>
       </c>
       <c r="P216" s="16" t="n">
-        <v>-0.0289913172500882</v>
+        <v>-0.0288968210348961</v>
       </c>
       <c r="Q216" s="17" t="n">
-        <v>-0.00576806108273553</v>
+        <v>-0.00743216169782379</v>
       </c>
       <c r="R216" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S216" s="19" t="n">
-        <v>1.00412983749435</v>
+        <v>1.00390524286252</v>
       </c>
     </row>
     <row r="217">
@@ -14614,46 +14614,46 @@
         <v>700509.934572323</v>
       </c>
       <c r="F217" s="6" t="n">
-        <v>-8588.68729830048</v>
+        <v>-8359.41384699579</v>
       </c>
       <c r="G217" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H217" s="8" t="n">
-        <v>707250.132932674</v>
+        <v>706930.757624317</v>
       </c>
       <c r="I217" s="9" t="n">
-        <v>714212.255057812</v>
+        <v>714798.929976563</v>
       </c>
       <c r="J217" s="10" t="n">
-        <v>717938.104037384</v>
+        <v>718396.12271323</v>
       </c>
       <c r="K217" s="11" t="n">
-        <v>709098.621870624</v>
+        <v>708869.348419319</v>
       </c>
       <c r="L217" s="12" t="n">
-        <v>709098.621870624</v>
+        <v>708869.348419319</v>
       </c>
       <c r="M217" s="13" t="n">
-        <v>709098.621870624</v>
+        <v>708869.348419319</v>
       </c>
       <c r="N217" s="14" t="n">
-        <v>709098.621870624</v>
+        <v>708869.348419319</v>
       </c>
       <c r="O217" s="15" t="n">
-        <v>-0.00786463558360951</v>
+        <v>-0.00871411969816522</v>
       </c>
       <c r="P217" s="16" t="n">
-        <v>-0.0180609696788037</v>
+        <v>-0.0187752907234696</v>
       </c>
       <c r="Q217" s="17" t="n">
-        <v>-0.00783379025257569</v>
+        <v>-0.0086762618029933</v>
       </c>
       <c r="R217" s="18" t="n">
-        <v>1.00261362826513</v>
+        <v>1.00274226403943</v>
       </c>
       <c r="S217" s="19" t="n">
-        <v>0.992840177200861</v>
+        <v>0.99170454611979</v>
       </c>
     </row>
     <row r="218">
@@ -14673,46 +14673,46 @@
         <v>669057.733385167</v>
       </c>
       <c r="F218" s="6" t="n">
-        <v>-26379.4898398554</v>
+        <v>-25503.8219604765</v>
       </c>
       <c r="G218" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H218" s="8" t="n">
-        <v>696598.439690834</v>
+        <v>696001.780992713</v>
       </c>
       <c r="I218" s="9" t="n">
-        <v>716705.984436909</v>
+        <v>717350.444837793</v>
       </c>
       <c r="J218" s="10" t="n">
-        <v>719403.889407383</v>
+        <v>719866.177204548</v>
       </c>
       <c r="K218" s="11" t="n">
-        <v>695437.223225022</v>
+        <v>694561.555345643</v>
       </c>
       <c r="L218" s="12" t="n">
-        <v>695437.223225022</v>
+        <v>694561.555345643</v>
       </c>
       <c r="M218" s="13" t="n">
-        <v>695437.223225022</v>
+        <v>694561.555345643</v>
       </c>
       <c r="N218" s="14" t="n">
-        <v>695437.223225022</v>
+        <v>694561.555345643</v>
       </c>
       <c r="O218" s="15" t="n">
-        <v>-0.0194538708861988</v>
+        <v>-0.0203904428230925</v>
       </c>
       <c r="P218" s="16" t="n">
-        <v>-0.0389954981660783</v>
+        <v>-0.0449276909633819</v>
       </c>
       <c r="Q218" s="17" t="n">
-        <v>-0.0192658654582665</v>
+        <v>-0.0201839635266784</v>
       </c>
       <c r="R218" s="18" t="n">
-        <v>0.998333018853262</v>
+        <v>0.997930715572286</v>
       </c>
       <c r="S218" s="19" t="n">
-        <v>0.970324286843235</v>
+        <v>0.968231859816714</v>
       </c>
     </row>
     <row r="219">
@@ -14732,46 +14732,46 @@
         <v>729947.785274553</v>
       </c>
       <c r="F219" s="6" t="n">
-        <v>34672.4565341723</v>
+        <v>34375.3391985698</v>
       </c>
       <c r="G219" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H219" s="8" t="n">
-        <v>697488.385362798</v>
+        <v>697821.670879931</v>
       </c>
       <c r="I219" s="9" t="n">
-        <v>719255.203054812</v>
+        <v>719963.673340473</v>
       </c>
       <c r="J219" s="10" t="n">
-        <v>721176.539768946</v>
+        <v>721664.927421119</v>
       </c>
       <c r="K219" s="11" t="n">
-        <v>695275.328740381</v>
+        <v>695572.446075983</v>
       </c>
       <c r="L219" s="12" t="n">
-        <v>695275.328740381</v>
+        <v>695572.446075983</v>
       </c>
       <c r="M219" s="13" t="n">
-        <v>695275.328740381</v>
+        <v>695572.446075983</v>
       </c>
       <c r="N219" s="14" t="n">
-        <v>695275.328740381</v>
+        <v>695572.446075983</v>
       </c>
       <c r="O219" s="15" t="n">
-        <v>-0.000232822354474189</v>
+        <v>0.00145437908502931</v>
       </c>
       <c r="P219" s="16" t="n">
-        <v>-0.0327865652439528</v>
+        <v>-0.0345008922616702</v>
       </c>
       <c r="Q219" s="17" t="n">
-        <v>-0.0002327952534531</v>
+        <v>0.00145543720719887</v>
       </c>
       <c r="R219" s="18" t="n">
-        <v>0.996827106129852</v>
+        <v>0.996776791409886</v>
       </c>
       <c r="S219" s="19" t="n">
-        <v>0.966660130906826</v>
+        <v>0.966121586174869</v>
       </c>
     </row>
     <row r="220">
@@ -14791,46 +14791,46 @@
         <v>714524.365549959</v>
       </c>
       <c r="F220" s="6" t="n">
-        <v>503.033075702028</v>
+        <v>-675.299374840395</v>
       </c>
       <c r="G220" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H220" s="8" t="n">
-        <v>712123.684724955</v>
+        <v>712738.689883563</v>
       </c>
       <c r="I220" s="9" t="n">
-        <v>721862.666105</v>
+        <v>722641.66038256</v>
       </c>
       <c r="J220" s="10" t="n">
-        <v>723319.990524193</v>
+        <v>723859.389128539</v>
       </c>
       <c r="K220" s="11" t="n">
-        <v>714021.332474257</v>
+        <v>715199.6649248</v>
       </c>
       <c r="L220" s="12" t="n">
-        <v>714021.332474257</v>
+        <v>715199.6649248</v>
       </c>
       <c r="M220" s="13" t="n">
-        <v>714021.332474257</v>
+        <v>715199.6649248</v>
       </c>
       <c r="N220" s="14" t="n">
-        <v>714021.332474257</v>
+        <v>715199.6649248</v>
       </c>
       <c r="O220" s="15" t="n">
-        <v>0.0266049157316703</v>
+        <v>0.0278265853946929</v>
       </c>
       <c r="P220" s="16" t="n">
-        <v>-0.000945965384991032</v>
+        <v>0.000176417518205074</v>
       </c>
       <c r="Q220" s="17" t="n">
-        <v>0.0269619860780019</v>
+        <v>0.0282173610520968</v>
       </c>
       <c r="R220" s="18" t="n">
-        <v>1.00266477269329</v>
+        <v>1.0034528433438</v>
       </c>
       <c r="S220" s="19" t="n">
-        <v>0.989137360887421</v>
+        <v>0.989701679455042</v>
       </c>
     </row>
     <row r="221">
@@ -14850,46 +14850,46 @@
         <v>718991.46093658</v>
       </c>
       <c r="F221" s="6" t="n">
-        <v>-7952.44402328256</v>
+        <v>-7117.09555906453</v>
       </c>
       <c r="G221" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H221" s="8" t="n">
-        <v>726726.70337157</v>
+        <v>726369.762982966</v>
       </c>
       <c r="I221" s="9" t="n">
-        <v>724516.141359501</v>
+        <v>725372.206344968</v>
       </c>
       <c r="J221" s="10" t="n">
-        <v>725768.671020098</v>
+        <v>726386.115685679</v>
       </c>
       <c r="K221" s="11" t="n">
-        <v>726943.904959862</v>
+        <v>726108.556495644</v>
       </c>
       <c r="L221" s="12" t="n">
-        <v>726943.904959862</v>
+        <v>726108.556495644</v>
       </c>
       <c r="M221" s="13" t="n">
-        <v>726943.904959862</v>
+        <v>726108.556495644</v>
       </c>
       <c r="N221" s="14" t="n">
-        <v>726943.904959862</v>
+        <v>726108.556495644</v>
       </c>
       <c r="O221" s="15" t="n">
-        <v>0.0179364756333286</v>
+        <v>0.0151377751466734</v>
       </c>
       <c r="P221" s="16" t="n">
-        <v>0.0251661511372874</v>
+        <v>0.0243193024423556</v>
       </c>
       <c r="Q221" s="17" t="n">
-        <v>0.0180983002858264</v>
+        <v>0.0152529316019625</v>
       </c>
       <c r="R221" s="18" t="n">
-        <v>1.00029887657531</v>
+        <v>0.999640394602538</v>
       </c>
       <c r="S221" s="19" t="n">
-        <v>1.00335087579389</v>
+        <v>1.00101513422245</v>
       </c>
     </row>
     <row r="222">
@@ -14909,46 +14909,46 @@
         <v>708113.805670176</v>
       </c>
       <c r="F222" s="6" t="n">
-        <v>-27042.0661221588</v>
+        <v>-26366.7959977886</v>
       </c>
       <c r="G222" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H222" s="8" t="n">
-        <v>736400.123149105</v>
+        <v>735632.293590181</v>
       </c>
       <c r="I222" s="9" t="n">
-        <v>727198.495756828</v>
+        <v>728138.46036145</v>
       </c>
       <c r="J222" s="10" t="n">
-        <v>728410.517313389</v>
+        <v>729138.361830389</v>
       </c>
       <c r="K222" s="11" t="n">
-        <v>735155.871792335</v>
+        <v>734480.601667965</v>
       </c>
       <c r="L222" s="12" t="n">
-        <v>735155.871792335</v>
+        <v>734480.601667965</v>
       </c>
       <c r="M222" s="13" t="n">
-        <v>735155.871792335</v>
+        <v>734480.601667965</v>
       </c>
       <c r="N222" s="14" t="n">
-        <v>735155.871792335</v>
+        <v>734480.601667965</v>
       </c>
       <c r="O222" s="15" t="n">
-        <v>0.0112332322533183</v>
+        <v>0.0114640545102577</v>
       </c>
       <c r="P222" s="16" t="n">
-        <v>0.057113204816851</v>
+        <v>0.0574737343509548</v>
       </c>
       <c r="Q222" s="17" t="n">
-        <v>0.0112965619168737</v>
+        <v>0.0115300186141947</v>
       </c>
       <c r="R222" s="18" t="n">
-        <v>0.998310359656855</v>
+        <v>0.998434419026664</v>
       </c>
       <c r="S222" s="19" t="n">
-        <v>1.01094250893248</v>
+        <v>1.00871007597012</v>
       </c>
     </row>
     <row r="223">
@@ -14968,46 +14968,46 @@
         <v>776528.776090785</v>
       </c>
       <c r="F223" s="6" t="n">
-        <v>33800.6387500781</v>
+        <v>33588.8783588198</v>
       </c>
       <c r="G223" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H223" s="8" t="n">
-        <v>740730.950951042</v>
+        <v>740605.519088374</v>
       </c>
       <c r="I223" s="9" t="n">
-        <v>729894.113587741</v>
+        <v>730924.031784605</v>
       </c>
       <c r="J223" s="10" t="n">
-        <v>731139.34163049</v>
+        <v>732007.994504572</v>
       </c>
       <c r="K223" s="11" t="n">
-        <v>742728.137340707</v>
+        <v>742939.897731966</v>
       </c>
       <c r="L223" s="12" t="n">
-        <v>742728.137340707</v>
+        <v>742939.897731966</v>
       </c>
       <c r="M223" s="13" t="n">
-        <v>742728.137340707</v>
+        <v>742939.897731966</v>
       </c>
       <c r="N223" s="14" t="n">
-        <v>742728.137340707</v>
+        <v>742939.897731966</v>
       </c>
       <c r="O223" s="15" t="n">
-        <v>0.0102475319663796</v>
+        <v>0.0114515650920962</v>
       </c>
       <c r="P223" s="16" t="n">
-        <v>0.068250384615683</v>
+        <v>0.0680985164423948</v>
       </c>
       <c r="Q223" s="17" t="n">
-        <v>0.0103002177346563</v>
+        <v>0.011517385271701</v>
       </c>
       <c r="R223" s="18" t="n">
-        <v>1.0026962372601</v>
+        <v>1.00315198656157</v>
       </c>
       <c r="S223" s="19" t="n">
-        <v>1.01758340492689</v>
+        <v>1.01643928154616</v>
       </c>
     </row>
     <row r="224">
@@ -15015,92 +15015,118 @@
         <v>273</v>
       </c>
       <c r="B224" s="2" t="n">
-        <v>737868.049792728</v>
+        <v>737795.741613431</v>
       </c>
       <c r="C224" s="3" t="n">
-        <v>737868.049792728</v>
+        <v>737795.741613431</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>737868.049792728</v>
+        <v>737795.741613431</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>737868.049792728</v>
+        <v>737795.741613431</v>
       </c>
       <c r="F224" s="6" t="n">
-        <v>1081.96229663661</v>
+        <v>-629.853233285096</v>
       </c>
       <c r="G224" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H224" s="8" t="n">
-        <v>737531.918831365</v>
+        <v>740400.516803348</v>
       </c>
       <c r="I224" s="9" t="n">
-        <v>732592.352503025</v>
+        <v>733716.493805345</v>
       </c>
       <c r="J224" s="10" t="n">
-        <v>733882.682970219</v>
+        <v>734913.591849315</v>
       </c>
       <c r="K224" s="11" t="n">
-        <v>736786.087496091</v>
+        <v>738425.594846716</v>
       </c>
       <c r="L224" s="12" t="n">
-        <v>736786.087496091</v>
+        <v>738425.594846716</v>
       </c>
       <c r="M224" s="13" t="n">
-        <v>736786.087496091</v>
+        <v>738425.594846716</v>
       </c>
       <c r="N224" s="14" t="n">
-        <v>736786.087496091</v>
+        <v>738425.594846716</v>
       </c>
       <c r="O224" s="15" t="n">
-        <v>-0.00803247673268745</v>
+        <v>-0.00609480493790925</v>
       </c>
       <c r="P224" s="16" t="n">
-        <v>0.0318824578293042</v>
+        <v>0.03247474944547</v>
       </c>
       <c r="Q224" s="17" t="n">
-        <v>-0.00800030259509366</v>
+        <v>-0.00607626929046379</v>
       </c>
       <c r="R224" s="18" t="n">
-        <v>0.998988747041002</v>
+        <v>0.997332630229436</v>
       </c>
       <c r="S224" s="19" t="n">
-        <v>1.00572451374729</v>
+        <v>1.00641814799194</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
         <v>274</v>
       </c>
-      <c r="B225" s="2"/>
+      <c r="B225" s="2" t="n">
+        <v>733788.66978506</v>
+      </c>
       <c r="C225" s="3" t="n">
-        <v>724250.61727998</v>
+        <v>733788.66978506</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>769280.785188484</v>
+        <v>733788.66978506</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>679220.449371476</v>
+        <v>733788.66978506</v>
       </c>
       <c r="F225" s="6" t="n">
-        <v>-7404.26741457972</v>
-      </c>
-      <c r="G225" s="7"/>
-      <c r="H225" s="8"/>
-      <c r="I225" s="9"/>
-      <c r="J225" s="10"/>
-      <c r="K225" s="11"/>
-      <c r="L225" s="12"/>
-      <c r="M225" s="13"/>
+        <v>-5880.18729418066</v>
+      </c>
+      <c r="G225" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H225" s="8" t="n">
+        <v>739245.003060546</v>
+      </c>
+      <c r="I225" s="9" t="n">
+        <v>736510.929530804</v>
+      </c>
+      <c r="J225" s="10" t="n">
+        <v>737828.391521845</v>
+      </c>
+      <c r="K225" s="11" t="n">
+        <v>739668.857079241</v>
+      </c>
+      <c r="L225" s="12" t="n">
+        <v>739668.857079241</v>
+      </c>
+      <c r="M225" s="13" t="n">
+        <v>739668.857079241</v>
+      </c>
       <c r="N225" s="14" t="n">
-        <v>731654.88469456</v>
-      </c>
-      <c r="O225" s="15"/>
-      <c r="P225" s="16"/>
-      <c r="Q225" s="17"/>
-      <c r="R225" s="18"/>
-      <c r="S225" s="19"/>
+        <v>739668.857079241</v>
+      </c>
+      <c r="O225" s="15" t="n">
+        <v>0.00168225044631438</v>
+      </c>
+      <c r="P225" s="16" t="n">
+        <v>0.0186753075174348</v>
+      </c>
+      <c r="Q225" s="17" t="n">
+        <v>0.00168366622338234</v>
+      </c>
+      <c r="R225" s="18" t="n">
+        <v>1.00057336068143</v>
+      </c>
+      <c r="S225" s="19" t="n">
+        <v>1.00428768592809</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
@@ -15108,16 +15134,16 @@
       </c>
       <c r="B226" s="2"/>
       <c r="C226" s="3" t="n">
-        <v>704005.071813106</v>
+        <v>711397.419274849</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>760489.603069962</v>
+        <v>756117.825347278</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>647520.540556249</v>
+        <v>666677.01320242</v>
       </c>
       <c r="F226" s="6" t="n">
-        <v>-27497.1070882129</v>
+        <v>-27106.873050446</v>
       </c>
       <c r="G226" s="7"/>
       <c r="H226" s="8"/>
@@ -15127,7 +15153,7 @@
       <c r="L226" s="12"/>
       <c r="M226" s="13"/>
       <c r="N226" s="14" t="n">
-        <v>731502.178901319</v>
+        <v>738504.292325295</v>
       </c>
       <c r="O226" s="15"/>
       <c r="P226" s="16"/>
@@ -15141,16 +15167,16 @@
       </c>
       <c r="B227" s="2"/>
       <c r="C227" s="3" t="n">
-        <v>760383.051733435</v>
+        <v>766108.12190621</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>822490.199013817</v>
+        <v>822337.333960242</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>698275.904453054</v>
+        <v>709878.909852177</v>
       </c>
       <c r="F227" s="6" t="n">
-        <v>33720.4052741149</v>
+        <v>33569.1253614406</v>
       </c>
       <c r="G227" s="7"/>
       <c r="H227" s="8"/>
@@ -15160,7 +15186,7 @@
       <c r="L227" s="12"/>
       <c r="M227" s="13"/>
       <c r="N227" s="14" t="n">
-        <v>726662.64645932</v>
+        <v>732538.996544769</v>
       </c>
       <c r="O227" s="15"/>
       <c r="P227" s="16"/>
@@ -15174,16 +15200,16 @@
       </c>
       <c r="B228" s="2"/>
       <c r="C228" s="3" t="n">
-        <v>724898.474348457</v>
+        <v>729321.957885213</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>790011.216107154</v>
+        <v>791262.686042764</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>659785.732589759</v>
+        <v>667381.229727663</v>
       </c>
       <c r="F228" s="6" t="n">
-        <v>1179.4120606785</v>
+        <v>-715.402541208025</v>
       </c>
       <c r="G228" s="7"/>
       <c r="H228" s="8"/>
@@ -15193,7 +15219,7 @@
       <c r="L228" s="12"/>
       <c r="M228" s="13"/>
       <c r="N228" s="14" t="n">
-        <v>723719.062287778</v>
+        <v>730037.360426421</v>
       </c>
       <c r="O228" s="15"/>
       <c r="P228" s="16"/>
@@ -15206,10 +15232,18 @@
         <v>278</v>
       </c>
       <c r="B229" s="2"/>
-      <c r="C229" s="3"/>
-      <c r="D229" s="4"/>
-      <c r="E229" s="5"/>
-      <c r="F229" s="6"/>
+      <c r="C229" s="3" t="n">
+        <v>720375.234142833</v>
+      </c>
+      <c r="D229" s="4" t="n">
+        <v>785403.999383243</v>
+      </c>
+      <c r="E229" s="5" t="n">
+        <v>655346.468902423</v>
+      </c>
+      <c r="F229" s="6" t="n">
+        <v>-5629.80823220515</v>
+      </c>
       <c r="G229" s="7"/>
       <c r="H229" s="8"/>
       <c r="I229" s="9"/>
@@ -15217,7 +15251,9 @@
       <c r="K229" s="11"/>
       <c r="L229" s="12"/>
       <c r="M229" s="13"/>
-      <c r="N229" s="14"/>
+      <c r="N229" s="14" t="n">
+        <v>726005.042375038</v>
+      </c>
       <c r="O229" s="15"/>
       <c r="P229" s="16"/>
       <c r="Q229" s="17"/>
@@ -15738,7 +15774,7 @@
         <v>316</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.00439937513385089</v>
+        <v>-0.00120555741476047</v>
       </c>
     </row>
     <row r="6">
@@ -15746,7 +15782,7 @@
         <v>317</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.139183420276649</v>
+        <v>0.136501784403018</v>
       </c>
     </row>
     <row r="7">
@@ -15754,7 +15790,7 @@
         <v>318</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.384914465135252</v>
+        <v>0.387779855208663</v>
       </c>
     </row>
     <row r="8">
@@ -15762,7 +15798,7 @@
         <v>319</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.642044945631027</v>
+        <v>0.643187517967728</v>
       </c>
     </row>
     <row r="9">
@@ -15770,7 +15806,7 @@
         <v>320</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.72114005649416</v>
+        <v>0.721251404033602</v>
       </c>
     </row>
     <row r="10">
@@ -15778,7 +15814,7 @@
         <v>321</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.509907861023004</v>
+        <v>0.508419114964576</v>
       </c>
     </row>
     <row r="11">
@@ -15786,7 +15822,7 @@
         <v>322</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.160309882800666</v>
+        <v>0.158853811652554</v>
       </c>
     </row>
     <row r="12">
@@ -15794,7 +15830,7 @@
         <v>323</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.0493548644001488</v>
+        <v>-0.0461316885701389</v>
       </c>
     </row>
     <row r="13">
@@ -15802,7 +15838,7 @@
         <v>324</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.105263379863882</v>
+        <v>-0.103003542679269</v>
       </c>
     </row>
     <row r="14">
@@ -15860,4 +15896,237 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
+    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
+    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB35234A-69CC-4480-B276-0142BF48427D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF26BE08-CA3E-42E6-9D32-0E9E282D00FD}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1156A039-7F4A-404A-AA59-0CFBD3EAAB70}"/>
 </file>
--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -104,7 +104,7 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">25/03/2026</t>
+    <t xml:space="preserve">08/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
@@ -1523,7 +1523,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.721251404033602</v>
+        <v>0.721364907978918</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1581,7 +1581,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.520203587820442</v>
+        <v>0.520367330463434</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1651,7 +1651,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.181327766662582</v>
+        <v>0.194861038674566</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1681,7 +1681,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.000115221997963427</v>
+        <v>0.00011630343719005</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -15774,7 +15774,7 @@
         <v>316</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.00120555741476047</v>
+        <v>-0.000769078242954611</v>
       </c>
     </row>
     <row r="6">
@@ -15782,7 +15782,7 @@
         <v>317</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.136501784403018</v>
+        <v>0.13657789050616</v>
       </c>
     </row>
     <row r="7">
@@ -15790,7 +15790,7 @@
         <v>318</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.387779855208663</v>
+        <v>0.386399397034226</v>
       </c>
     </row>
     <row r="8">
@@ -15798,7 +15798,7 @@
         <v>319</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.643187517967728</v>
+        <v>0.642797690787341</v>
       </c>
     </row>
     <row r="9">
@@ -15806,7 +15806,7 @@
         <v>320</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.721251404033602</v>
+        <v>0.721364907978918</v>
       </c>
     </row>
     <row r="10">
@@ -15814,7 +15814,7 @@
         <v>321</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.508419114964576</v>
+        <v>0.508228764556184</v>
       </c>
     </row>
     <row r="11">
@@ -15822,7 +15822,7 @@
         <v>322</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.158853811652554</v>
+        <v>0.158934456910895</v>
       </c>
     </row>
     <row r="12">
@@ -15830,7 +15830,7 @@
         <v>323</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.0461316885701389</v>
+        <v>-0.045118324356173</v>
       </c>
     </row>
     <row r="13">
@@ -15838,7 +15838,7 @@
         <v>324</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.103003542679269</v>
+        <v>-0.103108260403738</v>
       </c>
     </row>
     <row r="14">
@@ -15896,237 +15896,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
-    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB35234A-69CC-4480-B276-0142BF48427D}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF26BE08-CA3E-42E6-9D32-0E9E282D00FD}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1156A039-7F4A-404A-AA59-0CFBD3EAAB70}"/>
 </file>
--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">focampo</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>

--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -104,7 +104,7 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">08/05/2026</t>
+    <t xml:space="preserve">19/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
@@ -1523,7 +1523,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.721364907978918</v>
+        <v>0.717944991240825</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1581,7 +1581,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.520367330463434</v>
+        <v>0.515445010447788</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1651,7 +1651,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.194861038674566</v>
+        <v>0.196647137065288</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1681,7 +1681,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.00011630343719005</v>
+        <v>0.000107731607137423</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -15774,7 +15774,7 @@
         <v>316</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.000769078242954611</v>
+        <v>-0.000421437147776817</v>
       </c>
     </row>
     <row r="6">
@@ -15782,7 +15782,7 @@
         <v>317</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.13657789050616</v>
+        <v>0.138775419152784</v>
       </c>
     </row>
     <row r="7">
@@ -15790,7 +15790,7 @@
         <v>318</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.386399397034226</v>
+        <v>0.39200415755766</v>
       </c>
     </row>
     <row r="8">
@@ -15798,7 +15798,7 @@
         <v>319</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.642797690787341</v>
+        <v>0.640616110373754</v>
       </c>
     </row>
     <row r="9">
@@ -15806,7 +15806,7 @@
         <v>320</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.721364907978918</v>
+        <v>0.717944991240825</v>
       </c>
     </row>
     <row r="10">
@@ -15814,7 +15814,7 @@
         <v>321</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.508228764556184</v>
+        <v>0.507527805395759</v>
       </c>
     </row>
     <row r="11">
@@ -15822,7 +15822,7 @@
         <v>322</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.158934456910895</v>
+        <v>0.158390268508302</v>
       </c>
     </row>
     <row r="12">
@@ -15830,7 +15830,7 @@
         <v>323</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.045118324356173</v>
+        <v>-0.0423901973361968</v>
       </c>
     </row>
     <row r="13">
@@ -15838,7 +15838,7 @@
         <v>324</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.103108260403738</v>
+        <v>-0.100590409821635</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="327">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -71,6 +71,12 @@
     <t xml:space="preserve">Regresores</t>
   </si>
   <si>
+    <t xml:space="preserve">Alcance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argentina</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resumen del correlograma</t>
   </si>
   <si>
@@ -104,13 +110,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">19/05/2026</t>
+    <t xml:space="preserve">17/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">fleiva</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1491,9 +1497,13 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7">
-      <c r="A7"/>
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
       <c r="B7"/>
-      <c r="C7"/>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
@@ -1504,7 +1514,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8"/>
       <c r="C8"/>
@@ -1518,12 +1528,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.717944991240825</v>
+        <v>0.718351631330702</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1534,7 +1544,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
@@ -1562,7 +1572,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
@@ -1576,12 +1586,12 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.515445010447788</v>
+        <v>0.51602906623548</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1604,7 +1614,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -1618,7 +1628,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -1632,7 +1642,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1646,12 +1656,12 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.196647137065288</v>
+        <v>0.224264939275511</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1662,7 +1672,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1676,12 +1686,12 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.000107731607137423</v>
+        <v>0.0000792883206407128</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1824,10 +1834,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C32"/>
       <c r="D32"/>
@@ -1840,10 +1850,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C33"/>
       <c r="D33"/>
@@ -1867,66 +1877,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="R1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>274720.736810153</v>
@@ -1979,7 +1989,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>293673.715991951</v>
@@ -2036,7 +2046,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>286997.615166001</v>
@@ -2093,7 +2103,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>284846.968573894</v>
@@ -2150,7 +2160,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>279343.652369923</v>
@@ -2209,7 +2219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>307042.161198174</v>
@@ -2268,7 +2278,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>299264.747389256</v>
@@ -2327,7 +2337,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>297477.956413941</v>
@@ -2386,7 +2396,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>286838.428333654</v>
@@ -2445,7 +2455,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>303299.646282604</v>
@@ -2504,7 +2514,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>306691.300424839</v>
@@ -2563,7 +2573,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>310878.888728805</v>
@@ -2622,7 +2632,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>297656.635511472</v>
@@ -2681,7 +2691,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>316177.536148331</v>
@@ -2740,7 +2750,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>311431.169575721</v>
@@ -2799,7 +2809,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>327668.22647504</v>
@@ -2858,7 +2868,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>317571.233109077</v>
@@ -2917,7 +2927,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>336774.36302742</v>
@@ -2976,7 +2986,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>328317.968647882</v>
@@ -3035,7 +3045,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>338005.624444955</v>
@@ -3094,7 +3104,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>322824.398576504</v>
@@ -3153,7 +3163,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>337794.458238781</v>
@@ -3212,7 +3222,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>322171.407692798</v>
@@ -3271,7 +3281,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>330046.282827642</v>
@@ -3330,7 +3340,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>319289.801156244</v>
@@ -3389,7 +3399,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>328954.715977267</v>
@@ -3448,7 +3458,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>329916.334393073</v>
@@ -3507,7 +3517,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>334516.508976794</v>
@@ -3566,7 +3576,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>333324.232089629</v>
@@ -3625,7 +3635,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>354687.754732671</v>
@@ -3684,7 +3694,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>361155.938063312</v>
@@ -3743,7 +3753,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>347326.175914372</v>
@@ -3802,7 +3812,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>317805.1402913</v>
@@ -3861,7 +3871,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>336329.289639023</v>
@@ -3920,7 +3930,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>345471.162010909</v>
@@ -3979,7 +3989,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>351893.863389451</v>
@@ -4038,7 +4048,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>344733.704644733</v>
@@ -4097,7 +4107,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>365460.47995839</v>
@@ -4156,7 +4166,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>363105.164581838</v>
@@ -4215,7 +4225,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>373039.722404591</v>
@@ -4274,7 +4284,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>350886.763021546</v>
@@ -4333,7 +4343,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>375630.182793721</v>
@@ -4392,7 +4402,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>392787.639412916</v>
@@ -4451,7 +4461,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>387175.795813475</v>
@@ -4510,7 +4520,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>348787.74219593</v>
@@ -4569,7 +4579,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>365764.156070867</v>
@@ -4628,7 +4638,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>356438.374654421</v>
@@ -4687,7 +4697,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>353808.753269303</v>
@@ -4746,7 +4756,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>326438.28846154</v>
@@ -4805,7 +4815,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>336012.476528146</v>
@@ -4864,7 +4874,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>355257.567292421</v>
@@ -4923,7 +4933,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>362089.394512038</v>
@@ -4982,7 +4992,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>335280.801750139</v>
@@ -5041,7 +5051,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>361986.010937587</v>
@@ -5100,7 +5110,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>371728.866385673</v>
@@ -5159,7 +5169,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>367537.47434082</v>
@@ -5218,7 +5228,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>335440.414960448</v>
@@ -5277,7 +5287,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>372878.925634586</v>
@@ -5336,7 +5346,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>377126.467131091</v>
@@ -5395,7 +5405,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>379809.195369898</v>
@@ -5454,7 +5464,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>327369.620852271</v>
@@ -5513,7 +5523,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>342983.11820777</v>
@@ -5572,7 +5582,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>338381.469087693</v>
@@ -5631,7 +5641,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>354683.615755327</v>
@@ -5690,7 +5700,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>330021.402388751</v>
@@ -5749,7 +5759,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>367750.910840104</v>
@@ -5808,7 +5818,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>385564.691568936</v>
@@ -5867,7 +5877,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>377396.585608765</v>
@@ -5926,7 +5936,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>342518.805916862</v>
@@ -5985,7 +5995,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>384165.470300204</v>
@@ -6044,7 +6054,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>394585.944646856</v>
@@ -6103,7 +6113,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>377308.717854857</v>
@@ -6162,7 +6172,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>358624.233714962</v>
@@ -6221,7 +6231,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>379121.886615641</v>
@@ -6280,7 +6290,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>367102.679295591</v>
@@ -6339,7 +6349,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>365343.872206465</v>
@@ -6398,7 +6408,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>344056.129030727</v>
@@ -6457,7 +6467,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>344664.833564317</v>
@@ -6516,7 +6526,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>330724.443386007</v>
@@ -6575,7 +6585,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>348765.952516928</v>
@@ -6634,7 +6644,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>300955.694107537</v>
@@ -6693,7 +6703,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>333959.889781522</v>
@@ -6752,7 +6762,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>348762.379985619</v>
@@ -6811,7 +6821,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>359489.605138886</v>
@@ -6870,7 +6880,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>325091.525804152</v>
@@ -6929,7 +6939,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>376116.498579129</v>
@@ -6988,7 +6998,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>384748.078172234</v>
@@ -7047,7 +7057,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>399299.25475537</v>
@@ -7106,7 +7116,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>372951.254774255</v>
@@ -7165,7 +7175,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>421992.062398688</v>
@@ -7224,7 +7234,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>418269.85525714</v>
@@ -7283,7 +7293,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>414719.066729715</v>
@@ -7342,7 +7352,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>390107.470249262</v>
@@ -7401,7 +7411,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>436086.196210652</v>
@@ -7460,7 +7470,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>437481.084266889</v>
@@ -7519,7 +7529,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>441964.886493292</v>
@@ -7578,7 +7588,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>419991.981226533</v>
@@ -7637,7 +7647,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>464221.511045238</v>
@@ -7696,7 +7706,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>456993.219112459</v>
@@ -7755,7 +7765,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>463977.478231814</v>
@@ -7814,7 +7824,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>429047.866823909</v>
@@ -7873,7 +7883,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>447303.84163999</v>
@@ -7932,7 +7942,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>436704.325551312</v>
@@ -7991,7 +8001,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>440766.881538129</v>
@@ -8050,7 +8060,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>426519.991695787</v>
@@ -8109,7 +8119,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>470126.272390857</v>
@@ -8168,7 +8178,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>472677.535758481</v>
@@ -8227,7 +8237,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>481427.468387569</v>
@@ -8286,7 +8296,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>462258.015087104</v>
@@ -8345,7 +8355,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>508020.740483857</v>
@@ -8404,7 +8414,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>512208.063825329</v>
@@ -8463,7 +8473,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>518379.749569641</v>
@@ -8522,7 +8532,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>489869.523456675</v>
@@ -8581,7 +8591,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>543066.384243079</v>
@@ -8640,7 +8650,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>528837.044115363</v>
@@ -8699,7 +8709,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>516130.558988705</v>
@@ -8758,7 +8768,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>477829.815015122</v>
@@ -8817,7 +8827,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>516391.046914062</v>
@@ -8876,7 +8886,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>502076.175540002</v>
@@ -8935,7 +8945,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>511259.942382052</v>
@@ -8994,7 +9004,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>476984.733765134</v>
@@ -9053,7 +9063,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>514340.804852638</v>
@@ -9112,7 +9122,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B124" s="2" t="n">
         <v>499002.622761819</v>
@@ -9171,7 +9181,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B125" s="2" t="n">
         <v>501389.215538927</v>
@@ -9230,7 +9240,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>467327.980201225</v>
@@ -9289,7 +9299,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>513476.440667766</v>
@@ -9348,7 +9358,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>474407.554522122</v>
@@ -9407,7 +9417,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B129" s="2" t="n">
         <v>448693.775149267</v>
@@ -9466,7 +9476,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B130" s="2" t="n">
         <v>390971.781617488</v>
@@ -9525,7 +9535,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B131" s="2" t="n">
         <v>444096.358125271</v>
@@ -9584,7 +9594,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B132" s="2" t="n">
         <v>428054.007663138</v>
@@ -9643,7 +9653,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B133" s="2" t="n">
         <v>433362.880156828</v>
@@ -9702,7 +9712,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B134" s="2" t="n">
         <v>412150.09254573</v>
@@ -9761,7 +9771,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B135" s="2" t="n">
         <v>478511.050017991</v>
@@ -9820,7 +9830,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B136" s="2" t="n">
         <v>471537.267275214</v>
@@ -9879,7 +9889,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B137" s="2" t="n">
         <v>484205.691494541</v>
@@ -9938,7 +9948,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B138" s="2" t="n">
         <v>460369.442232949</v>
@@ -9997,7 +10007,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B139" s="2" t="n">
         <v>514395.681772362</v>
@@ -10056,7 +10066,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B140" s="2" t="n">
         <v>481151.979943508</v>
@@ -10115,7 +10125,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B141" s="2" t="n">
         <v>484543.676876562</v>
@@ -10174,7 +10184,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B142" s="2" t="n">
         <v>493602.530577855</v>
@@ -10233,7 +10243,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B143" s="2" t="n">
         <v>581668.249879602</v>
@@ -10292,7 +10302,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B144" s="2" t="n">
         <v>514697.789505428</v>
@@ -10351,7 +10361,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B145" s="2" t="n">
         <v>522255.200050771</v>
@@ -10410,7 +10420,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B146" s="2" t="n">
         <v>532348.212016917</v>
@@ -10469,7 +10479,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B147" s="2" t="n">
         <v>614076.392608544</v>
@@ -10528,7 +10538,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B148" s="2" t="n">
         <v>562978.965626877</v>
@@ -10587,7 +10597,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B149" s="2" t="n">
         <v>572794.046630588</v>
@@ -10646,7 +10656,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B150" s="2" t="n">
         <v>576846.885699427</v>
@@ -10705,7 +10715,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B151" s="2" t="n">
         <v>674620.563006485</v>
@@ -10764,7 +10774,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B152" s="2" t="n">
         <v>610425.694014854</v>
@@ -10823,7 +10833,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B153" s="2" t="n">
         <v>625876.867863597</v>
@@ -10882,7 +10892,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B154" s="2" t="n">
         <v>616720.357064478</v>
@@ -10941,7 +10951,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B155" s="2" t="n">
         <v>711405.500455233</v>
@@ -11000,7 +11010,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B156" s="2" t="n">
         <v>647087.959742494</v>
@@ -11059,7 +11069,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B157" s="2" t="n">
         <v>613490.821702641</v>
@@ -11118,7 +11128,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B158" s="2" t="n">
         <v>578553.044242405</v>
@@ -11177,7 +11187,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B159" s="2" t="n">
         <v>631197.751860069</v>
@@ -11236,7 +11246,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B160" s="2" t="n">
         <v>610519.854611727</v>
@@ -11295,7 +11305,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B161" s="2" t="n">
         <v>615220.854937297</v>
@@ -11354,7 +11364,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B162" s="2" t="n">
         <v>611607.33658973</v>
@@ -11413,7 +11423,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B163" s="2" t="n">
         <v>733730.773968903</v>
@@ -11472,7 +11482,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B164" s="2" t="n">
         <v>668566.509488986</v>
@@ -11531,7 +11541,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B165" s="2" t="n">
         <v>668190.097719574</v>
@@ -11590,7 +11600,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B166" s="2" t="n">
         <v>662325.585972695</v>
@@ -11649,7 +11659,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B167" s="2" t="n">
         <v>766332.954571613</v>
@@ -11708,7 +11718,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B168" s="2" t="n">
         <v>711417.391930105</v>
@@ -11767,7 +11777,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B169" s="2" t="n">
         <v>703050.456407993</v>
@@ -11826,7 +11836,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B170" s="2" t="n">
         <v>672685.993630504</v>
@@ -11885,7 +11895,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B171" s="2" t="n">
         <v>730838.272592776</v>
@@ -11944,7 +11954,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B172" s="2" t="n">
         <v>703461.652530196</v>
@@ -12003,7 +12013,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B173" s="2" t="n">
         <v>706958.039082319</v>
@@ -12062,7 +12072,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B174" s="2" t="n">
         <v>677085.529173151</v>
@@ -12121,7 +12131,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B175" s="2" t="n">
         <v>776486.60279942</v>
@@ -12180,7 +12190,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B176" s="2" t="n">
         <v>721458.944216182</v>
@@ -12239,7 +12249,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B177" s="2" t="n">
         <v>706597.345022507</v>
@@ -12298,7 +12308,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B178" s="2" t="n">
         <v>671066.046635063</v>
@@ -12357,7 +12367,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B179" s="2" t="n">
         <v>760576.868348004</v>
@@ -12416,7 +12426,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B180" s="2" t="n">
         <v>690879.798251683</v>
@@ -12475,7 +12485,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B181" s="2" t="n">
         <v>686701.470618711</v>
@@ -12534,7 +12544,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B182" s="2" t="n">
         <v>672749.811391699</v>
@@ -12593,7 +12603,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B183" s="2" t="n">
         <v>791235.96554167</v>
@@ -12652,7 +12662,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B184" s="2" t="n">
         <v>718281.265449782</v>
@@ -12711,7 +12721,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B185" s="2" t="n">
         <v>703681.544169008</v>
@@ -12770,7 +12780,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B186" s="2" t="n">
         <v>677652.089115703</v>
@@ -12829,7 +12839,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B187" s="2" t="n">
         <v>760703.280151656</v>
@@ -12888,7 +12898,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B188" s="2" t="n">
         <v>694382.47577623</v>
@@ -12947,7 +12957,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B189" s="2" t="n">
         <v>693173.549347058</v>
@@ -13006,7 +13016,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B190" s="2" t="n">
         <v>681444.766110222</v>
@@ -13065,7 +13075,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B191" s="2" t="n">
         <v>778401.676449317</v>
@@ -13124,7 +13134,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B192" s="2" t="n">
         <v>721120.426852794</v>
@@ -13183,7 +13193,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B193" s="2" t="n">
         <v>724592.921638963</v>
@@ -13242,7 +13252,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B194" s="2" t="n">
         <v>707324.268057214</v>
@@ -13301,7 +13311,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B195" s="2" t="n">
         <v>747428.299954575</v>
@@ -13360,7 +13370,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B196" s="2" t="n">
         <v>696101.583521808</v>
@@ -13419,7 +13429,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B197" s="2" t="n">
         <v>678655.620384454</v>
@@ -13478,7 +13488,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B198" s="2" t="n">
         <v>665848.715299709</v>
@@ -13537,7 +13547,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B199" s="2" t="n">
         <v>751784.460777133</v>
@@ -13596,7 +13606,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B200" s="2" t="n">
         <v>683900.898552578</v>
@@ -13655,7 +13665,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B201" s="2" t="n">
         <v>671361.13972242</v>
@@ -13714,7 +13724,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B202" s="2" t="n">
         <v>632389.35353461</v>
@@ -13773,7 +13783,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B203" s="2" t="n">
         <v>609379.989464801</v>
@@ -13832,7 +13842,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B204" s="2" t="n">
         <v>614192.478404223</v>
@@ -13891,7 +13901,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B205" s="2" t="n">
         <v>642403.32319795</v>
@@ -13950,7 +13960,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B206" s="2" t="n">
         <v>652831.976706322</v>
@@ -14009,7 +14019,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B207" s="2" t="n">
         <v>723516.622490675</v>
@@ -14068,7 +14078,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B208" s="2" t="n">
         <v>686756.467826674</v>
@@ -14127,7 +14137,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B209" s="2" t="n">
         <v>696134.669112115</v>
@@ -14186,7 +14196,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B210" s="2" t="n">
         <v>697625.284666358</v>
@@ -14245,7 +14255,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B211" s="2" t="n">
         <v>782338.628533735</v>
@@ -14304,7 +14314,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B212" s="2" t="n">
         <v>732662.163875501</v>
@@ -14363,7 +14373,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B213" s="2" t="n">
         <v>712740.457828738</v>
@@ -14422,7 +14432,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B214" s="2" t="n">
         <v>703987.504321577</v>
@@ -14481,7 +14491,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B215" s="2" t="n">
         <v>737941.909374072</v>
@@ -14540,7 +14550,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B216" s="2" t="n">
         <v>728638.584568682</v>
@@ -14599,7 +14609,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B217" s="2" t="n">
         <v>700509.934572323</v>
@@ -14658,7 +14668,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B218" s="2" t="n">
         <v>669057.733385167</v>
@@ -14717,7 +14727,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B219" s="2" t="n">
         <v>729947.785274553</v>
@@ -14776,7 +14786,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B220" s="2" t="n">
         <v>714524.365549959</v>
@@ -14835,7 +14845,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B221" s="2" t="n">
         <v>718991.46093658</v>
@@ -14894,7 +14904,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B222" s="2" t="n">
         <v>708113.805670176</v>
@@ -14953,7 +14963,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B223" s="2" t="n">
         <v>776528.776090785</v>
@@ -15012,7 +15022,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B224" s="2" t="n">
         <v>737795.741613431</v>
@@ -15071,7 +15081,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B225" s="2" t="n">
         <v>733788.66978506</v>
@@ -15130,7 +15140,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B226" s="2"/>
       <c r="C226" s="3" t="n">
@@ -15163,7 +15173,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B227" s="2"/>
       <c r="C227" s="3" t="n">
@@ -15196,7 +15206,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B228" s="2"/>
       <c r="C228" s="3" t="n">
@@ -15229,7 +15239,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B229" s="2"/>
       <c r="C229" s="3" t="n">
@@ -15262,7 +15272,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B230" s="2"/>
       <c r="C230" s="3"/>
@@ -15285,7 +15295,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B231" s="2"/>
       <c r="C231" s="3"/>
@@ -15308,7 +15318,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B232" s="2"/>
       <c r="C232" s="3"/>
@@ -15331,7 +15341,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B233" s="2"/>
       <c r="C233" s="3"/>
@@ -15354,7 +15364,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B234" s="2"/>
       <c r="C234" s="3"/>
@@ -15377,7 +15387,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B235" s="2"/>
       <c r="C235" s="3"/>
@@ -15400,7 +15410,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B236" s="2"/>
       <c r="C236" s="3"/>
@@ -15423,7 +15433,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B237" s="2"/>
       <c r="C237" s="3"/>
@@ -15446,7 +15456,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B238" s="2"/>
       <c r="C238" s="3"/>
@@ -15469,7 +15479,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B239" s="2"/>
       <c r="C239" s="3"/>
@@ -15492,7 +15502,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B240" s="2"/>
       <c r="C240" s="3"/>
@@ -15515,7 +15525,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B241" s="2"/>
       <c r="C241" s="3"/>
@@ -15538,7 +15548,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B242" s="2"/>
       <c r="C242" s="3"/>
@@ -15561,7 +15571,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B243" s="2"/>
       <c r="C243" s="3"/>
@@ -15584,7 +15594,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B244" s="2"/>
       <c r="C244" s="3"/>
@@ -15607,7 +15617,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B245" s="2"/>
       <c r="C245" s="3"/>
@@ -15641,97 +15651,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -15755,7 +15765,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -15765,80 +15775,80 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.000421437147776817</v>
+        <v>-0.000167205647467741</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.138775419152784</v>
+        <v>0.140096868939759</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.39200415755766</v>
+        <v>0.391439422807531</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.640616110373754</v>
+        <v>0.639736075454993</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.717944991240825</v>
+        <v>0.718351631330702</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.507527805395759</v>
+        <v>0.509737771049973</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.158390268508302</v>
+        <v>0.160042663783679</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.0423901973361968</v>
+        <v>-0.0424877196871654</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.100590409821635</v>
+        <v>-0.100533429495466</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -116,7 +116,7 @@
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">fleiva</t>
+    <t xml:space="preserve">pcohan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>

--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -116,7 +116,7 @@
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">fleiva</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>

--- a/indicadores/ARG-PIB_out.xlsx
+++ b/indicadores/ARG-PIB_out.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">17/06/2026</t>
+    <t xml:space="preserve">24/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
@@ -1513,9 +1513,7 @@
       <c r="J7" s="1"/>
     </row>
     <row r="8">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
+      <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
@@ -1527,14 +1525,10 @@
       <c r="J8" s="1"/>
     </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
+      <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
-      <c r="D9" t="n">
-        <v>0.718351631330702</v>
-      </c>
+      <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9"/>
@@ -1544,13 +1538,11 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
+      <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
@@ -1559,10 +1551,14 @@
       <c r="J10" s="1"/>
     </row>
     <row r="11">
-      <c r="A11"/>
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
       <c r="B11"/>
       <c r="C11"/>
-      <c r="D11"/>
+      <c r="D11" t="n">
+        <v>0.715931302042003</v>
+      </c>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
@@ -1572,11 +1568,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
-      <c r="D12"/>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12"/>
@@ -1585,14 +1583,10 @@
       <c r="J12" s="1"/>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
+      <c r="A13"/>
       <c r="B13"/>
       <c r="C13"/>
-      <c r="D13" t="n">
-        <v>0.51602906623548</v>
-      </c>
+      <c r="D13"/>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
@@ -1601,7 +1595,9 @@
       <c r="J13" s="1"/>
     </row>
     <row r="14">
-      <c r="A14"/>
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -1614,11 +1610,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
-      <c r="D15"/>
+      <c r="D15" t="n">
+        <v>0.512557629243557</v>
+      </c>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
@@ -1627,9 +1625,7 @@
       <c r="J15" s="1"/>
     </row>
     <row r="16">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
+      <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1642,7 +1638,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1656,13 +1652,11 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
-      <c r="D18" t="n">
-        <v>0.224264939275511</v>
-      </c>
+      <c r="D18"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -1672,7 +1666,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1691,7 +1685,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.0000792883206407128</v>
+        <v>0.155661922178664</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1701,7 +1695,9 @@
       <c r="J20" s="1"/>
     </row>
     <row r="21">
-      <c r="A21"/>
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1713,10 +1709,14 @@
       <c r="J21" s="1"/>
     </row>
     <row r="22">
-      <c r="A22"/>
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
       <c r="B22"/>
       <c r="C22"/>
-      <c r="D22"/>
+      <c r="D22" t="n">
+        <v>0.0000551084383052098</v>
+      </c>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
@@ -1960,7 +1960,7 @@
         <v>285684.43920487</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>282483.955622677</v>
+        <v>282483.955622755</v>
       </c>
       <c r="J2" s="10" t="n">
         <v>282294.983959635</v>
@@ -1984,7 +1984,7 @@
         <v>1.00046103871543</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>1.01179605107736</v>
+        <v>1.01179605107709</v>
       </c>
     </row>
     <row r="3">
@@ -2013,7 +2013,7 @@
         <v>285340.804386349</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>284815.242766627</v>
+        <v>284815.242766705</v>
       </c>
       <c r="J3" s="10" t="n">
         <v>284438.088812099</v>
@@ -2041,7 +2041,7 @@
         <v>0.999308938785785</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>1.00115293568486</v>
+        <v>1.00115293568459</v>
       </c>
     </row>
     <row r="4">
@@ -2070,7 +2070,7 @@
         <v>284470.468347331</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>287148.612532557</v>
+        <v>287148.612532636</v>
       </c>
       <c r="J4" s="10" t="n">
         <v>286598.799498723</v>
@@ -2098,7 +2098,7 @@
         <v>1.00252443782754</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.993174209839202</v>
+        <v>0.993174209838931</v>
       </c>
     </row>
     <row r="5">
@@ -2127,7 +2127,7 @@
         <v>285056.703379466</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>289486.352775985</v>
+        <v>289486.352776063</v>
       </c>
       <c r="J5" s="10" t="n">
         <v>288798.249491725</v>
@@ -2155,7 +2155,7 @@
         <v>0.996881092842427</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>0.981627062077366</v>
+        <v>0.981627062077099</v>
       </c>
     </row>
     <row r="6">
@@ -2184,7 +2184,7 @@
         <v>290673.079365178</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>291829.526342316</v>
+        <v>291829.526342395</v>
       </c>
       <c r="J6" s="10" t="n">
         <v>291050.521247623</v>
@@ -2214,7 +2214,7 @@
         <v>0.9979510621121</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.993996433176583</v>
+        <v>0.993996433176315</v>
       </c>
     </row>
     <row r="7">
@@ -2243,7 +2243,7 @@
         <v>297333.983694748</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>294175.871880217</v>
+        <v>294175.871880295</v>
       </c>
       <c r="J7" s="10" t="n">
         <v>293346.544165409</v>
@@ -2273,7 +2273,7 @@
         <v>1.00495324005029</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>1.01574187026721</v>
+        <v>1.01574187026694</v>
       </c>
     </row>
     <row r="8">
@@ -2302,7 +2302,7 @@
         <v>298338.509036201</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>296522.033027061</v>
+        <v>296522.033027138</v>
       </c>
       <c r="J8" s="10" t="n">
         <v>295672.382579237</v>
@@ -2332,7 +2332,7 @@
         <v>0.999310471405389</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>1.00543218680866</v>
+        <v>1.0054321868084</v>
       </c>
     </row>
     <row r="9">
@@ -2361,7 +2361,7 @@
         <v>296554.107385995</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>298867.547719231</v>
+        <v>298867.547719306</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>298041.401853891</v>
@@ -2391,7 +2391,7 @@
         <v>0.997763136093149</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.990039763315912</v>
+        <v>0.990039763315664</v>
       </c>
     </row>
     <row r="10">
@@ -2420,7 +2420,7 @@
         <v>296207.924142963</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>301212.960620033</v>
+        <v>301212.960620104</v>
       </c>
       <c r="J10" s="10" t="n">
         <v>300479.269421772</v>
@@ -2450,7 +2450,7 @@
         <v>1.00305934664891</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>0.98639223973455</v>
+        <v>0.986392239734317</v>
       </c>
     </row>
     <row r="11">
@@ -2479,7 +2479,7 @@
         <v>299499.92135201</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>303556.955898074</v>
+        <v>303556.95589814</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>303000.899487049</v>
@@ -2509,7 +2509,7 @@
         <v>0.99462528575941</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>0.981332132476933</v>
+        <v>0.98133213247672</v>
       </c>
     </row>
     <row r="12">
@@ -2538,7 +2538,7 @@
         <v>304816.47810658</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>305895.655950868</v>
+        <v>305895.655950926</v>
       </c>
       <c r="J12" s="10" t="n">
         <v>305604.380541096</v>
@@ -2568,7 +2568,7 @@
         <v>1.00526111923555</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.00171463040349</v>
+        <v>1.0017146304033</v>
       </c>
     </row>
     <row r="13">
@@ -2597,7 +2597,7 @@
         <v>307991.10820172</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>308221.641450276</v>
+        <v>308221.641450324</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>308262.24755215</v>
@@ -2627,7 +2627,7 @@
         <v>0.99942684316382</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>0.998679325514624</v>
+        <v>0.998679325514468</v>
       </c>
     </row>
     <row r="14">
@@ -2656,7 +2656,7 @@
         <v>307864.733218995</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>310527.820879405</v>
+        <v>310527.820879439</v>
       </c>
       <c r="J14" s="10" t="n">
         <v>310951.114355457</v>
@@ -2686,7 +2686,7 @@
         <v>0.999547953598189</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>0.990975826908616</v>
+        <v>0.990975826908505</v>
       </c>
     </row>
     <row r="15">
@@ -2715,7 +2715,7 @@
         <v>308739.245868716</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>312806.848308577</v>
+        <v>312806.848308594</v>
       </c>
       <c r="J15" s="10" t="n">
         <v>313645.356453464</v>
@@ -2745,7 +2745,7 @@
         <v>1.00081826239076</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>0.987804062644271</v>
+        <v>0.987804062644216</v>
       </c>
     </row>
     <row r="16">
@@ -2774,7 +2774,7 @@
         <v>314007.629332199</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>315049.62639761</v>
+        <v>315049.626397606</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>316303.221597213</v>
@@ -2804,7 +2804,7 @@
         <v>0.99577591035529</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>0.992482475005879</v>
+        <v>0.992482475005891</v>
       </c>
     </row>
     <row r="17">
@@ -2833,7 +2833,7 @@
         <v>321887.695157495</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>317244.673448367</v>
+        <v>317244.673448337</v>
       </c>
       <c r="J17" s="10" t="n">
         <v>318859.690133388</v>
@@ -2863,7 +2863,7 @@
         <v>1.0043935652066</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.01909332699322</v>
+        <v>1.01909332699331</v>
       </c>
     </row>
     <row r="18">
@@ -2892,7 +2892,7 @@
         <v>327936.667010804</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>319379.027516813</v>
+        <v>319379.027516751</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>321231.632465472</v>
@@ -2922,7 +2922,7 @@
         <v>0.998052480804151</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.02479491719145</v>
+        <v>1.02479491719165</v>
       </c>
     </row>
     <row r="19">
@@ -2951,7 +2951,7 @@
         <v>329514.964258324</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>321443.51244409</v>
+        <v>321443.51244399</v>
       </c>
       <c r="J19" s="10" t="n">
         <v>323358.130194958</v>
@@ -2981,7 +2981,7 @@
         <v>1.00260703748024</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>1.02778251646286</v>
+        <v>1.02778251646317</v>
       </c>
     </row>
     <row r="20">
@@ -3010,7 +3010,7 @@
         <v>330901.555524192</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>323433.901431678</v>
+        <v>323433.901431535</v>
       </c>
       <c r="J20" s="10" t="n">
         <v>325208.596781295</v>
@@ -3040,7 +3040,7 @@
         <v>0.995793882687134</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.01878542510255</v>
+        <v>1.018785425103</v>
       </c>
     </row>
     <row r="21">
@@ -3069,7 +3069,7 @@
         <v>332302.217379835</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>325351.549249606</v>
+        <v>325351.549249411</v>
       </c>
       <c r="J21" s="10" t="n">
         <v>326787.525143558</v>
@@ -3099,7 +3099,7 @@
         <v>1.00357975971416</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.02501979855239</v>
+        <v>1.025019798553</v>
       </c>
     </row>
     <row r="22">
@@ -3128,7 +3128,7 @@
         <v>333294.719506483</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>327201.608069983</v>
+        <v>327201.60806973</v>
       </c>
       <c r="J22" s="10" t="n">
         <v>328120.913940731</v>
@@ -3158,7 +3158,7 @@
         <v>0.997183429393455</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.01575286673139</v>
+        <v>1.01575286673217</v>
       </c>
     </row>
     <row r="23">
@@ -3187,7 +3187,7 @@
         <v>331290.922220052</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>328994.317708807</v>
+        <v>328994.317708488</v>
       </c>
       <c r="J23" s="10" t="n">
         <v>329268.283103432</v>
@@ -3217,7 +3217,7 @@
         <v>1.00348709509507</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>1.01049211878551</v>
+        <v>1.01049211878649</v>
       </c>
     </row>
     <row r="24">
@@ -3246,7 +3246,7 @@
         <v>327970.113392138</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>330743.139459155</v>
+        <v>330743.139458764</v>
       </c>
       <c r="J24" s="10" t="n">
         <v>330310.327849557</v>
@@ -3276,7 +3276,7 @@
         <v>1</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>0.991615771466788</v>
+        <v>0.991615771467963</v>
       </c>
     </row>
     <row r="25">
@@ -3305,7 +3305,7 @@
         <v>326990.187117292</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>332463.692018768</v>
+        <v>332463.692018295</v>
       </c>
       <c r="J25" s="10" t="n">
         <v>331343.632807333</v>
@@ -3335,7 +3335,7 @@
         <v>0.997481089023311</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>0.981059092393403</v>
+        <v>0.981059092394799</v>
       </c>
     </row>
     <row r="26">
@@ -3364,7 +3364,7 @@
         <v>327370.941931502</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>334169.860944093</v>
+        <v>334169.860943532</v>
       </c>
       <c r="J26" s="10" t="n">
         <v>332453.081532702</v>
@@ -3394,7 +3394,7 @@
         <v>1.00536347685521</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>0.984908655352026</v>
+        <v>0.984908655353679</v>
       </c>
     </row>
     <row r="27">
@@ -3423,7 +3423,7 @@
         <v>326147.212558088</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>335871.596064033</v>
+        <v>335871.596063378</v>
       </c>
       <c r="J27" s="10" t="n">
         <v>333697.672057297</v>
@@ -3453,7 +3453,7 @@
         <v>0.996551430987198</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>0.967698594332113</v>
+        <v>0.967698594334003</v>
       </c>
     </row>
     <row r="28">
@@ -3482,7 +3482,7 @@
         <v>326044.54700968</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>337575.695287152</v>
+        <v>337575.695286396</v>
       </c>
       <c r="J28" s="10" t="n">
         <v>335119.770947094</v>
@@ -3512,7 +3512,7 @@
         <v>1.00174562212335</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>0.967527289861047</v>
+        <v>0.967527289863213</v>
       </c>
     </row>
     <row r="29">
@@ -3541,7 +3541,7 @@
         <v>332763.639378441</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>339282.17581909</v>
+        <v>339282.17581823</v>
       </c>
       <c r="J29" s="10" t="n">
         <v>336718.368764721</v>
@@ -3571,7 +3571,7 @@
         <v>0.995551500331859</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>0.976424239320315</v>
+        <v>0.976424239322791</v>
       </c>
     </row>
     <row r="30">
@@ -3600,7 +3600,7 @@
         <v>343187.168381237</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>340984.203616923</v>
+        <v>340984.203615957</v>
       </c>
       <c r="J30" s="10" t="n">
         <v>338449.92570599</v>
@@ -3630,7 +3630,7 @@
         <v>1.00354258138292</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>1.0100260751132</v>
+        <v>1.01002607511607</v>
       </c>
     </row>
     <row r="31">
@@ -3659,7 +3659,7 @@
         <v>352724.681542238</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>342669.945365615</v>
+        <v>342669.945364542</v>
       </c>
       <c r="J31" s="10" t="n">
         <v>340243.726825086</v>
@@ -3689,7 +3689,7 @@
         <v>0.996913237538612</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>1.02616499927027</v>
+        <v>1.02616499927348</v>
       </c>
     </row>
     <row r="32">
@@ -3718,7 +3718,7 @@
         <v>353387.797369463</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>344329.704458402</v>
+        <v>344329.704457227</v>
       </c>
       <c r="J32" s="10" t="n">
         <v>342058.822231937</v>
@@ -3748,7 +3748,7 @@
         <v>1.00599607166605</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>1.0324602592378</v>
+        <v>1.03246025924132</v>
       </c>
     </row>
     <row r="33">
@@ -3777,7 +3777,7 @@
         <v>343392.460694242</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>345959.388012817</v>
+        <v>345959.388011546</v>
       </c>
       <c r="J33" s="10" t="n">
         <v>343911.222923526</v>
@@ -3807,7 +3807,7 @@
         <v>0.999987305577951</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.992567663788028</v>
+        <v>0.992567663791675</v>
       </c>
     </row>
     <row r="34">
@@ -3836,7 +3836,7 @@
         <v>333104.883162749</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>347561.888791059</v>
+        <v>347561.888789703</v>
       </c>
       <c r="J34" s="10" t="n">
         <v>345884.179465318</v>
@@ -3866,7 +3866,7 @@
         <v>0.993702135237003</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.952368612128487</v>
+        <v>0.952368612132201</v>
       </c>
     </row>
     <row r="35">
@@ -3895,7 +3895,7 @@
         <v>332714.377374735</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>349138.492501274</v>
+        <v>349138.49249985</v>
       </c>
       <c r="J35" s="10" t="n">
         <v>348058.326815788</v>
@@ -3925,7 +3925,7 @@
         <v>1.00316322292748</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.955972584776887</v>
+        <v>0.955972584780785</v>
       </c>
     </row>
     <row r="36">
@@ -3954,10 +3954,10 @@
         <v>338498.644473076</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>350680.138067148</v>
+        <v>350680.13806568</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>350439.914204369</v>
+        <v>350439.914204368</v>
       </c>
       <c r="K36" s="11" t="n">
         <v>338566.156924386</v>
@@ -3984,7 +3984,7 @@
         <v>1.00019944674052</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.96545575346944</v>
+        <v>0.965455753473483</v>
       </c>
     </row>
     <row r="37">
@@ -4013,7 +4013,7 @@
         <v>347979.550422056</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>352168.157121505</v>
+        <v>352168.157120022</v>
       </c>
       <c r="J37" s="10" t="n">
         <v>352963.733362019</v>
@@ -4043,7 +4043,7 @@
         <v>0.996142045898126</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.984294162542754</v>
+        <v>0.9842941625469</v>
       </c>
     </row>
     <row r="38">
@@ -4072,7 +4072,7 @@
         <v>358541.643456487</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>353576.310058956</v>
+        <v>353576.310057495</v>
       </c>
       <c r="J38" s="10" t="n">
         <v>355505.207233301</v>
@@ -4102,7 +4102,7 @@
         <v>1.00443293072789</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>1.01853835644403</v>
+        <v>1.01853835644824</v>
       </c>
     </row>
     <row r="39">
@@ -4131,7 +4131,7 @@
         <v>362366.703625266</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>354874.900339214</v>
+        <v>354874.900337821</v>
       </c>
       <c r="J39" s="10" t="n">
         <v>357908.125402406</v>
@@ -4161,7 +4161,7 @@
         <v>1.00151625597356</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>1.02265937646578</v>
+        <v>1.0226593764698</v>
       </c>
     </row>
     <row r="40">
@@ -4190,7 +4190,7 @@
         <v>362245.570448144</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>356038.328124284</v>
+        <v>356038.328123016</v>
       </c>
       <c r="J40" s="10" t="n">
         <v>360039.406585983</v>
@@ -4220,7 +4220,7 @@
         <v>0.998134267168734</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>1.01553593653592</v>
+        <v>1.01553593653954</v>
       </c>
     </row>
     <row r="41">
@@ -4249,7 +4249,7 @@
         <v>364723.397409161</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>357046.019353651</v>
+        <v>357046.019352575</v>
       </c>
       <c r="J41" s="10" t="n">
         <v>361791.00959519</v>
@@ -4279,7 +4279,7 @@
         <v>1.00322284927594</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>1.0247946374218</v>
+        <v>1.02479463742488</v>
       </c>
     </row>
     <row r="42">
@@ -4308,7 +4308,7 @@
         <v>368497.713638057</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>357880.857084841</v>
+        <v>357880.857084034</v>
       </c>
       <c r="J42" s="10" t="n">
         <v>363062.54479323</v>
@@ -4338,7 +4338,7 @@
         <v>0.999748465691122</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>1.02940690044508</v>
+        <v>1.0294069004474</v>
       </c>
     </row>
     <row r="43">
@@ -4367,7 +4367,7 @@
         <v>375399.56719607</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>358531.257392002</v>
+        <v>358531.257391555</v>
       </c>
       <c r="J43" s="10" t="n">
         <v>363774.161725059</v>
@@ -4397,7 +4397,7 @@
         <v>0.994527370073768</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.04131825773322</v>
+        <v>1.04131825773451</v>
       </c>
     </row>
     <row r="44">
@@ -4426,10 +4426,10 @@
         <v>382089.935726599</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>358992.213953491</v>
+        <v>358992.213953508</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>363872.722330769</v>
+        <v>363872.72233077</v>
       </c>
       <c r="K44" s="11" t="n">
         <v>384777.026136385</v>
@@ -4456,7 +4456,7 @@
         <v>1.00703261237351</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>1.07182554713076</v>
+        <v>1.07182554713072</v>
       </c>
     </row>
     <row r="45">
@@ -4485,7 +4485,7 @@
         <v>378915.098444103</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>359267.979126978</v>
+        <v>359267.979127573</v>
       </c>
       <c r="J45" s="10" t="n">
         <v>363352.943463281</v>
@@ -4515,7 +4515,7 @@
         <v>0.999641361114807</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>1.05430827895113</v>
+        <v>1.05430827894938</v>
       </c>
     </row>
     <row r="46">
@@ -4544,10 +4544,10 @@
         <v>370046.929067076</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>359378.920777746</v>
+        <v>359378.920779048</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>362314.063494539</v>
+        <v>362314.06349454</v>
       </c>
       <c r="K46" s="11" t="n">
         <v>368025.827792736</v>
@@ -4574,7 +4574,7 @@
         <v>0.994538256865323</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.02406069614845</v>
+        <v>1.02406069614474</v>
       </c>
     </row>
     <row r="47">
@@ -4603,7 +4603,7 @@
         <v>360467.602791213</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>359357.601287096</v>
+        <v>359357.601289245</v>
       </c>
       <c r="J47" s="10" t="n">
         <v>360932.452102955</v>
@@ -4633,7 +4633,7 @@
         <v>1.00796936386056</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>1.01108282940569</v>
+        <v>1.01108282939964</v>
       </c>
     </row>
     <row r="48">
@@ -4662,7 +4662,7 @@
         <v>350284.101753595</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>359241.987353213</v>
+        <v>359241.987356362</v>
       </c>
       <c r="J48" s="10" t="n">
         <v>359413.037788426</v>
@@ -4692,7 +4692,7 @@
         <v>0.993537962472264</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>0.968763577183183</v>
+        <v>0.96876357717469</v>
       </c>
     </row>
     <row r="49">
@@ -4721,7 +4721,7 @@
         <v>344341.392450618</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>359072.534861151</v>
+        <v>359072.534865464</v>
       </c>
       <c r="J49" s="10" t="n">
         <v>357972.788291728</v>
@@ -4751,7 +4751,7 @@
         <v>1.00042552866671</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>0.959382537340125</v>
+        <v>0.959382537328603</v>
       </c>
     </row>
     <row r="50">
@@ -4780,7 +4780,7 @@
         <v>343038.137188109</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>358882.686299335</v>
+        <v>358882.686304982</v>
       </c>
       <c r="J50" s="10" t="n">
         <v>356771.708928405</v>
@@ -4810,7 +4810,7 @@
         <v>1.00496537941978</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.960596498119059</v>
+        <v>0.960596498103945</v>
       </c>
     </row>
     <row r="51">
@@ -4839,7 +4839,7 @@
         <v>342533.362705206</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>358696.768771639</v>
+        <v>358696.768778797</v>
       </c>
       <c r="J51" s="10" t="n">
         <v>355902.380670466</v>
@@ -4869,7 +4869,7 @@
         <v>1</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.954938523361153</v>
+        <v>0.954938523342098</v>
       </c>
     </row>
     <row r="52">
@@ -4898,7 +4898,7 @@
         <v>345738.843049346</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>358530.27111031</v>
+        <v>358530.271119158</v>
       </c>
       <c r="J52" s="10" t="n">
         <v>355397.233203749</v>
@@ -4928,7 +4928,7 @@
         <v>1.00137704659263</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.965650516685622</v>
+        <v>0.965650516661791</v>
       </c>
     </row>
     <row r="53">
@@ -4957,7 +4957,7 @@
         <v>352241.305163862</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>358388.580018804</v>
+        <v>358388.580029518</v>
       </c>
       <c r="J53" s="10" t="n">
         <v>355221.851124268</v>
@@ -4987,7 +4987,7 @@
         <v>0.999366239739379</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>0.982224569220454</v>
+        <v>0.982224569191089</v>
       </c>
     </row>
     <row r="54">
@@ -5016,7 +5016,7 @@
         <v>356720.359659079</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>358269.385119598</v>
+        <v>358269.385132348</v>
       </c>
       <c r="J54" s="10" t="n">
         <v>355295.907569743</v>
@@ -5046,7 +5046,7 @@
         <v>1.00233064329099</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.997996933097483</v>
+        <v>0.997996933061967</v>
       </c>
     </row>
     <row r="55">
@@ -5075,10 +5075,10 @@
         <v>360288.803230216</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>358166.394465547</v>
+        <v>358166.394480486</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>355523.056765384</v>
+        <v>355523.056765383</v>
       </c>
       <c r="K55" s="11" t="n">
         <v>358762.708721785</v>
@@ -5105,7 +5105,7 @@
         <v>0.995764246641171</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>1.00166490844885</v>
+        <v>1.00166490840707</v>
       </c>
     </row>
     <row r="56">
@@ -5134,10 +5134,10 @@
         <v>360482.886469362</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>358072.867586038</v>
+        <v>358072.867603298</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>355818.232136414</v>
+        <v>355818.232136413</v>
       </c>
       <c r="K56" s="11" t="n">
         <v>362920.393976602</v>
@@ -5164,7 +5164,7 @@
         <v>1.00676178425865</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>1.01353782101181</v>
+        <v>1.01353782096295</v>
       </c>
     </row>
     <row r="57">
@@ -5193,10 +5193,10 @@
         <v>358110.320672532</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>357982.436706869</v>
+        <v>357982.43672655</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>356112.565367838</v>
+        <v>356112.565367837</v>
       </c>
       <c r="K57" s="11" t="n">
         <v>356510.291460031</v>
@@ -5223,7 +5223,7 @@
         <v>0.99553202150249</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>0.99588766068978</v>
+        <v>0.995887660635028</v>
       </c>
     </row>
     <row r="58">
@@ -5252,7 +5252,7 @@
         <v>360331.469236293</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>357891.763757831</v>
+        <v>357891.76377999</v>
       </c>
       <c r="J58" s="10" t="n">
         <v>356372.698953861</v>
@@ -5282,7 +5282,7 @@
         <v>0.996899940129559</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.0036956881509</v>
+        <v>1.00369568808876</v>
       </c>
     </row>
     <row r="59">
@@ -5311,7 +5311,7 @@
         <v>366903.325694328</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>357796.590577938</v>
+        <v>357796.590602576</v>
       </c>
       <c r="J59" s="10" t="n">
         <v>356567.26401915</v>
@@ -5341,7 +5341,7 @@
         <v>1.00550717037844</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.03109960948882</v>
+        <v>1.03109960941781</v>
       </c>
     </row>
     <row r="60">
@@ -5370,10 +5370,10 @@
         <v>370115.454503361</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>357693.48566642</v>
+        <v>357693.485693472</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>356679.100294146</v>
+        <v>356679.100294145</v>
       </c>
       <c r="K60" s="11" t="n">
         <v>368316.805233327</v>
@@ -5400,7 +5400,7 @@
         <v>0.995140302172879</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.02969950528206</v>
+        <v>1.02969950520418</v>
       </c>
     </row>
     <row r="61">
@@ -5429,10 +5429,10 @@
         <v>365416.806395414</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>357585.972106412</v>
+        <v>357585.972135725</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>356752.830813297</v>
+        <v>356752.830813296</v>
       </c>
       <c r="K61" s="11" t="n">
         <v>368231.377306891</v>
@@ -5459,7 +5459,7 @@
         <v>1.00654752764113</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>1.02859007826618</v>
+        <v>1.02859007818186</v>
       </c>
     </row>
     <row r="62">
@@ -5488,7 +5488,7 @@
         <v>353257.410748033</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>357484.212555776</v>
+        <v>357484.212587099</v>
       </c>
       <c r="J62" s="10" t="n">
         <v>356891.26713575</v>
@@ -5518,7 +5518,7 @@
         <v>0.997695543902323</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.985899047216793</v>
+        <v>0.985899047130408</v>
       </c>
     </row>
     <row r="63">
@@ -5547,10 +5547,10 @@
         <v>337044.713219182</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>357404.759304207</v>
+        <v>357404.759337167</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>357252.503581766</v>
+        <v>357252.503581765</v>
       </c>
       <c r="K63" s="11" t="n">
         <v>338171.190723661</v>
@@ -5577,7 +5577,7 @@
         <v>1.00334221977173</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>0.946185471570135</v>
+        <v>0.946185471482875</v>
       </c>
     </row>
     <row r="64">
@@ -5606,10 +5606,10 @@
         <v>332593.296431408</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>357361.014098896</v>
+        <v>357361.014132984</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>357972.394858692</v>
+        <v>357972.394858691</v>
       </c>
       <c r="K64" s="11" t="n">
         <v>328979.870909493</v>
@@ -5636,7 +5636,7 @@
         <v>0.989135603270764</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.920581311140031</v>
+        <v>0.920581311052218</v>
       </c>
     </row>
     <row r="65">
@@ -5665,7 +5665,7 @@
         <v>342073.449961899</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>357354.357706674</v>
+        <v>357354.35774122</v>
       </c>
       <c r="J65" s="10" t="n">
         <v>359091.389109587</v>
@@ -5695,7 +5695,7 @@
         <v>1.00685268504747</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>0.963798437461052</v>
+        <v>0.963798437367882</v>
       </c>
     </row>
     <row r="66">
@@ -5724,10 +5724,10 @@
         <v>354399.556297719</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>357368.432679878</v>
+        <v>357368.432714029</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>360504.971857765</v>
+        <v>360504.971857764</v>
       </c>
       <c r="K66" s="11" t="n">
         <v>354821.064943417</v>
@@ -5754,7 +5754,7 @@
         <v>1.00118935997014</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.992871872545209</v>
+        <v>0.992871872450326</v>
       </c>
     </row>
     <row r="67">
@@ -5783,7 +5783,7 @@
         <v>364796.360074642</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>357378.796079512</v>
+        <v>357378.796112216</v>
       </c>
       <c r="J67" s="10" t="n">
         <v>362035.259538877</v>
@@ -5813,7 +5813,7 @@
         <v>0.993573036357098</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>1.01419510924408</v>
+        <v>1.01419510915127</v>
       </c>
     </row>
     <row r="68">
@@ -5842,10 +5842,10 @@
         <v>372019.460486237</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>357359.412861748</v>
+        <v>357359.412891727</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>363475.949054005</v>
+        <v>363475.949054006</v>
       </c>
       <c r="K68" s="11" t="n">
         <v>375311.880583483</v>
@@ -5872,7 +5872,7 @@
         <v>1.00885012868129</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>1.05023644844828</v>
+        <v>1.05023644836017</v>
       </c>
     </row>
     <row r="69">
@@ -5901,10 +5901,10 @@
         <v>369996.847424842</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>357287.418627163</v>
+        <v>357287.418652895</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>364622.820142193</v>
+        <v>364622.820142194</v>
       </c>
       <c r="K69" s="11" t="n">
         <v>369472.941943006</v>
@@ -5931,7 +5931,7 @@
         <v>0.998584027173522</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>1.03410566026272</v>
+        <v>1.03410566018824</v>
       </c>
     </row>
     <row r="70">
@@ -5960,10 +5960,10 @@
         <v>368433.755783655</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>357151.169268662</v>
+        <v>357151.169288362</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>365330.832200131</v>
+        <v>365330.832200133</v>
       </c>
       <c r="K70" s="11" t="n">
         <v>365846.353939529</v>
@@ -5990,7 +5990,7 @@
         <v>0.992977294280155</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>1.02434595045194</v>
+        <v>1.02434595039544</v>
       </c>
     </row>
     <row r="71">
@@ -6019,10 +6019,10 @@
         <v>377461.405183315</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>356946.63663122</v>
+        <v>356946.636642824</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>365479.195233515</v>
+        <v>365479.195233517</v>
       </c>
       <c r="K71" s="11" t="n">
         <v>378208.365597628</v>
@@ -6049,7 +6049,7 @@
         <v>1.00197890540346</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.05956556746709</v>
+        <v>1.05956556743264</v>
       </c>
     </row>
     <row r="72">
@@ -6078,10 +6078,10 @@
         <v>381959.884844545</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>356675.227050234</v>
+        <v>356675.227051387</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>364949.696856735</v>
+        <v>364949.696856739</v>
       </c>
       <c r="K72" s="11" t="n">
         <v>385097.277017122</v>
@@ -6108,7 +6108,7 @@
         <v>1.00821393108822</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.0796860780098</v>
+        <v>1.07968607800631</v>
       </c>
     </row>
     <row r="73">
@@ -6137,10 +6137,10 @@
         <v>379478.493938744</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>356351.635441703</v>
+        <v>356351.63542975</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>363687.770536005</v>
+        <v>363687.77053601</v>
       </c>
       <c r="K73" s="11" t="n">
         <v>370679.133906637</v>
@@ -6167,7 +6167,7 @@
         <v>0.987289442631454</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>1.05136352273792</v>
+        <v>1.05136352277318</v>
       </c>
     </row>
     <row r="74">
@@ -6196,10 +6196,10 @@
         <v>377691.66064559</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>356008.320502856</v>
+        <v>356008.320474843</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>361739.587638339</v>
+        <v>361739.587638346</v>
       </c>
       <c r="K74" s="11" t="n">
         <v>380028.85074581</v>
@@ -6226,7 +6226,7 @@
         <v>1.00618809029626</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.06747182259399</v>
+        <v>1.06747182267799</v>
       </c>
     </row>
     <row r="75">
@@ -6255,10 +6255,10 @@
         <v>372086.14075127</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>355689.180603004</v>
+        <v>355689.180555685</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>359206.156231929</v>
+        <v>359206.156231937</v>
       </c>
       <c r="K75" s="11" t="n">
         <v>373012.106097125</v>
@@ -6285,7 +6285,7 @@
         <v>1.00248857789754</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.04870242458529</v>
+        <v>1.0487024247248</v>
       </c>
     </row>
     <row r="76">
@@ -6314,10 +6314,10 @@
         <v>361519.532084026</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>355453.126942857</v>
+        <v>355453.126872713</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>356279.930700503</v>
+        <v>356279.930700512</v>
       </c>
       <c r="K76" s="11" t="n">
         <v>359505.457165796</v>
@@ -6344,7 +6344,7 @@
         <v>0.994428862787525</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.01140046300279</v>
+        <v>1.01140046320238</v>
       </c>
     </row>
     <row r="77">
@@ -6373,10 +6373,10 @@
         <v>358299.904962271</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>355369.897551563</v>
+        <v>355369.897454828</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>353222.395177116</v>
+        <v>353222.395177127</v>
       </c>
       <c r="K77" s="11" t="n">
         <v>357451.083452559</v>
@@ -6403,7 +6403,7 @@
         <v>0.997630974784095</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>1.00585639333927</v>
+        <v>1.00585639361307</v>
       </c>
     </row>
     <row r="78">
@@ -6432,10 +6432,10 @@
         <v>354000.663396406</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>355511.763164654</v>
+        <v>355511.763037363</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>350311.161427149</v>
+        <v>350311.161427161</v>
       </c>
       <c r="K78" s="11" t="n">
         <v>365527.148096089</v>
@@ -6462,7 +6462,7 @@
         <v>1.00891203463004</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>1.00462366248691</v>
+        <v>1.00462366284661</v>
       </c>
     </row>
     <row r="79">
@@ -6491,10 +6491,10 @@
         <v>339078.88804116</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>355952.295258856</v>
+        <v>355952.295096902</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>347844.984657361</v>
+        <v>347844.984657374</v>
       </c>
       <c r="K79" s="11" t="n">
         <v>338188.610243677</v>
@@ -6521,7 +6521,7 @@
         <v>0.99737442279988</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>0.950095321053455</v>
+        <v>0.950095321485738</v>
       </c>
     </row>
     <row r="80">
@@ -6550,10 +6550,10 @@
         <v>327611.800456159</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>356766.092664893</v>
+        <v>356766.092464108</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>346156.841915214</v>
+        <v>346156.841915226</v>
       </c>
       <c r="K80" s="11" t="n">
         <v>324654.814132488</v>
@@ -6580,7 +6580,7 @@
         <v>0.990974115341529</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>0.909993468570549</v>
+        <v>0.909993469082685</v>
       </c>
     </row>
     <row r="81">
@@ -6609,10 +6609,10 @@
         <v>326146.061960052</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>358016.651910355</v>
+        <v>358016.651666612</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>345531.428376099</v>
+        <v>345531.428376109</v>
       </c>
       <c r="K81" s="11" t="n">
         <v>338630.833598453</v>
@@ -6639,7 +6639,7 @@
         <v>1.00770166791766</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>0.917996212936523</v>
+        <v>0.917996213561508</v>
       </c>
     </row>
     <row r="82">
@@ -6668,10 +6668,10 @@
         <v>325272.179419449</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>359747.399973752</v>
+        <v>359747.399683088</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>346145.929076495</v>
+        <v>346145.929076502</v>
       </c>
       <c r="K82" s="11" t="n">
         <v>324622.055794528</v>
@@ -6698,7 +6698,7 @@
         <v>0.998001293482641</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>0.902361089526187</v>
+        <v>0.902361090255264</v>
       </c>
     </row>
     <row r="83">
@@ -6727,10 +6727,10 @@
         <v>328709.244678886</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>361983.414632784</v>
+        <v>361983.414291558</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>348093.161564111</v>
+        <v>348093.161564113</v>
       </c>
       <c r="K83" s="11" t="n">
         <v>326509.110206825</v>
@@ -6757,7 +6757,7 @@
         <v>0.993306745983946</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>0.902000193953785</v>
+        <v>0.902000194804063</v>
       </c>
     </row>
     <row r="84">
@@ -6786,10 +6786,10 @@
         <v>340224.194523046</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>364727.820325043</v>
+        <v>364727.819930109</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>351358.324020244</v>
+        <v>351358.324020238</v>
       </c>
       <c r="K84" s="11" t="n">
         <v>342224.446725735</v>
@@ -6816,7 +6816,7 @@
         <v>1.00587921798299</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>0.938300912775851</v>
+        <v>0.938300913791861</v>
       </c>
     </row>
     <row r="85">
@@ -6845,10 +6845,10 @@
         <v>348079.280310373</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>367961.570047853</v>
+        <v>367961.56959678</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>355818.694369407</v>
+        <v>355818.69436939</v>
       </c>
       <c r="K85" s="11" t="n">
         <v>349010.307845754</v>
@@ -6875,7 +6875,7 @@
         <v>1.00267475712588</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>0.948496626428586</v>
+        <v>0.948496627591319</v>
       </c>
     </row>
     <row r="86">
@@ -6904,10 +6904,10 @@
         <v>353836.163763914</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>371651.552190039</v>
+        <v>371651.551681356</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>361305.881149638</v>
+        <v>361305.881149607</v>
       </c>
       <c r="K86" s="11" t="n">
         <v>351350.466059895</v>
@@ -6934,7 +6934,7 @@
         <v>0.992975003805214</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>0.945376022216199</v>
+        <v>0.945376023510142</v>
       </c>
     </row>
     <row r="87">
@@ -6963,10 +6963,10 @@
         <v>364755.318896553</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>375752.810601548</v>
+        <v>375752.810035026</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>367617.450966359</v>
+        <v>367617.450966309</v>
       </c>
       <c r="K87" s="11" t="n">
         <v>366408.402200179</v>
@@ -6993,7 +6993,7 @@
         <v>1.00453203344266</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>0.975131500982229</v>
+        <v>0.975131502452432</v>
       </c>
     </row>
     <row r="88">
@@ -7022,10 +7022,10 @@
         <v>378303.712625868</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>380207.700953498</v>
+        <v>380207.700330468</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>374501.193349542</v>
+        <v>374501.193349469</v>
       </c>
       <c r="K88" s="11" t="n">
         <v>377494.761701028</v>
@@ -7052,7 +7052,7 @@
         <v>0.997861636304797</v>
       </c>
       <c r="S88" s="19" t="n">
-        <v>0.992864586262546</v>
+        <v>0.99286458788951</v>
       </c>
     </row>
     <row r="89">
@@ -7081,10 +7081,10 @@
         <v>389765.083737746</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>384952.738661756</v>
+        <v>384952.737985461</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>381698.852585328</v>
+        <v>381698.852585228</v>
       </c>
       <c r="K89" s="11" t="n">
         <v>390433.610227195</v>
@@ -7111,7 +7111,7 @@
         <v>1.00171520363763</v>
       </c>
       <c r="S89" s="19" t="n">
-        <v>1.01423777782305</v>
+        <v>1.01423777960489</v>
       </c>
     </row>
     <row r="90">
@@ -7140,10 +7140,10 @@
         <v>401055.607921127</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>389922.743555154</v>
+        <v>389922.742831142</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>388967.140801616</v>
+        <v>388967.140801485</v>
       </c>
       <c r="K90" s="11" t="n">
         <v>400031.872276562</v>
@@ -7170,7 +7170,7 @@
         <v>0.997447397257774</v>
       </c>
       <c r="S90" s="19" t="n">
-        <v>1.02592597864192</v>
+        <v>1.02592598054687</v>
       </c>
     </row>
     <row r="91">
@@ -7199,10 +7199,10 @@
         <v>409029.445827794</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>395055.961007255</v>
+        <v>395055.960243798</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>396106.443914514</v>
+        <v>396106.443914349</v>
       </c>
       <c r="K91" s="11" t="n">
         <v>410201.166441417</v>
@@ -7229,7 +7229,7 @@
         <v>1.00286463633749</v>
       </c>
       <c r="S91" s="19" t="n">
-        <v>1.03833686092357</v>
+        <v>1.03833686293018</v>
       </c>
     </row>
     <row r="92">
@@ -7258,10 +7258,10 @@
         <v>410309.333992197</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>400296.954597071</v>
+        <v>400296.953805621</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>402972.471497505</v>
+        <v>402972.471497305</v>
       </c>
       <c r="K92" s="11" t="n">
         <v>410910.806821399</v>
@@ -7288,7 +7288,7 @@
         <v>1.00146590091761</v>
       </c>
       <c r="S92" s="19" t="n">
-        <v>1.02651494622289</v>
+        <v>1.02651494825247</v>
       </c>
     </row>
     <row r="93">
@@ -7317,10 +7317,10 @@
         <v>409913.621396463</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>405599.753657012</v>
+        <v>405599.752852675</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>409491.406736707</v>
+        <v>409491.406736472</v>
       </c>
       <c r="K93" s="11" t="n">
         <v>408087.826349299</v>
@@ -7347,7 +7347,7 @@
         <v>0.99554590296135</v>
       </c>
       <c r="S93" s="19" t="n">
-        <v>1.00613430523528</v>
+        <v>1.00613430723053</v>
       </c>
     </row>
     <row r="94">
@@ -7376,10 +7376,10 @@
         <v>415049.750870997</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>410925.021177127</v>
+        <v>410925.020379159</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>415629.124494856</v>
+        <v>415629.12449459</v>
       </c>
       <c r="K94" s="11" t="n">
         <v>415850.74506037</v>
@@ -7406,7 +7406,7 @@
         <v>1.00192987512387</v>
       </c>
       <c r="S94" s="19" t="n">
-        <v>1.0119869164188</v>
+        <v>1.01198691838396</v>
       </c>
     </row>
     <row r="95">
@@ -7435,10 +7435,10 @@
         <v>423625.21344142</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>416234.975192897</v>
+        <v>416234.974425209</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>421344.481732751</v>
+        <v>421344.481732464</v>
       </c>
       <c r="K95" s="11" t="n">
         <v>423452.493299921</v>
@@ -7465,7 +7465,7 @@
         <v>0.999592280780231</v>
       </c>
       <c r="S95" s="19" t="n">
-        <v>1.01734000873828</v>
+        <v>1.01734001061463</v>
       </c>
     </row>
     <row r="96">
@@ -7494,10 +7494,10 @@
         <v>430592.388294132</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>421494.912317232</v>
+        <v>421494.911608885</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>426597.443514021</v>
+        <v>426597.443513727</v>
       </c>
       <c r="K96" s="11" t="n">
         <v>431054.779420915</v>
@@ -7524,7 +7524,7 @@
         <v>1.00107384881701</v>
       </c>
       <c r="S96" s="19" t="n">
-        <v>1.0226808600159</v>
+        <v>1.02268086173458</v>
       </c>
     </row>
     <row r="97">
@@ -7553,10 +7553,10 @@
         <v>436858.365102814</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>426674.640111858</v>
+        <v>426674.639497544</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>431358.514960128</v>
+        <v>431358.514959849</v>
       </c>
       <c r="K97" s="11" t="n">
         <v>436467.027944467</v>
@@ -7583,7 +7583,7 @@
         <v>0.999104201293582</v>
       </c>
       <c r="S97" s="19" t="n">
-        <v>1.02295048008956</v>
+        <v>1.02295048156238</v>
       </c>
     </row>
     <row r="98">
@@ -7612,10 +7612,10 @@
         <v>444117.892457186</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>431749.941055439</v>
+        <v>431749.940575927</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>435620.487872071</v>
+        <v>435620.487871838</v>
       </c>
       <c r="K98" s="11" t="n">
         <v>443795.99016597</v>
@@ -7642,7 +7642,7 @@
         <v>0.999275187294447</v>
       </c>
       <c r="S98" s="19" t="n">
-        <v>1.02790052288388</v>
+        <v>1.02790052402549</v>
       </c>
     </row>
     <row r="99">
@@ -7671,10 +7671,10 @@
         <v>450989.582453002</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>436702.717869038</v>
+        <v>436702.717571551</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>439401.696615768</v>
+        <v>439401.696615621</v>
       </c>
       <c r="K99" s="11" t="n">
         <v>451818.777986187</v>
@@ -7701,7 +7701,7 @@
         <v>1.00183861349674</v>
       </c>
       <c r="S99" s="19" t="n">
-        <v>1.03461407382787</v>
+        <v>1.03461407453266</v>
       </c>
     </row>
     <row r="100">
@@ -7730,10 +7730,10 @@
         <v>456279.911013051</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>441522.40205441</v>
+        <v>441522.40199293</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>442761.353068608</v>
+        <v>442761.3530686</v>
       </c>
       <c r="K100" s="11" t="n">
         <v>451476.953294478</v>
@@ -7760,7 +7760,7 @@
         <v>0.997401110119194</v>
       </c>
       <c r="S100" s="19" t="n">
-        <v>1.03073838983468</v>
+        <v>1.03073838997821</v>
       </c>
     </row>
     <row r="101">
@@ -7789,10 +7789,10 @@
         <v>457513.638957149</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>446207.872650883</v>
+        <v>446207.872886336</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>445820.754514833</v>
+        <v>445820.754515028</v>
       </c>
       <c r="K101" s="11" t="n">
         <v>458811.120946735</v>
@@ -7819,7 +7819,7 @@
         <v>1.00283594166186</v>
       </c>
       <c r="S101" s="19" t="n">
-        <v>1.02824523964801</v>
+        <v>1.02824523910543</v>
       </c>
     </row>
     <row r="102">
@@ -7848,10 +7848,10 @@
         <v>449809.913939866</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>450766.491002606</v>
+        <v>450766.491602901</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>448762.861922188</v>
+        <v>448762.861922662</v>
       </c>
       <c r="K102" s="11" t="n">
         <v>451435.755328579</v>
@@ -7878,7 +7878,7 @@
         <v>1.00277742148344</v>
       </c>
       <c r="S102" s="19" t="n">
-        <v>1.00064941529937</v>
+        <v>1.00064941396678</v>
       </c>
     </row>
     <row r="103">
@@ -7907,10 +7907,10 @@
         <v>437134.935307832</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>455213.495483916</v>
+        <v>455213.496523796</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>451835.588090578</v>
+        <v>451835.588091418</v>
       </c>
       <c r="K103" s="11" t="n">
         <v>435460.48737933</v>
@@ -7937,7 +7937,7 @@
         <v>0.996492461639749</v>
       </c>
       <c r="S103" s="19" t="n">
-        <v>0.956917297213621</v>
+        <v>0.95691729502766</v>
       </c>
     </row>
     <row r="104">
@@ -7966,10 +7966,10 @@
         <v>431217.531936571</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>459564.307428307</v>
+        <v>459564.308988976</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>455298.327638588</v>
+        <v>455298.32763989</v>
       </c>
       <c r="K104" s="11" t="n">
         <v>431360.130054406</v>
@@ -7996,7 +7996,7 @@
         <v>1.00033068719909</v>
       </c>
       <c r="S104" s="19" t="n">
-        <v>0.938628442378978</v>
+        <v>0.93862843919142</v>
       </c>
     </row>
     <row r="105">
@@ -8025,10 +8025,10 @@
         <v>436762.485230905</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>463822.090776944</v>
+        <v>463822.092945413</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>459329.305583119</v>
+        <v>459329.305584985</v>
       </c>
       <c r="K105" s="11" t="n">
         <v>435799.091109637</v>
@@ -8055,7 +8055,7 @@
         <v>0.997794237935158</v>
       </c>
       <c r="S105" s="19" t="n">
-        <v>0.939582438558789</v>
+        <v>0.939582434166035</v>
       </c>
     </row>
     <row r="106">
@@ -8084,10 +8084,10 @@
         <v>447666.430741407</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>467972.38186013</v>
+        <v>467972.384728248</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>463987.055953151</v>
+        <v>463987.055955679</v>
       </c>
       <c r="K106" s="11" t="n">
         <v>448988.703096293</v>
@@ -8114,7 +8114,7 @@
         <v>1.00295370004111</v>
       </c>
       <c r="S106" s="19" t="n">
-        <v>0.959434189922962</v>
+        <v>0.959434184042764</v>
       </c>
     </row>
     <row r="107">
@@ -8143,10 +8143,10 @@
         <v>458155.610156058</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>471983.202633378</v>
+        <v>471983.206296471</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>469212.461705296</v>
+        <v>469212.461708575</v>
       </c>
       <c r="K107" s="11" t="n">
         <v>457790.588486101</v>
@@ -8173,7 +8173,7 @@
         <v>0.999203280147913</v>
       </c>
       <c r="S107" s="19" t="n">
-        <v>0.969929832104001</v>
+        <v>0.969929824576313</v>
       </c>
     </row>
     <row r="108">
@@ -8193,7 +8193,7 @@
         <v>472677.535758481</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>5603.07584114952</v>
+        <v>5603.07584114949</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>1</v>
@@ -8202,10 +8202,10 @@
         <v>467135.994843473</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>475810.710252975</v>
+        <v>475810.714808054</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>474871.414031884</v>
+        <v>474871.414035975</v>
       </c>
       <c r="K108" s="11" t="n">
         <v>467074.459917332</v>
@@ -8220,19 +8220,19 @@
         <v>467074.459917332</v>
       </c>
       <c r="O108" s="15" t="n">
-        <v>0.0200768388641884</v>
+        <v>0.0200768388641886</v>
       </c>
       <c r="P108" s="16" t="n">
-        <v>0.0827946937479387</v>
+        <v>0.0827946937479389</v>
       </c>
       <c r="Q108" s="17" t="n">
-        <v>0.0202797341507861</v>
+        <v>0.0202797341507863</v>
       </c>
       <c r="R108" s="18" t="n">
-        <v>0.999868271923335</v>
+        <v>0.999868271923336</v>
       </c>
       <c r="S108" s="19" t="n">
-        <v>0.981639231426718</v>
+        <v>0.981639222029191</v>
       </c>
     </row>
     <row r="109">
@@ -8252,7 +8252,7 @@
         <v>481427.468387569</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>4688.6858644417</v>
+        <v>4688.68586444163</v>
       </c>
       <c r="G109" s="7" t="n">
         <v>1</v>
@@ -8261,10 +8261,10 @@
         <v>476668.53884325</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>479402.191491363</v>
+        <v>479402.197034839</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>480772.694759145</v>
+        <v>480772.694764073</v>
       </c>
       <c r="K109" s="11" t="n">
         <v>476738.782523127</v>
@@ -8282,7 +8282,7 @@
         <v>0.0204800271119239</v>
       </c>
       <c r="P109" s="16" t="n">
-        <v>0.0939416631394283</v>
+        <v>0.0939416631394285</v>
       </c>
       <c r="Q109" s="17" t="n">
         <v>0.0206911818888709</v>
@@ -8291,7 +8291,7 @@
         <v>1.00014736378459</v>
       </c>
       <c r="S109" s="19" t="n">
-        <v>0.994444312071352</v>
+        <v>0.994444300572285</v>
       </c>
     </row>
     <row r="110">
@@ -8311,7 +8311,7 @@
         <v>462258.015087104</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>-23585.9592601683</v>
+        <v>-23585.959260168</v>
       </c>
       <c r="G110" s="7" t="n">
         <v>1</v>
@@ -8320,10 +8320,10 @@
         <v>485545.679474004</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>482699.472964526</v>
+        <v>482699.47958936</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>486686.10094274</v>
+        <v>486686.100948467</v>
       </c>
       <c r="K110" s="11" t="n">
         <v>485843.974347272</v>
@@ -8338,19 +8338,19 @@
         <v>485843.974347272</v>
       </c>
       <c r="O110" s="15" t="n">
-        <v>0.0189188167693457</v>
+        <v>0.0189188167693449</v>
       </c>
       <c r="P110" s="16" t="n">
-        <v>0.0820850747397865</v>
+        <v>0.0820850747397859</v>
       </c>
       <c r="Q110" s="17" t="n">
-        <v>0.0190989115170277</v>
+        <v>0.0190989115170268</v>
       </c>
       <c r="R110" s="18" t="n">
         <v>1.00061434976332</v>
       </c>
       <c r="S110" s="19" t="n">
-        <v>1.00651440815428</v>
+        <v>1.00651439434032</v>
       </c>
     </row>
     <row r="111">
@@ -8370,19 +8370,19 @@
         <v>508020.740483857</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>13613.635029117</v>
+        <v>13613.6350291173</v>
       </c>
       <c r="G111" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>495321.718474782</v>
+        <v>495321.718474781</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>485642.716657844</v>
+        <v>485642.724450079</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>492361.260077147</v>
+        <v>492361.260083551</v>
       </c>
       <c r="K111" s="11" t="n">
         <v>494407.10545474</v>
@@ -8400,16 +8400,16 @@
         <v>0.0174717459964136</v>
       </c>
       <c r="P111" s="16" t="n">
-        <v>0.0799852987142629</v>
+        <v>0.0799852987142622</v>
       </c>
       <c r="Q111" s="17" t="n">
         <v>0.0176252697565573</v>
       </c>
       <c r="R111" s="18" t="n">
-        <v>0.998153497038535</v>
+        <v>0.998153497038536</v>
       </c>
       <c r="S111" s="19" t="n">
-        <v>1.01804698906474</v>
+        <v>1.01804697272997</v>
       </c>
     </row>
     <row r="112">
@@ -8429,46 +8429,46 @@
         <v>512208.063825329</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>5700.32583127301</v>
+        <v>5700.32583127185</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>505624.920127525</v>
+        <v>505624.920127526</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>488174.049870057</v>
+        <v>488174.058904685</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>497543.58902387</v>
+        <v>497543.589030712</v>
       </c>
       <c r="K112" s="11" t="n">
-        <v>506507.737994056</v>
+        <v>506507.737994057</v>
       </c>
       <c r="L112" s="12" t="n">
-        <v>506507.737994056</v>
+        <v>506507.737994057</v>
       </c>
       <c r="M112" s="13" t="n">
-        <v>506507.737994056</v>
+        <v>506507.737994057</v>
       </c>
       <c r="N112" s="14" t="n">
-        <v>506507.737994056</v>
+        <v>506507.737994057</v>
       </c>
       <c r="O112" s="15" t="n">
-        <v>0.0241803230395032</v>
+        <v>0.024180323039506</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>0.0844261064578529</v>
+        <v>0.0844261064578551</v>
       </c>
       <c r="Q112" s="17" t="n">
-        <v>0.0244750376881944</v>
+        <v>0.0244750376881973</v>
       </c>
       <c r="R112" s="18" t="n">
         <v>1.00174599358415</v>
       </c>
       <c r="S112" s="19" t="n">
-        <v>1.03755563846313</v>
+        <v>1.0375556192611</v>
       </c>
     </row>
     <row r="113">
@@ -8488,7 +8488,7 @@
         <v>518379.749569641</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>4610.47372884152</v>
+        <v>4610.47372884125</v>
       </c>
       <c r="G113" s="7" t="n">
         <v>1</v>
@@ -8497,10 +8497,10 @@
         <v>513826.620962883</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>490241.077642907</v>
+        <v>490241.087978994</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>501988.733871297</v>
+        <v>501988.733878195</v>
       </c>
       <c r="K113" s="11" t="n">
         <v>513769.275840799</v>
@@ -8515,19 +8515,19 @@
         <v>513769.275840799</v>
       </c>
       <c r="O113" s="15" t="n">
-        <v>0.0142346840371737</v>
+        <v>0.0142346840371719</v>
       </c>
       <c r="P113" s="16" t="n">
-        <v>0.0776745980716926</v>
+        <v>0.0776745980716931</v>
       </c>
       <c r="Q113" s="17" t="n">
-        <v>0.0143364795876586</v>
+        <v>0.0143364795876568</v>
       </c>
       <c r="R113" s="18" t="n">
         <v>0.999888395969099</v>
       </c>
       <c r="S113" s="19" t="n">
-        <v>1.04799311863261</v>
+        <v>1.04799309653705</v>
       </c>
     </row>
     <row r="114">
@@ -8547,46 +8547,46 @@
         <v>489869.523456675</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>-25143.4923309819</v>
+        <v>-25143.4923309797</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>521028.173614833</v>
+        <v>521028.173614831</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>491802.863573212</v>
+        <v>491802.875248251</v>
       </c>
       <c r="J114" s="10" t="n">
-        <v>505497.16145267</v>
+        <v>505497.161459061</v>
       </c>
       <c r="K114" s="11" t="n">
-        <v>515013.015787657</v>
+        <v>515013.015787655</v>
       </c>
       <c r="L114" s="12" t="n">
-        <v>521028.173614833</v>
+        <v>521028.173614831</v>
       </c>
       <c r="M114" s="13" t="n">
-        <v>521028.173614833</v>
+        <v>521028.173614831</v>
       </c>
       <c r="N114" s="14" t="n">
-        <v>521028.173614833</v>
+        <v>521028.173614831</v>
       </c>
       <c r="O114" s="15" t="n">
-        <v>0.0140298313361003</v>
+        <v>0.0140298313360959</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>0.0724187210818676</v>
+        <v>0.0724187210818643</v>
       </c>
       <c r="Q114" s="17" t="n">
-        <v>0.0141287113016917</v>
+        <v>0.0141287113016872</v>
       </c>
       <c r="R114" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S114" s="19" t="n">
-        <v>1.05942484724323</v>
+        <v>1.05942482209326</v>
       </c>
     </row>
     <row r="115">
@@ -8606,7 +8606,7 @@
         <v>543066.384243079</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>15486.1329796388</v>
+        <v>15486.13297964</v>
       </c>
       <c r="G115" s="7" t="n">
         <v>1</v>
@@ -8615,37 +8615,37 @@
         <v>526357.985138881</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>492833.176381664</v>
+        <v>492833.189405117</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>507928.241311077</v>
+        <v>507928.241316182</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>527580.251263441</v>
+        <v>527580.251263439</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>527580.251263441</v>
+        <v>527580.251263439</v>
       </c>
       <c r="M115" s="13" t="n">
-        <v>527580.251263441</v>
+        <v>527580.251263439</v>
       </c>
       <c r="N115" s="14" t="n">
-        <v>527580.251263441</v>
+        <v>527580.251263439</v>
       </c>
       <c r="O115" s="15" t="n">
-        <v>0.0124968725479626</v>
+        <v>0.012496872547964</v>
       </c>
       <c r="P115" s="16" t="n">
-        <v>0.0670968225227841</v>
+        <v>0.0670968225227822</v>
       </c>
       <c r="Q115" s="17" t="n">
-        <v>0.0125752847550451</v>
+        <v>0.0125752847550464</v>
       </c>
       <c r="R115" s="18" t="n">
         <v>1.00232211946825</v>
       </c>
       <c r="S115" s="19" t="n">
-        <v>1.07050473983283</v>
+        <v>1.07050471154401</v>
       </c>
     </row>
     <row r="116">
@@ -8665,46 +8665,46 @@
         <v>528837.044115363</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>5181.7129513555</v>
+        <v>5181.71295135002</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>522900.172314504</v>
+        <v>522900.172314508</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>493324.05060773</v>
+        <v>493324.06495373</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>509218.998050417</v>
+        <v>509218.998053213</v>
       </c>
       <c r="K116" s="11" t="n">
-        <v>523655.331164008</v>
+        <v>523655.331164013</v>
       </c>
       <c r="L116" s="12" t="n">
-        <v>523655.331164008</v>
+        <v>523655.331164013</v>
       </c>
       <c r="M116" s="13" t="n">
-        <v>523655.331164008</v>
+        <v>523655.331164013</v>
       </c>
       <c r="N116" s="14" t="n">
-        <v>523655.331164008</v>
+        <v>523655.331164013</v>
       </c>
       <c r="O116" s="15" t="n">
-        <v>-0.00746728593083845</v>
+        <v>-0.00746728593082559</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>0.0338545532154395</v>
+        <v>0.0338545532154479</v>
       </c>
       <c r="Q116" s="17" t="n">
-        <v>-0.00743947501831876</v>
+        <v>-0.007439475018306</v>
       </c>
       <c r="R116" s="18" t="n">
         <v>1.0014441740307</v>
       </c>
       <c r="S116" s="19" t="n">
-        <v>1.06148348234576</v>
+        <v>1.06148345147754</v>
       </c>
     </row>
     <row r="117">
@@ -8724,7 +8724,7 @@
         <v>516130.558988705</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>4760.87146546456</v>
+        <v>4760.87146546419</v>
       </c>
       <c r="G117" s="7" t="n">
         <v>1</v>
@@ -8733,10 +8733,10 @@
         <v>512622.376606041</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>493289.237712681</v>
+        <v>493289.253311892</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>509404.716324352</v>
+        <v>509404.716323541</v>
       </c>
       <c r="K117" s="11" t="n">
         <v>511369.68752324</v>
@@ -8751,19 +8751,19 @@
         <v>511369.68752324</v>
       </c>
       <c r="O117" s="15" t="n">
-        <v>-0.023740915361566</v>
+        <v>-0.0237409153615757</v>
       </c>
       <c r="P117" s="16" t="n">
-        <v>-0.00467055627962998</v>
+        <v>-0.00467055627962976</v>
       </c>
       <c r="Q117" s="17" t="n">
-        <v>-0.023461316842624</v>
+        <v>-0.0234613168426334</v>
       </c>
       <c r="R117" s="18" t="n">
-        <v>0.997556312131564</v>
+        <v>0.997556312131565</v>
       </c>
       <c r="S117" s="19" t="n">
-        <v>1.03665283656784</v>
+        <v>1.03665280378593</v>
       </c>
     </row>
     <row r="118">
@@ -8783,46 +8783,46 @@
         <v>477829.815015122</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>-26484.2360450997</v>
+        <v>-26484.2360450927</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>503892.850307584</v>
+        <v>503892.850307578</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>492761.446208132</v>
+        <v>492761.462938785</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>508592.862452111</v>
+        <v>508592.862446109</v>
       </c>
       <c r="K118" s="11" t="n">
-        <v>504314.051060221</v>
+        <v>504314.051060214</v>
       </c>
       <c r="L118" s="12" t="n">
-        <v>504314.051060221</v>
+        <v>504314.051060214</v>
       </c>
       <c r="M118" s="13" t="n">
-        <v>504314.051060221</v>
+        <v>504314.051060214</v>
       </c>
       <c r="N118" s="14" t="n">
-        <v>504314.051060221</v>
+        <v>504314.051060214</v>
       </c>
       <c r="O118" s="15" t="n">
-        <v>-0.0138935963855719</v>
+        <v>-0.0138935963855865</v>
       </c>
       <c r="P118" s="16" t="n">
-        <v>-0.0320791147216685</v>
+        <v>-0.0320791147216782</v>
       </c>
       <c r="Q118" s="17" t="n">
-        <v>-0.0137975258118872</v>
+        <v>-0.0137975258119016</v>
       </c>
       <c r="R118" s="18" t="n">
         <v>1.00083589348882</v>
       </c>
       <c r="S118" s="19" t="n">
-        <v>1.02344461999003</v>
+        <v>1.02344458524116</v>
       </c>
     </row>
     <row r="119">
@@ -8842,46 +8842,46 @@
         <v>516391.046914062</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>17372.3266905498</v>
+        <v>17372.3266905535</v>
       </c>
       <c r="G119" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>498764.219123199</v>
+        <v>498764.219123197</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>491784.684886833</v>
+        <v>491784.702564973</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>506900.727608917</v>
+        <v>506900.727595859</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>499018.720223512</v>
+        <v>499018.720223509</v>
       </c>
       <c r="L119" s="12" t="n">
-        <v>499018.720223512</v>
+        <v>499018.720223509</v>
       </c>
       <c r="M119" s="13" t="n">
-        <v>499018.720223512</v>
+        <v>499018.720223509</v>
       </c>
       <c r="N119" s="14" t="n">
-        <v>499018.720223512</v>
+        <v>499018.720223509</v>
       </c>
       <c r="O119" s="15" t="n">
-        <v>-0.0105555806716336</v>
+        <v>-0.0105555806716272</v>
       </c>
       <c r="P119" s="16" t="n">
-        <v>-0.0541368464257894</v>
+        <v>-0.0541368464257942</v>
       </c>
       <c r="Q119" s="17" t="n">
-        <v>-0.0105000660314275</v>
+        <v>-0.0105000660314212</v>
       </c>
       <c r="R119" s="18" t="n">
         <v>1.000510263348</v>
       </c>
       <c r="S119" s="19" t="n">
-        <v>1.01470976132236</v>
+        <v>1.01470972484668</v>
       </c>
     </row>
     <row r="120">
@@ -8901,46 +8901,46 @@
         <v>502076.175540002</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>4325.82897098321</v>
+        <v>4325.82897097162</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>499613.110810707</v>
+        <v>499613.110810719</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>490410.182919563</v>
+        <v>490410.201288595</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>504424.208913034</v>
+        <v>504424.208890802</v>
       </c>
       <c r="K120" s="11" t="n">
-        <v>497750.346569019</v>
+        <v>497750.34656903</v>
       </c>
       <c r="L120" s="12" t="n">
-        <v>497750.346569019</v>
+        <v>497750.34656903</v>
       </c>
       <c r="M120" s="13" t="n">
-        <v>497750.346569019</v>
+        <v>497750.34656903</v>
       </c>
       <c r="N120" s="14" t="n">
-        <v>497750.346569019</v>
+        <v>497750.34656903</v>
       </c>
       <c r="O120" s="15" t="n">
-        <v>-0.00254497131048995</v>
+        <v>-0.00254497131045923</v>
       </c>
       <c r="P120" s="16" t="n">
-        <v>-0.049469532826881</v>
+        <v>-0.0494695328268688</v>
       </c>
       <c r="Q120" s="17" t="n">
-        <v>-0.00254173561650251</v>
+        <v>-0.00254173561647186</v>
       </c>
       <c r="R120" s="18" t="n">
-        <v>0.99627158655091</v>
+        <v>0.996271586550909</v>
       </c>
       <c r="S120" s="19" t="n">
-        <v>1.01496739648789</v>
+        <v>1.01496735847082</v>
       </c>
     </row>
     <row r="121">
@@ -8960,46 +8960,46 @@
         <v>511259.942382052</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5018.29812513245</v>
+        <v>5018.29812512343</v>
       </c>
       <c r="G121" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>504696.229750189</v>
+        <v>504696.22975018</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>488693.690749189</v>
+        <v>488693.709468828</v>
       </c>
       <c r="J121" s="10" t="n">
-        <v>501219.793445799</v>
+        <v>501219.793412088</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>506241.64425692</v>
+        <v>506241.644256929</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>506241.64425692</v>
+        <v>506241.644256929</v>
       </c>
       <c r="M121" s="13" t="n">
-        <v>506241.64425692</v>
+        <v>506241.644256929</v>
       </c>
       <c r="N121" s="14" t="n">
-        <v>506241.64425692</v>
+        <v>506241.644256929</v>
       </c>
       <c r="O121" s="15" t="n">
-        <v>0.0169154738976995</v>
+        <v>0.016915473897694</v>
       </c>
       <c r="P121" s="16" t="n">
-        <v>-0.01002805483281</v>
+        <v>-0.0100280548327931</v>
       </c>
       <c r="Q121" s="17" t="n">
-        <v>0.0170593506291488</v>
+        <v>0.0170593506291432</v>
       </c>
       <c r="R121" s="18" t="n">
-        <v>1.00306206865761</v>
+        <v>1.00306206865764</v>
       </c>
       <c r="S121" s="19" t="n">
-        <v>1.03590787816562</v>
+        <v>1.03590783848471</v>
       </c>
     </row>
     <row r="122">
@@ -9019,46 +9019,46 @@
         <v>476984.733765134</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>-27871.5187716517</v>
+        <v>-27871.5187716079</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>503615.456241015</v>
+        <v>503615.456241012</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>486695.546420859</v>
+        <v>486695.56505565</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>497310.598976829</v>
+        <v>497310.598929259</v>
       </c>
       <c r="K122" s="11" t="n">
-        <v>504856.252536786</v>
+        <v>504856.252536742</v>
       </c>
       <c r="L122" s="12" t="n">
-        <v>504856.252536786</v>
+        <v>504856.252536742</v>
       </c>
       <c r="M122" s="13" t="n">
-        <v>504856.252536786</v>
+        <v>504856.252536742</v>
       </c>
       <c r="N122" s="14" t="n">
-        <v>504856.252536786</v>
+        <v>504856.252536742</v>
       </c>
       <c r="O122" s="15" t="n">
-        <v>-0.00274037279972659</v>
+        <v>-0.00274037279983124</v>
       </c>
       <c r="P122" s="16" t="n">
-        <v>0.00107512665059528</v>
+        <v>0.00107512665052223</v>
       </c>
       <c r="Q122" s="17" t="n">
-        <v>-0.00273662140570763</v>
+        <v>-0.00273662140581199</v>
       </c>
       <c r="R122" s="18" t="n">
-        <v>1.00246377723399</v>
+        <v>1.00246377723391</v>
       </c>
       <c r="S122" s="19" t="n">
-        <v>1.03731430511226</v>
+        <v>1.03731426539507</v>
       </c>
     </row>
     <row r="123">
@@ -9078,46 +9078,46 @@
         <v>514340.804852638</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>19335.9204361233</v>
+        <v>19335.9204360519</v>
       </c>
       <c r="G123" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>496922.135204673</v>
+        <v>496922.135204726</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>484487.05545066</v>
+        <v>484487.073458278</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>492744.852529797</v>
+        <v>492744.852466081</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>495004.884416514</v>
+        <v>495004.884416586</v>
       </c>
       <c r="L123" s="12" t="n">
-        <v>495004.884416514</v>
+        <v>495004.884416586</v>
       </c>
       <c r="M123" s="13" t="n">
-        <v>495004.884416514</v>
+        <v>495004.884416586</v>
       </c>
       <c r="N123" s="14" t="n">
-        <v>495004.884416514</v>
+        <v>495004.884416586</v>
       </c>
       <c r="O123" s="15" t="n">
-        <v>-0.0197061102851779</v>
+        <v>-0.0197061102849468</v>
       </c>
       <c r="P123" s="16" t="n">
-        <v>-0.00804345737811241</v>
+        <v>-0.00804345737796186</v>
       </c>
       <c r="Q123" s="17" t="n">
-        <v>-0.01951321405008</v>
+        <v>-0.0195132140498534</v>
       </c>
       <c r="R123" s="18" t="n">
-        <v>0.996141748068097</v>
+        <v>0.996141748068135</v>
       </c>
       <c r="S123" s="19" t="n">
-        <v>1.02170920532866</v>
+        <v>1.02170916735349</v>
       </c>
     </row>
     <row r="124">
@@ -9137,46 +9137,46 @@
         <v>499002.622761819</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>4005.906020175</v>
+        <v>4005.90602015382</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>494767.383727462</v>
+        <v>494767.383727409</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>482150.873796006</v>
+        <v>482150.890515609</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>487608.509396174</v>
+        <v>487608.509314355</v>
       </c>
       <c r="K124" s="11" t="n">
-        <v>494996.716741644</v>
+        <v>494996.716741666</v>
       </c>
       <c r="L124" s="12" t="n">
-        <v>494996.716741644</v>
+        <v>494996.716741666</v>
       </c>
       <c r="M124" s="13" t="n">
-        <v>494996.716741644</v>
+        <v>494996.716741666</v>
       </c>
       <c r="N124" s="14" t="n">
-        <v>494996.716741644</v>
+        <v>494996.716741666</v>
       </c>
       <c r="O124" s="15" t="n">
-        <v>-0.0000165003265864874</v>
+        <v>-0.0000165003266879634</v>
       </c>
       <c r="P124" s="16" t="n">
-        <v>-0.00553215049744327</v>
+        <v>-0.00553215049742384</v>
       </c>
       <c r="Q124" s="17" t="n">
-        <v>-0.0000165001904568474</v>
+        <v>-0.0000165001905583217</v>
       </c>
       <c r="R124" s="18" t="n">
-        <v>1.00046351683988</v>
+        <v>1.00046351684003</v>
       </c>
       <c r="S124" s="19" t="n">
-        <v>1.02664278682003</v>
+        <v>1.02664275121906</v>
       </c>
     </row>
     <row r="125">
@@ -9196,46 +9196,46 @@
         <v>501389.215538927</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>4359.41896280493</v>
+        <v>4359.41896307207</v>
       </c>
       <c r="G125" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>496803.496841176</v>
+        <v>496803.496841033</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>479776.231057413</v>
+        <v>479776.245698388</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>481998.825026868</v>
+        <v>481998.824925638</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>497029.796576122</v>
+        <v>497029.796575855</v>
       </c>
       <c r="L125" s="12" t="n">
-        <v>497029.796576122</v>
+        <v>497029.796575855</v>
       </c>
       <c r="M125" s="13" t="n">
-        <v>497029.796576122</v>
+        <v>497029.796575855</v>
       </c>
       <c r="N125" s="14" t="n">
-        <v>497029.796576122</v>
+        <v>497029.796575855</v>
       </c>
       <c r="O125" s="15" t="n">
-        <v>0.00409884746745826</v>
+        <v>0.004098847466878</v>
       </c>
       <c r="P125" s="16" t="n">
-        <v>-0.0181965426694981</v>
+        <v>-0.0181965426700432</v>
       </c>
       <c r="Q125" s="17" t="n">
-        <v>0.00410725923165844</v>
+        <v>0.0041072592310758</v>
       </c>
       <c r="R125" s="18" t="n">
-        <v>1.00045551155816</v>
+        <v>1.00045551155791</v>
       </c>
       <c r="S125" s="19" t="n">
-        <v>1.0359616929765</v>
+        <v>1.03596166136227</v>
       </c>
     </row>
     <row r="126">
@@ -9255,46 +9255,46 @@
         <v>467327.980201225</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>-29097.488023433</v>
+        <v>-29097.4880235757</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>497163.376366403</v>
+        <v>497163.376366567</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>477460.385487236</v>
+        <v>477460.397118748</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>476049.995909511</v>
+        <v>476049.995788621</v>
       </c>
       <c r="K126" s="11" t="n">
-        <v>496425.468224658</v>
+        <v>496425.468224801</v>
       </c>
       <c r="L126" s="12" t="n">
-        <v>496425.468224658</v>
+        <v>496425.468224801</v>
       </c>
       <c r="M126" s="13" t="n">
-        <v>496425.468224658</v>
+        <v>496425.468224801</v>
       </c>
       <c r="N126" s="14" t="n">
-        <v>496425.468224658</v>
+        <v>496425.468224801</v>
       </c>
       <c r="O126" s="15" t="n">
-        <v>-0.00121661930318922</v>
+        <v>-0.00121661930236443</v>
       </c>
       <c r="P126" s="16" t="n">
-        <v>-0.0166993758515712</v>
+        <v>-0.0166993758512033</v>
       </c>
       <c r="Q126" s="17" t="n">
-        <v>-0.00121587952196589</v>
+        <v>-0.0012158795211421</v>
       </c>
       <c r="R126" s="18" t="n">
-        <v>0.998515763274564</v>
+        <v>0.998515763274522</v>
       </c>
       <c r="S126" s="19" t="n">
-        <v>1.03972074608466</v>
+        <v>1.03972072075611</v>
       </c>
     </row>
     <row r="127">
@@ -9314,46 +9314,46 @@
         <v>513476.440667766</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>21889.3778094036</v>
+        <v>21889.3778089025</v>
       </c>
       <c r="G127" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>489881.398318449</v>
+        <v>489881.398318818</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>475311.378816283</v>
+        <v>475311.386358125</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>469971.373389482</v>
+        <v>469971.373250248</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>491587.062858363</v>
+        <v>491587.062858864</v>
       </c>
       <c r="L127" s="12" t="n">
-        <v>491587.062858363</v>
+        <v>491587.062858864</v>
       </c>
       <c r="M127" s="13" t="n">
-        <v>491587.062858363</v>
+        <v>491587.062858864</v>
       </c>
       <c r="N127" s="14" t="n">
-        <v>491587.062858363</v>
+        <v>491587.062858864</v>
       </c>
       <c r="O127" s="15" t="n">
-        <v>-0.00979429691897544</v>
+        <v>-0.00979429691824366</v>
       </c>
       <c r="P127" s="16" t="n">
-        <v>-0.00690462188505525</v>
+        <v>-0.00690462188418628</v>
       </c>
       <c r="Q127" s="17" t="n">
-        <v>-0.00974648900186126</v>
+        <v>-0.00974648900113662</v>
       </c>
       <c r="R127" s="18" t="n">
-        <v>1.00348179078807</v>
+        <v>1.00348179078834</v>
       </c>
       <c r="S127" s="19" t="n">
-        <v>1.03424215107707</v>
+        <v>1.03424213466764</v>
       </c>
     </row>
     <row r="128">
@@ -9373,46 +9373,46 @@
         <v>474407.554522122</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>3539.24899468328</v>
+        <v>3539.24899491714</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>471132.771689566</v>
+        <v>471132.771689078</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>473449.10595207</v>
+        <v>473449.108167392</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>464074.186173737</v>
+        <v>464074.186019642</v>
       </c>
       <c r="K128" s="11" t="n">
-        <v>470868.305527439</v>
+        <v>470868.305527205</v>
       </c>
       <c r="L128" s="12" t="n">
-        <v>470868.305527439</v>
+        <v>470868.305527205</v>
       </c>
       <c r="M128" s="13" t="n">
-        <v>470868.305527439</v>
+        <v>470868.305527205</v>
       </c>
       <c r="N128" s="14" t="n">
-        <v>470868.305527439</v>
+        <v>470868.305527205</v>
       </c>
       <c r="O128" s="15" t="n">
-        <v>-0.043060612126335</v>
+        <v>-0.043060612127851</v>
       </c>
       <c r="P128" s="16" t="n">
-        <v>-0.0487445883945105</v>
+        <v>-0.0487445883950237</v>
       </c>
       <c r="Q128" s="17" t="n">
-        <v>-0.0421466692195956</v>
+        <v>-0.0421466692210477</v>
       </c>
       <c r="R128" s="18" t="n">
-        <v>0.999438658955566</v>
+        <v>0.999438658956105</v>
       </c>
       <c r="S128" s="19" t="n">
-        <v>0.994548938012162</v>
+        <v>0.994548933358061</v>
       </c>
     </row>
     <row r="129">
@@ -9432,46 +9432,46 @@
         <v>448693.775149267</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>2841.32727597507</v>
+        <v>2841.32727727668</v>
       </c>
       <c r="G129" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>445533.431675761</v>
+        <v>445533.431675265</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>472003.634104639</v>
+        <v>472003.629595239</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>458777.741416576</v>
+        <v>458777.74125397</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>445852.447873291</v>
+        <v>445852.44787199</v>
       </c>
       <c r="L129" s="12" t="n">
-        <v>445852.447873291</v>
+        <v>445852.44787199</v>
       </c>
       <c r="M129" s="13" t="n">
-        <v>445852.447873291</v>
+        <v>445852.44787199</v>
       </c>
       <c r="N129" s="14" t="n">
-        <v>445852.447873291</v>
+        <v>445852.44787199</v>
       </c>
       <c r="O129" s="15" t="n">
-        <v>-0.0545903859030033</v>
+        <v>-0.0545903859054259</v>
       </c>
       <c r="P129" s="16" t="n">
-        <v>-0.10296635947256</v>
+        <v>-0.102966359474697</v>
       </c>
       <c r="Q129" s="17" t="n">
-        <v>-0.0531270789740798</v>
+        <v>-0.0531270789763737</v>
       </c>
       <c r="R129" s="18" t="n">
-        <v>1.00071603200759</v>
+        <v>1.00071603200578</v>
       </c>
       <c r="S129" s="19" t="n">
-        <v>0.944595371006083</v>
+        <v>0.944595380027746</v>
       </c>
     </row>
     <row r="130">
@@ -9491,46 +9491,46 @@
         <v>390971.781617488</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>-29496.4285174423</v>
+        <v>-29496.4285185237</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>0.284622345919805</v>
+        <v>0.284622345843011</v>
       </c>
       <c r="H130" s="8" t="n">
-        <v>425765.319877388</v>
+        <v>425765.319878363</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>471103.417483769</v>
+        <v>471103.404688702</v>
       </c>
       <c r="J130" s="10" t="n">
-        <v>454535.316869067</v>
+        <v>454535.316707937</v>
       </c>
       <c r="K130" s="11" t="n">
-        <v>420468.21013493</v>
+        <v>420468.210136012</v>
       </c>
       <c r="L130" s="12" t="n">
-        <v>424257.644075895</v>
+        <v>424257.644077307</v>
       </c>
       <c r="M130" s="13" t="n">
-        <v>424257.644075895</v>
+        <v>424257.644077307</v>
       </c>
       <c r="N130" s="14" t="n">
-        <v>424257.644075895</v>
+        <v>424257.644077307</v>
       </c>
       <c r="O130" s="15" t="n">
-        <v>-0.0496471411083209</v>
+        <v>-0.0496471411020735</v>
       </c>
       <c r="P130" s="16" t="n">
-        <v>-0.145374943003737</v>
+        <v>-0.145374943001138</v>
       </c>
       <c r="Q130" s="17" t="n">
-        <v>-0.048434866513357</v>
+        <v>-0.0484348665074122</v>
       </c>
       <c r="R130" s="18" t="n">
-        <v>0.99645890416362</v>
+        <v>0.996458904164654</v>
       </c>
       <c r="S130" s="19" t="n">
-        <v>0.900561592912901</v>
+        <v>0.900561617374958</v>
       </c>
     </row>
     <row r="131">
@@ -9550,46 +9550,46 @@
         <v>444096.358125271</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>24896.3322014246</v>
+        <v>24896.3321999549</v>
       </c>
       <c r="G131" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H131" s="8" t="n">
-        <v>419507.296760419</v>
+        <v>419507.29676177</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>470860.565807843</v>
+        <v>470860.543006244</v>
       </c>
       <c r="J131" s="10" t="n">
-        <v>451735.563814561</v>
+        <v>451735.563669338</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>419200.025923846</v>
+        <v>419200.025925316</v>
       </c>
       <c r="L131" s="12" t="n">
-        <v>419200.025923846</v>
+        <v>419200.025925316</v>
       </c>
       <c r="M131" s="13" t="n">
-        <v>419200.025923846</v>
+        <v>419200.025925316</v>
       </c>
       <c r="N131" s="14" t="n">
-        <v>419200.025923846</v>
+        <v>419200.025925316</v>
       </c>
       <c r="O131" s="15" t="n">
-        <v>-0.0119927269610981</v>
+        <v>-0.0119927269609204</v>
       </c>
       <c r="P131" s="16" t="n">
-        <v>-0.147251712674492</v>
+        <v>-0.147251712672371</v>
       </c>
       <c r="Q131" s="17" t="n">
-        <v>-0.0119211008279309</v>
+        <v>-0.0119211008277552</v>
       </c>
       <c r="R131" s="18" t="n">
-        <v>0.99926754352321</v>
+        <v>0.999267543523495</v>
       </c>
       <c r="S131" s="19" t="n">
-        <v>0.890284845163527</v>
+        <v>0.890284888279027</v>
       </c>
     </row>
     <row r="132">
@@ -9609,46 +9609,46 @@
         <v>428054.007663138</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>2785.14180496253</v>
+        <v>2785.14180577655</v>
       </c>
       <c r="G132" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>424956.232145161</v>
+        <v>424956.232144147</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>471357.910186863</v>
+        <v>471357.875505942</v>
       </c>
       <c r="J132" s="10" t="n">
-        <v>450615.745172444</v>
+        <v>450615.745062815</v>
       </c>
       <c r="K132" s="11" t="n">
-        <v>425268.865858176</v>
+        <v>425268.865857362</v>
       </c>
       <c r="L132" s="12" t="n">
-        <v>425268.865858176</v>
+        <v>425268.865857362</v>
       </c>
       <c r="M132" s="13" t="n">
-        <v>425268.865858176</v>
+        <v>425268.865857362</v>
       </c>
       <c r="N132" s="14" t="n">
-        <v>425268.865858176</v>
+        <v>425268.865857362</v>
       </c>
       <c r="O132" s="15" t="n">
-        <v>0.0143733996018125</v>
+        <v>0.0143733995963923</v>
       </c>
       <c r="P132" s="16" t="n">
-        <v>-0.0968411743453095</v>
+        <v>-0.0968411743465897</v>
       </c>
       <c r="Q132" s="17" t="n">
-        <v>0.0144771936045449</v>
+        <v>0.0144771935990462</v>
       </c>
       <c r="R132" s="18" t="n">
-        <v>1.00073568449964</v>
+        <v>1.00073568450011</v>
       </c>
       <c r="S132" s="19" t="n">
-        <v>0.90222070462249</v>
+        <v>0.902220771003116</v>
       </c>
     </row>
     <row r="133">
@@ -9668,46 +9668,46 @@
         <v>433362.880156828</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>-559.10083105406</v>
+        <v>-559.10082797262</v>
       </c>
       <c r="G133" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H133" s="8" t="n">
-        <v>433334.880016396</v>
+        <v>433334.880013431</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>472645.993893404</v>
+        <v>472645.945322699</v>
       </c>
       <c r="J133" s="10" t="n">
-        <v>451250.44617265</v>
+        <v>451250.446124289</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>433921.980987882</v>
+        <v>433921.9809848</v>
       </c>
       <c r="L133" s="12" t="n">
-        <v>433921.980987882</v>
+        <v>433921.9809848</v>
       </c>
       <c r="M133" s="13" t="n">
-        <v>433921.980987882</v>
+        <v>433921.9809848</v>
       </c>
       <c r="N133" s="14" t="n">
-        <v>433921.980987882</v>
+        <v>433921.9809848</v>
       </c>
       <c r="O133" s="15" t="n">
-        <v>0.0201431561814191</v>
+        <v>0.020143156176232</v>
       </c>
       <c r="P133" s="16" t="n">
-        <v>-0.0267587784755196</v>
+        <v>-0.0267587784795896</v>
       </c>
       <c r="Q133" s="17" t="n">
-        <v>0.0203473986092177</v>
+        <v>0.0203473986039251</v>
       </c>
       <c r="R133" s="18" t="n">
-        <v>1.00135484355994</v>
+        <v>1.00135484355968</v>
       </c>
       <c r="S133" s="19" t="n">
-        <v>0.918069732091592</v>
+        <v>0.918069826429041</v>
       </c>
     </row>
     <row r="134">
@@ -9727,46 +9727,46 @@
         <v>412150.09254573</v>
       </c>
       <c r="F134" s="6" t="n">
-        <v>-28461.5490952954</v>
+        <v>-28461.5490949431</v>
       </c>
       <c r="G134" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H134" s="8" t="n">
-        <v>439922.40285131</v>
+        <v>439922.402854178</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>474746.55454734</v>
+        <v>474746.489960389</v>
       </c>
       <c r="J134" s="10" t="n">
-        <v>453587.517648538</v>
+        <v>453587.517693655</v>
       </c>
       <c r="K134" s="11" t="n">
-        <v>440611.641641025</v>
+        <v>440611.641640673</v>
       </c>
       <c r="L134" s="12" t="n">
-        <v>440611.641641025</v>
+        <v>440611.641640673</v>
       </c>
       <c r="M134" s="13" t="n">
-        <v>440611.641641025</v>
+        <v>440611.641640673</v>
       </c>
       <c r="N134" s="14" t="n">
-        <v>440611.641641025</v>
+        <v>440611.641640673</v>
       </c>
       <c r="O134" s="15" t="n">
-        <v>0.015299105632608</v>
+        <v>0.0152991056389095</v>
       </c>
       <c r="P134" s="16" t="n">
-        <v>0.0385473256486684</v>
+        <v>0.0385473256443813</v>
       </c>
       <c r="Q134" s="17" t="n">
-        <v>0.0154167360637358</v>
+        <v>0.0154167360701345</v>
       </c>
       <c r="R134" s="18" t="n">
-        <v>1.00156672809852</v>
+        <v>1.00156672809119</v>
       </c>
       <c r="S134" s="19" t="n">
-        <v>0.928098661108007</v>
+        <v>0.928098787370572</v>
       </c>
     </row>
     <row r="135">
@@ -9786,46 +9786,46 @@
         <v>478511.050017991</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>29725.1757844635</v>
+        <v>29725.1757736966</v>
       </c>
       <c r="G135" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H135" s="8" t="n">
-        <v>451101.618070857</v>
+        <v>451101.618074033</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>477657.127260471</v>
+        <v>477657.044445174</v>
       </c>
       <c r="J135" s="10" t="n">
-        <v>457488.168107546</v>
+        <v>457488.16828511</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>448785.874233527</v>
+        <v>448785.874244294</v>
       </c>
       <c r="L135" s="12" t="n">
-        <v>448785.874233527</v>
+        <v>448785.874244294</v>
       </c>
       <c r="M135" s="13" t="n">
-        <v>448785.874233527</v>
+        <v>448785.874244294</v>
       </c>
       <c r="N135" s="14" t="n">
-        <v>448785.874233527</v>
+        <v>448785.874244294</v>
       </c>
       <c r="O135" s="15" t="n">
-        <v>0.0183820229250221</v>
+        <v>0.0183820229498127</v>
       </c>
       <c r="P135" s="16" t="n">
-        <v>0.070576923855096</v>
+        <v>0.0705769238770269</v>
       </c>
       <c r="Q135" s="17" t="n">
-        <v>0.018552012293769</v>
+        <v>0.0185520123190195</v>
       </c>
       <c r="R135" s="18" t="n">
-        <v>0.994866469672104</v>
+        <v>0.994866469688968</v>
       </c>
       <c r="S135" s="19" t="n">
-        <v>0.939556532543478</v>
+        <v>0.939556695464598</v>
       </c>
     </row>
     <row r="136">
@@ -9845,46 +9845,46 @@
         <v>471537.267275214</v>
       </c>
       <c r="F136" s="6" t="n">
-        <v>257.786195876191</v>
+        <v>257.786206066049</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H136" s="8" t="n">
-        <v>471107.283703288</v>
+        <v>471107.283701152</v>
       </c>
       <c r="I136" s="9" t="n">
-        <v>481353.912824037</v>
+        <v>481353.809523014</v>
       </c>
       <c r="J136" s="10" t="n">
-        <v>462748.726677073</v>
+        <v>462748.727032585</v>
       </c>
       <c r="K136" s="11" t="n">
-        <v>471279.481079338</v>
+        <v>471279.481069148</v>
       </c>
       <c r="L136" s="12" t="n">
-        <v>471279.481079338</v>
+        <v>471279.481069148</v>
       </c>
       <c r="M136" s="13" t="n">
-        <v>471279.481079338</v>
+        <v>471279.481069148</v>
       </c>
       <c r="N136" s="14" t="n">
-        <v>471279.481079338</v>
+        <v>471279.481069148</v>
       </c>
       <c r="O136" s="15" t="n">
-        <v>0.0489054169360907</v>
+        <v>0.0489054168904779</v>
       </c>
       <c r="P136" s="16" t="n">
-        <v>0.108191826195211</v>
+        <v>0.108191826173372</v>
       </c>
       <c r="Q136" s="17" t="n">
-        <v>0.0501210223789397</v>
+        <v>0.0501210223310407</v>
       </c>
       <c r="R136" s="18" t="n">
-        <v>1.00036551626775</v>
+        <v>1.00036551625066</v>
       </c>
       <c r="S136" s="19" t="n">
-        <v>0.979070634981248</v>
+        <v>0.979070845073712</v>
       </c>
     </row>
     <row r="137">
@@ -9904,46 +9904,46 @@
         <v>484205.691494541</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>-5183.34740376056</v>
+        <v>-5183.34740344839</v>
       </c>
       <c r="G137" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H137" s="8" t="n">
-        <v>487083.264352766</v>
+        <v>487083.26434693</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>485795.067496133</v>
+        <v>485794.941458497</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>469122.01101515</v>
+        <v>469122.011599809</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>489389.038898301</v>
+        <v>489389.038897989</v>
       </c>
       <c r="L137" s="12" t="n">
-        <v>489389.038898301</v>
+        <v>489389.038897989</v>
       </c>
       <c r="M137" s="13" t="n">
-        <v>489389.038898301</v>
+        <v>489389.038897989</v>
       </c>
       <c r="N137" s="14" t="n">
-        <v>489389.038898301</v>
+        <v>489389.038897989</v>
       </c>
       <c r="O137" s="15" t="n">
-        <v>0.0377064576125098</v>
+        <v>0.0377064576334936</v>
       </c>
       <c r="P137" s="16" t="n">
-        <v>0.127827260062146</v>
+        <v>0.127827260069435</v>
       </c>
       <c r="Q137" s="17" t="n">
-        <v>0.0384263659803057</v>
+        <v>0.0384263660020958</v>
       </c>
       <c r="R137" s="18" t="n">
-        <v>1.00473384062702</v>
+        <v>1.00473384063842</v>
       </c>
       <c r="S137" s="19" t="n">
-        <v>1.00739812246487</v>
+        <v>1.00739838382981</v>
       </c>
     </row>
     <row r="138">
@@ -9963,46 +9963,46 @@
         <v>460369.442232949</v>
       </c>
       <c r="F138" s="6" t="n">
-        <v>-26386.8464416182</v>
+        <v>-26386.8464352325</v>
       </c>
       <c r="G138" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>486395.455470643</v>
+        <v>486395.455465753</v>
       </c>
       <c r="I138" s="9" t="n">
-        <v>490932.451015016</v>
+        <v>490932.300060925</v>
       </c>
       <c r="J138" s="10" t="n">
-        <v>476403.492551816</v>
+        <v>476403.493420693</v>
       </c>
       <c r="K138" s="11" t="n">
-        <v>486756.288674567</v>
+        <v>486756.288668181</v>
       </c>
       <c r="L138" s="12" t="n">
-        <v>486756.288674567</v>
+        <v>486756.288668181</v>
       </c>
       <c r="M138" s="13" t="n">
-        <v>486756.288674567</v>
+        <v>486756.288668181</v>
       </c>
       <c r="N138" s="14" t="n">
-        <v>486756.288674567</v>
+        <v>486756.288668181</v>
       </c>
       <c r="O138" s="15" t="n">
-        <v>-0.00539418984691721</v>
+        <v>-0.00539418985939831</v>
       </c>
       <c r="P138" s="16" t="n">
-        <v>0.104728615117111</v>
+        <v>0.104728615103502</v>
       </c>
       <c r="Q138" s="17" t="n">
-        <v>-0.00537966732900486</v>
+        <v>-0.00537966734141881</v>
       </c>
       <c r="R138" s="18" t="n">
-        <v>1.0007418515117</v>
+        <v>1.00074185150863</v>
       </c>
       <c r="S138" s="19" t="n">
-        <v>0.991493407429445</v>
+        <v>0.991493712285328</v>
       </c>
     </row>
     <row r="139">
@@ -10022,46 +10022,46 @@
         <v>514395.681772362</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>35970.25704564</v>
+        <v>35970.2570456107</v>
       </c>
       <c r="G139" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H139" s="8" t="n">
-        <v>480597.138120829</v>
+        <v>480597.138119865</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>496720.169351066</v>
+        <v>496719.9914505</v>
       </c>
       <c r="J139" s="10" t="n">
-        <v>484489.977856529</v>
+        <v>484489.979065637</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>478425.424726722</v>
+        <v>478425.424726751</v>
       </c>
       <c r="L139" s="12" t="n">
-        <v>478425.424726722</v>
+        <v>478425.424726751</v>
       </c>
       <c r="M139" s="13" t="n">
-        <v>478425.424726722</v>
+        <v>478425.424726751</v>
       </c>
       <c r="N139" s="14" t="n">
-        <v>478425.424726722</v>
+        <v>478425.424726751</v>
       </c>
       <c r="O139" s="15" t="n">
-        <v>-0.0172632173345758</v>
+        <v>-0.0172632173213955</v>
       </c>
       <c r="P139" s="16" t="n">
-        <v>0.0660438578727887</v>
+        <v>0.0660438578472784</v>
       </c>
       <c r="Q139" s="17" t="n">
-        <v>-0.0171150617705015</v>
+        <v>-0.0171150617575468</v>
       </c>
       <c r="R139" s="18" t="n">
-        <v>0.995481218630226</v>
+        <v>0.995481218632283</v>
       </c>
       <c r="S139" s="19" t="n">
-        <v>0.963168911284103</v>
+        <v>0.963169256243691</v>
       </c>
     </row>
     <row r="140">
@@ -10081,46 +10081,46 @@
         <v>481151.979943508</v>
       </c>
       <c r="F140" s="6" t="n">
-        <v>-3202.86601662116</v>
+        <v>-3202.86604362778</v>
       </c>
       <c r="G140" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H140" s="8" t="n">
-        <v>483033.808020358</v>
+        <v>483033.808082254</v>
       </c>
       <c r="I140" s="9" t="n">
-        <v>503109.718373204</v>
+        <v>503109.511740305</v>
       </c>
       <c r="J140" s="10" t="n">
-        <v>493330.037479358</v>
+        <v>493330.039081282</v>
       </c>
       <c r="K140" s="11" t="n">
-        <v>484354.845960129</v>
+        <v>484354.845987136</v>
       </c>
       <c r="L140" s="12" t="n">
-        <v>484354.845960129</v>
+        <v>484354.845987136</v>
       </c>
       <c r="M140" s="13" t="n">
-        <v>484354.845960129</v>
+        <v>484354.845987136</v>
       </c>
       <c r="N140" s="14" t="n">
-        <v>484354.845960129</v>
+        <v>484354.845987136</v>
       </c>
       <c r="O140" s="15" t="n">
-        <v>0.0123174443455471</v>
+        <v>0.0123174444012439</v>
       </c>
       <c r="P140" s="16" t="n">
-        <v>0.0277443967024527</v>
+        <v>0.027744396781979</v>
       </c>
       <c r="Q140" s="17" t="n">
-        <v>0.0123936164905836</v>
+        <v>0.0123936165469707</v>
       </c>
       <c r="R140" s="18" t="n">
-        <v>1.00273487676812</v>
+        <v>1.00273487669554</v>
       </c>
       <c r="S140" s="19" t="n">
-        <v>0.962722102698158</v>
+        <v>0.962722498152948</v>
       </c>
     </row>
     <row r="141">
@@ -10140,46 +10140,46 @@
         <v>484543.676876562</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>-10382.6062743269</v>
+        <v>-10382.6063704655</v>
       </c>
       <c r="G141" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H141" s="8" t="n">
-        <v>497199.618958473</v>
+        <v>497199.618960435</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>510041.159734958</v>
+        <v>510040.922939217</v>
       </c>
       <c r="J141" s="10" t="n">
-        <v>502841.919204725</v>
+        <v>502841.921242572</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>494926.283150889</v>
+        <v>494926.283247028</v>
       </c>
       <c r="L141" s="12" t="n">
-        <v>494926.283150889</v>
+        <v>494926.283247028</v>
       </c>
       <c r="M141" s="13" t="n">
-        <v>494926.283150889</v>
+        <v>494926.283247028</v>
       </c>
       <c r="N141" s="14" t="n">
-        <v>494926.283150889</v>
+        <v>494926.283247028</v>
       </c>
       <c r="O141" s="15" t="n">
-        <v>0.0215910376494912</v>
+        <v>0.0215910377879816</v>
       </c>
       <c r="P141" s="16" t="n">
-        <v>0.0113146061976648</v>
+        <v>0.011314606394756</v>
       </c>
       <c r="Q141" s="17" t="n">
-        <v>0.0218258107231368</v>
+        <v>0.0218258108646499</v>
       </c>
       <c r="R141" s="18" t="n">
-        <v>0.995427720133121</v>
+        <v>0.995427720322553</v>
       </c>
       <c r="S141" s="19" t="n">
-        <v>0.970365378762915</v>
+        <v>0.970365829461118</v>
       </c>
     </row>
     <row r="142">
@@ -10199,46 +10199,46 @@
         <v>493602.530577855</v>
       </c>
       <c r="F142" s="6" t="n">
-        <v>-24910.2151055623</v>
+        <v>-24910.2148594123</v>
       </c>
       <c r="G142" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>517466.951876083</v>
+        <v>517466.951677594</v>
       </c>
       <c r="I142" s="9" t="n">
-        <v>517442.833294599</v>
+        <v>517442.565390022</v>
       </c>
       <c r="J142" s="10" t="n">
-        <v>512898.994859456</v>
+        <v>512898.99735898</v>
       </c>
       <c r="K142" s="11" t="n">
-        <v>518512.745683417</v>
+        <v>518512.745437267</v>
       </c>
       <c r="L142" s="12" t="n">
-        <v>518512.745683417</v>
+        <v>518512.745437267</v>
       </c>
       <c r="M142" s="13" t="n">
-        <v>518512.745683417</v>
+        <v>518512.745437267</v>
       </c>
       <c r="N142" s="14" t="n">
-        <v>518512.745683417</v>
+        <v>518512.745437267</v>
       </c>
       <c r="O142" s="15" t="n">
-        <v>0.046555780655179</v>
+        <v>0.0465557799862075</v>
       </c>
       <c r="P142" s="16" t="n">
-        <v>0.0652409794135846</v>
+        <v>0.0652409789218649</v>
       </c>
       <c r="Q142" s="17" t="n">
-        <v>0.0476565164055698</v>
+        <v>0.0476565157047175</v>
       </c>
       <c r="R142" s="18" t="n">
-        <v>1.00202098666116</v>
+        <v>1.00202098656983</v>
       </c>
       <c r="S142" s="19" t="n">
-        <v>1.00206769196513</v>
+        <v>1.00206821030744</v>
       </c>
     </row>
     <row r="143">
@@ -10258,46 +10258,46 @@
         <v>581668.249879602</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>43713.7493417124</v>
+        <v>43713.7494283927</v>
       </c>
       <c r="G143" s="7" t="n">
-        <v>0.445514735180623</v>
+        <v>0.445514726382966</v>
       </c>
       <c r="H143" s="8" t="n">
-        <v>529792.920853365</v>
+        <v>529792.920794053</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>525233.632112532</v>
+        <v>525233.332785695</v>
       </c>
       <c r="J143" s="10" t="n">
-        <v>523335.058090105</v>
+        <v>523335.061050004</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>537954.50053789</v>
+        <v>537954.50045121</v>
       </c>
       <c r="L143" s="12" t="n">
-        <v>533429.024865172</v>
+        <v>533429.024721864</v>
       </c>
       <c r="M143" s="13" t="n">
-        <v>533429.024865172</v>
+        <v>533429.024721864</v>
       </c>
       <c r="N143" s="14" t="n">
-        <v>533429.024865172</v>
+        <v>533429.024721864</v>
       </c>
       <c r="O143" s="15" t="n">
-        <v>0.0283614158815731</v>
+        <v>0.0283614160876424</v>
       </c>
       <c r="P143" s="16" t="n">
-        <v>0.114967970546022</v>
+        <v>0.114967970246414</v>
       </c>
       <c r="Q143" s="17" t="n">
-        <v>0.0287674301276708</v>
+        <v>0.0287674303396681</v>
       </c>
       <c r="R143" s="18" t="n">
-        <v>1.00686325518648</v>
+        <v>1.0068632550287</v>
       </c>
       <c r="S143" s="19" t="n">
-        <v>1.01560332821734</v>
+        <v>1.0156039067298</v>
       </c>
     </row>
     <row r="144">
@@ -10317,46 +10317,46 @@
         <v>514697.789505428</v>
       </c>
       <c r="F144" s="6" t="n">
-        <v>-7732.82642396056</v>
+        <v>-7732.82682662774</v>
       </c>
       <c r="G144" s="7" t="n">
-        <v>0.385417578940682</v>
+        <v>0.385417569093625</v>
       </c>
       <c r="H144" s="8" t="n">
-        <v>530456.531080132</v>
+        <v>530456.531542601</v>
       </c>
       <c r="I144" s="9" t="n">
-        <v>533333.117944407</v>
+        <v>533332.787681742</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v>534011.97129735</v>
+        <v>534011.97467553</v>
       </c>
       <c r="K144" s="11" t="n">
-        <v>522430.615929389</v>
+        <v>522430.616332056</v>
       </c>
       <c r="L144" s="12" t="n">
-        <v>527363.202293949</v>
+        <v>527363.202812401</v>
       </c>
       <c r="M144" s="13" t="n">
-        <v>527363.202293949</v>
+        <v>527363.202812401</v>
       </c>
       <c r="N144" s="14" t="n">
-        <v>527363.202293949</v>
+        <v>527363.202812401</v>
       </c>
       <c r="O144" s="15" t="n">
-        <v>-0.0114365255141714</v>
+        <v>-0.0114365242624155</v>
       </c>
       <c r="P144" s="16" t="n">
-        <v>0.0887951399527449</v>
+        <v>0.088795140962433</v>
       </c>
       <c r="Q144" s="17" t="n">
-        <v>-0.0113713770501251</v>
+        <v>-0.0113713758126034</v>
       </c>
       <c r="R144" s="18" t="n">
-        <v>0.99416855367982</v>
+        <v>0.994168553790441</v>
       </c>
       <c r="S144" s="19" t="n">
-        <v>0.988806403634811</v>
+        <v>0.988807016918482</v>
       </c>
     </row>
     <row r="145">
@@ -10376,46 +10376,46 @@
         <v>522255.200050771</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>-13431.1123946296</v>
+        <v>-13431.1128278505</v>
       </c>
       <c r="G145" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H145" s="8" t="n">
-        <v>538178.201431869</v>
+        <v>538178.201509874</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>541665.974666342</v>
+        <v>541665.614941129</v>
       </c>
       <c r="J145" s="10" t="n">
-        <v>544842.06671574</v>
+        <v>544842.070413806</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>535686.312445401</v>
+        <v>535686.312878622</v>
       </c>
       <c r="L145" s="12" t="n">
-        <v>535686.312445401</v>
+        <v>535686.312878622</v>
       </c>
       <c r="M145" s="13" t="n">
-        <v>535686.312445401</v>
+        <v>535686.312878622</v>
       </c>
       <c r="N145" s="14" t="n">
-        <v>535686.312445401</v>
+        <v>535686.312878622</v>
       </c>
       <c r="O145" s="15" t="n">
-        <v>0.0156592522035616</v>
+        <v>0.0156592520291805</v>
       </c>
       <c r="P145" s="16" t="n">
-        <v>0.0823557581848715</v>
+        <v>0.0823557588499499</v>
       </c>
       <c r="Q145" s="17" t="n">
-        <v>0.0157825007798187</v>
+        <v>0.0157825006026855</v>
       </c>
       <c r="R145" s="18" t="n">
-        <v>0.995369769753145</v>
+        <v>0.99536977041385</v>
       </c>
       <c r="S145" s="19" t="n">
-        <v>0.988960609488857</v>
+        <v>0.988961267066663</v>
       </c>
     </row>
     <row r="146">
@@ -10435,46 +10435,46 @@
         <v>532348.212016917</v>
       </c>
       <c r="F146" s="6" t="n">
-        <v>-25280.3127868491</v>
+        <v>-25280.3116086524</v>
       </c>
       <c r="G146" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H146" s="8" t="n">
-        <v>554181.29274692</v>
+        <v>554181.291979931</v>
       </c>
       <c r="I146" s="9" t="n">
-        <v>550153.154957174</v>
+        <v>550152.768436278</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>555704.432734811</v>
+        <v>555704.436583764</v>
       </c>
       <c r="K146" s="11" t="n">
-        <v>557628.524803766</v>
+        <v>557628.52362557</v>
       </c>
       <c r="L146" s="12" t="n">
-        <v>557628.524803766</v>
+        <v>557628.52362557</v>
       </c>
       <c r="M146" s="13" t="n">
-        <v>557628.524803766</v>
+        <v>557628.52362557</v>
       </c>
       <c r="N146" s="14" t="n">
-        <v>557628.524803766</v>
+        <v>557628.52362557</v>
       </c>
       <c r="O146" s="15" t="n">
-        <v>0.0401442627519147</v>
+        <v>0.0401442598303232</v>
       </c>
       <c r="P146" s="16" t="n">
-        <v>0.0754384138981834</v>
+        <v>0.0754384121364571</v>
       </c>
       <c r="Q146" s="17" t="n">
-        <v>0.0409609352499589</v>
+        <v>0.0409609322086963</v>
       </c>
       <c r="R146" s="18" t="n">
-        <v>1.00622040495044</v>
+        <v>1.00622040421704</v>
       </c>
       <c r="S146" s="19" t="n">
-        <v>1.01358779783272</v>
+        <v>1.01358850780764</v>
       </c>
     </row>
     <row r="147">
@@ -10494,46 +10494,46 @@
         <v>614076.392608544</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>49652.5951467335</v>
+        <v>49652.5954424188</v>
       </c>
       <c r="G147" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H147" s="8" t="n">
-        <v>565360.865334907</v>
+        <v>565360.865119452</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>558711.874206855</v>
+        <v>558711.464975823</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v>566432.378972744</v>
+        <v>566432.382716657</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>564423.79746181</v>
+        <v>564423.797166125</v>
       </c>
       <c r="L147" s="12" t="n">
-        <v>564423.79746181</v>
+        <v>564423.797166125</v>
       </c>
       <c r="M147" s="13" t="n">
-        <v>564423.79746181</v>
+        <v>564423.797166125</v>
       </c>
       <c r="N147" s="14" t="n">
-        <v>564423.79746181</v>
+        <v>564423.797166125</v>
       </c>
       <c r="O147" s="15" t="n">
-        <v>0.0121123687381968</v>
+        <v>0.012112370327196</v>
       </c>
       <c r="P147" s="16" t="n">
-        <v>0.0581047733660029</v>
+        <v>0.0581047730959563</v>
       </c>
       <c r="Q147" s="17" t="n">
-        <v>0.0121860205419644</v>
+        <v>0.0121860221503272</v>
       </c>
       <c r="R147" s="18" t="n">
-        <v>0.99834253141568</v>
+        <v>0.998342531273138</v>
       </c>
       <c r="S147" s="19" t="n">
-        <v>1.01022337902352</v>
+        <v>1.0102241184375</v>
       </c>
     </row>
     <row r="148">
@@ -10553,46 +10553,46 @@
         <v>562978.965626877</v>
       </c>
       <c r="F148" s="6" t="n">
-        <v>-10015.5172125205</v>
+        <v>-10015.5187296057</v>
       </c>
       <c r="G148" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>573563.742488649</v>
+        <v>573563.744063941</v>
       </c>
       <c r="I148" s="9" t="n">
-        <v>567264.019911486</v>
+        <v>567263.59371539</v>
       </c>
       <c r="J148" s="10" t="n">
-        <v>576868.835508067</v>
+        <v>576868.838778952</v>
       </c>
       <c r="K148" s="11" t="n">
-        <v>572994.482839397</v>
+        <v>572994.484356482</v>
       </c>
       <c r="L148" s="12" t="n">
-        <v>572994.482839397</v>
+        <v>572994.484356482</v>
       </c>
       <c r="M148" s="13" t="n">
-        <v>572994.482839397</v>
+        <v>572994.484356482</v>
       </c>
       <c r="N148" s="14" t="n">
-        <v>572994.482839397</v>
+        <v>572994.484356482</v>
       </c>
       <c r="O148" s="15" t="n">
-        <v>0.0150707048485219</v>
+        <v>0.0150707080200368</v>
       </c>
       <c r="P148" s="16" t="n">
-        <v>0.0865272365363354</v>
+        <v>0.0865272383449052</v>
       </c>
       <c r="Q148" s="17" t="n">
-        <v>0.0151848405686092</v>
+        <v>0.0151848437882831</v>
       </c>
       <c r="R148" s="18" t="n">
-        <v>0.999007504123636</v>
+        <v>0.999007504024879</v>
       </c>
       <c r="S148" s="19" t="n">
-        <v>1.01010193265705</v>
+        <v>1.01010269424053</v>
       </c>
     </row>
     <row r="149">
@@ -10612,46 +10612,46 @@
         <v>572794.046630588</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>-14706.9147398183</v>
+        <v>-14706.9163436076</v>
       </c>
       <c r="G149" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H149" s="8" t="n">
-        <v>587400.45024153</v>
+        <v>587400.451010496</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>575735.049519206</v>
+        <v>575734.614018224</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>586846.689511752</v>
+        <v>586846.691809359</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>587500.961370407</v>
+        <v>587500.962974196</v>
       </c>
       <c r="L149" s="12" t="n">
-        <v>587500.961370407</v>
+        <v>587500.962974196</v>
       </c>
       <c r="M149" s="13" t="n">
-        <v>587500.961370407</v>
+        <v>587500.962974196</v>
       </c>
       <c r="N149" s="14" t="n">
-        <v>587500.961370407</v>
+        <v>587500.962974196</v>
       </c>
       <c r="O149" s="15" t="n">
-        <v>0.0250017942762864</v>
+        <v>0.0250017943584924</v>
       </c>
       <c r="P149" s="16" t="n">
-        <v>0.0967257286983354</v>
+        <v>0.0967257308052862</v>
       </c>
       <c r="Q149" s="17" t="n">
-        <v>0.0253169602246861</v>
+        <v>0.0253169603089733</v>
       </c>
       <c r="R149" s="18" t="n">
-        <v>1.00017111176683</v>
+        <v>1.00017111318782</v>
       </c>
       <c r="S149" s="19" t="n">
-        <v>1.02043633067159</v>
+        <v>1.02043710534243</v>
       </c>
     </row>
     <row r="150">
@@ -10671,46 +10671,46 @@
         <v>576846.885699427</v>
       </c>
       <c r="F150" s="6" t="n">
-        <v>-27503.9535185269</v>
+        <v>-27503.9500339087</v>
       </c>
       <c r="G150" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>605487.577257472</v>
+        <v>605487.572889423</v>
       </c>
       <c r="I150" s="9" t="n">
-        <v>584054.002017483</v>
+        <v>584053.567054223</v>
       </c>
       <c r="J150" s="10" t="n">
-        <v>596179.456391428</v>
+        <v>596179.457074478</v>
       </c>
       <c r="K150" s="11" t="n">
-        <v>604350.839217954</v>
+        <v>604350.835733336</v>
       </c>
       <c r="L150" s="12" t="n">
-        <v>604350.839217954</v>
+        <v>604350.835733336</v>
       </c>
       <c r="M150" s="13" t="n">
-        <v>604350.839217954</v>
+        <v>604350.835733336</v>
       </c>
       <c r="N150" s="14" t="n">
-        <v>604350.839217954</v>
+        <v>604350.835733336</v>
       </c>
       <c r="O150" s="15" t="n">
-        <v>0.028277006541396</v>
+        <v>0.0282769980456602</v>
       </c>
       <c r="P150" s="16" t="n">
-        <v>0.0837875258096412</v>
+        <v>0.0837875218505482</v>
       </c>
       <c r="Q150" s="17" t="n">
-        <v>0.0286805962125463</v>
+        <v>0.0286805874731477</v>
       </c>
       <c r="R150" s="18" t="n">
-        <v>0.998122607164516</v>
+        <v>0.998122608610012</v>
       </c>
       <c r="S150" s="19" t="n">
-        <v>1.03475164476292</v>
+        <v>1.0347524094091</v>
       </c>
     </row>
     <row r="151">
@@ -10730,46 +10730,46 @@
         <v>674620.563006485</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>53299.9746109196</v>
+        <v>53299.9804386019</v>
       </c>
       <c r="G151" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H151" s="8" t="n">
-        <v>617255.464077104</v>
+        <v>617255.463969821</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>592157.270088692</v>
+        <v>592156.847961379</v>
       </c>
       <c r="J151" s="10" t="n">
-        <v>604683.922914018</v>
+        <v>604683.921196733</v>
       </c>
       <c r="K151" s="11" t="n">
-        <v>621320.588395565</v>
+        <v>621320.582567883</v>
       </c>
       <c r="L151" s="12" t="n">
-        <v>621320.588395565</v>
+        <v>621320.582567883</v>
       </c>
       <c r="M151" s="13" t="n">
-        <v>621320.588395565</v>
+        <v>621320.582567883</v>
       </c>
       <c r="N151" s="14" t="n">
-        <v>621320.588395565</v>
+        <v>621320.582567883</v>
       </c>
       <c r="O151" s="15" t="n">
-        <v>0.0276923051946193</v>
+        <v>0.027692301580996</v>
       </c>
       <c r="P151" s="16" t="n">
-        <v>0.100805088640162</v>
+        <v>0.100805078891831</v>
       </c>
       <c r="Q151" s="17" t="n">
-        <v>0.0280793010887028</v>
+        <v>0.0280792973736115</v>
       </c>
       <c r="R151" s="18" t="n">
-        <v>1.00658580531894</v>
+        <v>1.00658579605261</v>
       </c>
       <c r="S151" s="19" t="n">
-        <v>1.04924927849405</v>
+        <v>1.04925001662466</v>
       </c>
     </row>
     <row r="152">
@@ -10789,46 +10789,46 @@
         <v>610425.694014854</v>
       </c>
       <c r="F152" s="6" t="n">
-        <v>-10279.6974113322</v>
+        <v>-10279.7119378741</v>
       </c>
       <c r="G152" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H152" s="8" t="n">
-        <v>625833.634963492</v>
+        <v>625833.642556101</v>
       </c>
       <c r="I152" s="9" t="n">
-        <v>599993.931938458</v>
+        <v>599993.537670612</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>612217.732760577</v>
+        <v>612217.727691842</v>
       </c>
       <c r="K152" s="11" t="n">
-        <v>620705.391426186</v>
+        <v>620705.405952728</v>
       </c>
       <c r="L152" s="12" t="n">
-        <v>620705.391426186</v>
+        <v>620705.405952728</v>
       </c>
       <c r="M152" s="13" t="n">
-        <v>620705.391426186</v>
+        <v>620705.405952728</v>
       </c>
       <c r="N152" s="14" t="n">
-        <v>620705.391426186</v>
+        <v>620705.405952728</v>
       </c>
       <c r="O152" s="15" t="n">
-        <v>-0.00099063470440211</v>
+        <v>-0.000990601921613066</v>
       </c>
       <c r="P152" s="16" t="n">
-        <v>0.0832659127019229</v>
+        <v>0.0832659351857958</v>
       </c>
       <c r="Q152" s="17" t="n">
-        <v>-0.000990144187830944</v>
+        <v>-0.000990111437501051</v>
       </c>
       <c r="R152" s="18" t="n">
-        <v>0.991805739974961</v>
+        <v>0.991805751153888</v>
       </c>
       <c r="S152" s="19" t="n">
-        <v>1.03451944825644</v>
+        <v>1.03452015227118</v>
       </c>
     </row>
     <row r="153">
@@ -10848,46 +10848,46 @@
         <v>625876.867863597</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>-14286.6846396409</v>
+        <v>-14286.6842632449</v>
       </c>
       <c r="G153" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H153" s="8" t="n">
-        <v>636769.947140659</v>
+        <v>636769.948527675</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>607531.292846347</v>
+        <v>607530.944446968</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>618721.712939568</v>
+        <v>618721.703382377</v>
       </c>
       <c r="K153" s="11" t="n">
-        <v>640163.552503238</v>
+        <v>640163.552126842</v>
       </c>
       <c r="L153" s="12" t="n">
-        <v>640163.552503238</v>
+        <v>640163.552126842</v>
       </c>
       <c r="M153" s="13" t="n">
-        <v>640163.552503238</v>
+        <v>640163.552126842</v>
       </c>
       <c r="N153" s="14" t="n">
-        <v>640163.552503238</v>
+        <v>640163.552126842</v>
       </c>
       <c r="O153" s="15" t="n">
-        <v>0.0308671350687374</v>
+        <v>0.0308671110774896</v>
       </c>
       <c r="P153" s="16" t="n">
-        <v>0.0896383063101549</v>
+        <v>0.0896383026949332</v>
       </c>
       <c r="Q153" s="17" t="n">
-        <v>0.0313484647400004</v>
+        <v>0.0313484399966641</v>
       </c>
       <c r="R153" s="18" t="n">
-        <v>1.00532940566341</v>
+        <v>1.00532940288249</v>
       </c>
       <c r="S153" s="19" t="n">
-        <v>1.0537128869593</v>
+        <v>1.05371349061006</v>
       </c>
     </row>
     <row r="154">
@@ -10907,46 +10907,46 @@
         <v>616720.357064478</v>
       </c>
       <c r="F154" s="6" t="n">
-        <v>-30791.225819021</v>
+        <v>-30791.2117616402</v>
       </c>
       <c r="G154" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H154" s="8" t="n">
-        <v>649481.526724572</v>
+        <v>649481.510245762</v>
       </c>
       <c r="I154" s="9" t="n">
-        <v>614749.602754107</v>
+        <v>614749.321473171</v>
       </c>
       <c r="J154" s="10" t="n">
-        <v>624179.128752781</v>
+        <v>624179.113482218</v>
       </c>
       <c r="K154" s="11" t="n">
-        <v>647511.582883499</v>
+        <v>647511.568826118</v>
       </c>
       <c r="L154" s="12" t="n">
-        <v>647511.582883499</v>
+        <v>647511.568826118</v>
       </c>
       <c r="M154" s="13" t="n">
-        <v>647511.582883499</v>
+        <v>647511.568826118</v>
       </c>
       <c r="N154" s="14" t="n">
-        <v>647511.582883499</v>
+        <v>647511.568826118</v>
       </c>
       <c r="O154" s="15" t="n">
-        <v>0.0114129875443721</v>
+        <v>0.011412966422488</v>
       </c>
       <c r="P154" s="16" t="n">
-        <v>0.0714167017975791</v>
+        <v>0.0714166847149473</v>
       </c>
       <c r="Q154" s="17" t="n">
-        <v>0.0114783641641711</v>
+        <v>0.0114783427998426</v>
       </c>
       <c r="R154" s="18" t="n">
-        <v>0.99696689781</v>
+        <v>0.996966901461293</v>
       </c>
       <c r="S154" s="19" t="n">
-        <v>1.05329321073591</v>
+        <v>1.05329366980745</v>
       </c>
     </row>
     <row r="155">
@@ -10966,46 +10966,46 @@
         <v>711405.500455233</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>54621.8335982692</v>
+        <v>54621.8476515583</v>
       </c>
       <c r="G155" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H155" s="8" t="n">
-        <v>656917.255560496</v>
+        <v>656917.25720046</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>621649.50676577</v>
+        <v>621649.317311744</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>628680.454699826</v>
+        <v>628680.432448965</v>
       </c>
       <c r="K155" s="11" t="n">
-        <v>656783.666856964</v>
+        <v>656783.652803675</v>
       </c>
       <c r="L155" s="12" t="n">
-        <v>656783.666856964</v>
+        <v>656783.652803675</v>
       </c>
       <c r="M155" s="13" t="n">
-        <v>656783.666856964</v>
+        <v>656783.652803675</v>
       </c>
       <c r="N155" s="14" t="n">
-        <v>656783.666856964</v>
+        <v>656783.652803675</v>
       </c>
       <c r="O155" s="15" t="n">
-        <v>0.0142180080347891</v>
+        <v>0.0142180083475058</v>
       </c>
       <c r="P155" s="16" t="n">
-        <v>0.0570769408317446</v>
+        <v>0.0570769281281891</v>
       </c>
       <c r="Q155" s="17" t="n">
-        <v>0.0143195646511434</v>
+        <v>0.0143195649683381</v>
       </c>
       <c r="R155" s="18" t="n">
-        <v>0.999796643028629</v>
+        <v>0.999796619139898</v>
       </c>
       <c r="S155" s="19" t="n">
-        <v>1.05651763527327</v>
+        <v>1.05651793465143</v>
       </c>
     </row>
     <row r="156">
@@ -11025,46 +11025,46 @@
         <v>647087.959742494</v>
       </c>
       <c r="F156" s="6" t="n">
-        <v>-8097.26999271418</v>
+        <v>-8097.31506926742</v>
       </c>
       <c r="G156" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H156" s="8" t="n">
-        <v>651444.850890689</v>
+        <v>651444.874429754</v>
       </c>
       <c r="I156" s="9" t="n">
-        <v>628252.126222949</v>
+        <v>628252.056929806</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v>632432.827550965</v>
+        <v>632432.797016937</v>
       </c>
       <c r="K156" s="11" t="n">
-        <v>655185.229735208</v>
+        <v>655185.274811762</v>
       </c>
       <c r="L156" s="12" t="n">
-        <v>655185.229735208</v>
+        <v>655185.274811762</v>
       </c>
       <c r="M156" s="13" t="n">
-        <v>655185.229735208</v>
+        <v>655185.274811762</v>
       </c>
       <c r="N156" s="14" t="n">
-        <v>655185.229735208</v>
+        <v>655185.274811762</v>
       </c>
       <c r="O156" s="15" t="n">
-        <v>-0.0024367009260695</v>
+        <v>-0.0024366107292268</v>
       </c>
       <c r="P156" s="16" t="n">
-        <v>0.0555494422721201</v>
+        <v>0.0555494901902946</v>
       </c>
       <c r="Q156" s="17" t="n">
-        <v>-0.002433734580223</v>
+        <v>-0.00243364460289142</v>
       </c>
       <c r="R156" s="18" t="n">
-        <v>1.0057416661432</v>
+        <v>1.00574169899684</v>
       </c>
       <c r="S156" s="19" t="n">
-        <v>1.04286989631723</v>
+        <v>1.04287008308986</v>
       </c>
     </row>
     <row r="157">
@@ -11084,46 +11084,46 @@
         <v>613490.821702641</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>-14611.524212401</v>
+        <v>-14611.5192580515</v>
       </c>
       <c r="G157" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H157" s="8" t="n">
-        <v>631536.037054675</v>
+        <v>631536.038540045</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>634600.541317315</v>
+        <v>634600.62425416</v>
       </c>
       <c r="J157" s="10" t="n">
-        <v>635783.900137248</v>
+        <v>635783.860022228</v>
       </c>
       <c r="K157" s="11" t="n">
-        <v>628102.345915042</v>
+        <v>628102.340960692</v>
       </c>
       <c r="L157" s="12" t="n">
-        <v>628102.345915042</v>
+        <v>628102.340960692</v>
       </c>
       <c r="M157" s="13" t="n">
-        <v>628102.345915042</v>
+        <v>628102.340960692</v>
       </c>
       <c r="N157" s="14" t="n">
-        <v>628102.345915042</v>
+        <v>628102.340960692</v>
       </c>
       <c r="O157" s="15" t="n">
-        <v>-0.0422148647534468</v>
+        <v>-0.0422149414409596</v>
       </c>
       <c r="P157" s="16" t="n">
-        <v>-0.0188408205075604</v>
+        <v>-0.0188408276698631</v>
       </c>
       <c r="Q157" s="17" t="n">
-        <v>-0.0413362246140864</v>
+        <v>-0.0413362981316241</v>
       </c>
       <c r="R157" s="18" t="n">
-        <v>0.99456295296204</v>
+        <v>0.994562942777913</v>
       </c>
       <c r="S157" s="19" t="n">
-        <v>0.989760179862463</v>
+        <v>0.989760042702283</v>
       </c>
     </row>
     <row r="158">
@@ -11143,46 +11143,46 @@
         <v>578553.044242405</v>
       </c>
       <c r="F158" s="6" t="n">
-        <v>-33308.4431476597</v>
+        <v>-33308.404035247</v>
       </c>
       <c r="G158" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H158" s="8" t="n">
-        <v>608928.104750917</v>
+        <v>608928.07279804</v>
       </c>
       <c r="I158" s="9" t="n">
-        <v>640754.665430232</v>
+        <v>640754.936472782</v>
       </c>
       <c r="J158" s="10" t="n">
-        <v>639195.087300643</v>
+        <v>639195.036689906</v>
       </c>
       <c r="K158" s="11" t="n">
-        <v>611861.487390064</v>
+        <v>611861.448277652</v>
       </c>
       <c r="L158" s="12" t="n">
-        <v>611861.487390064</v>
+        <v>611861.448277652</v>
       </c>
       <c r="M158" s="13" t="n">
-        <v>611861.487390064</v>
+        <v>611861.448277652</v>
       </c>
       <c r="N158" s="14" t="n">
-        <v>611861.487390064</v>
+        <v>611861.448277652</v>
       </c>
       <c r="O158" s="15" t="n">
-        <v>-0.0261971952898181</v>
+        <v>-0.0261972513256527</v>
       </c>
       <c r="P158" s="16" t="n">
-        <v>-0.0550570776428093</v>
+        <v>-0.0550571175324287</v>
       </c>
       <c r="Q158" s="17" t="n">
-        <v>-0.0258570257388826</v>
+        <v>-0.0258570803257957</v>
       </c>
       <c r="R158" s="18" t="n">
-        <v>1.00481728896443</v>
+        <v>1.00481727745961</v>
       </c>
       <c r="S158" s="19" t="n">
-        <v>0.954907580702877</v>
+        <v>0.954907115731043</v>
       </c>
     </row>
     <row r="159">
@@ -11202,46 +11202,46 @@
         <v>631197.751860069</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>55272.8481908001</v>
+        <v>55272.877849202</v>
       </c>
       <c r="G159" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H159" s="8" t="n">
-        <v>600012.43914754</v>
+        <v>600012.409319093</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>646770.35057094</v>
+        <v>646770.849346592</v>
       </c>
       <c r="J159" s="10" t="n">
-        <v>643089.39611201</v>
+        <v>643089.334649731</v>
       </c>
       <c r="K159" s="11" t="n">
-        <v>575924.903669269</v>
+        <v>575924.874010867</v>
       </c>
       <c r="L159" s="12" t="n">
-        <v>600012.43914754</v>
+        <v>600012.409319093</v>
       </c>
       <c r="M159" s="13" t="n">
-        <v>600012.43914754</v>
+        <v>600012.409319093</v>
       </c>
       <c r="N159" s="14" t="n">
-        <v>600012.43914754</v>
+        <v>600012.409319093</v>
       </c>
       <c r="O159" s="15" t="n">
-        <v>-0.019555542188503</v>
+        <v>-0.0195555279779114</v>
       </c>
       <c r="P159" s="16" t="n">
-        <v>-0.086438245307016</v>
+        <v>-0.086438271175351</v>
       </c>
       <c r="Q159" s="17" t="n">
-        <v>-0.0193655729061606</v>
+        <v>-0.0193655589707651</v>
       </c>
       <c r="R159" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S159" s="19" t="n">
-        <v>0.927705542806462</v>
+        <v>0.927704781261034</v>
       </c>
     </row>
     <row r="160">
@@ -11261,46 +11261,46 @@
         <v>610519.854611727</v>
       </c>
       <c r="F160" s="6" t="n">
-        <v>-6723.96681120924</v>
+        <v>-6724.05351037027</v>
       </c>
       <c r="G160" s="7" t="n">
-        <v>0.283997195839132</v>
+        <v>0.283989969893299</v>
       </c>
       <c r="H160" s="8" t="n">
-        <v>608782.502228805</v>
+        <v>608782.531969486</v>
       </c>
       <c r="I160" s="9" t="n">
-        <v>652685.390512403</v>
+        <v>652686.160206388</v>
       </c>
       <c r="J160" s="10" t="n">
-        <v>647753.165642654</v>
+        <v>647753.0935894</v>
       </c>
       <c r="K160" s="11" t="n">
-        <v>617243.821422937</v>
+        <v>617243.908122098</v>
       </c>
       <c r="L160" s="12" t="n">
-        <v>611185.493153038</v>
+        <v>611185.477928322</v>
       </c>
       <c r="M160" s="13" t="n">
-        <v>611185.493153038</v>
+        <v>611185.477928322</v>
       </c>
       <c r="N160" s="14" t="n">
-        <v>611185.493153038</v>
+        <v>611185.477928322</v>
       </c>
       <c r="O160" s="15" t="n">
-        <v>0.0184501156323412</v>
+        <v>0.0184501404352501</v>
       </c>
       <c r="P160" s="16" t="n">
-        <v>-0.0671561790242931</v>
+        <v>-0.0671562664409405</v>
       </c>
       <c r="Q160" s="17" t="n">
-        <v>0.0186213706192027</v>
+        <v>0.018621395883976</v>
       </c>
       <c r="R160" s="18" t="n">
-        <v>1.0039472076077</v>
+        <v>1.00394713355369</v>
       </c>
       <c r="S160" s="19" t="n">
-        <v>0.936416690242163</v>
+        <v>0.936415562626695</v>
       </c>
     </row>
     <row r="161">
@@ -11320,46 +11320,46 @@
         <v>615220.854937297</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>-14100.4079027471</v>
+        <v>-14100.47777926</v>
       </c>
       <c r="G161" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>627978.310355692</v>
+        <v>627978.278432199</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>658508.355332945</v>
+        <v>658509.44235795</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>653257.350179059</v>
+        <v>653257.26856996</v>
       </c>
       <c r="K161" s="11" t="n">
-        <v>629321.262840044</v>
+        <v>629321.332716557</v>
       </c>
       <c r="L161" s="12" t="n">
-        <v>629321.262840044</v>
+        <v>629321.332716557</v>
       </c>
       <c r="M161" s="13" t="n">
-        <v>629321.262840044</v>
+        <v>629321.332716557</v>
       </c>
       <c r="N161" s="14" t="n">
-        <v>629321.262840044</v>
+        <v>629321.332716557</v>
       </c>
       <c r="O161" s="15" t="n">
-        <v>0.0292413754979987</v>
+        <v>0.0292415114428569</v>
       </c>
       <c r="P161" s="16" t="n">
-        <v>0.00194063425002255</v>
+        <v>0.0019407534033391</v>
       </c>
       <c r="Q161" s="17" t="n">
-        <v>0.0296731023399226</v>
+        <v>0.0296732423186961</v>
       </c>
       <c r="R161" s="18" t="n">
-        <v>1.0021385332299</v>
+        <v>1.00213869544614</v>
       </c>
       <c r="S161" s="19" t="n">
-        <v>0.955676959515352</v>
+        <v>0.955675488058489</v>
       </c>
     </row>
     <row r="162">
@@ -11379,46 +11379,46 @@
         <v>611607.33658973</v>
       </c>
       <c r="F162" s="6" t="n">
-        <v>-35316.2375660842</v>
+        <v>-35316.0099770902</v>
       </c>
       <c r="G162" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H162" s="8" t="n">
-        <v>650523.088242741</v>
+        <v>650522.981671719</v>
       </c>
       <c r="I162" s="9" t="n">
-        <v>664221.877675041</v>
+        <v>664223.331180633</v>
       </c>
       <c r="J162" s="10" t="n">
-        <v>659490.065645259</v>
+        <v>659489.97657415</v>
       </c>
       <c r="K162" s="11" t="n">
-        <v>646923.574155814</v>
+        <v>646923.34656682</v>
       </c>
       <c r="L162" s="12" t="n">
-        <v>646923.574155814</v>
+        <v>646923.34656682</v>
       </c>
       <c r="M162" s="13" t="n">
-        <v>646923.574155814</v>
+        <v>646923.34656682</v>
       </c>
       <c r="N162" s="14" t="n">
-        <v>646923.574155814</v>
+        <v>646923.34656682</v>
       </c>
       <c r="O162" s="15" t="n">
-        <v>0.0275862860728532</v>
+        <v>0.0275858232360934</v>
       </c>
       <c r="P162" s="16" t="n">
-        <v>0.0573039609263688</v>
+        <v>0.0573036565514391</v>
       </c>
       <c r="Q162" s="17" t="n">
-        <v>0.0279703108017249</v>
+        <v>0.0279698350193871</v>
       </c>
       <c r="R162" s="18" t="n">
-        <v>0.994466738918291</v>
+        <v>0.994466551979995</v>
       </c>
       <c r="S162" s="19" t="n">
-        <v>0.973957040409786</v>
+        <v>0.973954566481332</v>
       </c>
     </row>
     <row r="163">
@@ -11438,46 +11438,46 @@
         <v>733730.773968903</v>
       </c>
       <c r="F163" s="6" t="n">
-        <v>55499.9355376401</v>
+        <v>55499.9049506251</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>0.562013015853083</v>
+        <v>0.562012863089362</v>
       </c>
       <c r="H163" s="8" t="n">
-        <v>669164.077597383</v>
+        <v>669164.072876947</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>669790.348248357</v>
+        <v>669792.21948527</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>666219.747528596</v>
+        <v>666219.654905444</v>
       </c>
       <c r="K163" s="11" t="n">
-        <v>678230.838431263</v>
+        <v>678230.869018278</v>
       </c>
       <c r="L163" s="12" t="n">
-        <v>674259.715197651</v>
+        <v>674259.728935384</v>
       </c>
       <c r="M163" s="13" t="n">
-        <v>674259.715197651</v>
+        <v>674259.728935384</v>
       </c>
       <c r="N163" s="14" t="n">
-        <v>674259.715197651</v>
+        <v>674259.728935384</v>
       </c>
       <c r="O163" s="15" t="n">
-        <v>0.0413872066943215</v>
+        <v>0.0413875788709055</v>
       </c>
       <c r="P163" s="16" t="n">
-        <v>0.123742894656645</v>
+        <v>0.123742973417081</v>
       </c>
       <c r="Q163" s="17" t="n">
-        <v>0.0422555957672559</v>
+        <v>0.0422559836704555</v>
       </c>
       <c r="R163" s="18" t="n">
-        <v>1.00761492998632</v>
+        <v>1.00761495762396</v>
       </c>
       <c r="S163" s="19" t="n">
-        <v>1.00667278494081</v>
+        <v>1.0066699930518</v>
       </c>
     </row>
     <row r="164">
@@ -11497,46 +11497,46 @@
         <v>668566.509488986</v>
       </c>
       <c r="F164" s="6" t="n">
-        <v>-5886.85712141578</v>
+        <v>-5887.04159871633</v>
       </c>
       <c r="G164" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H164" s="8" t="n">
-        <v>676786.677520392</v>
+        <v>676786.898237781</v>
       </c>
       <c r="I164" s="9" t="n">
-        <v>675167.34632286</v>
+        <v>675169.687592306</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>673151.998858962</v>
+        <v>673151.907717278</v>
       </c>
       <c r="K164" s="11" t="n">
-        <v>674453.366610402</v>
+        <v>674453.551087702</v>
       </c>
       <c r="L164" s="12" t="n">
-        <v>674453.366610402</v>
+        <v>674453.551087702</v>
       </c>
       <c r="M164" s="13" t="n">
-        <v>674453.366610402</v>
+        <v>674453.551087702</v>
       </c>
       <c r="N164" s="14" t="n">
-        <v>674453.366610402</v>
+        <v>674453.551087702</v>
       </c>
       <c r="O164" s="15" t="n">
-        <v>0.000287164730132336</v>
+        <v>0.000287417876761649</v>
       </c>
       <c r="P164" s="16" t="n">
-        <v>0.103516647836276</v>
+        <v>0.103516977160246</v>
       </c>
       <c r="Q164" s="17" t="n">
-        <v>0.000287205965870507</v>
+        <v>0.000287459185237093</v>
       </c>
       <c r="R164" s="18" t="n">
-        <v>0.996552368733765</v>
+        <v>0.996552316310859</v>
       </c>
       <c r="S164" s="19" t="n">
-        <v>0.998942514450162</v>
+        <v>0.998939323672604</v>
       </c>
     </row>
     <row r="165">
@@ -11556,46 +11556,46 @@
         <v>668190.097719574</v>
       </c>
       <c r="F165" s="6" t="n">
-        <v>-13359.7522339428</v>
+        <v>-13359.9162816858</v>
       </c>
       <c r="G165" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H165" s="8" t="n">
-        <v>682784.454800938</v>
+        <v>682784.437379384</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>680309.244522861</v>
+        <v>680312.108015596</v>
       </c>
       <c r="J165" s="10" t="n">
-        <v>680032.622504595</v>
+        <v>680032.539533239</v>
       </c>
       <c r="K165" s="11" t="n">
-        <v>681549.849953517</v>
+        <v>681550.01400126</v>
       </c>
       <c r="L165" s="12" t="n">
-        <v>681549.849953517</v>
+        <v>681550.01400126</v>
       </c>
       <c r="M165" s="13" t="n">
-        <v>681549.849953517</v>
+        <v>681550.01400126</v>
       </c>
       <c r="N165" s="14" t="n">
-        <v>681549.849953517</v>
+        <v>681550.01400126</v>
       </c>
       <c r="O165" s="15" t="n">
-        <v>0.0104668603206014</v>
+        <v>0.0104668274974843</v>
       </c>
       <c r="P165" s="16" t="n">
-        <v>0.0829919314624326</v>
+        <v>0.0829920718867891</v>
       </c>
       <c r="Q165" s="17" t="n">
-        <v>0.0105218295206677</v>
+        <v>0.010521796352192</v>
       </c>
       <c r="R165" s="18" t="n">
-        <v>0.998191808793038</v>
+        <v>0.998192074525216</v>
       </c>
       <c r="S165" s="19" t="n">
-        <v>1.00182359043427</v>
+        <v>1.00181961480779</v>
       </c>
     </row>
     <row r="166">
@@ -11615,46 +11615,46 @@
         <v>662325.585972695</v>
       </c>
       <c r="F166" s="6" t="n">
-        <v>-36291.4810588085</v>
+        <v>-36290.944013146</v>
       </c>
       <c r="G166" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H166" s="8" t="n">
-        <v>697896.470812913</v>
+        <v>697896.17786606</v>
       </c>
       <c r="I166" s="9" t="n">
-        <v>685171.969235349</v>
+        <v>685175.405683676</v>
       </c>
       <c r="J166" s="10" t="n">
-        <v>686613.928172492</v>
+        <v>686613.863093763</v>
       </c>
       <c r="K166" s="11" t="n">
-        <v>698617.067031504</v>
+        <v>698616.529985841</v>
       </c>
       <c r="L166" s="12" t="n">
-        <v>698617.067031504</v>
+        <v>698616.529985841</v>
       </c>
       <c r="M166" s="13" t="n">
-        <v>698617.067031504</v>
+        <v>698616.529985841</v>
       </c>
       <c r="N166" s="14" t="n">
-        <v>698617.067031504</v>
+        <v>698616.529985841</v>
       </c>
       <c r="O166" s="15" t="n">
-        <v>0.0247333665465029</v>
+        <v>0.0247323571213522</v>
       </c>
       <c r="P166" s="16" t="n">
-        <v>0.0799066457628252</v>
+        <v>0.0799061955227822</v>
       </c>
       <c r="Q166" s="17" t="n">
-        <v>0.0250417736562498</v>
+        <v>0.0250407389538252</v>
       </c>
       <c r="R166" s="18" t="n">
-        <v>1.00103252595296</v>
+        <v>1.00103217662258</v>
       </c>
       <c r="S166" s="19" t="n">
-        <v>1.01962295365229</v>
+        <v>1.01961705599861</v>
       </c>
     </row>
     <row r="167">
@@ -11674,46 +11674,46 @@
         <v>766332.954571613</v>
       </c>
       <c r="F167" s="6" t="n">
-        <v>54624.19029005</v>
+        <v>54624.1583093704</v>
       </c>
       <c r="G167" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H167" s="8" t="n">
-        <v>711304.010652527</v>
+        <v>711303.983742948</v>
       </c>
       <c r="I167" s="9" t="n">
-        <v>689712.22222571</v>
+        <v>689716.279216326</v>
       </c>
       <c r="J167" s="10" t="n">
-        <v>692655.811706891</v>
+        <v>692655.778511629</v>
       </c>
       <c r="K167" s="11" t="n">
-        <v>711708.764281563</v>
+        <v>711708.796262242</v>
       </c>
       <c r="L167" s="12" t="n">
-        <v>711708.764281563</v>
+        <v>711708.796262242</v>
       </c>
       <c r="M167" s="13" t="n">
-        <v>711708.764281563</v>
+        <v>711708.796262242</v>
       </c>
       <c r="N167" s="14" t="n">
-        <v>711708.764281563</v>
+        <v>711708.796262242</v>
       </c>
       <c r="O167" s="15" t="n">
-        <v>0.0185660263937825</v>
+        <v>0.0185668400559421</v>
       </c>
       <c r="P167" s="16" t="n">
-        <v>0.0555409855280087</v>
+        <v>0.0555410114526458</v>
       </c>
       <c r="Q167" s="17" t="n">
-        <v>0.0187394466409001</v>
+        <v>0.0187402755509756</v>
       </c>
       <c r="R167" s="18" t="n">
-        <v>1.0005690304328</v>
+        <v>1.0005691132463</v>
       </c>
       <c r="S167" s="19" t="n">
-        <v>1.03189234777495</v>
+        <v>1.03188632443315</v>
       </c>
     </row>
     <row r="168">
@@ -11733,46 +11733,46 @@
         <v>711417.391930105</v>
       </c>
       <c r="F168" s="6" t="n">
-        <v>-5275.13042588564</v>
+        <v>-5275.62794293304</v>
       </c>
       <c r="G168" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H168" s="8" t="n">
-        <v>716562.701020855</v>
+        <v>716563.021735347</v>
       </c>
       <c r="I168" s="9" t="n">
-        <v>693895.108445449</v>
+        <v>693899.827936014</v>
       </c>
       <c r="J168" s="10" t="n">
-        <v>697978.184646329</v>
+        <v>697978.199234077</v>
       </c>
       <c r="K168" s="11" t="n">
-        <v>716692.522355991</v>
+        <v>716693.019873038</v>
       </c>
       <c r="L168" s="12" t="n">
-        <v>716692.522355991</v>
+        <v>716693.019873038</v>
       </c>
       <c r="M168" s="13" t="n">
-        <v>716692.522355991</v>
+        <v>716693.019873038</v>
       </c>
       <c r="N168" s="14" t="n">
-        <v>716692.522355991</v>
+        <v>716693.019873038</v>
       </c>
       <c r="O168" s="15" t="n">
-        <v>0.006978120706504</v>
+        <v>0.00697876995598783</v>
       </c>
       <c r="P168" s="16" t="n">
-        <v>0.0626272442791267</v>
+        <v>0.0626276912875845</v>
       </c>
       <c r="Q168" s="17" t="n">
-        <v>0.00700252452203376</v>
+        <v>0.00700317831811526</v>
       </c>
       <c r="R168" s="18" t="n">
-        <v>1.0001811723314</v>
+        <v>1.00018141898723</v>
       </c>
       <c r="S168" s="19" t="n">
-        <v>1.03285426519523</v>
+        <v>1.03284795732667</v>
       </c>
     </row>
     <row r="169">
@@ -11792,46 +11792,46 @@
         <v>703050.456407993</v>
       </c>
       <c r="F169" s="6" t="n">
-        <v>-11897.8244469156</v>
+        <v>-11898.112429874</v>
       </c>
       <c r="G169" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H169" s="8" t="n">
-        <v>715431.08778301</v>
+        <v>715431.78287868</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>697699.480684859</v>
+        <v>697704.896488361</v>
       </c>
       <c r="J169" s="10" t="n">
-        <v>702496.223292214</v>
+        <v>702496.303797098</v>
       </c>
       <c r="K169" s="11" t="n">
-        <v>714948.280854908</v>
+        <v>714948.568837867</v>
       </c>
       <c r="L169" s="12" t="n">
-        <v>714948.280854908</v>
+        <v>714948.568837867</v>
       </c>
       <c r="M169" s="13" t="n">
-        <v>714948.280854908</v>
+        <v>714948.568837867</v>
       </c>
       <c r="N169" s="14" t="n">
-        <v>714948.280854908</v>
+        <v>714948.568837867</v>
       </c>
       <c r="O169" s="15" t="n">
-        <v>-0.00243670389976355</v>
+        <v>-0.00243699528188768</v>
       </c>
       <c r="P169" s="16" t="n">
-        <v>0.0490036508755292</v>
+        <v>0.0490038209236177</v>
       </c>
       <c r="Q169" s="17" t="n">
-        <v>-0.00243373754667986</v>
+        <v>-0.00243402821961403</v>
       </c>
       <c r="R169" s="18" t="n">
-        <v>0.999325152434181</v>
+        <v>0.99932458404508</v>
       </c>
       <c r="S169" s="19" t="n">
-        <v>1.02472239215818</v>
+        <v>1.0247148507002</v>
       </c>
     </row>
     <row r="170">
@@ -11851,46 +11851,46 @@
         <v>672685.993630504</v>
       </c>
       <c r="F170" s="6" t="n">
-        <v>-37503.3684933611</v>
+        <v>-37502.3259685763</v>
       </c>
       <c r="G170" s="7" t="n">
-        <v>0.900069498159122</v>
+        <v>0.900456265482922</v>
       </c>
       <c r="H170" s="8" t="n">
-        <v>707157.417898837</v>
+        <v>707157.988826543</v>
       </c>
       <c r="I170" s="9" t="n">
-        <v>701118.440117925</v>
+        <v>701124.575263948</v>
       </c>
       <c r="J170" s="10" t="n">
-        <v>706218.675634503</v>
+        <v>706218.844839878</v>
       </c>
       <c r="K170" s="11" t="n">
-        <v>710189.362123865</v>
+        <v>710188.31959908</v>
       </c>
       <c r="L170" s="12" t="n">
-        <v>709886.378415905</v>
+        <v>709886.66915716</v>
       </c>
       <c r="M170" s="13" t="n">
-        <v>709886.378415905</v>
+        <v>709886.66915716</v>
       </c>
       <c r="N170" s="14" t="n">
-        <v>709886.378415905</v>
+        <v>709886.66915716</v>
       </c>
       <c r="O170" s="15" t="n">
-        <v>-0.00710527878008772</v>
+        <v>-0.00710527202232742</v>
       </c>
       <c r="P170" s="16" t="n">
-        <v>0.0161308847381665</v>
+        <v>0.0161320820329678</v>
       </c>
       <c r="Q170" s="17" t="n">
-        <v>-0.00708009596575376</v>
+        <v>-0.00708008925583903</v>
       </c>
       <c r="R170" s="18" t="n">
-        <v>1.00385905662303</v>
+        <v>1.00385865729262</v>
       </c>
       <c r="S170" s="19" t="n">
-        <v>1.01250564497563</v>
+        <v>1.0124971997878</v>
       </c>
     </row>
     <row r="171">
@@ -11910,46 +11910,46 @@
         <v>730838.272592776</v>
       </c>
       <c r="F171" s="6" t="n">
-        <v>54045.6251948423</v>
+        <v>54045.7394249439</v>
       </c>
       <c r="G171" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H171" s="8" t="n">
-        <v>701246.123409486</v>
+        <v>701246.431415367</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>704155.868418739</v>
+        <v>704162.731948577</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v>709216.549950966</v>
+        <v>709216.836326808</v>
       </c>
       <c r="K171" s="11" t="n">
-        <v>676792.647397934</v>
+        <v>676792.533167832</v>
       </c>
       <c r="L171" s="12" t="n">
-        <v>701246.123409486</v>
+        <v>701246.431415367</v>
       </c>
       <c r="M171" s="13" t="n">
-        <v>701246.123409486</v>
+        <v>701246.431415367</v>
       </c>
       <c r="N171" s="14" t="n">
-        <v>701246.123409486</v>
+        <v>701246.431415367</v>
       </c>
       <c r="O171" s="15" t="n">
-        <v>-0.0122459981221851</v>
+        <v>-0.0122459684559648</v>
       </c>
       <c r="P171" s="16" t="n">
-        <v>-0.0147007334982564</v>
+        <v>-0.0147003450032113</v>
       </c>
       <c r="Q171" s="17" t="n">
-        <v>-0.0121713210298516</v>
+        <v>-0.012171291724708</v>
       </c>
       <c r="R171" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S171" s="19" t="n">
-        <v>0.99586775437122</v>
+        <v>0.995858484976704</v>
       </c>
     </row>
     <row r="172">
@@ -11969,46 +11969,46 @@
         <v>703461.652530196</v>
       </c>
       <c r="F172" s="6" t="n">
-        <v>-4657.05276153612</v>
+        <v>-4657.95456327896</v>
       </c>
       <c r="G172" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H172" s="8" t="n">
-        <v>707330.316025566</v>
+        <v>707331.253584538</v>
       </c>
       <c r="I172" s="9" t="n">
-        <v>706821.127222831</v>
+        <v>706828.710536733</v>
       </c>
       <c r="J172" s="10" t="n">
-        <v>711579.19303328</v>
+        <v>711579.631343865</v>
       </c>
       <c r="K172" s="11" t="n">
-        <v>708118.705291732</v>
+        <v>708119.607093475</v>
       </c>
       <c r="L172" s="12" t="n">
-        <v>708118.705291732</v>
+        <v>708119.607093475</v>
       </c>
       <c r="M172" s="13" t="n">
-        <v>708118.705291732</v>
+        <v>708119.607093475</v>
       </c>
       <c r="N172" s="14" t="n">
-        <v>708118.705291732</v>
+        <v>708119.607093475</v>
       </c>
       <c r="O172" s="15" t="n">
-        <v>0.00975281377449511</v>
+        <v>0.00975364806503355</v>
       </c>
       <c r="P172" s="16" t="n">
-        <v>-0.0119630340722315</v>
+        <v>-0.0119624616702442</v>
       </c>
       <c r="Q172" s="17" t="n">
-        <v>0.0098005274508064</v>
+        <v>0.00980136991818359</v>
       </c>
       <c r="R172" s="18" t="n">
-        <v>1.00111459843909</v>
+        <v>1.0011145464094</v>
       </c>
       <c r="S172" s="19" t="n">
-        <v>1.00183579411951</v>
+        <v>1.00182632162149</v>
       </c>
     </row>
     <row r="173">
@@ -12028,46 +12028,46 @@
         <v>706958.039082319</v>
       </c>
       <c r="F173" s="6" t="n">
-        <v>-11463.9289498805</v>
+        <v>-11465.302996061</v>
       </c>
       <c r="G173" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H173" s="8" t="n">
-        <v>715749.07258689</v>
+        <v>715749.203219501</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>709121.759575097</v>
+        <v>709130.032335064</v>
       </c>
       <c r="J173" s="10" t="n">
-        <v>713356.099540416</v>
+        <v>713356.730952468</v>
       </c>
       <c r="K173" s="11" t="n">
-        <v>718421.968032199</v>
+        <v>718423.34207838</v>
       </c>
       <c r="L173" s="12" t="n">
-        <v>718421.968032199</v>
+        <v>718423.34207838</v>
       </c>
       <c r="M173" s="13" t="n">
-        <v>718421.968032199</v>
+        <v>718423.34207838</v>
       </c>
       <c r="N173" s="14" t="n">
-        <v>718421.968032199</v>
+        <v>718423.34207838</v>
       </c>
       <c r="O173" s="15" t="n">
-        <v>0.0144453531485609</v>
+        <v>0.0144459922191054</v>
       </c>
       <c r="P173" s="16" t="n">
-        <v>0.00485865519270501</v>
+        <v>0.00486017231443858</v>
       </c>
       <c r="Q173" s="17" t="n">
-        <v>0.014550191462916</v>
+        <v>0.0145508398322665</v>
       </c>
       <c r="R173" s="18" t="n">
-        <v>1.00373440294606</v>
+        <v>1.00373613948412</v>
       </c>
       <c r="S173" s="19" t="n">
-        <v>1.01311510799313</v>
+        <v>1.01310522657278</v>
       </c>
     </row>
     <row r="174">
@@ -12087,46 +12087,46 @@
         <v>677085.529173151</v>
       </c>
       <c r="F174" s="6" t="n">
-        <v>-38172.6348912062</v>
+        <v>-38169.5713006668</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H174" s="8" t="n">
-        <v>717930.719970636</v>
+        <v>717929.353259878</v>
       </c>
       <c r="I174" s="9" t="n">
-        <v>711066.119506727</v>
+        <v>711075.025460569</v>
       </c>
       <c r="J174" s="10" t="n">
-        <v>714579.461692635</v>
+        <v>714580.336092785</v>
       </c>
       <c r="K174" s="11" t="n">
-        <v>715258.164064357</v>
+        <v>715255.100473818</v>
       </c>
       <c r="L174" s="12" t="n">
-        <v>715258.164064357</v>
+        <v>715255.100473818</v>
       </c>
       <c r="M174" s="13" t="n">
-        <v>715258.164064357</v>
+        <v>715255.100473818</v>
       </c>
       <c r="N174" s="14" t="n">
-        <v>715258.164064357</v>
+        <v>715255.100473818</v>
       </c>
       <c r="O174" s="15" t="n">
-        <v>-0.00441354948396926</v>
+        <v>-0.00441974527611492</v>
       </c>
       <c r="P174" s="16" t="n">
-        <v>0.00756710624655077</v>
+        <v>0.00756237798215231</v>
       </c>
       <c r="Q174" s="17" t="n">
-        <v>-0.0044038240875458</v>
+        <v>-0.00440999257540342</v>
       </c>
       <c r="R174" s="18" t="n">
-        <v>0.996277418096292</v>
+        <v>0.996275047434796</v>
       </c>
       <c r="S174" s="19" t="n">
-        <v>1.0058954356601</v>
+        <v>1.00587852879595</v>
       </c>
     </row>
     <row r="175">
@@ -12146,46 +12146,46 @@
         <v>776486.60279942</v>
       </c>
       <c r="F175" s="6" t="n">
-        <v>54401.0019806777</v>
+        <v>54400.6037280793</v>
       </c>
       <c r="G175" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H175" s="8" t="n">
-        <v>721719.230278475</v>
+        <v>721718.710580521</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>712668.373679199</v>
+        <v>712677.826348837</v>
       </c>
       <c r="J175" s="10" t="n">
-        <v>715306.801052659</v>
+        <v>715307.980760613</v>
       </c>
       <c r="K175" s="11" t="n">
-        <v>722085.600818742</v>
+        <v>722085.999071341</v>
       </c>
       <c r="L175" s="12" t="n">
-        <v>722085.600818742</v>
+        <v>722085.999071341</v>
       </c>
       <c r="M175" s="13" t="n">
-        <v>722085.600818742</v>
+        <v>722085.999071341</v>
       </c>
       <c r="N175" s="14" t="n">
-        <v>722085.600818742</v>
+        <v>722085.999071341</v>
       </c>
       <c r="O175" s="15" t="n">
-        <v>0.00950014640994391</v>
+        <v>0.00950498114545707</v>
       </c>
       <c r="P175" s="16" t="n">
-        <v>0.0297177791271543</v>
+        <v>0.0297178947690497</v>
       </c>
       <c r="Q175" s="17" t="n">
-        <v>0.0095454160433337</v>
+        <v>0.0095502969402077</v>
       </c>
       <c r="R175" s="18" t="n">
-        <v>1.00050763582969</v>
+        <v>1.00050890809042</v>
       </c>
       <c r="S175" s="19" t="n">
-        <v>1.01321403823622</v>
+        <v>1.01320115818771</v>
       </c>
     </row>
     <row r="176">
@@ -12205,46 +12205,46 @@
         <v>721458.944216182</v>
       </c>
       <c r="F176" s="6" t="n">
-        <v>-4505.97535752763</v>
+        <v>-4507.43440759956</v>
       </c>
       <c r="G176" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H176" s="8" t="n">
-        <v>724815.409618577</v>
+        <v>724817.620305716</v>
       </c>
       <c r="I176" s="9" t="n">
-        <v>713945.308781837</v>
+        <v>713955.183982339</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>715599.032695067</v>
+        <v>715600.572773655</v>
       </c>
       <c r="K176" s="11" t="n">
-        <v>725964.91957371</v>
+        <v>725966.378623782</v>
       </c>
       <c r="L176" s="12" t="n">
-        <v>725964.91957371</v>
+        <v>725966.378623782</v>
       </c>
       <c r="M176" s="13" t="n">
-        <v>725964.91957371</v>
+        <v>725966.378623782</v>
       </c>
       <c r="N176" s="14" t="n">
-        <v>725964.91957371</v>
+        <v>725966.378623782</v>
       </c>
       <c r="O176" s="15" t="n">
-        <v>0.00535800095509338</v>
+        <v>0.00535945923017619</v>
       </c>
       <c r="P176" s="16" t="n">
-        <v>0.0252022918595622</v>
+        <v>0.0252030467050051</v>
       </c>
       <c r="Q176" s="17" t="n">
-        <v>0.00537238071299173</v>
+        <v>0.00537384682355246</v>
       </c>
       <c r="R176" s="18" t="n">
-        <v>1.00158593476336</v>
+        <v>1.00158489292462</v>
       </c>
       <c r="S176" s="19" t="n">
-        <v>1.01683547835391</v>
+        <v>1.0168234574255</v>
       </c>
     </row>
     <row r="177">
@@ -12264,46 +12264,46 @@
         <v>706597.345022507</v>
       </c>
       <c r="F177" s="6" t="n">
-        <v>-12349.0344192221</v>
+        <v>-12351.3543078666</v>
       </c>
       <c r="G177" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H177" s="8" t="n">
-        <v>718805.619825272</v>
+        <v>718805.759224064</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>714919.597270929</v>
+        <v>714929.727451497</v>
       </c>
       <c r="J177" s="10" t="n">
-        <v>715550.96569327</v>
+        <v>715552.910041166</v>
       </c>
       <c r="K177" s="11" t="n">
-        <v>718946.379441729</v>
+        <v>718948.699330374</v>
       </c>
       <c r="L177" s="12" t="n">
-        <v>718946.379441729</v>
+        <v>718948.699330374</v>
       </c>
       <c r="M177" s="13" t="n">
-        <v>718946.379441729</v>
+        <v>718948.699330374</v>
       </c>
       <c r="N177" s="14" t="n">
-        <v>718946.379441729</v>
+        <v>718948.699330374</v>
       </c>
       <c r="O177" s="15" t="n">
-        <v>-0.00971491514703616</v>
+        <v>-0.00971369816865704</v>
       </c>
       <c r="P177" s="16" t="n">
-        <v>0.000729949017241438</v>
+        <v>0.000731264174231638</v>
       </c>
       <c r="Q177" s="17" t="n">
-        <v>-0.0096678778033823</v>
+        <v>-0.00966667258986809</v>
       </c>
       <c r="R177" s="18" t="n">
-        <v>1.00019582431269</v>
+        <v>1.00019885776439</v>
       </c>
       <c r="S177" s="19" t="n">
-        <v>1.0056324965579</v>
+        <v>1.00562149218945</v>
       </c>
     </row>
     <row r="178">
@@ -12323,46 +12323,46 @@
         <v>671066.046635063</v>
       </c>
       <c r="F178" s="6" t="n">
-        <v>-37669.4237177219</v>
+        <v>-37664.368991795</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H178" s="8" t="n">
-        <v>710248.48314784</v>
+        <v>710246.392083369</v>
       </c>
       <c r="I178" s="9" t="n">
-        <v>715621.423859504</v>
+        <v>715631.592843386</v>
       </c>
       <c r="J178" s="10" t="n">
-        <v>715309.23855507</v>
+        <v>715311.619501653</v>
       </c>
       <c r="K178" s="11" t="n">
-        <v>708735.470352785</v>
+        <v>708730.415626858</v>
       </c>
       <c r="L178" s="12" t="n">
-        <v>708735.470352785</v>
+        <v>708730.415626858</v>
       </c>
       <c r="M178" s="13" t="n">
-        <v>708735.470352785</v>
+        <v>708730.415626858</v>
       </c>
       <c r="N178" s="14" t="n">
-        <v>708735.470352785</v>
+        <v>708730.415626858</v>
       </c>
       <c r="O178" s="15" t="n">
-        <v>-0.014304423916151</v>
+        <v>-0.0143147827605432</v>
       </c>
       <c r="P178" s="16" t="n">
-        <v>-0.00911935583441381</v>
+        <v>-0.00912217870608367</v>
       </c>
       <c r="Q178" s="17" t="n">
-        <v>-0.014202601725143</v>
+        <v>-0.0142128133941033</v>
       </c>
       <c r="R178" s="18" t="n">
-        <v>0.997869741603179</v>
+        <v>0.997865562608401</v>
       </c>
       <c r="S178" s="19" t="n">
-        <v>0.990377658805151</v>
+        <v>0.990356522426424</v>
       </c>
     </row>
     <row r="179">
@@ -12382,46 +12382,46 @@
         <v>760576.868348004</v>
       </c>
       <c r="F179" s="6" t="n">
-        <v>55622.1741917762</v>
+        <v>55621.1782845195</v>
       </c>
       <c r="G179" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H179" s="8" t="n">
-        <v>702939.590579461</v>
+        <v>702938.776970415</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>716083.489999454</v>
+        <v>716093.428102503</v>
       </c>
       <c r="J179" s="10" t="n">
-        <v>715037.466857014</v>
+        <v>715040.30704007</v>
       </c>
       <c r="K179" s="11" t="n">
-        <v>704954.694156228</v>
+        <v>704955.690063485</v>
       </c>
       <c r="L179" s="12" t="n">
-        <v>704954.694156228</v>
+        <v>704955.690063485</v>
       </c>
       <c r="M179" s="13" t="n">
-        <v>704954.694156228</v>
+        <v>704955.690063485</v>
       </c>
       <c r="N179" s="14" t="n">
-        <v>704954.694156228</v>
+        <v>704955.690063485</v>
       </c>
       <c r="O179" s="15" t="n">
-        <v>-0.00534881730866089</v>
+        <v>-0.00534027252438956</v>
       </c>
       <c r="P179" s="16" t="n">
-        <v>-0.0237242047800017</v>
+        <v>-0.0237233640174259</v>
       </c>
       <c r="Q179" s="17" t="n">
-        <v>-0.00533453785609861</v>
+        <v>-0.00532603861799041</v>
       </c>
       <c r="R179" s="18" t="n">
-        <v>1.00286668101181</v>
+        <v>1.0028692585459</v>
       </c>
       <c r="S179" s="19" t="n">
-        <v>0.984458801245041</v>
+        <v>0.98444652945841</v>
       </c>
     </row>
     <row r="180">
@@ -12441,46 +12441,46 @@
         <v>690879.798251683</v>
       </c>
       <c r="F180" s="6" t="n">
-        <v>-5740.96114564641</v>
+        <v>-5742.73138823935</v>
       </c>
       <c r="G180" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H180" s="8" t="n">
-        <v>697900.863708725</v>
+        <v>697901.538508668</v>
       </c>
       <c r="I180" s="9" t="n">
-        <v>716334.193421725</v>
+        <v>716343.567937587</v>
       </c>
       <c r="J180" s="10" t="n">
-        <v>714866.397334636</v>
+        <v>714869.672521994</v>
       </c>
       <c r="K180" s="11" t="n">
-        <v>696620.75939733</v>
+        <v>696622.529639923</v>
       </c>
       <c r="L180" s="12" t="n">
-        <v>696620.75939733</v>
+        <v>696622.529639923</v>
       </c>
       <c r="M180" s="13" t="n">
-        <v>696620.75939733</v>
+        <v>696622.529639923</v>
       </c>
       <c r="N180" s="14" t="n">
-        <v>696620.75939733</v>
+        <v>696622.529639923</v>
       </c>
       <c r="O180" s="15" t="n">
-        <v>-0.0118923786214697</v>
+        <v>-0.0118912501633652</v>
       </c>
       <c r="P180" s="16" t="n">
-        <v>-0.0404209065551145</v>
+        <v>-0.0404203966573307</v>
       </c>
       <c r="Q180" s="17" t="n">
-        <v>-0.0118219437759375</v>
+        <v>-0.0118208286577721</v>
       </c>
       <c r="R180" s="18" t="n">
-        <v>0.998165779155807</v>
+        <v>0.998167350552804</v>
       </c>
       <c r="S180" s="19" t="n">
-        <v>0.972480115837791</v>
+        <v>0.972469860580388</v>
       </c>
     </row>
     <row r="181">
@@ -12500,46 +12500,46 @@
         <v>686701.470618711</v>
       </c>
       <c r="F181" s="6" t="n">
-        <v>-13492.6955719484</v>
+        <v>-13495.906195128</v>
       </c>
       <c r="G181" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H181" s="8" t="n">
-        <v>701394.839822896</v>
+        <v>701404.263479165</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>716394.976359861</v>
+        <v>716403.385971101</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>714876.362859966</v>
+        <v>714879.992728121</v>
       </c>
       <c r="K181" s="11" t="n">
-        <v>700194.166190659</v>
+        <v>700197.376813838</v>
       </c>
       <c r="L181" s="12" t="n">
-        <v>700194.166190659</v>
+        <v>700197.376813838</v>
       </c>
       <c r="M181" s="13" t="n">
-        <v>700194.166190659</v>
+        <v>700197.376813838</v>
       </c>
       <c r="N181" s="14" t="n">
-        <v>700194.166190659</v>
+        <v>700197.376813838</v>
       </c>
       <c r="O181" s="15" t="n">
-        <v>0.0051165183353617</v>
+        <v>0.00511856247521053</v>
       </c>
       <c r="P181" s="16" t="n">
-        <v>-0.0260829093619352</v>
+        <v>-0.0260815862578234</v>
       </c>
       <c r="Q181" s="17" t="n">
-        <v>0.00512963006790179</v>
+        <v>0.00513168469553182</v>
       </c>
       <c r="R181" s="18" t="n">
-        <v>0.998288163008812</v>
+        <v>0.998279328016428</v>
       </c>
       <c r="S181" s="19" t="n">
-        <v>0.977385645204379</v>
+        <v>0.977378653598497</v>
       </c>
     </row>
     <row r="182">
@@ -12559,46 +12559,46 @@
         <v>672749.811391699</v>
       </c>
       <c r="F182" s="6" t="n">
-        <v>-35845.5937296366</v>
+        <v>-35838.8889536653</v>
       </c>
       <c r="G182" s="7" t="n">
-        <v>0.0660559235067559</v>
+        <v>0.062712646304365</v>
       </c>
       <c r="H182" s="8" t="n">
-        <v>713342.498473123</v>
+        <v>713359.858035176</v>
       </c>
       <c r="I182" s="9" t="n">
-        <v>716274.960151144</v>
+        <v>716281.930176572</v>
       </c>
       <c r="J182" s="10" t="n">
-        <v>715056.468115347</v>
+        <v>715060.308724738</v>
       </c>
       <c r="K182" s="11" t="n">
-        <v>708595.405121336</v>
+        <v>708588.700345365</v>
       </c>
       <c r="L182" s="12" t="n">
-        <v>713028.924837798</v>
+        <v>713060.646110512</v>
       </c>
       <c r="M182" s="13" t="n">
-        <v>713028.924837798</v>
+        <v>713060.646110512</v>
       </c>
       <c r="N182" s="14" t="n">
-        <v>713028.924837798</v>
+        <v>713060.646110512</v>
       </c>
       <c r="O182" s="15" t="n">
-        <v>0.018164310533414</v>
+        <v>0.018204212280473</v>
       </c>
       <c r="P182" s="16" t="n">
-        <v>0.00605790829528563</v>
+        <v>0.00610984146888183</v>
       </c>
       <c r="Q182" s="17" t="n">
-        <v>0.0183302850364568</v>
+        <v>0.0183709190045906</v>
       </c>
       <c r="R182" s="18" t="n">
-        <v>0.999560416439514</v>
+        <v>0.999580559627384</v>
       </c>
       <c r="S182" s="19" t="n">
-        <v>0.995468171451002</v>
+        <v>0.99550277072428</v>
       </c>
     </row>
     <row r="183">
@@ -12618,46 +12618,46 @@
         <v>791235.96554167</v>
       </c>
       <c r="F183" s="6" t="n">
-        <v>56037.7986198276</v>
+        <v>56035.9632560903</v>
       </c>
       <c r="G183" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H183" s="8" t="n">
-        <v>723329.795970137</v>
+        <v>723341.474300222</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>715973.140626495</v>
+        <v>715978.119771804</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v>715322.406799778</v>
+        <v>715326.248498557</v>
       </c>
       <c r="K183" s="11" t="n">
-        <v>735198.166921843</v>
+        <v>735200.00228558</v>
       </c>
       <c r="L183" s="12" t="n">
-        <v>723329.795970137</v>
+        <v>723341.474300222</v>
       </c>
       <c r="M183" s="13" t="n">
-        <v>723329.795970137</v>
+        <v>723341.474300222</v>
       </c>
       <c r="N183" s="14" t="n">
-        <v>723329.795970137</v>
+        <v>723341.474300222</v>
       </c>
       <c r="O183" s="15" t="n">
-        <v>0.0143432801041786</v>
+        <v>0.0143149381403933</v>
       </c>
       <c r="P183" s="16" t="n">
-        <v>0.0260656492767988</v>
+        <v>0.0260807657784585</v>
       </c>
       <c r="Q183" s="17" t="n">
-        <v>0.0144466385212667</v>
+        <v>0.0144178875188075</v>
       </c>
       <c r="R183" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S183" s="19" t="n">
-        <v>1.01027504374983</v>
+        <v>1.01028432898308</v>
       </c>
     </row>
     <row r="184">
@@ -12677,46 +12677,46 @@
         <v>718281.265449782</v>
       </c>
       <c r="F184" s="6" t="n">
-        <v>-7445.87685164463</v>
+        <v>-7447.65730990614</v>
       </c>
       <c r="G184" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H184" s="8" t="n">
-        <v>724456.111537977</v>
+        <v>724458.236475064</v>
       </c>
       <c r="I184" s="9" t="n">
-        <v>715486.48484477</v>
+        <v>715488.860672061</v>
       </c>
       <c r="J184" s="10" t="n">
-        <v>715579.734895866</v>
+        <v>715583.441723222</v>
       </c>
       <c r="K184" s="11" t="n">
-        <v>725727.142301426</v>
+        <v>725728.922759688</v>
       </c>
       <c r="L184" s="12" t="n">
-        <v>725727.142301426</v>
+        <v>725728.922759688</v>
       </c>
       <c r="M184" s="13" t="n">
-        <v>725727.142301426</v>
+        <v>725728.922759688</v>
       </c>
       <c r="N184" s="14" t="n">
-        <v>725727.142301426</v>
+        <v>725728.922759688</v>
       </c>
       <c r="O184" s="15" t="n">
-        <v>0.00330883963940191</v>
+        <v>0.0032951478748752</v>
       </c>
       <c r="P184" s="16" t="n">
-        <v>0.0417822502580563</v>
+        <v>0.0417821587464446</v>
       </c>
       <c r="Q184" s="17" t="n">
-        <v>0.00331431989204023</v>
+        <v>0.00330058284266843</v>
       </c>
       <c r="R184" s="18" t="n">
-        <v>1.00175446206224</v>
+        <v>1.00175398141763</v>
       </c>
       <c r="S184" s="19" t="n">
-        <v>1.01431285939507</v>
+        <v>1.01431197975327</v>
       </c>
     </row>
     <row r="185">
@@ -12736,46 +12736,46 @@
         <v>703681.544169008</v>
       </c>
       <c r="F185" s="6" t="n">
-        <v>-13959.36392403</v>
+        <v>-13961.6554937205</v>
       </c>
       <c r="G185" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H185" s="8" t="n">
-        <v>718178.151160283</v>
+        <v>718178.019065748</v>
       </c>
       <c r="I185" s="9" t="n">
-        <v>714816.55777441</v>
+        <v>714815.660889185</v>
       </c>
       <c r="J185" s="10" t="n">
-        <v>715774.045332075</v>
+        <v>715777.594201384</v>
       </c>
       <c r="K185" s="11" t="n">
-        <v>717640.908093038</v>
+        <v>717643.199662729</v>
       </c>
       <c r="L185" s="12" t="n">
-        <v>717640.908093038</v>
+        <v>717643.199662729</v>
       </c>
       <c r="M185" s="13" t="n">
-        <v>717640.908093038</v>
+        <v>717643.199662729</v>
       </c>
       <c r="N185" s="14" t="n">
-        <v>717640.908093038</v>
+        <v>717643.199662729</v>
       </c>
       <c r="O185" s="15" t="n">
-        <v>-0.0112047911915994</v>
+        <v>-0.0112040513393454</v>
       </c>
       <c r="P185" s="16" t="n">
-        <v>0.0249170055176215</v>
+        <v>0.02491557870193</v>
       </c>
       <c r="Q185" s="17" t="n">
-        <v>-0.0111422513187879</v>
+        <v>-0.011141519709883</v>
       </c>
       <c r="R185" s="18" t="n">
-        <v>0.999251936213352</v>
+        <v>0.999255310815952</v>
       </c>
       <c r="S185" s="19" t="n">
-        <v>1.00395115402394</v>
+        <v>1.00395561950899</v>
       </c>
     </row>
     <row r="186">
@@ -12795,46 +12795,46 @@
         <v>677652.089115703</v>
       </c>
       <c r="F186" s="6" t="n">
-        <v>-32428.3737557426</v>
+        <v>-32423.6628994577</v>
       </c>
       <c r="G186" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H186" s="8" t="n">
-        <v>710868.335284049</v>
+        <v>710866.358617014</v>
       </c>
       <c r="I186" s="9" t="n">
-        <v>713971.32479477</v>
+        <v>713966.428473824</v>
       </c>
       <c r="J186" s="10" t="n">
-        <v>715901.668073892</v>
+        <v>715905.139140877</v>
       </c>
       <c r="K186" s="11" t="n">
-        <v>710080.462871445</v>
+        <v>710075.75201516</v>
       </c>
       <c r="L186" s="12" t="n">
-        <v>710080.462871445</v>
+        <v>710075.75201516</v>
       </c>
       <c r="M186" s="13" t="n">
-        <v>710080.462871445</v>
+        <v>710075.75201516</v>
       </c>
       <c r="N186" s="14" t="n">
-        <v>710080.462871445</v>
+        <v>710075.75201516</v>
       </c>
       <c r="O186" s="15" t="n">
-        <v>-0.0105910243361935</v>
+        <v>-0.0106008518083551</v>
       </c>
       <c r="P186" s="16" t="n">
-        <v>-0.00413512252258685</v>
+        <v>-0.00418603117649752</v>
       </c>
       <c r="Q186" s="17" t="n">
-        <v>-0.0105351369136452</v>
+        <v>-0.0105448608042613</v>
       </c>
       <c r="R186" s="18" t="n">
-        <v>0.998891676034087</v>
+        <v>0.998887826674775</v>
       </c>
       <c r="S186" s="19" t="n">
-        <v>0.99455039468925</v>
+        <v>0.994550617082962</v>
       </c>
     </row>
     <row r="187">
@@ -12854,46 +12854,46 @@
         <v>760703.280151656</v>
       </c>
       <c r="F187" s="6" t="n">
-        <v>53452.8141571245</v>
+        <v>53452.1960103145</v>
       </c>
       <c r="G187" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H187" s="8" t="n">
-        <v>706022.060046034</v>
+        <v>706020.915662084</v>
       </c>
       <c r="I187" s="9" t="n">
-        <v>712960.516504151</v>
+        <v>712950.838688359</v>
       </c>
       <c r="J187" s="10" t="n">
-        <v>715968.267400612</v>
+        <v>715971.83777684</v>
       </c>
       <c r="K187" s="11" t="n">
-        <v>707250.465994532</v>
+        <v>707251.084141342</v>
       </c>
       <c r="L187" s="12" t="n">
-        <v>707250.465994532</v>
+        <v>707251.084141342</v>
       </c>
       <c r="M187" s="13" t="n">
-        <v>707250.465994532</v>
+        <v>707251.084141342</v>
       </c>
       <c r="N187" s="14" t="n">
-        <v>707250.465994532</v>
+        <v>707251.084141342</v>
       </c>
       <c r="O187" s="15" t="n">
-        <v>-0.00399342253838565</v>
+        <v>-0.00398591424575426</v>
       </c>
       <c r="P187" s="16" t="n">
-        <v>-0.0222295971563558</v>
+        <v>-0.0222445286639292</v>
       </c>
       <c r="Q187" s="17" t="n">
-        <v>-0.00398545943014583</v>
+        <v>-0.00397798103343516</v>
       </c>
       <c r="R187" s="18" t="n">
-        <v>1.00173989740266</v>
+        <v>1.00174239665139</v>
       </c>
       <c r="S187" s="19" t="n">
-        <v>0.991991070504693</v>
+        <v>0.992005403124985</v>
       </c>
     </row>
     <row r="188">
@@ -12913,46 +12913,46 @@
         <v>694382.47577623</v>
       </c>
       <c r="F188" s="6" t="n">
-        <v>-8243.02913896229</v>
+        <v>-8243.91563082002</v>
       </c>
       <c r="G188" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H188" s="8" t="n">
-        <v>703935.941755356</v>
+        <v>703937.925411706</v>
       </c>
       <c r="I188" s="9" t="n">
-        <v>711791.431712154</v>
+        <v>711776.135122386</v>
       </c>
       <c r="J188" s="10" t="n">
-        <v>715950.401565516</v>
+        <v>715954.304408786</v>
       </c>
       <c r="K188" s="11" t="n">
-        <v>702625.504915193</v>
+        <v>702626.39140705</v>
       </c>
       <c r="L188" s="12" t="n">
-        <v>702625.504915193</v>
+        <v>702626.39140705</v>
       </c>
       <c r="M188" s="13" t="n">
-        <v>702625.504915193</v>
+        <v>702626.39140705</v>
       </c>
       <c r="N188" s="14" t="n">
-        <v>702625.504915193</v>
+        <v>702626.39140705</v>
       </c>
       <c r="O188" s="15" t="n">
-        <v>-0.00656082912919341</v>
+        <v>-0.00656044145889723</v>
       </c>
       <c r="P188" s="16" t="n">
-        <v>-0.0318324009668064</v>
+        <v>-0.0318335546897961</v>
       </c>
       <c r="Q188" s="17" t="n">
-        <v>-0.00653935388057403</v>
+        <v>-0.00653896874531645</v>
       </c>
       <c r="R188" s="18" t="n">
-        <v>0.99813841464481</v>
+        <v>0.998136861280931</v>
       </c>
       <c r="S188" s="19" t="n">
-        <v>0.987122735131956</v>
+        <v>0.987145194585989</v>
       </c>
     </row>
     <row r="189">
@@ -12972,46 +12972,46 @@
         <v>693173.549347058</v>
       </c>
       <c r="F189" s="6" t="n">
-        <v>-13236.3368473724</v>
+        <v>-13239.0429294613</v>
       </c>
       <c r="G189" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H189" s="8" t="n">
-        <v>704953.658209257</v>
+        <v>704954.833303221</v>
       </c>
       <c r="I189" s="9" t="n">
-        <v>710467.800446811</v>
+        <v>710445.999018906</v>
       </c>
       <c r="J189" s="10" t="n">
-        <v>715781.039814855</v>
+        <v>715785.549568048</v>
       </c>
       <c r="K189" s="11" t="n">
-        <v>706409.88619443</v>
+        <v>706412.592276519</v>
       </c>
       <c r="L189" s="12" t="n">
-        <v>706409.88619443</v>
+        <v>706412.592276519</v>
       </c>
       <c r="M189" s="13" t="n">
-        <v>706409.88619443</v>
+        <v>706412.592276519</v>
       </c>
       <c r="N189" s="14" t="n">
-        <v>706409.88619443</v>
+        <v>706412.592276519</v>
       </c>
       <c r="O189" s="15" t="n">
-        <v>0.0053716044361951</v>
+        <v>0.00537417349836396</v>
       </c>
       <c r="P189" s="16" t="n">
-        <v>-0.0156499187434167</v>
+        <v>-0.0156492911679335</v>
       </c>
       <c r="Q189" s="17" t="n">
-        <v>0.00538605737019782</v>
+        <v>0.00538864027280073</v>
       </c>
       <c r="R189" s="18" t="n">
-        <v>1.00206570739539</v>
+        <v>1.00206787570555</v>
       </c>
       <c r="S189" s="19" t="n">
-        <v>0.994288391043438</v>
+        <v>0.994322711721994</v>
       </c>
     </row>
     <row r="190">
@@ -13031,46 +13031,46 @@
         <v>681444.766110222</v>
       </c>
       <c r="F190" s="6" t="n">
-        <v>-29516.2485550834</v>
+        <v>-29513.9950403516</v>
       </c>
       <c r="G190" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H190" s="8" t="n">
-        <v>713982.476021145</v>
+        <v>713981.579233139</v>
       </c>
       <c r="I190" s="9" t="n">
-        <v>708987.624031906</v>
+        <v>708958.3930311</v>
       </c>
       <c r="J190" s="10" t="n">
-        <v>715326.52691163</v>
+        <v>715331.944220953</v>
       </c>
       <c r="K190" s="11" t="n">
-        <v>710961.014665306</v>
+        <v>710958.761150574</v>
       </c>
       <c r="L190" s="12" t="n">
-        <v>710961.014665306</v>
+        <v>710958.761150574</v>
       </c>
       <c r="M190" s="13" t="n">
-        <v>710961.014665306</v>
+        <v>710958.761150574</v>
       </c>
       <c r="N190" s="14" t="n">
-        <v>710961.014665306</v>
+        <v>710958.761150574</v>
       </c>
       <c r="O190" s="15" t="n">
-        <v>0.00642195223476584</v>
+        <v>0.00641495180953307</v>
       </c>
       <c r="P190" s="16" t="n">
-        <v>0.00124007325916242</v>
+        <v>0.001243542161393</v>
       </c>
       <c r="Q190" s="17" t="n">
-        <v>0.00644261718277117</v>
+        <v>0.00643557168113928</v>
       </c>
       <c r="R190" s="18" t="n">
-        <v>0.995768157542637</v>
+        <v>0.995766252000771</v>
       </c>
       <c r="S190" s="19" t="n">
-        <v>1.00278339221519</v>
+        <v>1.00282155926093</v>
       </c>
     </row>
     <row r="191">
@@ -13090,46 +13090,46 @@
         <v>778401.676449317</v>
       </c>
       <c r="F191" s="6" t="n">
-        <v>49932.9430141731</v>
+        <v>49934.4151448394</v>
       </c>
       <c r="G191" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H191" s="8" t="n">
-        <v>724849.87372788</v>
+        <v>724847.704574438</v>
       </c>
       <c r="I191" s="9" t="n">
-        <v>707346.367594815</v>
+        <v>707308.758932935</v>
       </c>
       <c r="J191" s="10" t="n">
-        <v>714406.351850737</v>
+        <v>714412.994547368</v>
       </c>
       <c r="K191" s="11" t="n">
-        <v>728468.733435144</v>
+        <v>728467.261304477</v>
       </c>
       <c r="L191" s="12" t="n">
-        <v>728468.733435144</v>
+        <v>728467.261304477</v>
       </c>
       <c r="M191" s="13" t="n">
-        <v>728468.733435144</v>
+        <v>728467.261304477</v>
       </c>
       <c r="N191" s="14" t="n">
-        <v>728468.733435144</v>
+        <v>728467.261304477</v>
       </c>
       <c r="O191" s="15" t="n">
-        <v>0.0243271090079507</v>
+        <v>0.0243282578287059</v>
       </c>
       <c r="P191" s="16" t="n">
-        <v>0.0300010653379701</v>
+        <v>0.029998083621029</v>
       </c>
       <c r="Q191" s="17" t="n">
-        <v>0.0246254272860231</v>
+        <v>0.0246266043976564</v>
       </c>
       <c r="R191" s="18" t="n">
-        <v>1.00499256444462</v>
+        <v>1.00499354099792</v>
       </c>
       <c r="S191" s="19" t="n">
-        <v>1.02986141840546</v>
+        <v>1.02991409636078</v>
       </c>
     </row>
     <row r="192">
@@ -13149,46 +13149,46 @@
         <v>721120.426852794</v>
       </c>
       <c r="F192" s="6" t="n">
-        <v>-8853.03267418518</v>
+        <v>-8852.12575052391</v>
       </c>
       <c r="G192" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H192" s="8" t="n">
-        <v>732342.703116805</v>
+        <v>732342.325220361</v>
       </c>
       <c r="I192" s="9" t="n">
-        <v>705540.729632059</v>
+        <v>705493.788728452</v>
       </c>
       <c r="J192" s="10" t="n">
-        <v>712818.176065843</v>
+        <v>712826.340811809</v>
       </c>
       <c r="K192" s="11" t="n">
-        <v>729973.459526979</v>
+        <v>729972.552603318</v>
       </c>
       <c r="L192" s="12" t="n">
-        <v>729973.459526979</v>
+        <v>729972.552603318</v>
       </c>
       <c r="M192" s="13" t="n">
-        <v>729973.459526979</v>
+        <v>729972.552603318</v>
       </c>
       <c r="N192" s="14" t="n">
-        <v>729973.459526979</v>
+        <v>729972.552603318</v>
       </c>
       <c r="O192" s="15" t="n">
-        <v>0.00206347105564143</v>
+        <v>0.00206424950691245</v>
       </c>
       <c r="P192" s="16" t="n">
-        <v>0.0389225190666649</v>
+        <v>0.0389199175133534</v>
       </c>
       <c r="Q192" s="17" t="n">
-        <v>0.00206560147714252</v>
+        <v>0.00206638153668726</v>
       </c>
       <c r="R192" s="18" t="n">
-        <v>0.996764843044462</v>
+        <v>0.996764118998134</v>
       </c>
       <c r="S192" s="19" t="n">
-        <v>1.03462979367281</v>
+        <v>1.03469734853227</v>
       </c>
     </row>
     <row r="193">
@@ -13208,46 +13208,46 @@
         <v>724592.921638963</v>
       </c>
       <c r="F193" s="6" t="n">
-        <v>-11208.1110047555</v>
+        <v>-11211.0887394704</v>
       </c>
       <c r="G193" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H193" s="8" t="n">
-        <v>736528.336808629</v>
+        <v>736532.778154151</v>
       </c>
       <c r="I193" s="9" t="n">
-        <v>703580.610118811</v>
+        <v>703523.398485676</v>
       </c>
       <c r="J193" s="10" t="n">
-        <v>710429.972898536</v>
+        <v>710439.894612577</v>
       </c>
       <c r="K193" s="11" t="n">
-        <v>735801.032643718</v>
+        <v>735804.010378433</v>
       </c>
       <c r="L193" s="12" t="n">
-        <v>735801.032643718</v>
+        <v>735804.010378433</v>
       </c>
       <c r="M193" s="13" t="n">
-        <v>735801.032643718</v>
+        <v>735804.010378433</v>
       </c>
       <c r="N193" s="14" t="n">
-        <v>735801.032643718</v>
+        <v>735804.010378433</v>
       </c>
       <c r="O193" s="15" t="n">
-        <v>0.00795156943043163</v>
+        <v>0.00795685875860585</v>
       </c>
       <c r="P193" s="16" t="n">
-        <v>0.0416063634211352</v>
+        <v>0.0416065885903816</v>
       </c>
       <c r="Q193" s="17" t="n">
-        <v>0.00798326711838993</v>
+        <v>0.00798859868678403</v>
       </c>
       <c r="R193" s="18" t="n">
-        <v>0.999012523852019</v>
+        <v>0.999010542643405</v>
       </c>
       <c r="S193" s="19" t="n">
-        <v>1.04579492678098</v>
+        <v>1.04588420507725</v>
       </c>
     </row>
     <row r="194">
@@ -13267,46 +13267,46 @@
         <v>707324.268057214</v>
       </c>
       <c r="F194" s="6" t="n">
-        <v>-26686.1831600911</v>
+        <v>-26692.6957861179</v>
       </c>
       <c r="G194" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H194" s="8" t="n">
-        <v>727832.54784464</v>
+        <v>727832.806435653</v>
       </c>
       <c r="I194" s="9" t="n">
-        <v>701491.179486428</v>
+        <v>701422.80350005</v>
       </c>
       <c r="J194" s="10" t="n">
-        <v>707195.492107708</v>
+        <v>707207.298606933</v>
       </c>
       <c r="K194" s="11" t="n">
-        <v>734010.451217305</v>
+        <v>734016.963843332</v>
       </c>
       <c r="L194" s="12" t="n">
-        <v>734010.451217305</v>
+        <v>734016.963843332</v>
       </c>
       <c r="M194" s="13" t="n">
-        <v>734010.451217305</v>
+        <v>734016.963843332</v>
       </c>
       <c r="N194" s="14" t="n">
-        <v>734010.451217305</v>
+        <v>734016.963843332</v>
       </c>
       <c r="O194" s="15" t="n">
-        <v>-0.00243647887076578</v>
+        <v>-0.00243165317001298</v>
       </c>
       <c r="P194" s="16" t="n">
-        <v>0.0324201131659099</v>
+        <v>0.0324325459544825</v>
       </c>
       <c r="Q194" s="17" t="n">
-        <v>-0.00243351306531836</v>
+        <v>-0.00242869909635601</v>
       </c>
       <c r="R194" s="18" t="n">
-        <v>1.00848808340732</v>
+        <v>1.00849667307244</v>
       </c>
       <c r="S194" s="19" t="n">
-        <v>1.04635734943194</v>
+        <v>1.04646863515221</v>
       </c>
     </row>
     <row r="195">
@@ -13326,46 +13326,46 @@
         <v>747428.299954575</v>
       </c>
       <c r="F195" s="6" t="n">
-        <v>44672.7763303434</v>
+        <v>44686.6807837756</v>
       </c>
       <c r="G195" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H195" s="8" t="n">
-        <v>711081.235799925</v>
+        <v>711075.710739738</v>
       </c>
       <c r="I195" s="9" t="n">
-        <v>699317.745930343</v>
+        <v>699237.394449454</v>
       </c>
       <c r="J195" s="10" t="n">
-        <v>703195.33875098</v>
+        <v>703209.016030963</v>
       </c>
       <c r="K195" s="11" t="n">
-        <v>702755.523624231</v>
+        <v>702741.619170799</v>
       </c>
       <c r="L195" s="12" t="n">
-        <v>702755.523624231</v>
+        <v>702741.619170799</v>
       </c>
       <c r="M195" s="13" t="n">
-        <v>702755.523624231</v>
+        <v>702741.619170799</v>
       </c>
       <c r="N195" s="14" t="n">
-        <v>702755.523624231</v>
+        <v>702741.619170799</v>
       </c>
       <c r="O195" s="15" t="n">
-        <v>-0.0435141974599334</v>
+        <v>-0.0435428558970341</v>
       </c>
       <c r="P195" s="16" t="n">
-        <v>-0.0352976162609754</v>
+        <v>-0.03531475400502</v>
       </c>
       <c r="Q195" s="17" t="n">
-        <v>-0.0425810389228654</v>
+        <v>-0.0426084766607772</v>
       </c>
       <c r="R195" s="18" t="n">
-        <v>0.988291475352562</v>
+        <v>0.988279600268909</v>
       </c>
       <c r="S195" s="19" t="n">
-        <v>1.00491590226888</v>
+        <v>1.00501149502181</v>
       </c>
     </row>
     <row r="196">
@@ -13385,46 +13385,46 @@
         <v>696101.583521808</v>
       </c>
       <c r="F196" s="6" t="n">
-        <v>-8225.6349373822</v>
+        <v>-8228.93323067837</v>
       </c>
       <c r="G196" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H196" s="8" t="n">
-        <v>697725.731832115</v>
+        <v>697723.919307708</v>
       </c>
       <c r="I196" s="9" t="n">
-        <v>697125.942190824</v>
+        <v>697032.933361981</v>
       </c>
       <c r="J196" s="10" t="n">
-        <v>698644.192681519</v>
+        <v>698659.558446938</v>
       </c>
       <c r="K196" s="11" t="n">
-        <v>704327.21845919</v>
+        <v>704330.516752486</v>
       </c>
       <c r="L196" s="12" t="n">
-        <v>704327.21845919</v>
+        <v>704330.516752486</v>
       </c>
       <c r="M196" s="13" t="n">
-        <v>704327.21845919</v>
+        <v>704330.516752486</v>
       </c>
       <c r="N196" s="14" t="n">
-        <v>704327.21845919</v>
+        <v>704330.516752486</v>
       </c>
       <c r="O196" s="15" t="n">
-        <v>0.00223397735129684</v>
+        <v>0.00225844605472546</v>
       </c>
       <c r="P196" s="16" t="n">
-        <v>-0.0351331144072119</v>
+        <v>-0.0351273972690951</v>
       </c>
       <c r="Q196" s="17" t="n">
-        <v>0.00223647453790643</v>
+        <v>0.00226099826499793</v>
       </c>
       <c r="R196" s="18" t="n">
-        <v>1.00946143495345</v>
+        <v>1.00946878451771</v>
       </c>
       <c r="S196" s="19" t="n">
-        <v>1.01032995020345</v>
+        <v>1.01046949583186</v>
       </c>
     </row>
     <row r="197">
@@ -13444,46 +13444,46 @@
         <v>678655.620384454</v>
       </c>
       <c r="F197" s="6" t="n">
-        <v>-8972.61334916359</v>
+        <v>-8978.18665671191</v>
       </c>
       <c r="G197" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H197" s="8" t="n">
-        <v>690912.361445414</v>
+        <v>690922.323040265</v>
       </c>
       <c r="I197" s="9" t="n">
-        <v>694983.549619195</v>
+        <v>694877.372406173</v>
       </c>
       <c r="J197" s="10" t="n">
-        <v>693754.534676859</v>
+        <v>693771.100432829</v>
       </c>
       <c r="K197" s="11" t="n">
-        <v>687628.233733617</v>
+        <v>687633.807041165</v>
       </c>
       <c r="L197" s="12" t="n">
-        <v>687628.233733617</v>
+        <v>687633.807041165</v>
       </c>
       <c r="M197" s="13" t="n">
-        <v>687628.233733617</v>
+        <v>687633.807041165</v>
       </c>
       <c r="N197" s="14" t="n">
-        <v>687628.233733617</v>
+        <v>687633.807041165</v>
       </c>
       <c r="O197" s="15" t="n">
-        <v>-0.0239947131781326</v>
+        <v>-0.0239912909817322</v>
       </c>
       <c r="P197" s="16" t="n">
-        <v>-0.065469871300693</v>
+        <v>-0.0654660788169574</v>
       </c>
       <c r="Q197" s="17" t="n">
-        <v>-0.0237091287798077</v>
+        <v>-0.0237057877149855</v>
       </c>
       <c r="R197" s="18" t="n">
-        <v>0.995246679759895</v>
+        <v>0.995240396945594</v>
       </c>
       <c r="S197" s="19" t="n">
-        <v>0.98941656116953</v>
+        <v>0.989575764512341</v>
       </c>
     </row>
     <row r="198">
@@ -13503,46 +13503,46 @@
         <v>665848.715299709</v>
       </c>
       <c r="F198" s="6" t="n">
-        <v>-25618.5128898886</v>
+        <v>-25628.4903902221</v>
       </c>
       <c r="G198" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H198" s="8" t="n">
-        <v>694726.186112924</v>
+        <v>694724.624413779</v>
       </c>
       <c r="I198" s="9" t="n">
-        <v>692962.850364449</v>
+        <v>692843.224740195</v>
       </c>
       <c r="J198" s="10" t="n">
-        <v>688767.260643422</v>
+        <v>688784.171358131</v>
       </c>
       <c r="K198" s="11" t="n">
-        <v>691467.228189597</v>
+        <v>691477.205689931</v>
       </c>
       <c r="L198" s="12" t="n">
-        <v>691467.228189597</v>
+        <v>691477.205689931</v>
       </c>
       <c r="M198" s="13" t="n">
-        <v>691467.228189597</v>
+        <v>691477.205689931</v>
       </c>
       <c r="N198" s="14" t="n">
-        <v>691467.228189597</v>
+        <v>691477.205689931</v>
       </c>
       <c r="O198" s="15" t="n">
-        <v>0.00556742368916259</v>
+        <v>0.00557374796287231</v>
       </c>
       <c r="P198" s="16" t="n">
-        <v>-0.0579599690401583</v>
+        <v>-0.0579547343574484</v>
       </c>
       <c r="Q198" s="17" t="n">
-        <v>0.00558295059400882</v>
+        <v>0.00558931019593611</v>
       </c>
       <c r="R198" s="18" t="n">
-        <v>0.995309003765123</v>
+        <v>0.99532560296594</v>
       </c>
       <c r="S198" s="19" t="n">
-        <v>0.99784169934353</v>
+        <v>0.998028386507242</v>
       </c>
     </row>
     <row r="199">
@@ -13562,46 +13562,46 @@
         <v>751784.460777133</v>
       </c>
       <c r="F199" s="6" t="n">
-        <v>41858.2919019098</v>
+        <v>41884.4884129887</v>
       </c>
       <c r="G199" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H199" s="8" t="n">
-        <v>703419.181475476</v>
+        <v>703409.714450558</v>
       </c>
       <c r="I199" s="9" t="n">
-        <v>691131.52950315</v>
+        <v>690998.476293855</v>
       </c>
       <c r="J199" s="10" t="n">
-        <v>683892.634982914</v>
+        <v>683908.614125385</v>
       </c>
       <c r="K199" s="11" t="n">
-        <v>709926.168875223</v>
+        <v>709899.972364144</v>
       </c>
       <c r="L199" s="12" t="n">
-        <v>709926.168875223</v>
+        <v>709899.972364144</v>
       </c>
       <c r="M199" s="13" t="n">
-        <v>709926.168875223</v>
+        <v>709899.972364144</v>
       </c>
       <c r="N199" s="14" t="n">
-        <v>709926.168875223</v>
+        <v>709899.972364144</v>
       </c>
       <c r="O199" s="15" t="n">
-        <v>0.0263452194973859</v>
+        <v>0.026293889126658</v>
       </c>
       <c r="P199" s="16" t="n">
-        <v>0.0102036127926983</v>
+        <v>0.0101863231066226</v>
       </c>
       <c r="Q199" s="17" t="n">
-        <v>0.0266953225447206</v>
+        <v>0.0266426232457386</v>
       </c>
       <c r="R199" s="18" t="n">
-        <v>1.00925051174479</v>
+        <v>1.0092268528288</v>
       </c>
       <c r="S199" s="19" t="n">
-        <v>1.0271940123837</v>
+        <v>1.02735388965207</v>
       </c>
     </row>
     <row r="200">
@@ -13621,46 +13621,46 @@
         <v>683900.898552578</v>
       </c>
       <c r="F200" s="6" t="n">
-        <v>-8802.22113975885</v>
+        <v>-8813.71793751895</v>
       </c>
       <c r="G200" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H200" s="8" t="n">
-        <v>697794.531025909</v>
+        <v>697796.71768964</v>
       </c>
       <c r="I200" s="9" t="n">
-        <v>689556.337348003</v>
+        <v>689410.259235056</v>
       </c>
       <c r="J200" s="10" t="n">
-        <v>679354.421934771</v>
+        <v>679367.736808788</v>
       </c>
       <c r="K200" s="11" t="n">
-        <v>692703.119692337</v>
+        <v>692714.616490097</v>
       </c>
       <c r="L200" s="12" t="n">
-        <v>692703.119692337</v>
+        <v>692714.616490097</v>
       </c>
       <c r="M200" s="13" t="n">
-        <v>692703.119692337</v>
+        <v>692714.616490097</v>
       </c>
       <c r="N200" s="14" t="n">
-        <v>692703.119692337</v>
+        <v>692714.616490097</v>
       </c>
       <c r="O200" s="15" t="n">
-        <v>-0.024559468439997</v>
+        <v>-0.0245059705593474</v>
       </c>
       <c r="P200" s="16" t="n">
-        <v>-0.0165038329659924</v>
+        <v>-0.0164921155424969</v>
       </c>
       <c r="Q200" s="17" t="n">
-        <v>-0.0242603385224875</v>
+        <v>-0.024208137122213</v>
       </c>
       <c r="R200" s="18" t="n">
-        <v>0.992703566584154</v>
+        <v>0.992716931635378</v>
       </c>
       <c r="S200" s="19" t="n">
-        <v>1.00456348839666</v>
+        <v>1.00479302013682</v>
       </c>
     </row>
     <row r="201">
@@ -13680,46 +13680,46 @@
         <v>671361.13972242</v>
       </c>
       <c r="F201" s="6" t="n">
-        <v>-6753.97607406567</v>
+        <v>-6763.63935669318</v>
       </c>
       <c r="G201" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H201" s="8" t="n">
-        <v>672616.878387971</v>
+        <v>672614.057325446</v>
       </c>
       <c r="I201" s="9" t="n">
-        <v>688315.770861321</v>
+        <v>688157.519166746</v>
       </c>
       <c r="J201" s="10" t="n">
-        <v>675506.553407892</v>
+        <v>675514.804273732</v>
       </c>
       <c r="K201" s="11" t="n">
-        <v>678115.115796486</v>
+        <v>678124.779079113</v>
       </c>
       <c r="L201" s="12" t="n">
-        <v>678115.115796486</v>
+        <v>678124.779079113</v>
       </c>
       <c r="M201" s="13" t="n">
-        <v>678115.115796486</v>
+        <v>678124.779079113</v>
       </c>
       <c r="N201" s="14" t="n">
-        <v>678115.115796486</v>
+        <v>678124.779079113</v>
       </c>
       <c r="O201" s="15" t="n">
-        <v>-0.0212844478499906</v>
+        <v>-0.0212867946099495</v>
       </c>
       <c r="P201" s="16" t="n">
-        <v>-0.0138346819843014</v>
+        <v>-0.013828621956458</v>
       </c>
       <c r="Q201" s="17" t="n">
-        <v>-0.0210595325488512</v>
+        <v>-0.0210618298844467</v>
       </c>
       <c r="R201" s="18" t="n">
-        <v>1.0081743970233</v>
+        <v>1.00819299224221</v>
       </c>
       <c r="S201" s="19" t="n">
-        <v>0.985180268277057</v>
+        <v>0.985420866868125</v>
       </c>
     </row>
     <row r="202">
@@ -13739,46 +13739,46 @@
         <v>632389.35353461</v>
       </c>
       <c r="F202" s="6" t="n">
-        <v>-24778.7173309361</v>
+        <v>-24784.3907514822</v>
       </c>
       <c r="G202" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H202" s="8" t="n">
-        <v>636437.826726455</v>
+        <v>636460.279791407</v>
       </c>
       <c r="I202" s="9" t="n">
-        <v>687490.293744382</v>
+        <v>687321.266915156</v>
       </c>
       <c r="J202" s="10" t="n">
-        <v>672769.704799964</v>
+        <v>672769.815784014</v>
       </c>
       <c r="K202" s="11" t="n">
-        <v>657168.070865546</v>
+        <v>657173.744286092</v>
       </c>
       <c r="L202" s="12" t="n">
-        <v>636437.826726455</v>
+        <v>636460.279791407</v>
       </c>
       <c r="M202" s="13" t="n">
-        <v>636437.826726455</v>
+        <v>636460.279791407</v>
       </c>
       <c r="N202" s="14" t="n">
-        <v>636437.826726455</v>
+        <v>636460.279791407</v>
       </c>
       <c r="O202" s="15" t="n">
-        <v>-0.0634303275391609</v>
+        <v>-0.0634092989949132</v>
       </c>
       <c r="P202" s="16" t="n">
-        <v>-0.0795835279239779</v>
+        <v>-0.0795643376901051</v>
       </c>
       <c r="Q202" s="17" t="n">
-        <v>-0.0614604926201627</v>
+        <v>-0.0614407562930912</v>
       </c>
       <c r="R202" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S202" s="19" t="n">
-        <v>0.925740817750499</v>
+        <v>0.926001144483679</v>
       </c>
     </row>
     <row r="203">
@@ -13798,46 +13798,46 @@
         <v>609379.989464801</v>
       </c>
       <c r="F203" s="6" t="n">
-        <v>39262.8137599983</v>
+        <v>39300.5771761554</v>
       </c>
       <c r="G203" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H203" s="8" t="n">
-        <v>611590.560069316</v>
+        <v>611652.189635686</v>
       </c>
       <c r="I203" s="9" t="n">
-        <v>687153.994289047</v>
+        <v>686976.242843964</v>
       </c>
       <c r="J203" s="10" t="n">
-        <v>671577.594320614</v>
+        <v>671565.820477461</v>
       </c>
       <c r="K203" s="11" t="n">
-        <v>570117.175704803</v>
+        <v>570079.412288646</v>
       </c>
       <c r="L203" s="12" t="n">
-        <v>611590.560069316</v>
+        <v>611652.189635686</v>
       </c>
       <c r="M203" s="13" t="n">
-        <v>611590.560069316</v>
+        <v>611652.189635686</v>
       </c>
       <c r="N203" s="14" t="n">
-        <v>611590.560069316</v>
+        <v>611652.189635686</v>
       </c>
       <c r="O203" s="15" t="n">
-        <v>-0.0398236941751142</v>
+        <v>-0.0397582085819804</v>
       </c>
       <c r="P203" s="16" t="n">
-        <v>-0.138515261328802</v>
+        <v>-0.138396656646243</v>
       </c>
       <c r="Q203" s="17" t="n">
-        <v>-0.0390411531397215</v>
+        <v>-0.0389782221191425</v>
       </c>
       <c r="R203" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S203" s="19" t="n">
-        <v>0.890034206527589</v>
+        <v>0.89035420948991</v>
       </c>
     </row>
     <row r="204">
@@ -13857,46 +13857,46 @@
         <v>614192.478404223</v>
       </c>
       <c r="F204" s="6" t="n">
-        <v>-7572.01828206623</v>
+        <v>-7598.16575635988</v>
       </c>
       <c r="G204" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H204" s="8" t="n">
-        <v>620819.081240061</v>
+        <v>620878.041995616</v>
       </c>
       <c r="I204" s="9" t="n">
-        <v>687349.052995293</v>
+        <v>687165.399199893</v>
       </c>
       <c r="J204" s="10" t="n">
-        <v>672182.280789106</v>
+        <v>672154.319811935</v>
       </c>
       <c r="K204" s="11" t="n">
-        <v>621764.496686289</v>
+        <v>621790.644160583</v>
       </c>
       <c r="L204" s="12" t="n">
-        <v>621764.496686289</v>
+        <v>621790.644160583</v>
       </c>
       <c r="M204" s="13" t="n">
-        <v>621764.496686289</v>
+        <v>621790.644160583</v>
       </c>
       <c r="N204" s="14" t="n">
-        <v>621764.496686289</v>
+        <v>621790.644160583</v>
       </c>
       <c r="O204" s="15" t="n">
-        <v>0.0164983592283199</v>
+        <v>0.0164396477609948</v>
       </c>
       <c r="P204" s="16" t="n">
-        <v>-0.102408406991953</v>
+        <v>-0.102385557690233</v>
       </c>
       <c r="Q204" s="17" t="n">
-        <v>0.0166352087184276</v>
+        <v>0.0165755223257444</v>
       </c>
       <c r="R204" s="18" t="n">
-        <v>1.00152285178532</v>
+        <v>1.0014698573685</v>
       </c>
       <c r="S204" s="19" t="n">
-        <v>0.904583332117498</v>
+        <v>0.904863144862314</v>
       </c>
     </row>
     <row r="205">
@@ -13916,46 +13916,46 @@
         <v>642403.32319795</v>
       </c>
       <c r="F205" s="6" t="n">
-        <v>-7395.21858026428</v>
+        <v>-7423.68010888921</v>
       </c>
       <c r="G205" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H205" s="8" t="n">
-        <v>650041.595424714</v>
+        <v>650054.934010711</v>
       </c>
       <c r="I205" s="9" t="n">
-        <v>688070.423216709</v>
+        <v>687884.610696413</v>
       </c>
       <c r="J205" s="10" t="n">
-        <v>674535.887853443</v>
+        <v>674487.247091088</v>
       </c>
       <c r="K205" s="11" t="n">
-        <v>649798.541778215</v>
+        <v>649827.003306839</v>
       </c>
       <c r="L205" s="12" t="n">
-        <v>649798.541778215</v>
+        <v>649827.003306839</v>
       </c>
       <c r="M205" s="13" t="n">
-        <v>649798.541778215</v>
+        <v>649827.003306839</v>
       </c>
       <c r="N205" s="14" t="n">
-        <v>649798.541778215</v>
+        <v>649827.003306839</v>
       </c>
       <c r="O205" s="15" t="n">
-        <v>0.0441009807711981</v>
+        <v>0.0441027275761884</v>
       </c>
       <c r="P205" s="16" t="n">
-        <v>-0.0417577684948252</v>
+        <v>-0.0417294525215577</v>
       </c>
       <c r="Q205" s="17" t="n">
-        <v>0.0450878833406114</v>
+        <v>0.0450897089069358</v>
       </c>
       <c r="R205" s="18" t="n">
-        <v>0.99962609524035</v>
+        <v>0.999649367012007</v>
       </c>
       <c r="S205" s="19" t="n">
-        <v>0.944377958785709</v>
+        <v>0.944674431150532</v>
       </c>
     </row>
     <row r="206">
@@ -13975,46 +13975,46 @@
         <v>652831.976706322</v>
       </c>
       <c r="F206" s="6" t="n">
-        <v>-24041.6412281711</v>
+        <v>-24014.1918165623</v>
       </c>
       <c r="G206" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H206" s="8" t="n">
-        <v>674103.307563351</v>
+        <v>674060.67177802</v>
       </c>
       <c r="I206" s="9" t="n">
-        <v>689272.06795919</v>
+        <v>689088.892825094</v>
       </c>
       <c r="J206" s="10" t="n">
-        <v>678338.450241117</v>
+        <v>678264.717240317</v>
       </c>
       <c r="K206" s="11" t="n">
-        <v>676873.617934493</v>
+        <v>676846.168522884</v>
       </c>
       <c r="L206" s="12" t="n">
-        <v>676873.617934493</v>
+        <v>676846.168522884</v>
       </c>
       <c r="M206" s="13" t="n">
-        <v>676873.617934493</v>
+        <v>676846.168522884</v>
       </c>
       <c r="N206" s="14" t="n">
-        <v>676873.617934493</v>
+        <v>676846.168522884</v>
       </c>
       <c r="O206" s="15" t="n">
-        <v>0.0408221967966173</v>
+        <v>0.0407378431609129</v>
       </c>
       <c r="P206" s="16" t="n">
-        <v>0.0635345504462248</v>
+        <v>0.0634539028024073</v>
       </c>
       <c r="Q206" s="17" t="n">
-        <v>0.0416668773712319</v>
+        <v>0.0415790126888376</v>
       </c>
       <c r="R206" s="18" t="n">
-        <v>1.00410962287243</v>
+        <v>1.00413241249859</v>
       </c>
       <c r="S206" s="19" t="n">
-        <v>0.982012255245731</v>
+        <v>0.982233461561079</v>
       </c>
     </row>
     <row r="207">
@@ -14034,46 +14034,46 @@
         <v>723516.622490675</v>
       </c>
       <c r="F207" s="6" t="n">
-        <v>38698.0218376303</v>
+        <v>38779.0834122693</v>
       </c>
       <c r="G207" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H207" s="8" t="n">
-        <v>686065.921763108</v>
+        <v>686049.83016221</v>
       </c>
       <c r="I207" s="9" t="n">
-        <v>690884.030302732</v>
+        <v>690709.475072887</v>
       </c>
       <c r="J207" s="10" t="n">
-        <v>683166.315949243</v>
+        <v>683063.543966098</v>
       </c>
       <c r="K207" s="11" t="n">
-        <v>684818.600653045</v>
+        <v>684737.539078406</v>
       </c>
       <c r="L207" s="12" t="n">
-        <v>684818.600653045</v>
+        <v>684737.539078406</v>
       </c>
       <c r="M207" s="13" t="n">
-        <v>684818.600653045</v>
+        <v>684737.539078406</v>
       </c>
       <c r="N207" s="14" t="n">
-        <v>684818.600653045</v>
+        <v>684737.539078406</v>
       </c>
       <c r="O207" s="15" t="n">
-        <v>0.0116694107067559</v>
+        <v>0.011591588341649</v>
       </c>
       <c r="P207" s="16" t="n">
-        <v>0.119733765307674</v>
+        <v>0.119488412992114</v>
       </c>
       <c r="Q207" s="17" t="n">
-        <v>0.0117377639016221</v>
+        <v>0.0116590311395919</v>
       </c>
       <c r="R207" s="18" t="n">
-        <v>0.998181922362711</v>
+        <v>0.998087178181366</v>
       </c>
       <c r="S207" s="19" t="n">
-        <v>0.991220770225316</v>
+        <v>0.991353910421091</v>
       </c>
     </row>
     <row r="208">
@@ -14093,46 +14093,46 @@
         <v>686756.467826674</v>
       </c>
       <c r="F208" s="6" t="n">
-        <v>-6434.8864692473</v>
+        <v>-6569.85922742374</v>
       </c>
       <c r="G208" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H208" s="8" t="n">
-        <v>693194.266681655</v>
+        <v>693253.840382607</v>
       </c>
       <c r="I208" s="9" t="n">
-        <v>692828.604296066</v>
+        <v>692669.935224054</v>
       </c>
       <c r="J208" s="10" t="n">
-        <v>688588.508813402</v>
+        <v>688453.448231319</v>
       </c>
       <c r="K208" s="11" t="n">
-        <v>693191.354295922</v>
+        <v>693326.327054098</v>
       </c>
       <c r="L208" s="12" t="n">
-        <v>693191.354295922</v>
+        <v>693326.327054098</v>
       </c>
       <c r="M208" s="13" t="n">
-        <v>693191.354295922</v>
+        <v>693326.327054098</v>
       </c>
       <c r="N208" s="14" t="n">
-        <v>693191.354295922</v>
+        <v>693326.327054098</v>
       </c>
       <c r="O208" s="15" t="n">
-        <v>0.0121520989724534</v>
+        <v>0.0124651685560905</v>
       </c>
       <c r="P208" s="16" t="n">
-        <v>0.114877671514382</v>
+        <v>0.115047859863006</v>
       </c>
       <c r="Q208" s="17" t="n">
-        <v>0.0122262357285459</v>
+        <v>0.0125431825853335</v>
       </c>
       <c r="R208" s="18" t="n">
-        <v>0.99999579860095</v>
+        <v>1.00010456007204</v>
       </c>
       <c r="S208" s="19" t="n">
-        <v>1.00052357826684</v>
+        <v>1.00094762569684</v>
       </c>
     </row>
     <row r="209">
@@ -14152,46 +14152,46 @@
         <v>696134.669112115</v>
       </c>
       <c r="F209" s="6" t="n">
-        <v>-8427.74851886134</v>
+        <v>-8430.92065816327</v>
       </c>
       <c r="G209" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H209" s="8" t="n">
-        <v>704670.255848506</v>
+        <v>704712.695102046</v>
       </c>
       <c r="I209" s="9" t="n">
-        <v>695024.293094393</v>
+        <v>694890.11860286</v>
       </c>
       <c r="J209" s="10" t="n">
-        <v>694182.314092695</v>
+        <v>694012.520974429</v>
       </c>
       <c r="K209" s="11" t="n">
-        <v>704562.417630976</v>
+        <v>704565.589770278</v>
       </c>
       <c r="L209" s="12" t="n">
-        <v>704562.417630976</v>
+        <v>704565.589770278</v>
       </c>
       <c r="M209" s="13" t="n">
-        <v>704562.417630976</v>
+        <v>704565.589770278</v>
       </c>
       <c r="N209" s="14" t="n">
-        <v>704562.417630976</v>
+        <v>704565.589770278</v>
       </c>
       <c r="O209" s="15" t="n">
-        <v>0.0162708402970175</v>
+        <v>0.0160806494036712</v>
       </c>
       <c r="P209" s="16" t="n">
-        <v>0.0842782375332778</v>
+        <v>0.0842356291518898</v>
       </c>
       <c r="Q209" s="17" t="n">
-        <v>0.0164039312732118</v>
+        <v>0.0162106388833312</v>
       </c>
       <c r="R209" s="18" t="n">
-        <v>0.999846966412113</v>
+        <v>0.999791254886154</v>
       </c>
       <c r="S209" s="19" t="n">
-        <v>1.01372344050611</v>
+        <v>1.0139237426298</v>
       </c>
     </row>
     <row r="210">
@@ -14211,46 +14211,46 @@
         <v>697625.284666358</v>
       </c>
       <c r="F210" s="6" t="n">
-        <v>-23837.3808397101</v>
+        <v>-23770.2993116839</v>
       </c>
       <c r="G210" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H210" s="8" t="n">
-        <v>724381.214752991</v>
+        <v>724249.319584369</v>
       </c>
       <c r="I210" s="9" t="n">
-        <v>697389.826571662</v>
+        <v>697290.280778465</v>
       </c>
       <c r="J210" s="10" t="n">
-        <v>699548.031273636</v>
+        <v>699343.217527992</v>
       </c>
       <c r="K210" s="11" t="n">
-        <v>721462.665506068</v>
+        <v>721395.583978042</v>
       </c>
       <c r="L210" s="12" t="n">
-        <v>721462.665506068</v>
+        <v>721395.583978042</v>
       </c>
       <c r="M210" s="13" t="n">
-        <v>721462.665506068</v>
+        <v>721395.583978042</v>
       </c>
       <c r="N210" s="14" t="n">
-        <v>721462.665506068</v>
+        <v>721395.583978042</v>
       </c>
       <c r="O210" s="15" t="n">
-        <v>0.0237037053180381</v>
+        <v>0.023606218820281</v>
       </c>
       <c r="P210" s="16" t="n">
-        <v>0.0658749970306731</v>
+        <v>0.0658191144856157</v>
       </c>
       <c r="Q210" s="17" t="n">
-        <v>0.0239868710737046</v>
+        <v>0.0238870510455258</v>
       </c>
       <c r="R210" s="18" t="n">
-        <v>0.995970976072429</v>
+        <v>0.996059733120682</v>
       </c>
       <c r="S210" s="19" t="n">
-        <v>1.03451848308821</v>
+        <v>1.03456996872617</v>
       </c>
     </row>
     <row r="211">
@@ -14270,46 +14270,46 @@
         <v>782338.628533735</v>
       </c>
       <c r="F211" s="6" t="n">
-        <v>37384.3095843713</v>
+        <v>37585.4966236147</v>
       </c>
       <c r="G211" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H211" s="8" t="n">
-        <v>740147.524638597</v>
+        <v>740118.467724703</v>
       </c>
       <c r="I211" s="9" t="n">
-        <v>699849.895929658</v>
+        <v>699796.72448951</v>
       </c>
       <c r="J211" s="10" t="n">
-        <v>704337.860360429</v>
+        <v>704100.75856855</v>
       </c>
       <c r="K211" s="11" t="n">
-        <v>744954.318949364</v>
+        <v>744753.13191012</v>
       </c>
       <c r="L211" s="12" t="n">
-        <v>744954.318949364</v>
+        <v>744753.13191012</v>
       </c>
       <c r="M211" s="13" t="n">
-        <v>744954.318949364</v>
+        <v>744753.13191012</v>
       </c>
       <c r="N211" s="14" t="n">
-        <v>744954.318949364</v>
+        <v>744753.13191012</v>
       </c>
       <c r="O211" s="15" t="n">
-        <v>0.0320422684383756</v>
+        <v>0.0318651499122189</v>
       </c>
       <c r="P211" s="16" t="n">
-        <v>0.0878126240130943</v>
+        <v>0.087647586712553</v>
       </c>
       <c r="Q211" s="17" t="n">
-        <v>0.0325611491300348</v>
+        <v>0.0323782796164016</v>
       </c>
       <c r="R211" s="18" t="n">
-        <v>1.00649437328472</v>
+        <v>1.00626205720777</v>
       </c>
       <c r="S211" s="19" t="n">
-        <v>1.06444871004773</v>
+        <v>1.06424209466457</v>
       </c>
     </row>
     <row r="212">
@@ -14329,46 +14329,46 @@
         <v>732662.163875501</v>
       </c>
       <c r="F212" s="6" t="n">
-        <v>-3689.5739411472</v>
+        <v>-4047.73080899796</v>
       </c>
       <c r="G212" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H212" s="8" t="n">
-        <v>736560.178839925</v>
+        <v>736715.669667693</v>
       </c>
       <c r="I212" s="9" t="n">
-        <v>702344.237894502</v>
+        <v>702350.818289131</v>
       </c>
       <c r="J212" s="10" t="n">
-        <v>708313.574528441</v>
+        <v>708050.626604898</v>
       </c>
       <c r="K212" s="11" t="n">
-        <v>736351.737816648</v>
+        <v>736709.894684499</v>
       </c>
       <c r="L212" s="12" t="n">
-        <v>736351.737816648</v>
+        <v>736709.894684499</v>
       </c>
       <c r="M212" s="13" t="n">
-        <v>736351.737816648</v>
+        <v>736709.894684499</v>
       </c>
       <c r="N212" s="14" t="n">
-        <v>736351.737816648</v>
+        <v>736709.894684499</v>
       </c>
       <c r="O212" s="15" t="n">
-        <v>-0.0116149904421049</v>
+        <v>-0.0108586122126863</v>
       </c>
       <c r="P212" s="16" t="n">
-        <v>0.0622633032758539</v>
+        <v>0.0625730856272766</v>
       </c>
       <c r="Q212" s="17" t="n">
-        <v>-0.0115477968432318</v>
+        <v>-0.0107998702939215</v>
       </c>
       <c r="R212" s="18" t="n">
-        <v>0.999717007477101</v>
+        <v>0.999992161177736</v>
       </c>
       <c r="S212" s="19" t="n">
-        <v>1.04841998850036</v>
+        <v>1.04892010587966</v>
       </c>
     </row>
     <row r="213">
@@ -14388,46 +14388,46 @@
         <v>712740.457828738</v>
       </c>
       <c r="F213" s="6" t="n">
-        <v>-9692.784748263</v>
+        <v>-9716.78782991864</v>
       </c>
       <c r="G213" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H213" s="8" t="n">
-        <v>726560.737975003</v>
+        <v>726702.901032187</v>
       </c>
       <c r="I213" s="9" t="n">
-        <v>704840.779456699</v>
+        <v>704922.028485107</v>
       </c>
       <c r="J213" s="10" t="n">
-        <v>711440.029245983</v>
+        <v>711161.566012534</v>
       </c>
       <c r="K213" s="11" t="n">
-        <v>722433.242577001</v>
+        <v>722457.245658657</v>
       </c>
       <c r="L213" s="12" t="n">
-        <v>722433.242577001</v>
+        <v>722457.245658657</v>
       </c>
       <c r="M213" s="13" t="n">
-        <v>722433.242577001</v>
+        <v>722457.245658657</v>
       </c>
       <c r="N213" s="14" t="n">
-        <v>722433.242577001</v>
+        <v>722457.245658657</v>
       </c>
       <c r="O213" s="15" t="n">
-        <v>-0.0190828913106618</v>
+        <v>-0.0195359420125528</v>
       </c>
       <c r="P213" s="16" t="n">
-        <v>0.0253644311686589</v>
+        <v>0.0253938826251963</v>
       </c>
       <c r="Q213" s="17" t="n">
-        <v>-0.0189019656297911</v>
+        <v>-0.0193463521104819</v>
       </c>
       <c r="R213" s="18" t="n">
-        <v>0.994319132341908</v>
+        <v>0.994157646312544</v>
       </c>
       <c r="S213" s="19" t="n">
-        <v>1.02495948536613</v>
+        <v>1.02487539963992</v>
       </c>
     </row>
     <row r="214">
@@ -14435,58 +14435,58 @@
         <v>265</v>
       </c>
       <c r="B214" s="2" t="n">
-        <v>703987.504321577</v>
+        <v>704009.035177002</v>
       </c>
       <c r="C214" s="3" t="n">
-        <v>703987.504321577</v>
+        <v>704009.035177002</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>703987.504321577</v>
+        <v>704009.035177002</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>703987.504321577</v>
+        <v>704009.035177002</v>
       </c>
       <c r="F214" s="6" t="n">
-        <v>-23976.2753262874</v>
+        <v>-23774.7852016269</v>
       </c>
       <c r="G214" s="7" t="n">
-        <v>0.843587141454005</v>
+        <v>0.869053298505175</v>
       </c>
       <c r="H214" s="8" t="n">
-        <v>723301.398371429</v>
+        <v>723218.513252464</v>
       </c>
       <c r="I214" s="9" t="n">
-        <v>707328.702294208</v>
+        <v>707501.295807962</v>
       </c>
       <c r="J214" s="10" t="n">
-        <v>713822.270797809</v>
+        <v>713545.617507359</v>
       </c>
       <c r="K214" s="11" t="n">
-        <v>727963.779647865</v>
+        <v>727783.820378629</v>
       </c>
       <c r="L214" s="12" t="n">
-        <v>727234.523264786</v>
+        <v>727186.008469146</v>
       </c>
       <c r="M214" s="13" t="n">
-        <v>727234.523264786</v>
+        <v>727186.008469146</v>
       </c>
       <c r="N214" s="14" t="n">
-        <v>727234.523264786</v>
+        <v>727186.008469146</v>
       </c>
       <c r="O214" s="15" t="n">
-        <v>0.00662399807256098</v>
+        <v>0.00652405972252856</v>
       </c>
       <c r="P214" s="16" t="n">
-        <v>0.00800021682988827</v>
+        <v>0.00802669799997102</v>
       </c>
       <c r="Q214" s="17" t="n">
-        <v>0.00664598526869842</v>
+        <v>0.00654538775672231</v>
       </c>
       <c r="R214" s="18" t="n">
-        <v>1.00543773992725</v>
+        <v>1.00548588724428</v>
       </c>
       <c r="S214" s="19" t="n">
-        <v>1.02814224971504</v>
+        <v>1.02782286446374</v>
       </c>
     </row>
     <row r="215">
@@ -14494,58 +14494,58 @@
         <v>266</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>737941.909374072</v>
+        <v>738128.411227304</v>
       </c>
       <c r="C215" s="3" t="n">
-        <v>737941.909374072</v>
+        <v>738128.411227304</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>737941.909374072</v>
+        <v>738128.411227304</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>737941.909374072</v>
+        <v>738128.411227304</v>
       </c>
       <c r="F215" s="6" t="n">
-        <v>35888.3388976219</v>
+        <v>36356.6531931205</v>
       </c>
       <c r="G215" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H215" s="8" t="n">
-        <v>720427.849700818</v>
+        <v>720154.442326776</v>
       </c>
       <c r="I215" s="9" t="n">
-        <v>709808.183374436</v>
+        <v>710090.520498951</v>
       </c>
       <c r="J215" s="10" t="n">
-        <v>715620.311535326</v>
+        <v>715371.300203503</v>
       </c>
       <c r="K215" s="11" t="n">
-        <v>702053.57047645</v>
+        <v>701771.758034184</v>
       </c>
       <c r="L215" s="12" t="n">
-        <v>720427.849700818</v>
+        <v>720154.442326776</v>
       </c>
       <c r="M215" s="13" t="n">
-        <v>720427.849700818</v>
+        <v>720154.442326776</v>
       </c>
       <c r="N215" s="14" t="n">
-        <v>720427.849700818</v>
+        <v>720154.442326776</v>
       </c>
       <c r="O215" s="15" t="n">
-        <v>-0.00940374475534341</v>
+        <v>-0.00971661016001555</v>
       </c>
       <c r="P215" s="16" t="n">
-        <v>-0.032923453995322</v>
+        <v>-0.0330293200919537</v>
       </c>
       <c r="Q215" s="17" t="n">
-        <v>-0.00935966781858855</v>
+        <v>-0.00966955642776068</v>
       </c>
       <c r="R215" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S215" s="19" t="n">
-        <v>1.0149613185296</v>
+        <v>1.01417273085233</v>
       </c>
     </row>
     <row r="216">
@@ -14553,58 +14553,58 @@
         <v>267</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>728638.584568682</v>
+        <v>728542.255847487</v>
       </c>
       <c r="C216" s="3" t="n">
-        <v>728638.584568682</v>
+        <v>728542.255847487</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>728638.584568682</v>
+        <v>728542.255847487</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>728638.584568682</v>
+        <v>728542.255847487</v>
       </c>
       <c r="F216" s="6" t="n">
-        <v>-1991.47285404021</v>
+        <v>-2707.0112646247</v>
       </c>
       <c r="G216" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H216" s="8" t="n">
-        <v>715073.513430226</v>
+        <v>715064.600498318</v>
       </c>
       <c r="I216" s="9" t="n">
-        <v>712291.840802898</v>
+        <v>712703.905744747</v>
       </c>
       <c r="J216" s="10" t="n">
-        <v>717061.225072276</v>
+        <v>716875.335169902</v>
       </c>
       <c r="K216" s="11" t="n">
-        <v>730630.057422722</v>
+        <v>731249.267112111</v>
       </c>
       <c r="L216" s="12" t="n">
-        <v>715073.513430226</v>
+        <v>715064.600498318</v>
       </c>
       <c r="M216" s="13" t="n">
-        <v>715073.513430226</v>
+        <v>715064.600498318</v>
       </c>
       <c r="N216" s="14" t="n">
-        <v>715073.513430226</v>
+        <v>715064.600498318</v>
       </c>
       <c r="O216" s="15" t="n">
-        <v>-0.00745991782242766</v>
+        <v>-0.00709280327924673</v>
       </c>
       <c r="P216" s="16" t="n">
-        <v>-0.0288968210348961</v>
+        <v>-0.0293810281935347</v>
       </c>
       <c r="Q216" s="17" t="n">
-        <v>-0.00743216169782379</v>
+        <v>-0.00706770871538753</v>
       </c>
       <c r="R216" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S216" s="19" t="n">
-        <v>1.00390524286252</v>
+        <v>1.00331230786662</v>
       </c>
     </row>
     <row r="217">
@@ -14612,58 +14612,58 @@
         <v>268</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>700509.934572323</v>
+        <v>700543.19869756</v>
       </c>
       <c r="C217" s="3" t="n">
-        <v>700509.934572323</v>
+        <v>700543.19869756</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>700509.934572323</v>
+        <v>700543.19869756</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>700509.934572323</v>
+        <v>700543.19869756</v>
       </c>
       <c r="F217" s="6" t="n">
-        <v>-8359.41384699579</v>
+        <v>-8741.46251282303</v>
       </c>
       <c r="G217" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H217" s="8" t="n">
-        <v>706930.757624317</v>
+        <v>706639.758366907</v>
       </c>
       <c r="I217" s="9" t="n">
-        <v>714798.929976563</v>
+        <v>715361.944683163</v>
       </c>
       <c r="J217" s="10" t="n">
-        <v>718396.12271323</v>
+        <v>718318.359186113</v>
       </c>
       <c r="K217" s="11" t="n">
-        <v>708869.348419319</v>
+        <v>709284.661210383</v>
       </c>
       <c r="L217" s="12" t="n">
-        <v>708869.348419319</v>
+        <v>709284.661210383</v>
       </c>
       <c r="M217" s="13" t="n">
-        <v>708869.348419319</v>
+        <v>709284.661210383</v>
       </c>
       <c r="N217" s="14" t="n">
-        <v>708869.348419319</v>
+        <v>709284.661210383</v>
       </c>
       <c r="O217" s="15" t="n">
-        <v>-0.00871411969816522</v>
+        <v>-0.00811594623545336</v>
       </c>
       <c r="P217" s="16" t="n">
-        <v>-0.0187752907234696</v>
+        <v>-0.0182330297431851</v>
       </c>
       <c r="Q217" s="17" t="n">
-        <v>-0.0086762618029933</v>
+        <v>-0.00808310086096686</v>
       </c>
       <c r="R217" s="18" t="n">
-        <v>1.00274226403943</v>
+        <v>1.00374292956511</v>
       </c>
       <c r="S217" s="19" t="n">
-        <v>0.99170454611979</v>
+        <v>0.991504603343876</v>
       </c>
     </row>
     <row r="218">
@@ -14671,58 +14671,58 @@
         <v>269</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>669057.733385167</v>
+        <v>668219.630827054</v>
       </c>
       <c r="C218" s="3" t="n">
-        <v>669057.733385167</v>
+        <v>668219.630827054</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>669057.733385167</v>
+        <v>668219.630827054</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>669057.733385167</v>
+        <v>668219.630827054</v>
       </c>
       <c r="F218" s="6" t="n">
-        <v>-25503.8219604765</v>
+        <v>-24668.6288602371</v>
       </c>
       <c r="G218" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H218" s="8" t="n">
-        <v>696001.780992713</v>
+        <v>694961.657825744</v>
       </c>
       <c r="I218" s="9" t="n">
-        <v>717350.444837793</v>
+        <v>718086.605886232</v>
       </c>
       <c r="J218" s="10" t="n">
-        <v>719866.177204548</v>
+        <v>719951.955358332</v>
       </c>
       <c r="K218" s="11" t="n">
-        <v>694561.555345643</v>
+        <v>692888.259687291</v>
       </c>
       <c r="L218" s="12" t="n">
-        <v>694561.555345643</v>
+        <v>692888.259687291</v>
       </c>
       <c r="M218" s="13" t="n">
-        <v>694561.555345643</v>
+        <v>692888.259687291</v>
       </c>
       <c r="N218" s="14" t="n">
-        <v>694561.555345643</v>
+        <v>692888.259687291</v>
       </c>
       <c r="O218" s="15" t="n">
-        <v>-0.0203904428230925</v>
+        <v>-0.0233881979678801</v>
       </c>
       <c r="P218" s="16" t="n">
-        <v>-0.0449276909633819</v>
+        <v>-0.0471650284554543</v>
       </c>
       <c r="Q218" s="17" t="n">
-        <v>-0.0201839635266784</v>
+        <v>-0.0231168139109508</v>
       </c>
       <c r="R218" s="18" t="n">
-        <v>0.997930715572286</v>
+        <v>0.997016528732045</v>
       </c>
       <c r="S218" s="19" t="n">
-        <v>0.968231859816714</v>
+        <v>0.964909043014607</v>
       </c>
     </row>
     <row r="219">
@@ -14730,58 +14730,58 @@
         <v>270</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>729947.785274553</v>
+        <v>729909.368719823</v>
       </c>
       <c r="C219" s="3" t="n">
-        <v>729947.785274553</v>
+        <v>729909.368719823</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>729947.785274553</v>
+        <v>729909.368719823</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>729947.785274553</v>
+        <v>729909.368719823</v>
       </c>
       <c r="F219" s="6" t="n">
-        <v>34375.3391985698</v>
+        <v>34984.9001041864</v>
       </c>
       <c r="G219" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H219" s="8" t="n">
-        <v>697821.670879931</v>
+        <v>697055.009120445</v>
       </c>
       <c r="I219" s="9" t="n">
-        <v>719963.673340473</v>
+        <v>720896.059623817</v>
       </c>
       <c r="J219" s="10" t="n">
-        <v>721664.927421119</v>
+        <v>721982.538302877</v>
       </c>
       <c r="K219" s="11" t="n">
-        <v>695572.446075983</v>
+        <v>694924.468615637</v>
       </c>
       <c r="L219" s="12" t="n">
-        <v>695572.446075983</v>
+        <v>694924.468615637</v>
       </c>
       <c r="M219" s="13" t="n">
-        <v>695572.446075983</v>
+        <v>694924.468615637</v>
       </c>
       <c r="N219" s="14" t="n">
-        <v>695572.446075983</v>
+        <v>694924.468615637</v>
       </c>
       <c r="O219" s="15" t="n">
-        <v>0.00145437908502931</v>
+        <v>0.00293441665137571</v>
       </c>
       <c r="P219" s="16" t="n">
-        <v>-0.0345008922616702</v>
+        <v>-0.0350341152234271</v>
       </c>
       <c r="Q219" s="17" t="n">
-        <v>0.00145543720719887</v>
+        <v>0.00293872626628855</v>
       </c>
       <c r="R219" s="18" t="n">
-        <v>0.996776791409886</v>
+        <v>0.996943511664171</v>
       </c>
       <c r="S219" s="19" t="n">
-        <v>0.966121586174869</v>
+        <v>0.963973182178672</v>
       </c>
     </row>
     <row r="220">
@@ -14789,58 +14789,58 @@
         <v>271</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>714524.365549959</v>
+        <v>714299.21795624</v>
       </c>
       <c r="C220" s="3" t="n">
-        <v>714524.365549959</v>
+        <v>714299.21795624</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>714524.365549959</v>
+        <v>714299.21795624</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>714524.365549959</v>
+        <v>714299.21795624</v>
       </c>
       <c r="F220" s="6" t="n">
-        <v>-675.299374840395</v>
+        <v>-1717.24444294311</v>
       </c>
       <c r="G220" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H220" s="8" t="n">
-        <v>712738.689883563</v>
+        <v>713684.271579094</v>
       </c>
       <c r="I220" s="9" t="n">
-        <v>722641.66038256</v>
+        <v>723792.727199408</v>
       </c>
       <c r="J220" s="10" t="n">
-        <v>723859.389128539</v>
+        <v>724481.204157712</v>
       </c>
       <c r="K220" s="11" t="n">
-        <v>715199.6649248</v>
+        <v>716016.462399183</v>
       </c>
       <c r="L220" s="12" t="n">
-        <v>715199.6649248</v>
+        <v>716016.462399183</v>
       </c>
       <c r="M220" s="13" t="n">
-        <v>715199.6649248</v>
+        <v>716016.462399183</v>
       </c>
       <c r="N220" s="14" t="n">
-        <v>715199.6649248</v>
+        <v>716016.462399183</v>
       </c>
       <c r="O220" s="15" t="n">
-        <v>0.0278265853946929</v>
+        <v>0.0298999974659591</v>
       </c>
       <c r="P220" s="16" t="n">
-        <v>0.000176417518205074</v>
+        <v>0.00133115511549886</v>
       </c>
       <c r="Q220" s="17" t="n">
-        <v>0.0282173610520968</v>
+        <v>0.0303514910412697</v>
       </c>
       <c r="R220" s="18" t="n">
-        <v>1.0034528433438</v>
+        <v>1.00326781871615</v>
       </c>
       <c r="S220" s="19" t="n">
-        <v>0.989701679455042</v>
+        <v>0.989256226944537</v>
       </c>
     </row>
     <row r="221">
@@ -14848,58 +14848,58 @@
         <v>272</v>
       </c>
       <c r="B221" s="2" t="n">
-        <v>718991.46093658</v>
+        <v>719523.320730935</v>
       </c>
       <c r="C221" s="3" t="n">
-        <v>718991.46093658</v>
+        <v>719523.320730935</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>718991.46093658</v>
+        <v>719523.320730935</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>718991.46093658</v>
+        <v>719523.320730935</v>
       </c>
       <c r="F221" s="6" t="n">
-        <v>-7117.09555906453</v>
+        <v>-8248.16212145605</v>
       </c>
       <c r="G221" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H221" s="8" t="n">
-        <v>726369.762982966</v>
+        <v>727292.617624648</v>
       </c>
       <c r="I221" s="9" t="n">
-        <v>725372.206344968</v>
+        <v>726762.797672115</v>
       </c>
       <c r="J221" s="10" t="n">
-        <v>726386.115685679</v>
+        <v>727383.758712363</v>
       </c>
       <c r="K221" s="11" t="n">
-        <v>726108.556495644</v>
+        <v>727771.482852391</v>
       </c>
       <c r="L221" s="12" t="n">
-        <v>726108.556495644</v>
+        <v>727771.482852391</v>
       </c>
       <c r="M221" s="13" t="n">
-        <v>726108.556495644</v>
+        <v>727771.482852391</v>
       </c>
       <c r="N221" s="14" t="n">
-        <v>726108.556495644</v>
+        <v>727771.482852391</v>
       </c>
       <c r="O221" s="15" t="n">
-        <v>0.0151377751466734</v>
+        <v>0.0162839428659121</v>
       </c>
       <c r="P221" s="16" t="n">
-        <v>0.0243193024423556</v>
+        <v>0.0260640369840515</v>
       </c>
       <c r="Q221" s="17" t="n">
-        <v>0.0152529316019625</v>
+        <v>0.0164172488629932</v>
       </c>
       <c r="R221" s="18" t="n">
-        <v>0.999640394602538</v>
+        <v>1.00065842168082</v>
       </c>
       <c r="S221" s="19" t="n">
-        <v>1.00101513422245</v>
+        <v>1.00138791526411</v>
       </c>
     </row>
     <row r="222">
@@ -14907,58 +14907,58 @@
         <v>273</v>
       </c>
       <c r="B222" s="2" t="n">
-        <v>708113.805670176</v>
+        <v>709095.124696624</v>
       </c>
       <c r="C222" s="3" t="n">
-        <v>708113.805670176</v>
+        <v>709095.124696624</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>708113.805670176</v>
+        <v>709095.124696624</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>708113.805670176</v>
+        <v>709095.124696624</v>
       </c>
       <c r="F222" s="6" t="n">
-        <v>-26366.7959977886</v>
+        <v>-24463.8649285938</v>
       </c>
       <c r="G222" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H222" s="8" t="n">
-        <v>735632.293590181</v>
+        <v>735593.981896699</v>
       </c>
       <c r="I222" s="9" t="n">
-        <v>728138.46036145</v>
+        <v>729787.599935545</v>
       </c>
       <c r="J222" s="10" t="n">
-        <v>729138.361830389</v>
+        <v>730583.684047564</v>
       </c>
       <c r="K222" s="11" t="n">
-        <v>734480.601667965</v>
+        <v>733558.989625218</v>
       </c>
       <c r="L222" s="12" t="n">
-        <v>734480.601667965</v>
+        <v>733558.989625218</v>
       </c>
       <c r="M222" s="13" t="n">
-        <v>734480.601667965</v>
+        <v>733558.989625218</v>
       </c>
       <c r="N222" s="14" t="n">
-        <v>734480.601667965</v>
+        <v>733558.989625218</v>
       </c>
       <c r="O222" s="15" t="n">
-        <v>0.0114640545102577</v>
+        <v>0.00792091472974912</v>
       </c>
       <c r="P222" s="16" t="n">
-        <v>0.0574737343509548</v>
+        <v>0.0586973864390232</v>
       </c>
       <c r="Q222" s="17" t="n">
-        <v>0.0115300186141947</v>
+        <v>0.00795236816664491</v>
       </c>
       <c r="R222" s="18" t="n">
-        <v>0.998434419026664</v>
+        <v>0.997233538716244</v>
       </c>
       <c r="S222" s="19" t="n">
-        <v>1.00871007597012</v>
+        <v>1.00516779086135</v>
       </c>
     </row>
     <row r="223">
@@ -14966,58 +14966,58 @@
         <v>274</v>
       </c>
       <c r="B223" s="2" t="n">
-        <v>776528.776090785</v>
+        <v>777482.5556069</v>
       </c>
       <c r="C223" s="3" t="n">
-        <v>776528.776090785</v>
+        <v>777482.5556069</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>776528.776090785</v>
+        <v>777482.5556069</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>776528.776090785</v>
+        <v>777482.5556069</v>
       </c>
       <c r="F223" s="6" t="n">
-        <v>33588.8783588198</v>
+        <v>34212.4248995394</v>
       </c>
       <c r="G223" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H223" s="8" t="n">
-        <v>740605.519088374</v>
+        <v>740335.789408632</v>
       </c>
       <c r="I223" s="9" t="n">
-        <v>730924.031784605</v>
+        <v>732849.093311545</v>
       </c>
       <c r="J223" s="10" t="n">
-        <v>732007.994504572</v>
+        <v>733976.40086475</v>
       </c>
       <c r="K223" s="11" t="n">
-        <v>742939.897731966</v>
+        <v>743270.130707361</v>
       </c>
       <c r="L223" s="12" t="n">
-        <v>742939.897731966</v>
+        <v>743270.130707361</v>
       </c>
       <c r="M223" s="13" t="n">
-        <v>742939.897731966</v>
+        <v>743270.130707361</v>
       </c>
       <c r="N223" s="14" t="n">
-        <v>742939.897731966</v>
+        <v>743270.130707361</v>
       </c>
       <c r="O223" s="15" t="n">
-        <v>0.0114515650920962</v>
+        <v>0.013151529747299</v>
       </c>
       <c r="P223" s="16" t="n">
-        <v>0.0680985164423948</v>
+        <v>0.0695696644385448</v>
       </c>
       <c r="Q223" s="17" t="n">
-        <v>0.011517385271701</v>
+        <v>0.0132383914851948</v>
       </c>
       <c r="R223" s="18" t="n">
-        <v>1.00315198656157</v>
+        <v>1.00396352755156</v>
       </c>
       <c r="S223" s="19" t="n">
-        <v>1.01643928154616</v>
+        <v>1.01421989532487</v>
       </c>
     </row>
     <row r="224">
@@ -15025,58 +15025,58 @@
         <v>275</v>
       </c>
       <c r="B224" s="2" t="n">
-        <v>737795.741613431</v>
+        <v>737135.067677709</v>
       </c>
       <c r="C224" s="3" t="n">
-        <v>737795.741613431</v>
+        <v>737135.067677709</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>737795.741613431</v>
+        <v>737135.067677709</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>737795.741613431</v>
+        <v>737135.067677709</v>
       </c>
       <c r="F224" s="6" t="n">
-        <v>-629.853233285096</v>
+        <v>-1946.32976111565</v>
       </c>
       <c r="G224" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H224" s="8" t="n">
-        <v>740400.516803348</v>
+        <v>741138.849011826</v>
       </c>
       <c r="I224" s="9" t="n">
-        <v>733716.493805345</v>
+        <v>735931.594240519</v>
       </c>
       <c r="J224" s="10" t="n">
-        <v>734913.591849315</v>
+        <v>737472.206393244</v>
       </c>
       <c r="K224" s="11" t="n">
-        <v>738425.594846716</v>
+        <v>739081.397438825</v>
       </c>
       <c r="L224" s="12" t="n">
-        <v>738425.594846716</v>
+        <v>739081.397438825</v>
       </c>
       <c r="M224" s="13" t="n">
-        <v>738425.594846716</v>
+        <v>739081.397438825</v>
       </c>
       <c r="N224" s="14" t="n">
-        <v>738425.594846716</v>
+        <v>739081.397438825</v>
       </c>
       <c r="O224" s="15" t="n">
-        <v>-0.00609480493790925</v>
+        <v>-0.0056514859502095</v>
       </c>
       <c r="P224" s="16" t="n">
-        <v>0.03247474944547</v>
+        <v>0.0322128557803782</v>
       </c>
       <c r="Q224" s="17" t="n">
-        <v>-0.00607626929046379</v>
+        <v>-0.00563554634510788</v>
       </c>
       <c r="R224" s="18" t="n">
-        <v>0.997332630229436</v>
+        <v>0.997223932363356</v>
       </c>
       <c r="S224" s="19" t="n">
-        <v>1.00641814799194</v>
+        <v>1.00428002170712</v>
       </c>
     </row>
     <row r="225">
@@ -15084,92 +15084,118 @@
         <v>276</v>
       </c>
       <c r="B225" s="2" t="n">
-        <v>733788.66978506</v>
+        <v>735202.105508002</v>
       </c>
       <c r="C225" s="3" t="n">
-        <v>733788.66978506</v>
+        <v>735202.105508002</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>733788.66978506</v>
+        <v>735202.105508002</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>733788.66978506</v>
+        <v>735202.105508002</v>
       </c>
       <c r="F225" s="6" t="n">
-        <v>-5880.18729418066</v>
+        <v>-7930.10952953862</v>
       </c>
       <c r="G225" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H225" s="8" t="n">
-        <v>739245.003060546</v>
+        <v>743791.699829468</v>
       </c>
       <c r="I225" s="9" t="n">
-        <v>736510.929530804</v>
+        <v>739025.932311241</v>
       </c>
       <c r="J225" s="10" t="n">
-        <v>737828.391521845</v>
+        <v>741027.866511581</v>
       </c>
       <c r="K225" s="11" t="n">
-        <v>739668.857079241</v>
+        <v>743132.21503754</v>
       </c>
       <c r="L225" s="12" t="n">
-        <v>739668.857079241</v>
+        <v>743132.21503754</v>
       </c>
       <c r="M225" s="13" t="n">
-        <v>739668.857079241</v>
+        <v>743132.21503754</v>
       </c>
       <c r="N225" s="14" t="n">
-        <v>739668.857079241</v>
+        <v>743132.21503754</v>
       </c>
       <c r="O225" s="15" t="n">
-        <v>0.00168225044631438</v>
+        <v>0.00546591618087863</v>
       </c>
       <c r="P225" s="16" t="n">
-        <v>0.0186753075174348</v>
+        <v>0.0211065321286639</v>
       </c>
       <c r="Q225" s="17" t="n">
-        <v>0.00168366622338234</v>
+        <v>0.00548088155479576</v>
       </c>
       <c r="R225" s="18" t="n">
-        <v>1.00057336068143</v>
+        <v>0.999113347470698</v>
       </c>
       <c r="S225" s="19" t="n">
-        <v>1.00428768592809</v>
+        <v>1.00555634457029</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
         <v>277</v>
       </c>
-      <c r="B226" s="2"/>
+      <c r="B226" s="2" t="n">
+        <v>725600.244568253</v>
+      </c>
       <c r="C226" s="3" t="n">
-        <v>711397.419274849</v>
+        <v>725600.244568253</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>756117.825347278</v>
+        <v>725600.244568253</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>666677.01320242</v>
+        <v>725600.244568253</v>
       </c>
       <c r="F226" s="6" t="n">
-        <v>-27106.873050446</v>
-      </c>
-      <c r="G226" s="7"/>
-      <c r="H226" s="8"/>
-      <c r="I226" s="9"/>
-      <c r="J226" s="10"/>
-      <c r="K226" s="11"/>
-      <c r="L226" s="12"/>
-      <c r="M226" s="13"/>
+        <v>-23941.2332065971</v>
+      </c>
+      <c r="G226" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H226" s="8" t="n">
+        <v>747334.865388655</v>
+      </c>
+      <c r="I226" s="9" t="n">
+        <v>742124.905739485</v>
+      </c>
+      <c r="J226" s="10" t="n">
+        <v>744608.193053524</v>
+      </c>
+      <c r="K226" s="11" t="n">
+        <v>749541.477774851</v>
+      </c>
+      <c r="L226" s="12" t="n">
+        <v>749541.477774851</v>
+      </c>
+      <c r="M226" s="13" t="n">
+        <v>749541.477774851</v>
+      </c>
       <c r="N226" s="14" t="n">
-        <v>738504.292325295</v>
-      </c>
-      <c r="O226" s="15"/>
-      <c r="P226" s="16"/>
-      <c r="Q226" s="17"/>
-      <c r="R226" s="18"/>
-      <c r="S226" s="19"/>
+        <v>749541.477774851</v>
+      </c>
+      <c r="O226" s="15" t="n">
+        <v>0.00858768015735857</v>
+      </c>
+      <c r="P226" s="16" t="n">
+        <v>0.0217875976924475</v>
+      </c>
+      <c r="Q226" s="17" t="n">
+        <v>0.00862466006400564</v>
+      </c>
+      <c r="R226" s="18" t="n">
+        <v>1.0029526420998</v>
+      </c>
+      <c r="S226" s="19" t="n">
+        <v>1.0099936977967</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
@@ -15177,16 +15203,16 @@
       </c>
       <c r="B227" s="2"/>
       <c r="C227" s="3" t="n">
-        <v>766108.12190621</v>
+        <v>777449.317267898</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>822337.333960242</v>
+        <v>821981.856289926</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>709878.909852177</v>
+        <v>732916.778245871</v>
       </c>
       <c r="F227" s="6" t="n">
-        <v>33569.1253614406</v>
+        <v>34002.7921310961</v>
       </c>
       <c r="G227" s="7"/>
       <c r="H227" s="8"/>
@@ -15196,7 +15222,7 @@
       <c r="L227" s="12"/>
       <c r="M227" s="13"/>
       <c r="N227" s="14" t="n">
-        <v>732538.996544769</v>
+        <v>743446.525136802</v>
       </c>
       <c r="O227" s="15"/>
       <c r="P227" s="16"/>
@@ -15210,16 +15236,16 @@
       </c>
       <c r="B228" s="2"/>
       <c r="C228" s="3" t="n">
-        <v>729321.957885213</v>
+        <v>737794.877292727</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>791262.686042764</v>
+        <v>794006.064581993</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>667381.229727663</v>
+        <v>681583.690003462</v>
       </c>
       <c r="F228" s="6" t="n">
-        <v>-715.402541208025</v>
+        <v>-2241.77848109039</v>
       </c>
       <c r="G228" s="7"/>
       <c r="H228" s="8"/>
@@ -15229,7 +15255,7 @@
       <c r="L228" s="12"/>
       <c r="M228" s="13"/>
       <c r="N228" s="14" t="n">
-        <v>730037.360426421</v>
+        <v>740036.655773817</v>
       </c>
       <c r="O228" s="15"/>
       <c r="P228" s="16"/>
@@ -15243,16 +15269,16 @@
       </c>
       <c r="B229" s="2"/>
       <c r="C229" s="3" t="n">
-        <v>720375.234142833</v>
+        <v>727686.53485258</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>785403.999383243</v>
+        <v>789797.041221151</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>655346.468902423</v>
+        <v>665576.028484009</v>
       </c>
       <c r="F229" s="6" t="n">
-        <v>-5629.80823220515</v>
+        <v>-8187.23729149833</v>
       </c>
       <c r="G229" s="7"/>
       <c r="H229" s="8"/>
@@ -15262,7 +15288,7 @@
       <c r="L229" s="12"/>
       <c r="M229" s="13"/>
       <c r="N229" s="14" t="n">
-        <v>726005.042375038</v>
+        <v>735873.772144078</v>
       </c>
       <c r="O229" s="15"/>
       <c r="P229" s="16"/>
@@ -15275,10 +15301,18 @@
         <v>281</v>
       </c>
       <c r="B230" s="2"/>
-      <c r="C230" s="3"/>
-      <c r="D230" s="4"/>
-      <c r="E230" s="5"/>
-      <c r="F230" s="6"/>
+      <c r="C230" s="3" t="n">
+        <v>710342.95950772</v>
+      </c>
+      <c r="D230" s="4" t="n">
+        <v>775702.204710127</v>
+      </c>
+      <c r="E230" s="5" t="n">
+        <v>644983.714305314</v>
+      </c>
+      <c r="F230" s="6" t="n">
+        <v>-23101.3641190502</v>
+      </c>
       <c r="G230" s="7"/>
       <c r="H230" s="8"/>
       <c r="I230" s="9"/>
@@ -15286,7 +15320,9 @@
       <c r="K230" s="11"/>
       <c r="L230" s="12"/>
       <c r="M230" s="13"/>
-      <c r="N230" s="14"/>
+      <c r="N230" s="14" t="n">
+        <v>733444.32362677</v>
+      </c>
       <c r="O230" s="15"/>
       <c r="P230" s="16"/>
       <c r="Q230" s="17"/>
@@ -15784,7 +15820,7 @@
         <v>318</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.000167205647467741</v>
+        <v>0.0000834569266478342</v>
       </c>
     </row>
     <row r="6">
@@ -15792,7 +15828,7 @@
         <v>319</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.140096868939759</v>
+        <v>0.129672520269508</v>
       </c>
     </row>
     <row r="7">
@@ -15800,7 +15836,7 @@
         <v>320</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.391439422807531</v>
+        <v>0.376919765488509</v>
       </c>
     </row>
     <row r="8">
@@ -15808,7 +15844,7 @@
         <v>321</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.639736075454993</v>
+        <v>0.63429963020155</v>
       </c>
     </row>
     <row r="9">
@@ -15816,7 +15852,7 @@
         <v>322</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.718351631330702</v>
+        <v>0.715931302042003</v>
       </c>
     </row>
     <row r="10">
@@ -15824,7 +15860,7 @@
         <v>323</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.509737771049973</v>
+        <v>0.511030332746107</v>
       </c>
     </row>
     <row r="11">
@@ -15832,7 +15868,7 @@
         <v>324</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.160042663783679</v>
+        <v>0.155997766141614</v>
       </c>
     </row>
     <row r="12">
@@ -15840,7 +15876,7 @@
         <v>325</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.0424877196871654</v>
+        <v>-0.0474254193364707</v>
       </c>
     </row>
     <row r="13">
@@ -15848,7 +15884,7 @@
         <v>326</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.100533429495466</v>
+        <v>-0.0998750673271038</v>
       </c>
     </row>
     <row r="14">
